--- a/CN_Electronic_Industry.xlsx
+++ b/CN_Electronic_Industry.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Fact and Comp-Shanghai" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Semi-Product" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Comp-Product" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Name-History" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fact and Comp-Shanghai" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semi-Product" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comp-Product" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Name-History" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -393,11 +393,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:S122"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="33.28515625" customWidth="1" min="1" max="1"/>
-    <col width="14.28515625" customWidth="1" min="2" max="3"/>
+    <col width="33.26953125" customWidth="1" min="1" max="1"/>
+    <col width="14.26953125" customWidth="1" min="2" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -449,6 +449,11 @@
           <t>Source</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>别名</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="I2" t="inlineStr">
@@ -1614,6 +1619,2596 @@
       <c r="B31" t="inlineStr">
         <is>
           <t>研究所</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>国营738厂</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>生产微型计算机、微型计算机、0520CH机、生产10台BCM0530机</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>19860000</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>自动导航专用的集成电路</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>清华大学</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DJS-5小型晶体管鼓字计算机、555型小型台式模拟计算机、微型计算机、0520CH机</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>19600000</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>北京无线电一厂</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>大型晶体管模数混合计算机</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>19700000改名北京计算机一厂</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>北京计算机五厂</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>微型计算机、天坛牌TEC系列学习机</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>19840600</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>19840600改名北京计算机五厂</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>中科院计算所</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>119电子管通用数字计算机、109乙计算机</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>19560600</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>北京计算机一厂</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>大型晶体管模数混合计算机、S-100总线单板系列机</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>北京北优计算机系统有限公司</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>BUCC微型机</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>19950200</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>北京无线电三厂</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>DJS-5小型晶体管鼓字计算机、DJS-4晶体管台式数字计算机</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>19050400改名北京计算机三厂</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>航空部第20研究所</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>研究所</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>大型晶体管模数混合计算机</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>北京计算机二厂</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>BY-0520I型银行信息处理机</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>19790000</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>中国科学院计算所</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>19841100</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·二、 汉字信息系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>中国科学院计算所公司</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>19841100</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·二、 汉字信息系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>北京市旅游汽车公司</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>19840600</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>19840600改名北京计算机五厂</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 管理信息系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>北京联想计算机集团公司</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>联想系列微机</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>19880000改名联想集团公司</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>联想计算机集团公司</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>联想系列微机</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>首钢电子公司</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>19790000</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>改名自动化研究所</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>北京工控计算机厂</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>19830000</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>北京工业大学电子厂</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>TP系列微型打印机</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>北京四通办公设备有限公司</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>19870000</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>电子部6所</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>长城0520B微型机</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>北京市计算机技术研究所</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>生产10台BCM0530机、10台BCM0530机</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>19790000</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机；北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>四机部15所</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>DJS-200系列计算机</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>北京计算机三厂</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>DJS-5小型晶体管鼓字计算机</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>北京市无线电制造厂</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>改名北京无线电一厂</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>北京电子显示设备厂</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>外围设备</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>19830700</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·三、 显示器</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>联想集团公司</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>并投人批量生产联想激光打印机、联想激光打印机、联想系列微机</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·四、 打印机</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>联想集团</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>自动化研究所</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>研究所</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>19790000</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 计算机辅助软件工程系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>长沙工业学院</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>电子部第15所</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>NCI-2780超级小型计算机</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>四机部6所</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>微型计算机、S-100总线单板系列机</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>安徽无线电厂</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>微型计算机</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>北京崇文电子仪器厂</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>微型计算机</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>北京市计算机服务公司</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>0520CH机</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>北京开关厂</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>19060000改名北京控制机厂</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>北京计算机配件五厂</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>19830000</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>华北制药厂</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>亚运村</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>美国COMPAQ公司</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>外围设备</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>19830700</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>北京计算机外部设备三厂</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>中国长城计算机集团公司</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>北大方正集团公司</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>北京科海高技术集团公司</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>北京希望电脑公司</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>北京王码电脑公司</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>电子部15所</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>北京航星机器制造公司</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>哈尔滨军事工程学院</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>哈军工</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>四机部标准化研究所4所</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>研究所</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>北京市计算机工业总公司</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>北京东风电视机厂</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>外围设备</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·三、 显示器</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>一机部15所</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>北京大学</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·二、 汉字信息系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>北京大学计算机技术研究所</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·二、 汉字信息系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>中科院自动化研究所</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>研究所</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 计算机辅助软件工程系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>北京市半导体器件二厂</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>清华大学计算机厂</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>上海复旦大学</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>山东省烟台市电子技术研究所</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>研究所</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>北京四通集团公司</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>19870000</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（四） 文字处理机</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>北京开关厂平谷分厂</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>北京控制机厂</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>北京电器科学研究院</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>研究所</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>兰州炼油厂</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>大庆石油化工总厂</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>唐山陡河发电总厂</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>陡河发电总厂</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>首钢自动化研究所</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>研究所</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>中国管理科学研究院</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>研究所</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>华胜计算机公司</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·六、 工作站</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>中国软件技术公司</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>外围设备</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>北京华海新技术开发公司</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>外围设备</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>北京西城广播设备厂</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>北京无线电厂</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>国营774厂音响分厂</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>508所</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>302所</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>上海华东师范大学</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>六机部705所</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>航空部601所</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>北京三洋电子有限公司</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>北京第三棉纺织厂</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>中国人民解放军3509厂</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>第二钢轧厂</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>南京微电机厂</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(二) 单板机</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>机电部4所</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>新疆水泥厂</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>双羊水泥厂</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>美国钢铁公司</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>北京水泵厂</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>华胜公司</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·六、 工作站</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>首钢公司</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
         </is>
       </c>
     </row>
@@ -1628,12 +4223,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="40.7109375" customWidth="1" min="1" max="1"/>
-    <col width="22.28515625" customWidth="1" min="2" max="2"/>
-    <col width="12.5703125" customWidth="1" min="4" max="4"/>
+    <col width="40.7265625" customWidth="1" min="1" max="1"/>
+    <col width="22.26953125" customWidth="1" min="2" max="2"/>
+    <col width="12.54296875" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1662,6 +4257,11 @@
           <t>Remark</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>产量</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2364,6 +4964,39 @@
         <is>
           <t>上海无线电十四厂</t>
         </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DK-100型</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>19780000</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>M401-45</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>19840000</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产589台」。北京工业志·电子志</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>589</v>
       </c>
     </row>
   </sheetData>
@@ -2377,15 +5010,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:L199"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="23.28515625" customWidth="1" min="1" max="1"/>
-    <col width="11.7109375" customWidth="1" min="2" max="2"/>
-    <col width="15.85546875" customWidth="1" min="3" max="3"/>
-    <col width="14.85546875" customWidth="1" min="4" max="4"/>
-    <col width="22.28515625" customWidth="1" min="5" max="5"/>
-    <col width="22.28515625" customWidth="1" min="7" max="7"/>
+    <col width="23.26953125" customWidth="1" min="1" max="1"/>
+    <col width="11.7265625" customWidth="1" min="2" max="2"/>
+    <col width="15.81640625" customWidth="1" min="3" max="3"/>
+    <col width="14.81640625" customWidth="1" min="4" max="4"/>
+    <col width="22.26953125" customWidth="1" min="5" max="5"/>
+    <col width="22.26953125" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -2435,6 +5068,21 @@
           <t>Remark</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>用户</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>产量</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>别名</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2529,368 +5177,386 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>X-2型计算机计算中心阿尔巴尼亚</t>
-        </is>
+          <t>TQ-1型工业控制计算机</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4069-16384</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>30000</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>上无十三培训阿国实习生、华东计算所何上海市计算技术研究所派员</t>
+          <t>上无十三设计、华东计算所何上海无线电技术研究所派员</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>19700800-19710400</t>
+          <t>19670000-19690000</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>生产3台，有打印机，用于上海南市发电厂监控何北京有机化工厂生产控制</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TQ-1型工业控制计算机</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>18</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>4069-16384</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>30000</v>
+          <t>晶体管数字控制仪</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>上无十三设计、华东计算所何上海无线电技术研究所派员</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>19670000-19690000</t>
+          <t>上海无线电技术研究所</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>生产3台，有打印机，用于上海南市发电厂监控何北京有机化工厂生产控制</t>
+          <t>上海炼油厂减压装置</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>晶体管数字控制仪</t>
+          <t>JDK-331型工业控制机</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>上海无线电技术研究所</t>
+          <t>上海自动化仪表研究所</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>上海炼油厂减压装置</t>
+          <t>上海炼油厂常压蒸馏装置</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JDK-331型工业控制机</t>
+          <t>DK-1型数字集成电路计算机</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>上海自动化仪表研究所</t>
+          <t>上无十三</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>19690000</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>陈国尧</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>上海炼油厂常压蒸馏装置</t>
+          <t>用作电子束加工</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DK-1型数字集成电路计算机</t>
+          <t>DJS-130小型计算机</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>16</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4-32K</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>400K-500K</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>上无十三</t>
+          <t>上五十三、上海中兴无线电厂、华东计算所、华东师范大学附属工厂</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>19690000</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>陈国尧</t>
-        </is>
+        <v>19740800</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>用作电子束加工</t>
+          <t>生产30台</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DJS-130小型计算机</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>16</v>
+          <t>DJS-130B小型计算机</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4-32K</t>
+          <t>半导体储存器</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>400K-500K</t>
+          <t>800K</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>上五十三、上海中兴无线电厂、华东计算所、华东师范大学附属工厂</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>19740800</v>
+          <t>中兴无线电厂</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>生产30台</t>
+          <t>生产16台</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DJS-130B小型计算机</t>
-        </is>
+          <t>DJS-131小型多功能电子计算机</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>16</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>半导体储存器</t>
+          <t>4~32K-64K</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>800K</t>
+          <t>500K</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>中兴无线电厂</t>
-        </is>
+          <t>复旦大学、上海交通大学、吴泾化工厂、新安电工厂、上海自动化仪表研究所、浙江大学、长沙国防大学、上海师范大学、上海科技大学、上海中兴无线电厂</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>上五十三</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>19750000</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>生产16台</t>
+          <t>上海和北京的元器件标准不一样，上海市革委会工交组和第三办公室鉴定，可配62个外围设备，实时操作系统，生产334台；上海市优质产品；国际展览展出过</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DJS-131小型多功能电子计算机</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>16</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>4~32K-64K</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>500K</t>
+          <t>DJS-185</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>复旦大学、上海交通大学、吴泾化工厂、新安电工厂、上海自动化仪表研究所、浙江大学、长沙国防大学、上海师范大学、上海科技大学、上海中兴无线电厂</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>上五十三</t>
+          <t>上海电子计算机厂</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>19750000</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>上海和北京的元器件标准不一样，上海市革委会工交组和第三办公室鉴定，可配62个外围设备，实时操作系统，生产334台；上海市优质产品；国际展览展出过</t>
-        </is>
+        <v>19810000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DJS-185</t>
+          <t>709型计算机</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>上海电子计算机厂</t>
+          <t>上海市计算中心、长宁手拉厂</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>19810000</v>
+        <v>19711226</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>毛泽东生日献礼、国内第一台集成电路通用计算机</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>709型计算机</t>
+          <t>CJ-709型计算机</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>上海市计算中心、长宁手拉厂</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>19711226</v>
+          <t>上海长宁拉手厂、上海市计算中心、复旦大学实习厂</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>上海长宁拉手厂，以后上海中兴无线电厂、新安电工厂投入生产</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>19710800-19720000, 19730000生产</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>毛泽东生日献礼、国内第一台集成电路通用计算机</t>
+          <t>生产73台</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CJ-709型计算机</t>
-        </is>
+          <t>TQ-16中型通用数字集成电路计算机</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>48</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>120K</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>32768</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>上海长宁拉手厂、上海市计算中心、复旦大学实习厂</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>上海长宁拉手厂，以后上海中兴无线电厂、新安电工厂投入生产</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>19710800-19720000, 19730000生产</t>
-        </is>
+          <t>上无十三</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>19730300</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>生产73台</t>
+          <t>吸收X-2计算机和709部分指令系统和设计思想；生产153台，国产中投产最多的中型机</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TQ-16中型通用数字集成电路计算机</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>48</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>120K</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>32768</v>
+          <t>655大型通用数字集成电路计算机</t>
+        </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>上无十三</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>19730300</v>
+          <t>华东计算技术研究所</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>19650000-19720500；19730000技术鉴定</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>陈仁甫</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>吸收X-2计算机和709部分指令系统和设计思想；生产153台，国产中投产最多的中型机</t>
+          <t>参照国际上同类计算机；中科院冶金所、上元五厂、华东计算所研制TTL集成电路；华东计算机所和上无六厂研制厚膜电路</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>655大型通用数字集成电路计算机</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>华东计算技术研究所</t>
+          <t>TQ-6大型计算机</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>48</v>
+      </c>
+      <c r="C17" t="n">
+        <v>131072</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>上无十三接产</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>19650000-19720500；19730000技术鉴定</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>陈仁甫</t>
+          <t>19690200-19740400</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>参照国际上同类计算机；中科院冶金所、上元五厂、华东计算所研制TTL集成电路；华东计算机所和上无六厂研制厚膜电路</t>
+          <t>生产23台，国内唯一百万次大型计算机；1976上无十三一台TQ-6作为给劳动党礼物</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TQ-6大型计算机</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>48</v>
-      </c>
-      <c r="C18" t="n">
-        <v>131072</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>上无十三接产</t>
+          <t>DJS-220计算机</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>32+7海明校验</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>64K-128K</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>100~150K</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>上无十三</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>19690200-19740400</t>
+          <t>19740000-19810000</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>生产23台，国内唯一百万次大型计算机；1976上无十三一台TQ-6作为给劳动党礼物</t>
+          <t>上海和北京的元器件标准不一样；19811100通过国家计算机总局鉴定；有操作系统、扩充FORTRAN语言</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DJS-220计算机</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>32+7海明校验</t>
-        </is>
+          <t>CJ-1001中型集成电路通用电子计算机</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>32</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2899,50 +5565,2928 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>100~150K</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>上无十三</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>19740000-19810000</t>
-        </is>
+          <t>500K</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>19800000</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>上海和北京的元器件标准不一样；19811100通过国家计算机总局鉴定；有操作系统、扩充FORTRAN语言</t>
+          <t>FORTRAN-IV编译程序、汇编语言、操作系统等、分时系统、先行控制技术、大容量磁盘及标准接口</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CJ-1001中型集成电路通用电子计算机</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>32</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>64K-128K</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>500K</t>
+          <t>119电子管通用数字计算机</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>中科院计算所</t>
         </is>
       </c>
       <c r="G20" t="n">
+        <v>19640400</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·一、 电子管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>109乙计算机</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>中科院计算所</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>19650000</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0520CH机</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>清华大学</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>国营738厂、计算机服务公司</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>19840000</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>协作:计算机服务公司、清华大学。产量据「共生产1.5万台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BCM0530机</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>北京市计算机技术研究所</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>国营738厂</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>19860000</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>协作:市计算机技术研究所。产量据「生产10台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>大型晶体管模数混合计算机</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>航空部第20研究所</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>北京计算机一厂、北京无线电一厂</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>产量据「共生产9个」。北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>S-100总线单板系列机</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>北京计算机一厂、四机部6所</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>19830000</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>产量据「累计生产各种单板机1.5万多台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(二) 单板机</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BUCC微型机</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>北京北优计算机系统有限公司</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>19950200</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>产量据「年产量2000台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>联想系列微机</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>联想计算机集团公司、北京联想计算机集团公司</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>19880000</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>联想集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TP系列微型打印机</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>北京工业大学</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>19830000</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>产量据「年产20万台」。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·四、 打印机</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>国产化TP单板机</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>北京工业大学</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
         <v>19800000</v>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>FORTRAN-IV编译程序、汇编语言、操作系统等、分时系统、先行控制技术、大容量磁盘及标准接口</t>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>产量据「生产100台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(二) 单板机</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>长城0520B微型机</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>电子部6所</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>19840000</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>产量据「共生产200台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DJS-200系列计算机</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>四机部15所</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>DJS-5小型晶体管鼓字计算机</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>21</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>4K</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>清华大学</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>北京无线电三厂</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>19650400</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>协作:清华大学。北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>北京计算机三厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DJS-4晶体管台式数字计算机</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>北京无线电三厂</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>产量据「共生产350台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 计算机辅助软件工程系统</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>555型小型台式模拟计算机</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>清华大学</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>19590000</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>天坛牌TEC系列学习机</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>北京计算机五厂</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>19880000</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>产量据「共生产4000台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BY-0520I型银行信息处理机</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>北京计算机二厂</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>19890000</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>产量据「共生产100台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>联想激光打印机</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>联想集团公司</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>19930000</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·四、 打印机</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>NCI-2780超级小型计算机</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>电子部第15所</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>19830900</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>103型通用数字计算机</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>中科院计算所</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>国营有线电厂</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>19610600</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>研制单位未详。北京工业志·电子志·第三章电子计算机·第一节数字计算机·一、 电子管计算机</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>DJS-1, M-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>104型通用数字计算机</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>研制单位未详。北京工业志·电子志·第三章电子计算机·第一节数字计算机·一、 电子管计算机</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>DJS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第一节数字计算机·一、 电子管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DJS-2</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第一节数字计算机·一、 电子管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>F50型</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产18台」。北京工业志·电子志·第三章电子计算机·第一节数字计算机·一、 电子管计算机</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>U-2型</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第一节数字计算机·一、 电子管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>109丙晶体管大型通用数字计算机</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>研制单位未详。北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>109乙晶体管计算机</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DMJ-16</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>19600000</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MH-7型</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DMJ-3型</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>19640600</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产274台」。北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>DMI-2型</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产16台」。北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>B301型</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>19830000</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产94台」。北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>HMJ-200</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产9个」。北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>DJM300</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>DJM330型</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>JK-01型</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>DJS-130型</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>HADL-1</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>DJM310</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>19810000</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>DP-101</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>19740000</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>DP201</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>DP-301</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>CX-111</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产191.45万台」。北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>1914500</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>CX-200</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>FC-888</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>CZ-1206</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>G-1型</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>19580000</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·一、 磁鼓</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>G-2型</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>19580000</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·一、 磁鼓</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>G-3型</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>19640000</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·一、 磁鼓</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>108乙机</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>19640000</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·一、 磁鼓</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>320机</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>19670000</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·一、 磁鼓</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>350型</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>19670000</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·一、 磁鼓</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ZGC403型</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>19670000</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·一、 磁鼓</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>154机</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·一、 磁鼓</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ZGC-201型</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产磁鼓358台」。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·一、 磁鼓</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>102机</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·一、 磁鼓</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>107机</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·一、 磁鼓</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>DJS-240机</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产7台」。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·一、 磁鼓</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>CJ-14</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>19640000</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·二、 磁带机</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>CJ-160数字磁带机</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>19650000</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>研制单位未详。产量据「共生产23台」。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·二、 磁带机</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ZDC-102</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>19740000</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·二、 磁带机</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ZDC-205</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·二、 磁带机</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>265机</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>19810000</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「生产10台」。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·二、 磁带机</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>TU77</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>19830000</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·二、 磁带机</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>TM03</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>19830000</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·二、 磁带机</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ZDC-215高密度中速磁带机</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>19840000</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·二、 磁带机</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>VAX-11</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·二、 磁带机</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>JS-11</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>19871000</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产1.71万台」。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·三、 显示器</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>17100</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>CZX-16</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>19880700</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·三、 显示器</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>CGA640</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产452台」。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·三、 显示器</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>MDA720</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产452台」。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·三、 显示器</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>GTX-1型</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>19871000</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·三、 显示器</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>TPuP16</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>19840200</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「年产20万台」。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·四、 打印机</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>108甲机</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>DJS-6机</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>DJS-8机</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ST-3</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>DJS-265机</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>DJS-260机</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>RT-11</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>RSX-11</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>DJS-180</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>NCJ2780机</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2220机</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>127机</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>153机</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>BCM-820</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>19840000</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·二、 汉字信息系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>UCDOS1</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>19870000</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·二、 汉字信息系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>PLAN2000-5000</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 管理信息系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>DJS-7</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>19650000</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 计算机辅助软件工程系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>141机</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>19660000</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>143专用机</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>144专用机</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>DJS-11</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>19730500</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>DJS-12</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>19710300</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>DJS154</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>19771000</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产84台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+      <c r="K115" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>DJS140机</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>19790000</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>DJS-100</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>DJS-210</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>19730000</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>DJS-2023</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>19820000</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>DJS2024</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>19820000</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2780机</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>19850718</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>AP-2701数组处理机</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>19850927</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>研制单位未详。产量据「共生产100台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+      <c r="K122" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>AP-2901</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>19860700</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>TJ2220</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>19870514</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>DJS050</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>19020000</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产17台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K125" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>DJS-054机</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>个人计算机</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>19820900</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>BCT-1</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>19790000</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>BCM-0530</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>19850000</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>19820000</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产1575台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K130" t="n">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>19820000</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产1575台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K131" t="n">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>TS2605</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>19820000</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产1575台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K132" t="n">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>S6800</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>19820000</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产1575台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K133" t="n">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>PDP11</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>19820000</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产1575台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K134" t="n">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>GW0520微型计算机</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>19860000</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>BD2861</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>19890000</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>BD386微型计算机</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>19890000</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>研制单位未详。产量据「共生产332台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K137" t="n">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>BD286-20</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>19910000</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>BD3862</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>19910000</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>BD386-33C</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>19910000</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>BD486</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>19910000</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>长城0520A机</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>19020000</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>研制单位未详。产量据「共生产3500台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K142" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>0530HM等系列微机</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>研制单位未详。产量据「年产量2000台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K143" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>0540A微机</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>19870000</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>研制单位未详。产量据「年产量2000台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K144" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>CWV40</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>19950200</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「年产量2000台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K145" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>CWP500</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>19950200</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「年产量2000台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K146" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>GW386</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>19880420</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产1.5万台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K147" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>GW486</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>19930222</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>GW586</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>19940519</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>EISA486</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>N80</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(二) 单板机</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>TP801</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>19810000</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「生产100台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(二) 单板机</t>
+        </is>
+      </c>
+      <c r="K152" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>P-16</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>19810000</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「生产100台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(二) 单板机</t>
+        </is>
+      </c>
+      <c r="K153" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>DJS-041</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>19810000</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(二) 单板机</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>BSBC86</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>19830000</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(二) 单板机</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>RC51-2型</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>19880200</v>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(二) 单板机</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>PC51-9型</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(二) 单板机</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>PC51-11型</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(二) 单板机</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>CEC-1型</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>19870000</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产6918台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
+        </is>
+      </c>
+      <c r="K159" t="n">
+        <v>6918</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产4000台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
+        </is>
+      </c>
+      <c r="K160" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>MS－2400</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>19860000</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（四） 文字处理机</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>MS-2401中外文文字处理机</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（四） 文字处理机</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>MS-2402</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（四） 文字处理机</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>MS-2403机</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（四） 文字处理机</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>MS-2406</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（四） 文字处理机</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>MS100等各种类型的文字处理机</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（四） 文字处理机</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>MS2410</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（四） 文字处理机</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>MS2411</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（四） 文字处理机</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>SK100</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>19660000</v>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>K9</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>19650000</v>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>K10</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>19650000</v>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>19670000</v>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产30台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+      <c r="K172" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>19680300</v>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「生产1台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+      <c r="K173" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>19690000</v>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>K7</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>19690000</v>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>K11</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>K18</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>19710000</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>SSK-100</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>19040000</v>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>130机</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>PCS16</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>19840100</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「年产20套」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+      <c r="K180" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>APCS-2000</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>19931100</v>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>HS2000</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v>19951000</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>I0</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>S32</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>P-200</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="G186" t="n">
+        <v>19830000</v>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>FY-11</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>19860000</v>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「年产量达3000多台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+      <c r="K187" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>SRX201型</t>
+        </is>
+      </c>
+      <c r="G188" t="n">
+        <v>19901116</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产4套」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+      <c r="K188" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>SUN3</t>
+        </is>
+      </c>
+      <c r="G189" t="n">
+        <v>19870000</v>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·六、 工作站</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>DT-800</t>
+        </is>
+      </c>
+      <c r="G190" t="n">
+        <v>19850700</v>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>HT-382</t>
+        </is>
+      </c>
+      <c r="G191" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>MC6800</t>
+        </is>
+      </c>
+      <c r="G192" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>生产微型计算机</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>国营738厂</t>
+        </is>
+      </c>
+      <c r="G193" t="n">
+        <v>19820000</v>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>产量据「共生产1.5万台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K193" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>微型计算机</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>国营738厂</t>
+        </is>
+      </c>
+      <c r="G194" t="n">
+        <v>19820000</v>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>产量据「共生产1.5万台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K194" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>生产10台BCM0530机</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>市计算机技术研究所</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>国营738厂</t>
+        </is>
+      </c>
+      <c r="G195" t="n">
+        <v>19860000</v>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>协作:市计算机技术研究所。产量据「生产10台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K195" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>10台BCM0530机</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>市计算机技术研究所</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>国营738厂</t>
+        </is>
+      </c>
+      <c r="G196" t="n">
+        <v>19860000</v>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>协作:市计算机技术研究所。产量据「生产10台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K196" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>微型计算机</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>清华大学</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>四机部6所、安徽无线电厂、北京崇文电子仪器厂、北京计算机五厂</t>
+        </is>
+      </c>
+      <c r="G197" t="n">
+        <v>19740000</v>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>协作:四机部6所、安徽无线电厂、北京崇文电子仪器厂、北京计算机五厂。产量据「共生产17台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K197" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>并投人批量生产联想激光打印机</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>联想集团公司</t>
+        </is>
+      </c>
+      <c r="G198" t="n">
+        <v>19930000</v>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·四、 打印机</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>模拟计算机和晶体管数字计算机</t>
+        </is>
+      </c>
+      <c r="G199" t="n">
+        <v>19600000</v>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>研制单位未详。北京工业志·电子志·第三章电子计算机</t>
         </is>
       </c>
     </row>
@@ -2957,8 +8501,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -3037,7 +8581,6 @@
           <t>19610000</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>据 Founder 列推定,待核</t>
@@ -3114,7 +8657,6 @@
           <t>19490000</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>据 Founder 列推定,待核</t>
@@ -3137,7 +8679,6 @@
           <t>19530000</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>据 Founder 列推定,待核</t>
@@ -3160,7 +8701,6 @@
           <t>19600000</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>据 Founder 列推定,待核</t>
@@ -3183,7 +8723,6 @@
           <t>19700000</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>据 Founder 列推定,待核</t>
@@ -3233,7 +8772,6 @@
           <t>19580800</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>据 Founder 列推定,待核</t>
@@ -3418,7 +8956,6 @@
           <t>19640506</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>据 Founder 列推定,待核</t>
@@ -3441,10 +8978,171 @@
           <t>19791200</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>据 Founder 列推定,待核</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>北京无线电三厂</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>北京计算机三厂</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>19050400</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1965年4月，北京无线电三厂（后更名为北京计算机三厂）与清华大学合作研制成功DJS-5小型晶体管鼓字计算机，字长21位，内存4K，当年12月通过技术鉴定。</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>北京无线电一厂</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>北京计算机一厂</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>19700000</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1970年初，北京无线电一厂（后更名为北京计算机一厂）接受原航空部第20研究所的委托，开始研制大型晶体管模数混合计算机，1975年，完成研制任务，定名为HMJ-200大型晶体管模数混合计算机。</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>北京计算机五厂</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>北京计算机五厂</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>19840600</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1984年6月，北京市计算机软件中心（后更名为北京计算机五厂）承接了市旅游汽车公司组建计算机管理系统任务。</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>北京市旅游汽车公司</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>北京计算机五厂</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>19840600</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1984年6月，北京市计算机软件中心（后更名为北京计算机五厂）承接了市旅游汽车公司组建计算机管理系统任务。</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 管理信息系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>北京联想计算机集团公司</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>联想集团公司</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>19880000</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1988年，北京联想计算机集团公司（后更名为联想集团公司，以下简称联想集团）开始研制联想系列微机。</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>北京开关厂平谷分厂</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>北京控制机厂</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>19060000</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1966年，北京开关厂平谷分厂（后更名为北京控制机厂）接受北京电器科学研究院的科研成果，为兰州炼油厂生产了SK100工业控制计算机及其外部设备，交付使用后运行良好，并获1978年全国科学大会奖。</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
         </is>
       </c>
     </row>

--- a/CN_Electronic_Industry.xlsx
+++ b/CN_Electronic_Industry.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Fact and Comp-Shanghai" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Semi-Product" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Comp-Product" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Name-History" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fact and Comp-Shanghai" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semi-Product" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comp-Product" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Name-History" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -393,7 +393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:S122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.28515625" customWidth="1" min="1" max="1"/>
@@ -449,6 +449,11 @@
           <t>Source</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>别名</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="I2" t="inlineStr">
@@ -1614,6 +1619,2596 @@
       <c r="B31" t="inlineStr">
         <is>
           <t>研究所</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>国营738厂</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>生产微型计算机、微型计算机、0520CH机、生产10台BCM0530机</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>19860000</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>自动导航专用的集成电路</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>清华大学</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DJS-5小型晶体管鼓字计算机、555型小型台式模拟计算机、微型计算机、0520CH机</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>19600000</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>北京无线电一厂</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>大型晶体管模数混合计算机</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>19700000改名北京计算机一厂</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>北京计算机五厂</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>微型计算机、天坛牌TEC系列学习机</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>19840600</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>19840600改名北京计算机五厂</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>中科院计算所</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>119电子管通用数字计算机、109乙计算机</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>19560600</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>北京计算机一厂</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>大型晶体管模数混合计算机、S-100总线单板系列机</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>北京北优计算机系统有限公司</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>BUCC微型机</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>19950200</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>北京无线电三厂</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>DJS-5小型晶体管鼓字计算机、DJS-4晶体管台式数字计算机</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>19050400改名北京计算机三厂</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>航空部第20研究所</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>研究所</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>大型晶体管模数混合计算机</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>北京计算机二厂</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>BY-0520I型银行信息处理机</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>19790000</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>中国科学院计算所</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>19841100</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·二、 汉字信息系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>中国科学院计算所公司</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>19841100</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·二、 汉字信息系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>北京市旅游汽车公司</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>19840600</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>19840600改名北京计算机五厂</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 管理信息系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>北京联想计算机集团公司</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>联想系列微机</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>19880000改名联想集团公司</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>联想计算机集团公司</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>联想系列微机</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>首钢电子公司</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>19790000</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>改名自动化研究所</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>北京工控计算机厂</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>19830000</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>北京工业大学电子厂</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>TP系列微型打印机</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>北京四通办公设备有限公司</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>19870000</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>电子部6所</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>长城0520B微型机</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>北京市计算机技术研究所</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>生产10台BCM0530机、10台BCM0530机</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>19790000</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机；北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>四机部15所</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>DJS-200系列计算机</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>北京计算机三厂</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>DJS-5小型晶体管鼓字计算机</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>北京市无线电制造厂</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>改名北京无线电一厂</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>北京电子显示设备厂</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>外围设备</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>19830700</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·三、 显示器</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>联想集团公司</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>并投人批量生产联想激光打印机、联想激光打印机、联想系列微机</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·四、 打印机</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>联想集团</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>自动化研究所</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>研究所</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>19790000</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 计算机辅助软件工程系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>长沙工业学院</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>电子部第15所</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>NCI-2780超级小型计算机</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>四机部6所</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>微型计算机、S-100总线单板系列机</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>安徽无线电厂</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>微型计算机</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>北京崇文电子仪器厂</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>微型计算机</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>北京市计算机服务公司</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>0520CH机</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>北京开关厂</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>19060000改名北京控制机厂</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>北京计算机配件五厂</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>19830000</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>华北制药厂</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>亚运村</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>美国COMPAQ公司</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>外围设备</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>19830700</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>北京计算机外部设备三厂</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>中国长城计算机集团公司</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>北大方正集团公司</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>北京科海高技术集团公司</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>北京希望电脑公司</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>北京王码电脑公司</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>电子部15所</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>北京航星机器制造公司</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>哈尔滨军事工程学院</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>哈军工</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>四机部标准化研究所4所</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>研究所</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>北京市计算机工业总公司</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>北京东风电视机厂</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>外围设备</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·三、 显示器</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>一机部15所</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>北京大学</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·二、 汉字信息系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>北京大学计算机技术研究所</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·二、 汉字信息系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>中科院自动化研究所</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>研究所</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 计算机辅助软件工程系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>北京市半导体器件二厂</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>清华大学计算机厂</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>北京师范大学</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>上海复旦大学</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>山东省烟台市电子技术研究所</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>研究所</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>北京四通集团公司</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>19870000</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（四） 文字处理机</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>北京开关厂平谷分厂</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>北京控制机厂</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>北京电器科学研究院</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>研究所</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>兰州炼油厂</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>大庆石油化工总厂</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>唐山陡河发电总厂</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>陡河发电总厂</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>首钢自动化研究所</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>研究所</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>中国管理科学研究院</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>研究所</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>华胜计算机公司</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·六、 工作站</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>中国软件技术公司</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>外围设备</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>北京华海新技术开发公司</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>外围设备</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>北京西城广播设备厂</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>北京无线电厂</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>国营774厂音响分厂</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>508所</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>302所</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>上海华东师范大学</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>六机部705所</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>航空部601所</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>北京三洋电子有限公司</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>北京第三棉纺织厂</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>中国人民解放军3509厂</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>第二钢轧厂</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>南京微电机厂</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(二) 单板机</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>机电部4所</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>新疆水泥厂</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>双羊水泥厂</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>美国钢铁公司</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>北京水泵厂</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>华胜公司</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·六、 工作站</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>首钢公司</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
         </is>
       </c>
     </row>
@@ -1628,7 +4223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.7109375" customWidth="1" min="1" max="1"/>
@@ -1662,6 +4257,11 @@
           <t>Remark</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>产量</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2364,6 +4964,39 @@
         <is>
           <t>上海无线电十四厂</t>
         </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DK-100型</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>19780000</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>M401-45</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>19840000</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产589台」。北京工业志·电子志</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>589</v>
       </c>
     </row>
   </sheetData>
@@ -2377,7 +5010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:L199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23.28515625" customWidth="1" min="1" max="1"/>
@@ -2435,6 +5068,21 @@
           <t>Remark</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>用户</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>产量</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>别名</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2943,6 +5591,2891 @@
       <c r="I20" t="inlineStr">
         <is>
           <t>FORTRAN-IV编译程序、汇编语言、操作系统等、分时系统、先行控制技术、大容量磁盘及标准接口</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>119电子管通用数字计算机</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>中科院计算所</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>19640400</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·一、 电子管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>109乙计算机</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>中科院计算所</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>19650000</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>生产微型计算机</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>国营738厂</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>19820000</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>产量据「共生产1.5万台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>微型计算机</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>国营738厂</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>19820000</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>产量据「共生产1.5万台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0520CH机</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>清华大学</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>国营738厂、计算机服务公司</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>19840000</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>协作:计算机服务公司、清华大学。产量据「共生产1.5万台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>生产10台BCM0530机</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>市计算机技术研究所</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>国营738厂</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>19860000</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>协作:市计算机技术研究所。产量据「生产10台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>10台BCM0530机</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>市计算机技术研究所</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>国营738厂</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>19860000</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>协作:市计算机技术研究所。产量据「生产10台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>大型晶体管模数混合计算机</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>航空部第20研究所</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>北京计算机一厂、北京无线电一厂</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>产量据「共生产9个」。北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>S-100总线单板系列机</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>北京计算机一厂、四机部6所</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>19830000</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>产量据「累计生产各种单板机1.5万多台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(二) 单板机</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BUCC微型机</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>北京北优计算机系统有限公司</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>19950200</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>产量据「年产量2000台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>联想系列微机</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>联想计算机集团公司、北京联想计算机集团公司</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>19880000</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>联想集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TP系列微型打印机</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>北京工业大学</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>19830000</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>产量据「年产20万台」。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·四、 打印机</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>国产化TP单板机</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>北京工业大学</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>产量据「生产100台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(二) 单板机</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>长城0520B微型机</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>电子部6所</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>19840000</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>产量据「共生产200台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>DJS-200系列计算机</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>四机部15所</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>DJS-5小型晶体管鼓字计算机</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>21</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>4K</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>清华大学</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>北京无线电三厂</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>19650400</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>协作:清华大学。北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>北京计算机三厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>DJS-4晶体管台式数字计算机</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>北京无线电三厂</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>产量据「共生产350台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 计算机辅助软件工程系统</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>555型小型台式模拟计算机</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>清华大学</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>19590000</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>微型计算机</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>清华大学</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>四机部6所、安徽无线电厂、北京崇文电子仪器厂、北京计算机五厂</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>19740000</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>协作:四机部6所、安徽无线电厂、北京崇文电子仪器厂、北京计算机五厂。产量据「共生产17台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>天坛牌TEC系列学习机</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>北京计算机五厂</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>19880000</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>产量据「共生产4000台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BY-0520I型银行信息处理机</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>北京计算机二厂</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>19890000</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>产量据「共生产100台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>并投人批量生产联想激光打印机</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>联想集团公司</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>19930000</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·四、 打印机</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>联想激光打印机</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>联想集团公司</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>19930000</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·四、 打印机</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>NCI-2780超级小型计算机</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>电子部第15所</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>19830900</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>模拟计算机和晶体管数字计算机</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>19600000</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>研制单位未详。北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>103型通用数字计算机</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>中科院计算所</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>国营有线电厂</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>19610600</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>研制单位未详。北京工业志·电子志·第三章电子计算机·第一节数字计算机·一、 电子管计算机</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>DJS-1, M-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>104型通用数字计算机</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>研制单位未详。北京工业志·电子志·第三章电子计算机·第一节数字计算机·一、 电子管计算机</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>DJS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第一节数字计算机·一、 电子管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DJS-2</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第一节数字计算机·一、 电子管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>F50型</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产18台」。北京工业志·电子志·第三章电子计算机·第一节数字计算机·一、 电子管计算机</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>U-2型</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第一节数字计算机·一、 电子管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>109丙晶体管大型通用数字计算机</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>研制单位未详。北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>109乙晶体管计算机</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>DMJ-16</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>19600000</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MH-7型</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>DMJ-3型</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>19640600</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产274台」。北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>DMI-2型</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产16台」。北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>B301型</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>19830000</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产94台」。北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>HMJ-200</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产9个」。北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>DJM300</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>DJM330型</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>JK-01型</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>DJS-130型</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>HADL-1</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>DJM310</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>19810000</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>DP-101</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>19740000</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>DP201</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>DP-301</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>CX-111</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产191.45万台」。北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>1914500</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>CX-200</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>FC-888</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>CZ-1206</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>G-1型</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>19580000</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·一、 磁鼓</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>G-2型</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>19580000</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·一、 磁鼓</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>G-3型</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>19640000</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·一、 磁鼓</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>108乙机</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>19640000</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·一、 磁鼓</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>320机</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>19670000</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·一、 磁鼓</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>350型</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>19670000</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·一、 磁鼓</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ZGC403型</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>19670000</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·一、 磁鼓</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>154机</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·一、 磁鼓</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ZGC-201型</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产磁鼓358台」。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·一、 磁鼓</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>102机</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·一、 磁鼓</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>107机</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·一、 磁鼓</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>DJS-240机</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产7台」。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·一、 磁鼓</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>CJ-14</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>19640000</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·二、 磁带机</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>CJ-160数字磁带机</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>19650000</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>研制单位未详。产量据「共生产23台」。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·二、 磁带机</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>ZDC-102</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>19740000</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·二、 磁带机</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>ZDC-205</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·二、 磁带机</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>265机</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>19810000</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「生产10台」。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·二、 磁带机</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>TU77</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>19830000</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·二、 磁带机</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>TM03</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>19830000</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·二、 磁带机</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ZDC-215高密度中速磁带机</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>19840000</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·二、 磁带机</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>VAX-11</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·二、 磁带机</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>JS-11</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>19871000</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产1.71万台」。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·三、 显示器</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>17100</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>CZX-16</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>19880700</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·三、 显示器</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>CGA640</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产452台」。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·三、 显示器</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>MDA720</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产452台」。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·三、 显示器</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>GTX-1型</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>19871000</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·三、 显示器</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>TPuP16</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>19840200</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「年产20万台」。北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·四、 打印机</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>108甲机</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>DJS-6机</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>DJS-8机</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>ST-3</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>DJS-265机</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>DJS-260机</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>RT-11</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>RSX-11</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>DJS-180</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>NCJ2780机</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2220机</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>127机</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>153机</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>BCM-820</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>19840000</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·二、 汉字信息系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>UCDOS1</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>19870000</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·二、 汉字信息系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>PLAN2000-5000</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 管理信息系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>DJS-7</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>19650000</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 计算机辅助软件工程系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>141机</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>19660000</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>143专用机</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>144专用机</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>DJS-11</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>19730500</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>DJS-12</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>19710300</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>DJS154</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>19771000</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产84台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+      <c r="K122" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>DJS140机</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>19790000</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>DJS-100</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>DJS-210</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>19730000</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>DJS-2023</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>19820000</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>DJS2024</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>19820000</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2780机</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>19850718</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>AP-2701数组处理机</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>19850927</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>研制单位未详。产量据「共生产100台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+      <c r="K129" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>AP-2901</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>19860700</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>TJ2220</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>19870514</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>DJS050</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>19020000</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产17台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K132" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>DJS-054机</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>个人计算机</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>19820900</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>BCT-1</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>19790000</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>BCM-0530</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>19850000</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>19820000</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产1575台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K137" t="n">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>19820000</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产1575台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K138" t="n">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>TS2605</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>19820000</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产1575台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K139" t="n">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>S6800</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>19820000</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产1575台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K140" t="n">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>PDP11</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>19820000</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产1575台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K141" t="n">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>GW0520微型计算机</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>19860000</v>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>BD2861</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>19890000</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>BD386微型计算机</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>19890000</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>研制单位未详。产量据「共生产332台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K144" t="n">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>BD286-20</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>19910000</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>BD3862</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>19910000</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>BD386-33C</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>19910000</v>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>BD486</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>19910000</v>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>长城0520A机</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>19020000</v>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>研制单位未详。产量据「共生产3500台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K149" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>0530HM等系列微机</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>研制单位未详。产量据「年产量2000台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K150" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>0540A微机</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>19870000</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>研制单位未详。产量据「年产量2000台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K151" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>CWV40</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>19950200</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「年产量2000台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K152" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>CWP500</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>19950200</v>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「年产量2000台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K153" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>GW386</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>19880420</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产1.5万台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="K154" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>GW486</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>19930222</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>GW586</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>19940519</v>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>EISA486</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>N80</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(二) 单板机</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>TP801</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>19810000</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「生产100台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(二) 单板机</t>
+        </is>
+      </c>
+      <c r="K159" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>P-16</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>19810000</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「生产100台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(二) 单板机</t>
+        </is>
+      </c>
+      <c r="K160" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>DJS-041</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>19810000</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(二) 单板机</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>BSBC86</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>19830000</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(二) 单板机</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>RC51-2型</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>19880200</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(二) 单板机</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>PC51-9型</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(二) 单板机</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>PC51-11型</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(二) 单板机</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>CEC-1型</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>19870000</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产6918台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
+        </is>
+      </c>
+      <c r="K166" t="n">
+        <v>6918</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产4000台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
+        </is>
+      </c>
+      <c r="K167" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>MS－2400</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>19860000</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（四） 文字处理机</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>MS-2401中外文文字处理机</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（四） 文字处理机</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>MS-2402</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（四） 文字处理机</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>MS-2403机</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（四） 文字处理机</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>MS-2406</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（四） 文字处理机</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>MS100等各种类型的文字处理机</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（四） 文字处理机</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>MS2410</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（四） 文字处理机</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>MS2411</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（四） 文字处理机</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>SK100</t>
+        </is>
+      </c>
+      <c r="G176" t="n">
+        <v>19660000</v>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>K9</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>19650000</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>K10</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>19650000</v>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>K2</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>19670000</v>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产30台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+      <c r="K179" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>K1</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>19680300</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「生产1台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+      <c r="K180" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>19690000</v>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>K7</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v>19690000</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>K11</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>K18</t>
+        </is>
+      </c>
+      <c r="G184" t="n">
+        <v>19710000</v>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>SSK-100</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>19040000</v>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>130机</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>PCS16</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>19840100</v>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「年产20套」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+      <c r="K187" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>APCS-2000</t>
+        </is>
+      </c>
+      <c r="G188" t="n">
+        <v>19931100</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>HS2000</t>
+        </is>
+      </c>
+      <c r="G189" t="n">
+        <v>19951000</v>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>I0</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>S32</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>P-200</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="G193" t="n">
+        <v>19830000</v>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>FY-11</t>
+        </is>
+      </c>
+      <c r="G194" t="n">
+        <v>19860000</v>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「年产量达3000多台」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+      <c r="K194" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>SRX201型</t>
+        </is>
+      </c>
+      <c r="G195" t="n">
+        <v>19901116</v>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产4套」。北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+      <c r="K195" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>SUN3</t>
+        </is>
+      </c>
+      <c r="G196" t="n">
+        <v>19870000</v>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·六、 工作站</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>DT-800</t>
+        </is>
+      </c>
+      <c r="G197" t="n">
+        <v>19850700</v>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>HT-382</t>
+        </is>
+      </c>
+      <c r="G198" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>MC6800</t>
+        </is>
+      </c>
+      <c r="G199" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
         </is>
       </c>
     </row>
@@ -2957,7 +8490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3037,7 +8570,6 @@
           <t>19610000</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>据 Founder 列推定,待核</t>
@@ -3114,7 +8646,6 @@
           <t>19490000</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>据 Founder 列推定,待核</t>
@@ -3137,7 +8668,6 @@
           <t>19530000</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>据 Founder 列推定,待核</t>
@@ -3160,7 +8690,6 @@
           <t>19600000</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>据 Founder 列推定,待核</t>
@@ -3183,7 +8712,6 @@
           <t>19700000</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>据 Founder 列推定,待核</t>
@@ -3233,7 +8761,6 @@
           <t>19580800</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>据 Founder 列推定,待核</t>
@@ -3418,7 +8945,6 @@
           <t>19640506</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>据 Founder 列推定,待核</t>
@@ -3441,10 +8967,171 @@
           <t>19791200</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>据 Founder 列推定,待核</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>北京无线电三厂</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>北京计算机三厂</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>19050400</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1965年4月，北京无线电三厂（后更名为北京计算机三厂）与清华大学合作研制成功DJS-5小型晶体管鼓字计算机，字长21位，内存4K，当年12月通过技术鉴定。</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>北京无线电一厂</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>北京计算机一厂</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>19700000</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1970年初，北京无线电一厂（后更名为北京计算机一厂）接受原航空部第20研究所的委托，开始研制大型晶体管模数混合计算机，1975年，完成研制任务，定名为HMJ-200大型晶体管模数混合计算机。</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>北京计算机五厂</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>北京计算机五厂</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>19840600</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1984年6月，北京市计算机软件中心（后更名为北京计算机五厂）承接了市旅游汽车公司组建计算机管理系统任务。</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>北京市旅游汽车公司</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>北京计算机五厂</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>19840600</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1984年6月，北京市计算机软件中心（后更名为北京计算机五厂）承接了市旅游汽车公司组建计算机管理系统任务。</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 管理信息系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>北京联想计算机集团公司</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>联想集团公司</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>19880000</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1988年，北京联想计算机集团公司（后更名为联想集团公司，以下简称联想集团）开始研制联想系列微机。</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>北京开关厂平谷分厂</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>北京控制机厂</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>19060000</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1966年，北京开关厂平谷分厂（后更名为北京控制机厂）接受北京电器科学研究院的科研成果，为兰州炼油厂生产了SK100工业控制计算机及其外部设备，交付使用后运行良好，并获1978年全国科学大会奖。</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
         </is>
       </c>
     </row>

--- a/CN_Electronic_Industry.xlsx
+++ b/CN_Electronic_Industry.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fact and Comp-Shanghai" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semi-Product" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comp-Product" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Name-History" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Fact and Comp-Shanghai" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Semi-Product" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Comp-Product" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Name-History" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -8490,7 +8490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -8976,162 +8976,54 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>北京无线电三厂</t>
+          <t>北京无线电一厂</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>北京计算机三厂</t>
+          <t>北京计算机一厂</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>19050400</t>
+          <t>19700000</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1965年4月，北京无线电三厂（后更名为北京计算机三厂）与清华大学合作研制成功DJS-5小型晶体管鼓字计算机，字长21位，内存4K，当年12月通过技术鉴定。</t>
+          <t>1970年初，北京无线电一厂（后更名为北京计算机一厂）接受原航空部第20研究所的委托，开始研制大型晶体管模数混合计算机，1975年，完成研制任务，定名为HMJ-200大型晶体管模数混合计算机。</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>北京无线电一厂</t>
+          <t>北京联想计算机集团公司</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>北京计算机一厂</t>
+          <t>联想集团公司</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>19700000</t>
+          <t>19880000</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1970年初，北京无线电一厂（后更名为北京计算机一厂）接受原航空部第20研究所的委托，开始研制大型晶体管模数混合计算机，1975年，完成研制任务，定名为HMJ-200大型晶体管模数混合计算机。</t>
+          <t>1988年，北京联想计算机集团公司（后更名为联想集团公司，以下简称联想集团）开始研制联想系列微机。</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>北京计算机五厂</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>北京计算机五厂</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>19840600</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>1984年6月，北京市计算机软件中心（后更名为北京计算机五厂）承接了市旅游汽车公司组建计算机管理系统任务。</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>北京工业志·电子志·第三章电子计算机·第三节计算器</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>北京市旅游汽车公司</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>北京计算机五厂</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>19840600</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>1984年6月，北京市计算机软件中心（后更名为北京计算机五厂）承接了市旅游汽车公司组建计算机管理系统任务。</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 管理信息系统</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>北京联想计算机集团公司</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>联想集团公司</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>19880000</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>1988年，北京联想计算机集团公司（后更名为联想集团公司，以下简称联想集团）开始研制联想系列微机。</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
           <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>北京开关厂平谷分厂</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>北京控制机厂</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>19060000</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>1966年，北京开关厂平谷分厂（后更名为北京控制机厂）接受北京电器科学研究院的科研成果，为兰州炼油厂生产了SK100工业控制计算机及其外部设备，交付使用后运行良好，并获1978年全国科学大会奖。</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
         </is>
       </c>
     </row>

--- a/CN_Electronic_Industry.xlsx
+++ b/CN_Electronic_Industry.xlsx
@@ -545,6 +545,11 @@
       <c r="P3" t="n">
         <v>510.2</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>上五十三</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1257,6 +1262,11 @@
       <c r="L20" t="n">
         <v>3.37</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>上海自动化仪表研究所</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1296,6 +1306,11 @@
       <c r="L21" t="n">
         <v>5.4</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>华东计算所</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1546,6 +1561,11 @@
           <t>淮海西路432号</t>
         </is>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>上海无线电技术研究所</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2346,6 +2366,11 @@
           <t>北京工业志·电子志·第三章电子计算机；北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
         </is>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>市计算机技术研究所</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2726,6 +2751,11 @@
           <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
         </is>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>计算机服务公司</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3395,6 +3425,11 @@
           <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
         </is>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3901,6 +3936,11 @@
       <c r="R108" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>华东师范</t>
         </is>
       </c>
     </row>
@@ -5182,7 +5222,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>上无十三培训阿国实习生、华东计算所何上海市计算技术研究所派员</t>
+          <t>上无十三、华东计算所、上海市计算技术研究所</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5210,7 +5250,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>上无十三设计、华东计算所何上海无线电技术研究所派员</t>
+          <t>上无十三、华东计算所、上海无线电技术研究所</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5334,7 +5374,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>中兴无线电厂</t>
+          <t>上海中兴无线电厂</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5404,7 +5444,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>上海市计算中心、长宁手拉厂</t>
+          <t>上海市计算中心、上海长宁拉手厂</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -5429,7 +5469,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>上海长宁拉手厂，以后上海中兴无线电厂、新安电工厂投入生产</t>
+          <t>上海长宁拉手厂、上海中兴无线电厂、新安电工厂</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -5515,7 +5555,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>上无十三接产</t>
+          <t>上无十三</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">

--- a/CN_Electronic_Industry.xlsx
+++ b/CN_Electronic_Industry.xlsx
@@ -1681,6 +1681,11 @@
           <t>北京工业志·电子志·第三章电子计算机</t>
         </is>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>北京有线电厂、国营有线电厂</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">

--- a/CN_Electronic_Industry.xlsx
+++ b/CN_Electronic_Industry.xlsx
@@ -8535,538 +8535,681 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>序</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>至</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>关系</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>上海仪器仪表研究所</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>第一机械工业部上海电工仪器研究室</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>19580524</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>19580603</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>始建时名称</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>据 Founder 列推定,待核</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>上海仪器仪表研究所</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>上海电工仪器研究室</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>19580603</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>19640506</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>改称上海电工仪器研究室</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>据 Founder 列推定,待核</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>上海仪器仪表研究所</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>上海电工仪器研究所</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>19640506</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>19791200</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>据 Founder 列推定,待核</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>上海仪器仪表研究所</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>上海仪器仪表研究所</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>19791200</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>据 Founder 列推定,待核</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>上海市无线电技术研究所</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>上海市电讯电器工业公司中心试验室</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>19580700</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>19580800</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>始建时名称</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>据 Founder 列推定,待核</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>上海市无线电技术研究所</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>中国科学院上海无线电技术研究所</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>19580800</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>19690701</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>据 Founder 列推定,待核</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>上海市无线电技术研究所</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>上海市无线电技术研究所</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>19690701</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>划归国防科学技术委员会，组建成航空电子设备研究所</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>据 Founder 列推定,待核</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>上海市电子光学技术研究所</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>上海市电子光学技术研究所</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>19640300</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>19750200</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>原表未著录此段名称,暂用表内名称</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>据 Founder 列推定,待核</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>上海市电子光学技术研究所</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>上海新跃仪表厂</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>19750200</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>19861212</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>改名上海新跃仪表厂</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>据 Founder 列推定,待核</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>上海市电子光学技术研究所</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>上海市电子光学技术研究所</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>19861212</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>从新跃仪表厂划出</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>据 Founder 列推定,待核</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>上海微波设备研究所</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>上海金星制铜厂</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>19501100</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>19610000</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>始建时名称</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>据 Founder 列推定,待核</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>上海微波设备研究所</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>上海仪表铜厂</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>19610000</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>19680000</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>据 Founder 列推定,待核</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>上海微波设备研究所</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>上海微波设备研究所</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>19680000</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>划归四机部</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>据 Founder 列推定,待核</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>中国科学院上海冶金研究所</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>中央研究院工学研究所</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>19280000</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>19490000</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>始建时名称</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>据 Founder 列推定,待核</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>中国科学院上海冶金研究所</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>中国科学院工学实验馆</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>19490000</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>19530000</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
         <is>
           <t>据 Founder 列推定,待核</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>中国科学院上海冶金研究所</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>中国科学院冶金陶瓷研究所</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>19530000</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>19600000</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>据 Founder 列推定,待核</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>中国科学院上海冶金研究所</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>中国科学院冶金研究所</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>19600000</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>19700000</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>据 Founder 列推定,待核</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>中国科学院上海冶金研究所</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>中国科学院上海冶金研究所</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>19700000</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>据 Founder 列推定,待核</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>上海市无线电技术研究所</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>上海市电讯电器工业公司中心试验室</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>19580700</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>始建时名称</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>据 Founder 列推定,待核</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>上海市无线电技术研究所</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>中国科学院上海无线电技术研究所</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>19580800</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>据 Founder 列推定,待核</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>上海市无线电技术研究所</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>上海市无线电技术研究所</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>19690701</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>划归国防科学技术委员会，组建成航空电子设备研究所</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>据 Founder 列推定,待核</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>上海市电子光学技术研究所</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>上海市电子光学技术研究所</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>19640300</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>原表未著录此段名称,暂用表内名称</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>据 Founder 列推定,待核</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>上海市电子光学技术研究所</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>上海新跃仪表厂</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>19750200</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>改名上海新跃仪表厂</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>据 Founder 列推定,待核</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>上海市电子光学技术研究所</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>上海市电子光学技术研究所</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>19861212</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>从新跃仪表厂划出</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>据 Founder 列推定,待核</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>上海仪器仪表研究所</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>第一机械工业部上海电工仪器研究室</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>19580524</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>始建时名称</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>据 Founder 列推定,待核</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>上海仪器仪表研究所</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>上海电工仪器研究室</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>19580603</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>改称上海电工仪器研究室</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>据 Founder 列推定,待核</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>上海仪器仪表研究所</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>上海电工仪器研究所</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>19640506</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>据 Founder 列推定,待核</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>上海仪器仪表研究所</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>上海仪器仪表研究所</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>19791200</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>据 Founder 列推定,待核</t>
-        </is>
-      </c>
-    </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>北京无线电一厂</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>北京计算机一厂</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>19700000</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>1970年初，北京无线电一厂（后更名为北京计算机一厂）接受原航空部第20研究所的委托，开始研制大型晶体管模数混合计算机，1975年，完成研制任务，定名为HMJ-200大型晶体管模数混合计算机。</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>北京联想计算机集团公司</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>联想集团公司</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>19880000</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>1988年，北京联想计算机集团公司（后更名为联想集团公司，以下简称联想集团）开始研制联想系列微机。</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
         </is>

--- a/CN_Electronic_Industry.xlsx
+++ b/CN_Electronic_Industry.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Fact and Comp-Shanghai" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Semi-Product" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Comp-Product" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Name-History" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fact and Comp-Shanghai" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semi-Product" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comp-Product" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Name-History" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -393,7 +393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S122"/>
+  <dimension ref="A1:T197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.28515625" customWidth="1" min="1" max="1"/>
@@ -454,6 +454,11 @@
           <t>别名</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>统计年</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="I2" t="inlineStr">
@@ -4254,6 +4259,3393 @@
       <c r="R122" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>北京东光电工厂</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>19680200</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>酒仙桥路12号</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>1499</v>
+      </c>
+      <c r="J123" t="n">
+        <v>142</v>
+      </c>
+      <c r="L123" t="n">
+        <v>90600</v>
+      </c>
+      <c r="M123" t="n">
+        <v>11100</v>
+      </c>
+      <c r="N123" t="n">
+        <v>686</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十二节北京东光电工厂</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>国营第878厂</t>
+        </is>
+      </c>
+      <c r="T123" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>北京牡丹电子集团公司</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>外围设备</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>彩色电视机</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>19900216</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>19650000北京无线电精密元件厂-&gt;19731100改名北京电视机厂-&gt;北京电视机厂与北京电子显示设各厂合并-&gt;19910000北京东风电视机厂合并</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>5617</v>
+      </c>
+      <c r="J124" t="n">
+        <v>896</v>
+      </c>
+      <c r="L124" t="n">
+        <v>136200</v>
+      </c>
+      <c r="M124" t="n">
+        <v>45000</v>
+      </c>
+      <c r="N124" t="n">
+        <v>146000</v>
+      </c>
+      <c r="O124" t="n">
+        <v>107000</v>
+      </c>
+      <c r="P124" t="n">
+        <v>2504.5</v>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
+        </is>
+      </c>
+      <c r="T124" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>北京电视设备厂</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>彩色摄像机、彩色锁相同步机、J52等十余种型号的录像机</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>19710500</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>国营761厂电视车间与北京被服厂合并</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>东四北大街107号</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>1139</v>
+      </c>
+      <c r="J125" t="n">
+        <v>264</v>
+      </c>
+      <c r="L125" t="n">
+        <v>18100</v>
+      </c>
+      <c r="M125" t="n">
+        <v>12000</v>
+      </c>
+      <c r="N125" t="n">
+        <v>29200</v>
+      </c>
+      <c r="P125" t="n">
+        <v>1972</v>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十四节北京电视设备厂</t>
+        </is>
+      </c>
+      <c r="T125" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>北京飞达电子集团公司</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>收录机</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>19930200</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>19540000北京电影机械修理厂-&gt;19700000改名北京电影机械厂-&gt;19810000改名北京录音机厂</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>苏州街75号</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>792</v>
+      </c>
+      <c r="J126" t="n">
+        <v>95</v>
+      </c>
+      <c r="L126" t="n">
+        <v>30200</v>
+      </c>
+      <c r="N126" t="n">
+        <v>1444</v>
+      </c>
+      <c r="P126" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
+        </is>
+      </c>
+      <c r="T126" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>北京显像管总厂</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>低频大功率管、23厘米黑白显像管和50厘米显像管、35厘米黑白显像管、彩色显示管</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>19700000北京呢绒服装厂-&gt;19721100改名北京显值管厂-&gt;19900000改名北京显像管总厂</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>光明西路1号</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>1023</v>
+      </c>
+      <c r="J127" t="n">
+        <v>138</v>
+      </c>
+      <c r="L127" t="n">
+        <v>52800</v>
+      </c>
+      <c r="M127" t="n">
+        <v>4637.2</v>
+      </c>
+      <c r="N127" t="n">
+        <v>1124</v>
+      </c>
+      <c r="P127" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
+        </is>
+      </c>
+      <c r="T127" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>北京广播电视配件一厂</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>19540000</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>19570000合并改建为北京无线电电匣厂-&gt;19610000并入北京电子仪器厂-&gt;19650000改名北京无线电非金属元件厂-&gt;19700000改名北京无线电元件厂</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>东铁匠营横七条30号</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>910</v>
+      </c>
+      <c r="J128" t="n">
+        <v>62</v>
+      </c>
+      <c r="L128" t="n">
+        <v>34800</v>
+      </c>
+      <c r="M128" t="n">
+        <v>2918.8</v>
+      </c>
+      <c r="N128" t="n">
+        <v>929</v>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十九节北京广播电视配件一厂</t>
+        </is>
+      </c>
+      <c r="T128" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>北京电视配件三厂</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>改名北京广播电视配件三厂-&gt;19660000东红路塑料制品厂-&gt;19700000改名东红路无线电元件厂-&gt;19750000改名朝阳区东红路无线电元件厂</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>酒仙桥南路5号</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>1057</v>
+      </c>
+      <c r="J129" t="n">
+        <v>130</v>
+      </c>
+      <c r="L129" t="n">
+        <v>35200</v>
+      </c>
+      <c r="M129" t="n">
+        <v>7816.1</v>
+      </c>
+      <c r="N129" t="n">
+        <v>12700</v>
+      </c>
+      <c r="P129" t="n">
+        <v>1812.7</v>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
+        </is>
+      </c>
+      <c r="T129" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>北京市调谐器厂</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>19810200</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>19691000合并为西城区无线电元件厂-&gt;19790000改名北京广播电视配件五厂</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>家来街月台胡同18号</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>545</v>
+      </c>
+      <c r="J130" t="n">
+        <v>21</v>
+      </c>
+      <c r="L130" t="n">
+        <v>39700</v>
+      </c>
+      <c r="M130" t="n">
+        <v>2835.3</v>
+      </c>
+      <c r="N130" t="n">
+        <v>1245</v>
+      </c>
+      <c r="O130" t="n">
+        <v>1504.8</v>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十一节北京市调谐器厂</t>
+        </is>
+      </c>
+      <c r="T130" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>北京广播通讯电源厂</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>19540000</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>19570000改名北京鞋底厂-&gt;19600000改名北京鞋厂-&gt;19720000改名北京东风电池厂-&gt;19790500改名北京广播电视配件六厂-&gt;19880000改名北京广播通讯电源厂</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>396</v>
+      </c>
+      <c r="J131" t="n">
+        <v>15</v>
+      </c>
+      <c r="L131" t="n">
+        <v>30100</v>
+      </c>
+      <c r="N131" t="n">
+        <v>240</v>
+      </c>
+      <c r="P131" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十二节北京广播通讯电源厂</t>
+        </is>
+      </c>
+      <c r="T131" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>北京无线电仪器厂</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>19620600</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>北京崇文电器仪器厂、北京电器厂合并</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>福长街四条4号</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>709</v>
+      </c>
+      <c r="J132" t="n">
+        <v>172</v>
+      </c>
+      <c r="L132" t="n">
+        <v>21200</v>
+      </c>
+      <c r="M132" t="n">
+        <v>1873.8</v>
+      </c>
+      <c r="N132" t="n">
+        <v>3453</v>
+      </c>
+      <c r="P132" t="n">
+        <v>165.5</v>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十七节北京无线电仪器厂</t>
+        </is>
+      </c>
+      <c r="T132" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>北京无线电仪器二厂</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>19700400</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>改名北京广播器材厂-&gt;合并组建了北京市综合仪器厂-&gt;19590000之一的北京电子仪器厂-&gt;19620900东城无线电仪器装配厂和电讯仪表厂合并-&gt;19700000北京无线电二厂合并-&gt;北京电子仪器厂、北京无线电二厂合并</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>符台路2号</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>622</v>
+      </c>
+      <c r="L133" t="n">
+        <v>36900</v>
+      </c>
+      <c r="M133" t="n">
+        <v>2209</v>
+      </c>
+      <c r="N133" t="n">
+        <v>237</v>
+      </c>
+      <c r="O133" t="n">
+        <v>206.7</v>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
+        </is>
+      </c>
+      <c r="T133" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>北京广播器材厂</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>广播发射机、电视发射机、电视差转机、盒式录像机</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>19500601北京人民广播器材厂</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>今四环胡同4号</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>3486</v>
+      </c>
+      <c r="J134" t="n">
+        <v>783</v>
+      </c>
+      <c r="L134" t="n">
+        <v>227200</v>
+      </c>
+      <c r="M134" t="n">
+        <v>23900</v>
+      </c>
+      <c r="N134" t="n">
+        <v>7904.9</v>
+      </c>
+      <c r="P134" t="n">
+        <v>683.6</v>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第九节北京广播器材厂</t>
+        </is>
+      </c>
+      <c r="T134" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>北京邮电通信设备厂</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>生产微波三大固体器件、微波三大固体器件</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>19410900</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>组建了4个合资公司-&gt;1941年9月建立的华北电信电话股份有限公司</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>将台路5号</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>1367</v>
+      </c>
+      <c r="J135" t="n">
+        <v>724</v>
+      </c>
+      <c r="L135" t="n">
+        <v>86000</v>
+      </c>
+      <c r="M135" t="n">
+        <v>8359.4</v>
+      </c>
+      <c r="N135" t="n">
+        <v>7489</v>
+      </c>
+      <c r="P135" t="n">
+        <v>189</v>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第一节北京邮电通信设备厂</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>邮电506厂</t>
+        </is>
+      </c>
+      <c r="T135" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>北京通信元件厂</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>半导体器件、高反压复合场效应晶体管、和销售BP机</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>新街口外大街28号</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>450</v>
+      </c>
+      <c r="L136" t="n">
+        <v>70000</v>
+      </c>
+      <c r="M136" t="n">
+        <v>3040.9</v>
+      </c>
+      <c r="N136" t="n">
+        <v>4423.4</v>
+      </c>
+      <c r="O136" t="n">
+        <v>12000</v>
+      </c>
+      <c r="P136" t="n">
+        <v>360</v>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第二节邮电部北京通信元件厂</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>邮电508厂</t>
+        </is>
+      </c>
+      <c r="T136" t="n">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>北京长城无线电厂</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>19740000下放北京市</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>学院南路34号</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>790</v>
+      </c>
+      <c r="L137" t="n">
+        <v>36300</v>
+      </c>
+      <c r="M137" t="n">
+        <v>3226</v>
+      </c>
+      <c r="N137" t="n">
+        <v>3523</v>
+      </c>
+      <c r="P137" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第三节北京长城无线电厂</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>国营第6971厂</t>
+        </is>
+      </c>
+      <c r="T137" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>北京核仪器厂</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>19560000</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>当时的北京市电器厂、北京市钻探机械厂、北京市公私合营电话器材厂和亚细亚商行喇叭组四单位合并-&gt;北京市综合仪器厂-&gt;19620000划归第二机械工业部-&gt;19630000二机部北京第十研究所合并</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>东环北路42号</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>1307</v>
+      </c>
+      <c r="J138" t="n">
+        <v>348</v>
+      </c>
+      <c r="L138" t="n">
+        <v>181500</v>
+      </c>
+      <c r="N138" t="n">
+        <v>2148</v>
+      </c>
+      <c r="O138" t="n">
+        <v>2201</v>
+      </c>
+      <c r="P138" t="n">
+        <v>287</v>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第四节北京核仪器厂</t>
+        </is>
+      </c>
+      <c r="T138" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>北京建中机器厂</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>19561000</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>酒仙桥万红路1号</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>1418</v>
+      </c>
+      <c r="J139" t="n">
+        <v>290</v>
+      </c>
+      <c r="L139" t="n">
+        <v>133700</v>
+      </c>
+      <c r="N139" t="n">
+        <v>4348.8</v>
+      </c>
+      <c r="P139" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第一节北京建中机器厂</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>国营第700厂</t>
+        </is>
+      </c>
+      <c r="T139" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>北京市电声器材总厂</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>北京扬声器厂、北京无线电元件十四厂、北京广播电视配件四厂合并</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>广安门内德泉胡同10号</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>722</v>
+      </c>
+      <c r="J140" t="n">
+        <v>39</v>
+      </c>
+      <c r="L140" t="n">
+        <v>48500</v>
+      </c>
+      <c r="M140" t="n">
+        <v>3087</v>
+      </c>
+      <c r="N140" t="n">
+        <v>1165</v>
+      </c>
+      <c r="P140" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十节北京市电声器材总厂</t>
+        </is>
+      </c>
+      <c r="T140" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>北京市无线电元件一厂</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>19680000</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>19640000改名北京竹藤制品厂-&gt;19680000改名北京市无线电元件一厂</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>德胜门外后九条小市口胡同1号</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>448</v>
+      </c>
+      <c r="J141" t="n">
+        <v>52</v>
+      </c>
+      <c r="L141" t="n">
+        <v>11500</v>
+      </c>
+      <c r="M141" t="n">
+        <v>2209.8</v>
+      </c>
+      <c r="N141" t="n">
+        <v>910.3</v>
+      </c>
+      <c r="P141" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十一节北京市无线电元件一厂</t>
+        </is>
+      </c>
+      <c r="T141" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>北京无线电元件四厂</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>19670000</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>北京市石景山电容器厂-&gt;19780000划归北京市仪表工业局-&gt;19790000改名北京无线电元件四厂</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>古城北路甲4号</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>511</v>
+      </c>
+      <c r="J142" t="n">
+        <v>51</v>
+      </c>
+      <c r="L142" t="n">
+        <v>13700</v>
+      </c>
+      <c r="M142" t="n">
+        <v>2090.4</v>
+      </c>
+      <c r="N142" t="n">
+        <v>3054</v>
+      </c>
+      <c r="P142" t="n">
+        <v>416.1</v>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十三节北京无线电元件四厂</t>
+        </is>
+      </c>
+      <c r="T142" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>北京市无线电元件六厂</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>计算机、收录机</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>19700100</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>19720300年8月与北京皮毛三厂合并-&gt;19790300并入北京市无线电元件六厂</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>北京站东街10号</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>747</v>
+      </c>
+      <c r="J143" t="n">
+        <v>108</v>
+      </c>
+      <c r="L143" t="n">
+        <v>12600</v>
+      </c>
+      <c r="M143" t="n">
+        <v>1844.3</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十四节北京市无线电元件六厂</t>
+        </is>
+      </c>
+      <c r="T143" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>北京无线电元件九厂</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>19600000</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>北京市东城区无线电元件厂-&gt;19620000改名北京无线电插接元件厂-&gt;19790000改名北京无线电元件九厂</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>深沟村</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>785</v>
+      </c>
+      <c r="J144" t="n">
+        <v>128</v>
+      </c>
+      <c r="L144" t="n">
+        <v>51700</v>
+      </c>
+      <c r="M144" t="n">
+        <v>3258.4</v>
+      </c>
+      <c r="N144" t="n">
+        <v>3182</v>
+      </c>
+      <c r="O144" t="n">
+        <v>905.8</v>
+      </c>
+      <c r="P144" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十五节北京无线电元件九厂</t>
+        </is>
+      </c>
+      <c r="T144" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>北京市半导体器件一厂</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>19650000</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>组建的北京市无线电综合元件厂-&gt;19780600改名北京市半导体器件一厂</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>幸福三村北街1号</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>874</v>
+      </c>
+      <c r="J145" t="n">
+        <v>192</v>
+      </c>
+      <c r="L145" t="n">
+        <v>33700</v>
+      </c>
+      <c r="M145" t="n">
+        <v>4427.5</v>
+      </c>
+      <c r="N145" t="n">
+        <v>889</v>
+      </c>
+      <c r="P145" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>行业据单位名</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十七节北京市半导体器件一厂</t>
+        </is>
+      </c>
+      <c r="T145" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>北京市半导体器件三厂</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>错三极管、中高档电子琴音律发生器电路</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>19680000</v>
+      </c>
+      <c r="E146" t="n">
+        <v>19680000</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>北京市第二轻工业局所属的金漆厂、玉器厂和象牙厂合并-&gt;19730900划归北京市位器仪表工业局领导后</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>龙潭路3号</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>813</v>
+      </c>
+      <c r="J146" t="n">
+        <v>126</v>
+      </c>
+      <c r="L146" t="n">
+        <v>40500</v>
+      </c>
+      <c r="N146" t="n">
+        <v>1058.8</v>
+      </c>
+      <c r="P146" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>行业据单位名</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十八节北京市半导体器件三厂</t>
+        </is>
+      </c>
+      <c r="T146" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>北京半导体器件五厂</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>19690900</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>北京市西城区半导体器件厂-&gt;19780400改名北京半导体器件五厂</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>德胜门外五路通14号</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>635</v>
+      </c>
+      <c r="J147" t="n">
+        <v>81</v>
+      </c>
+      <c r="L147" t="n">
+        <v>21000</v>
+      </c>
+      <c r="N147" t="n">
+        <v>1141</v>
+      </c>
+      <c r="O147" t="n">
+        <v>1466</v>
+      </c>
+      <c r="P147" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>行业据单位名</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十九节北京半导体器件五厂</t>
+        </is>
+      </c>
+      <c r="T147" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>北京市半导体器件六厂</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>合并后的器件六厂-&gt;原北京市半导体器件六厂与北京市半导体器件七厂合并</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>482</v>
+      </c>
+      <c r="J148" t="n">
+        <v>71</v>
+      </c>
+      <c r="L148" t="n">
+        <v>10600</v>
+      </c>
+      <c r="N148" t="n">
+        <v>4546</v>
+      </c>
+      <c r="P148" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>行业据单位名</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第四十节北京市半导体器件六厂</t>
+        </is>
+      </c>
+      <c r="T148" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>北京市可控硅元件厂</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>19680000</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>北京市朝阳可控硅元件厂-&gt;19680000改名朝外大街乒乓球拍厂-&gt;19780000改名北京半导体材料加工厂</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>建国门外砖厂胡同12号</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>292</v>
+      </c>
+      <c r="J149" t="n">
+        <v>27</v>
+      </c>
+      <c r="L149" t="n">
+        <v>16500</v>
+      </c>
+      <c r="N149" t="n">
+        <v>456</v>
+      </c>
+      <c r="O149" t="n">
+        <v>350.1</v>
+      </c>
+      <c r="P149" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>行业据单位名</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第四十一节北京市可控硅元件厂</t>
+        </is>
+      </c>
+      <c r="T149" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>北京701厂</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>微波二极管</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>19700000第四机械工业部-&gt;19790000朝阳器件厂合并</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>双桥西里7号</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>832</v>
+      </c>
+      <c r="J150" t="n">
+        <v>114</v>
+      </c>
+      <c r="L150" t="n">
+        <v>21800</v>
+      </c>
+      <c r="M150" t="n">
+        <v>1885.1</v>
+      </c>
+      <c r="N150" t="n">
+        <v>1947</v>
+      </c>
+      <c r="O150" t="n">
+        <v>1754.9</v>
+      </c>
+      <c r="P150" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第四十二节北京七〇一厂</t>
+        </is>
+      </c>
+      <c r="T150" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>北京无线电工具设备厂</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>外围设备</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>球磨机、油压机、游丝辗压机、自动刺铆机</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>19640000</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>合并组建为北京无线电工具设备厂</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>酒仙桥路2号</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>1269</v>
+      </c>
+      <c r="J151" t="n">
+        <v>123</v>
+      </c>
+      <c r="L151" t="n">
+        <v>107000</v>
+      </c>
+      <c r="M151" t="n">
+        <v>5295.9</v>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第二节北京无线电工具设备厂</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>国营第706厂</t>
+        </is>
+      </c>
+      <c r="T151" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>北京晨星无线电器材厂</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>19500000</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>19590000并入华北无线电器材联合厂为七分厂</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>酒仙桥路2号</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>1513</v>
+      </c>
+      <c r="L152" t="n">
+        <v>49100</v>
+      </c>
+      <c r="N152" t="n">
+        <v>8709.5</v>
+      </c>
+      <c r="P152" t="n">
+        <v>130.9</v>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第三节北京晨星无线电器材厂</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>国营第707厂</t>
+        </is>
+      </c>
+      <c r="T152" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>北京北大方正集团公司</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>制造的5大系列电脑</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>19860000</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>北京大学新技术公司</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>672</v>
+      </c>
+      <c r="J153" t="n">
+        <v>404</v>
+      </c>
+      <c r="L153" t="n">
+        <v>12000</v>
+      </c>
+      <c r="M153" t="n">
+        <v>4217.4</v>
+      </c>
+      <c r="N153" t="n">
+        <v>13200</v>
+      </c>
+      <c r="O153" t="n">
+        <v>84700</v>
+      </c>
+      <c r="P153" t="n">
+        <v>9443.1</v>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章行业归口电子工业企业·第三节北京北大方正集团公司</t>
+        </is>
+      </c>
+      <c r="T153" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>北京京海集团公司</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>19830700</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>计算机机房技术开发公司</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>白石桥络33号</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>727</v>
+      </c>
+      <c r="J154" t="n">
+        <v>349</v>
+      </c>
+      <c r="L154" t="n">
+        <v>2268</v>
+      </c>
+      <c r="M154" t="n">
+        <v>8674</v>
+      </c>
+      <c r="O154" t="n">
+        <v>45599.99999999999</v>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章行业归口电子工业企业·第四节北京京海集团公司</t>
+        </is>
+      </c>
+      <c r="T154" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>北京·松下彩色显像管有限公司</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>14型球面彩色显像管、线并行生产两个品种的彩管、两个品种的彩管</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>19870900</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>酒仙桥北路9号</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>4180</v>
+      </c>
+      <c r="J155" t="n">
+        <v>570</v>
+      </c>
+      <c r="L155" t="n">
+        <v>136000</v>
+      </c>
+      <c r="M155" t="n">
+        <v>159200</v>
+      </c>
+      <c r="N155" t="n">
+        <v>274300</v>
+      </c>
+      <c r="P155" t="n">
+        <v>12020</v>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第一节北京·松下彩色显像管有限公司</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>BMCC</t>
+        </is>
+      </c>
+      <c r="T155" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>北京飞利浦有限公司</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>经营值携式收录机</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>19850810</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>北洼路4号</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>647</v>
+      </c>
+      <c r="J156" t="n">
+        <v>85</v>
+      </c>
+      <c r="L156" t="n">
+        <v>8000</v>
+      </c>
+      <c r="M156" t="n">
+        <v>2187.9</v>
+      </c>
+      <c r="N156" t="n">
+        <v>33000</v>
+      </c>
+      <c r="O156" t="n">
+        <v>21800</v>
+      </c>
+      <c r="P156" t="n">
+        <v>1021.5</v>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第三节北京飞利浦有限公司</t>
+        </is>
+      </c>
+      <c r="T156" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>中国惠普有限公司</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>经营业务范围包括计算机系统及微机</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>19850600</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>建国门外东三环南路2号</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>585</v>
+      </c>
+      <c r="J157" t="n">
+        <v>358</v>
+      </c>
+      <c r="M157" t="n">
+        <v>8758.299999999999</v>
+      </c>
+      <c r="N157" t="n">
+        <v>3763</v>
+      </c>
+      <c r="P157" t="n">
+        <v>32700</v>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第四节中国惠普有限公司</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>CHP</t>
+        </is>
+      </c>
+      <c r="T157" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>北京有线电总厂</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>生产步进制自动电话交换机、步进制自动电话交换机、生产纵横制自动电话交换机、纵横制自动电话交换机</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>19570900</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>北京有线电厂</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>酒仙桥路14号</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>3259</v>
+      </c>
+      <c r="L158" t="n">
+        <v>321700</v>
+      </c>
+      <c r="M158" t="n">
+        <v>18700</v>
+      </c>
+      <c r="N158" t="n">
+        <v>54800.00000000001</v>
+      </c>
+      <c r="P158" t="n">
+        <v>3202</v>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第七节北京有线电总厂</t>
+        </is>
+      </c>
+      <c r="T158" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>北京·松下电子部品有限公司</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>销售电视机</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>19930900</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>720</v>
+      </c>
+      <c r="J159" t="n">
+        <v>130</v>
+      </c>
+      <c r="L159" t="n">
+        <v>19600</v>
+      </c>
+      <c r="N159" t="n">
+        <v>30900</v>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第六节北京·松下电子部品有限公司</t>
+        </is>
+      </c>
+      <c r="T159" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>北京第一无线电器材厂</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>电子节能灯等显示管、收录音机</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>19571000</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>酒仙桥路2号</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>2050</v>
+      </c>
+      <c r="J160" t="n">
+        <v>77</v>
+      </c>
+      <c r="L160" t="n">
+        <v>120000</v>
+      </c>
+      <c r="N160" t="n">
+        <v>3771</v>
+      </c>
+      <c r="P160" t="n">
+        <v>163.8</v>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第四节北京第一无线电器材厂</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>国营第797厂</t>
+        </is>
+      </c>
+      <c r="T160" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>北京第二无线电器材厂</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>19640000</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>酒仙桥路4号</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>1529</v>
+      </c>
+      <c r="J161" t="n">
+        <v>67</v>
+      </c>
+      <c r="L161" t="n">
+        <v>104100</v>
+      </c>
+      <c r="M161" t="n">
+        <v>10000</v>
+      </c>
+      <c r="N161" t="n">
+        <v>3686</v>
+      </c>
+      <c r="P161" t="n">
+        <v>111.3</v>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第五节北京第二无线电器材厂</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>国营第718厂</t>
+        </is>
+      </c>
+      <c r="T161" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>北京电子动力公司</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>19570000</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>酒仙桥路4号</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>2847</v>
+      </c>
+      <c r="J162" t="n">
+        <v>237</v>
+      </c>
+      <c r="L162" t="n">
+        <v>319000</v>
+      </c>
+      <c r="N162" t="n">
+        <v>11900</v>
+      </c>
+      <c r="P162" t="n">
+        <v>366</v>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第八节北京电子动力公司</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>国营第751厂</t>
+        </is>
+      </c>
+      <c r="T162" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>北京大华无线电仪器厂</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>19580800</v>
+      </c>
+      <c r="E163" t="n">
+        <v>19841200</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>北京微技测量仪器厂</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>学院路5号</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>1258</v>
+      </c>
+      <c r="J163" t="n">
+        <v>298</v>
+      </c>
+      <c r="L163" t="n">
+        <v>192000</v>
+      </c>
+      <c r="M163" t="n">
+        <v>742.6</v>
+      </c>
+      <c r="O163" t="n">
+        <v>2282.7</v>
+      </c>
+      <c r="P163" t="n">
+        <v>624.2</v>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第十节北京大华无线电仪器厂</t>
+        </is>
+      </c>
+      <c r="T163" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>北京东方电子集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>18种电子管</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>19520000</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>19920618组建了北京东方电子集团公司-&gt;19930408组建为北京东方电子集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>酒仙桥路10号</t>
+        </is>
+      </c>
+      <c r="L164" t="n">
+        <v>320000</v>
+      </c>
+      <c r="M164" t="n">
+        <v>25000</v>
+      </c>
+      <c r="P164" t="n">
+        <v>1859</v>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第十一节 北京东方电子集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="T164" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>北京飞行电子总公司</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>19640000</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>19571000北京第三无线电器材厂</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>酒仙桥路4号</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>2639</v>
+      </c>
+      <c r="J165" t="n">
+        <v>285</v>
+      </c>
+      <c r="L165" t="n">
+        <v>211700</v>
+      </c>
+      <c r="M165" t="n">
+        <v>13600</v>
+      </c>
+      <c r="N165" t="n">
+        <v>8188</v>
+      </c>
+      <c r="P165" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第六节北京飞行电子总公司</t>
+        </is>
+      </c>
+      <c r="T165" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>北京市电镀总厂</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>19580000</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>488</v>
+      </c>
+      <c r="J166" t="n">
+        <v>20</v>
+      </c>
+      <c r="L166" t="n">
+        <v>24800</v>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第二十九节北京市电镀总厂</t>
+        </is>
+      </c>
+      <c r="T166" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>北京市无线电元件二厂</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>19681200</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>德胜门外塔院胡同8号</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>540</v>
+      </c>
+      <c r="J167" t="n">
+        <v>58</v>
+      </c>
+      <c r="L167" t="n">
+        <v>4887</v>
+      </c>
+      <c r="M167" t="n">
+        <v>1796.9</v>
+      </c>
+      <c r="N167" t="n">
+        <v>1614</v>
+      </c>
+      <c r="O167" t="n">
+        <v>989.1</v>
+      </c>
+      <c r="P167" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十二节北京市无线电元件二厂</t>
+        </is>
+      </c>
+      <c r="T167" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>北京市无线电元件十厂</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>19710000</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>朝阳门外二条67号</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>654</v>
+      </c>
+      <c r="J168" t="n">
+        <v>32</v>
+      </c>
+      <c r="L168" t="n">
+        <v>56300</v>
+      </c>
+      <c r="M168" t="n">
+        <v>3673</v>
+      </c>
+      <c r="N168" t="n">
+        <v>4742</v>
+      </c>
+      <c r="P168" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十六节北京市无线电元件十厂</t>
+        </is>
+      </c>
+      <c r="T168" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>北京国兴电子有限公司</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>19880400</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>775</v>
+      </c>
+      <c r="J169" t="n">
+        <v>132</v>
+      </c>
+      <c r="L169" t="n">
+        <v>10400</v>
+      </c>
+      <c r="N169" t="n">
+        <v>10400</v>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第二节北京国兴电子有限公司</t>
+        </is>
+      </c>
+      <c r="T169" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>北京国际交换系统有限公司</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>19901100</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>酒仙桥路14号</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>1108</v>
+      </c>
+      <c r="J170" t="n">
+        <v>404</v>
+      </c>
+      <c r="L170" t="n">
+        <v>3929</v>
+      </c>
+      <c r="N170" t="n">
+        <v>110400</v>
+      </c>
+      <c r="O170" t="n">
+        <v>102300</v>
+      </c>
+      <c r="P170" t="n">
+        <v>24000</v>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>另有他年数字:floor=1990年</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第五节北京国际交换系统有限公司</t>
+        </is>
+      </c>
+      <c r="T170" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>北京电视机厂</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>北京电子显示设各厂</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>北京市无线电元件三厂</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>国营761厂</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十四节北京电视设备厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>公私合营广播器材厂</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十五节北京无线电厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>北京电子仪器厂</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十五节北京无线电厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>北京录音机厂</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>北京鸿达电器公司</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>北京飞达电子有限公司</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>北京市半导体器件五厂</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>北京显像管厂</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>北京无线电电匣厂</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十九节北京广播电视配件一厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>北京安乐福塑料制品有限公司</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十九节北京广播电视配件一厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>北京松下彩色显像管有限公司</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>北京无线电二厂</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>北京人民广播器材厂</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>华北无线电器材联合厂</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>国营774厂</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>北京市综合仪器厂</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>北京铭信电子有限公司</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十一节北京市无线电元件一厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>北京无线电插接元件厂</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十五节北京无线电元件九厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>半导体器件六厂</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第四十节北京市半导体器件六厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>中国邮电工业总公司</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第一节北京邮电通信设备厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>海淀区学院</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第三节北京长城无线电厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>中国烟草总公司</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第三节北京长城无线电厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>北京第三无线电器材厂</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第六节北京飞行电子总公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>北京旭硝子电子玻璃有限公司</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志</t>
         </is>
       </c>
     </row>
@@ -4268,7 +7660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.7109375" customWidth="1" min="1" max="1"/>
@@ -5042,6 +8434,2565 @@
       </c>
       <c r="F50" t="n">
         <v>589</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>彩色电视机</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>北京牡丹电子集团公司</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>19731100</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>彩色摄像机</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>北京电视设备厂</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>19720000</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>产量据「年产量高达30万套」。北京工业志·电子志·第十四节北京电视设备厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>彩色锁相同步机</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>北京电视设备厂</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>19720000</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>产量据「年产量高达30万套」。北京工业志·电子志·第十四节北京电视设备厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>J52等十余种型号的录像机</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>北京电视设备厂</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十四节北京电视设备厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>电视组合机</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>北京无线电厂</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>19610000</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>产量据「产量达到4.9万台」。北京工业志·电子志·第十五节北京无线电厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>半导体收音机</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>北京无线电厂</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>19620000</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>产量据「产量达到4.9万台」。北京工业志·电子志·第十五节北京无线电厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>盒式磁带录音机</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>北京无线电厂</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>19780000</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>产量据「产量达到4.9万台」。北京工业志·电子志·第十五节北京无线电厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>研制VCD视盘机</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>北京无线电厂</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>产量据「产量达到4.9万台」。北京工业志·电子志·第十五节北京无线电厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>VCD视盘机</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>北京无线电厂</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>产量据「产量达到4.9万台」。北京工业志·电子志·第十五节北京无线电厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>牡丹牌收音机</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>北京无线电厂</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>19950000</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十五节北京无线电厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>收音机</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>北京无线电三厂</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十六节北京无线电三厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>收录机</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>北京飞达电子集团公司</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>低频大功率管</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>北京显像管总厂</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>23厘米黑白显像管</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>北京显像管总厂</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>19710000</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>50厘米显像管</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>北京显像管总厂</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>19710000</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>35厘米黑白显像管</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>北京显像管总厂</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>19820000</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>收音机</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>北京计算机一厂</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>19500000</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十三节北京计算机一厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>广播发射机</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>北京广播器材厂</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第九节北京广播器材厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>电视发射机</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>北京广播器材厂</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第九节北京广播器材厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>电视差转机</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>北京广播器材厂</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第九节北京广播器材厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>盒式录像机</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>北京广播器材厂</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第九节北京广播器材厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>收录机</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>北京广播器材厂</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第九节北京广播器材厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>彩色投影电视机</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>北京广播器材厂</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第九节北京广播器材厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>彩色盒式录像机</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>北京广播器材厂</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第九节北京广播器材厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1千瓦全固态电视发射机</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>北京广播器材厂</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第九节北京广播器材厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>生产微波三大固体器件</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>北京邮电通信设备厂</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第一节北京邮电通信设备厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>微波三大固体器件</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>北京邮电通信设备厂</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第一节北京邮电通信设备厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>半导体器件</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>北京通信元件厂</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第二节邮电部北京通信元件厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>高反压复合场效应晶体管</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>北京通信元件厂</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>19820000</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第二节邮电部北京通信元件厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>和销售BP机</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>北京通信元件厂</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>19920000</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第二节邮电部北京通信元件厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>收录机</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>北京市无线电元件六厂</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十四节北京市无线电元件六厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>错三极管</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>北京市半导体器件三厂</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>19730000</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十八节北京市半导体器件三厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>中高档电子琴音律发生器电路</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>北京市半导体器件三厂</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>19810000</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十八节北京市半导体器件三厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>微波二极管</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>北京七〇一厂</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第四十二节北京七〇一厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>球磨机</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>北京无线电工具设备厂</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>19500000</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>产量据「累计生产备类专用设备1.5万台」。北京工业志·电子志·第二章中央在京电子工业企业·第二节北京无线电工具设备厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>油压机</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>北京无线电工具设备厂</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>19500000</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>产量据「累计生产备类专用设备1.5万台」。北京工业志·电子志·第二章中央在京电子工业企业·第二节北京无线电工具设备厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>游丝辗压机</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>北京无线电工具设备厂</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>19500000</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>产量据「累计生产备类专用设备1.5万台」。北京工业志·电子志·第二章中央在京电子工业企业·第二节北京无线电工具设备厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>自动刺铆机</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>北京无线电工具设备厂</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>19500000</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>产量据「累计生产备类专用设备1.5万台」。北京工业志·电子志·第二章中央在京电子工业企业·第二节北京无线电工具设备厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>自动卷绕机</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>北京无线电工具设备厂</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>19500000</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>产量据「累计生产备类专用设备1.5万台」。北京工业志·电子志·第二章中央在京电子工业企业·第二节北京无线电工具设备厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>自动装配机</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>北京无线电工具设备厂</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>19500000</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>产量据「累计生产备类专用设备1.5万台」。北京工业志·电子志·第二章中央在京电子工业企业·第二节北京无线电工具设备厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>程控交换机</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>北京航星机器制造公司</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章行业归口电子工业企业·第八节北京航星机器制造公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>14型球面彩色显像管</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>北京·松下彩色显像管有限公司</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>19900500</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>产量据「生产能力120万只」。北京工业志·电子志·第四章中外合资电子工业企业·第一节北京·松下彩色显像管有限公司</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>线并行生产两个品种的彩管</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>北京·松下彩色显像管有限公司</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>产量据「年产2358万只」。北京工业志·电子志·第四章中外合资电子工业企业·第一节北京·松下彩色显像管有限公司</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>23580000</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>两个品种的彩管</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>北京·松下彩色显像管有限公司</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>产量据「年产2358万只」。北京工业志·电子志·第四章中外合资电子工业企业·第一节北京·松下彩色显像管有限公司</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>23580000</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>经营值携式收录机</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>北京飞利浦有限公司</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第三节北京飞利浦有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>生产步进制自动电话交换机</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>北京有线电总厂</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>19020000</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第七节北京有线电总厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>步进制自动电话交换机</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>北京有线电总厂</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>19020000</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第七节北京有线电总厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>生产纵横制自动电话交换机</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>北京有线电总厂</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>19500000</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第七节北京有线电总厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>纵横制自动电话交换机</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>北京有线电总厂</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>19500000</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第七节北京有线电总厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>生产电子管</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>北京有线电总厂</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>19950000</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第七节北京有线电总厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>MS2100等各种类型的文字处理机</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>北京四通办公设备有限公司</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第七节北京四通办公设备有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>电子节能灯等显示管</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>北京第一无线电器材厂</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>19950000</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第四节北京第一无线电器材厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>收录音机</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>北京第一无线电器材厂</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>19950000</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第四节北京第一无线电器材厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>18种电子管</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>北京东方电子集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第十一节 北京东方电子集团股份有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>T0</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「生产品种多达400多个」。北京工业志·电子志·第十二节北京东光电工厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>DG54</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「生产品种多达400多个」。北京工业志·电子志·第十二节北京东光电工厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>DG74</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「生产品种多达400多个」。北京工业志·电子志·第十二节北京东光电工厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>DG4000</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「生产品种多达400多个」。北京工业志·电子志·第十二节北京东光电工厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>T076</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>19810000</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第十二节北京东光电工厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>TO63</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>19810000</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第十二节北京东光电工厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>T078</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>19810000</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第十二节北京东光电工厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>T065</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>19810000</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第十二节北京东光电工厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>HT382</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>19911100</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>KY-1型</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>19940400</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>KY310型</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>19810000</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「年产量高达30万套」。北京工业志·电子志·第十四节北京电视设备厂</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>LX-2210</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第十四节北京电视设备厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>NB-3</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第十四节北京电视设备厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>6101型</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>19610000</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「产量达到4.9万台」。北京工业志·电子志·第十五节北京无线电厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>198型</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>19950000</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「产量达到4.9万台」。北京工业志·电子志·第十五节北京无线电厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>HA-10型</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>19860000</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第十六节北京无线电三厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>N7401</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>19910000</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「年产量3.4万支」。北京工业志·电子志·第二十节北京电视配件三厂</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>34000</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>KB12型</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>19760400</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十一节北京市调谐器厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>TDQ-2型</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十一节北京市调谐器厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>JSS-1型</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>19630000</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十七节北京无线电仪器厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>JSS-2型</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>19640000</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十七节北京无线电仪器厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>JS-6型</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十七节北京无线电仪器厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>QT-1型</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十七节北京无线电仪器厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>HQ-2型</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十七节北京无线电仪器厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>QT-11型</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>19740000</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十七节北京无线电仪器厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>QL-1</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十七节北京无线电仪器厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>QL-11型</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十七节北京无线电仪器厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>QL-12</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十七节北京无线电仪器厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>QL-13</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十七节北京无线电仪器厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>QT-16型</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十七节北京无线电仪器厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>QR-3型</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「累计生产计价器13万台」。北京工业志·电子志·第二十七节北京无线电仪器厂</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>130000</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>BJ3140型</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十七节北京无线电仪器厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>GR1732</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十七节北京无线电仪器厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>201型</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>SZ-1型</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>24型</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>ZN5970型</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>ZN1040</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>ZN3760</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>B3110</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第一章直属电子工业企业·第二十九节北京市电镀总厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>RJ91</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>19880000</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「生产能力达2200万只」。北京工业志·电子志·第一章直属电子工业企业·第三十一节北京市无线电元件一厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>RJ92型</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>19880000</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「生产能力达2200万只」。北京工业志·电子志·第一章直属电子工业企业·第三十一节北京市无线电元件一厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>RJ14</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第一章直属电子工业企业·第三十一节北京市无线电元件一厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>RX70型</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第一章直属电子工业企业·第三十一节北京市无线电元件一厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>CJ10型</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第一章直属电子工业企业·第三十二节北京市无线电元件二厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>CJ11</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第一章直属电子工业企业·第三十二节北京市无线电元件二厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>CL11</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第一章直属电子工业企业·第三十三节北京无线电元件四厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>CL12</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第一章直属电子工业企业·第三十三节北京无线电元件四厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>CL21</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第一章直属电子工业企业·第三十三节北京无线电元件四厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>CL61</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第一章直属电子工业企业·第三十三节北京无线电元件四厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>CBB11</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第一章直属电子工业企业·第三十三节北京无线电元件四厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>CBB12</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第一章直属电子工业企业·第三十三节北京无线电元件四厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>CBB21</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第一章直属电子工业企业·第三十三节北京无线电元件四厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>CBB212</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第一章直属电子工业企业·第三十三节北京无线电元件四厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>CH11</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第一章直属电子工业企业·第三十三节北京无线电元件四厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>CH12</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「累计生产10.8亿只」。北京工业志·电子志·第一章直属电子工业企业·第三十三节北京无线电元件四厂</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>1080000000</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>LBN-38</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第一章直属电子工业企业·第三十四节北京市无线电元件六厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>CC1型</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第一章直属电子工业企业·第三十四节北京市无线电元件六厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>CT1-2F4型</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第一章直属电子工业企业·第三十四节北京市无线电元件六厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>KG2型</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第一章直属电子工业企业·第三十五节北京无线电元件九厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>CC4000</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第一章直属电子工业企业·第三十八节北京市半导体器件三厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>SSII-13型</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>19840000</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「生产2000套」。北京工业志·电子志·第一章直属电子工业企业·第四十一节北京市可控硅元件厂</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>HA06</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>19830000</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二章中央在京电子工业企业·第二节邮电部北京通信元件厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>ZT860</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>19840000</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二章中央在京电子工业企业·第二节邮电部北京通信元件厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>ZT-528</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>19840000</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二章中央在京电子工业企业·第二节邮电部北京通信元件厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Z1320</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>19840000</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二章中央在京电子工业企业·第二节邮电部北京通信元件厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>HJD-80型</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>19920000</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二章中央在京电子工业企业·第二节邮电部北京通信元件厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>DXE0248</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>19930000</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二章中央在京电子工业企业·第二节邮电部北京通信元件厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>HJD-256型</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>19930000</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二章中央在京电子工业企业·第二节邮电部北京通信元件厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>DXZ02型</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>19930000</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二章中央在京电子工业企业·第二节邮电部北京通信元件厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>OPH03型</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>19940000</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二章中央在京电子工业企业·第二节邮电部北京通信元件厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>DEW80型</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>19940000</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二章中央在京电子工业企业·第二节邮电部北京通信元件厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>YJ15-YJ35</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>19931000</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二章中央在京电子工业企业·第三节北京长城无线电厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>19950000</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二章中央在京电子工业企业·第三节北京长城无线电厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>D07-2</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>19790000</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产6100台」。北京工业志·电子志·第二章中央在京电子工业企业·第四节北京核仪器厂</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>6100</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>D0710</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>19790000</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产6100台」。北京工业志·电子志·第二章中央在京电子工业企业·第四节北京核仪器厂</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>6100</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>21型</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>19890700</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「年产2358万只」。北京工业志·电子志·第四章中外合资电子工业企业·第一节北京·松下彩色显像管有限公司</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>23580000</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>19型</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>19900500</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「生产能力120万只」。北京工业志·电子志·第四章中外合资电子工业企业·第一节北京·松下彩色显像管有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>29型</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>19930700</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「生产能力90万只」。北京工业志·电子志·第四章中外合资电子工业企业·第一节北京·松下彩色显像管有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>HP3394</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>19900400</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第四节中国惠普有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>HP3396</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>19900400</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第四节中国惠普有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>HP3488</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>19900400</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第四节中国惠普有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>MS2401</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第七节北京四通办公设备有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>MS2410</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第七节北京四通办公设备有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>MS2411</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第七节北京四通办公设备有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>MS2403</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>19890700</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第七节北京四通办公设备有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>ECR－202</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>19950000</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第七节北京四通办公设备有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>JA18型</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第七节北京四通办公设备有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>JA-311型</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第七节北京四通办公设备有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>JA51</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第七节北京四通办公设备有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>CD1-3型</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「生产能力为300万只」。北京工业志·电子志·第四章中外合资电子工业企业·第四节北京第一无线电器材厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>CD1-40</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「生产能力为300万只」。北京工业志·电子志·第四章中外合资电子工业企业·第四节北京第一无线电器材厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>41型</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「生产能力为300万只」。北京工业志·电子志·第四章中外合资电子工业企业·第四节北京第一无线电器材厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>CR1-3型</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「生产能力为300万只」。北京工业志·电子志·第四章中外合资电子工业企业·第四节北京第一无线电器材厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>CR1-6型</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「生产能力为300万只」。北京工业志·电子志·第四章中外合资电子工业企业·第四节北京第一无线电器材厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>MD110</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>19950000</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第四节北京第一无线电器材厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>CA30型</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第五节北京第二无线电器材厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>CA70型</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第五节北京第二无线电器材厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>GJ40型</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>19790000</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第五节北京第二无线电器材厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>RJ15型</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>19790000</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第五节北京第二无线电器材厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>CS52</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第六节北京飞行电子总公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>CC52</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第六节北京飞行电子总公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>104机</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>19590400</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第七节北京有线电总厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>HJD04机</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第七节北京有线电总厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>RS155</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>19710000</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第十节北京大华无线电仪器厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>P01型</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>19760000</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第十节北京大华无线电仪器厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>DH3241型</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>19841200</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第十节北京大华无线电仪器厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>DH804</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第十节北京大华无线电仪器厂</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5055,7 +11006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23.28515625" customWidth="1" min="1" max="1"/>
@@ -8524,6 +14475,827 @@
         </is>
       </c>
     </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>DMJ-16A小型模拟计算机</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>北京计算机一厂</t>
+        </is>
+      </c>
+      <c r="G200" t="n">
+        <v>19640000</v>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十三节北京计算机一厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>DMJ-3型20阶中型模拟计算机</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>北京计算机一厂</t>
+        </is>
+      </c>
+      <c r="G201" t="n">
+        <v>19650000</v>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>产量据「共生产300多台」。北京工业志·电子志·第二十三节北京计算机一厂</t>
+        </is>
+      </c>
+      <c r="K201" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>橡胶平板硫化机</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>北京计算机二厂</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>产量据「产量达91.6万台」。北京工业志·电子志·第二十四节北京计算机二厂</t>
+        </is>
+      </c>
+      <c r="K202" t="n">
+        <v>916000</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>DJS5晶体管小型数字计算机</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>清华大学</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>北京计算机三厂</t>
+        </is>
+      </c>
+      <c r="G203" t="n">
+        <v>19650000</v>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>协作:清华大学。产量据「共生产小型计算机258台」。北京工业志·电子志·第二十五节北京计算机三厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>DJS-4台式计算机</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>北京计算机三厂</t>
+        </is>
+      </c>
+      <c r="G204" t="n">
+        <v>19660000</v>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>产量据「共生产小型计算机258台」。北京工业志·电子志·第二十五节北京计算机三厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>科研专用和通用计算机</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>北京计算机三厂</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>产量据「共生产小型计算机258台」。北京工业志·电子志·第二十五节北京计算机三厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>DJS-200小型和中型计算机</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>北京计算机三厂</t>
+        </is>
+      </c>
+      <c r="G206" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>产量据「共生产小型计算机258台」。北京工业志·电子志·第二十五节北京计算机三厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>BCM系列机</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>北京计算机三厂</t>
+        </is>
+      </c>
+      <c r="G207" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>产量据「共生产小型计算机258台」。北京工业志·电子志·第二十五节北京计算机三厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>TS2605HPC/XT计算机</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>北京计算机三厂</t>
+        </is>
+      </c>
+      <c r="G208" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>产量据「共生产小型计算机258台」。北京工业志·电子志·第二十五节北京计算机三厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>长城286多用户高档数机</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>北京计算机三厂</t>
+        </is>
+      </c>
+      <c r="G209" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>产量据「共生产小型计算机258台」。北京工业志·电子志·第二十五节北京计算机三厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>ZDD-10型电力载波机</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>北京计算机外部设备三厂</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十六节北京计算机外部设备三厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>生产语言教学设备I型机</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>北京计算机外部设备三厂</t>
+        </is>
+      </c>
+      <c r="G211" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十六节北京计算机外部设备三厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>语言教学设备I型机</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>北京计算机外部设备三厂</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十六节北京计算机外部设备三厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>YYC-IV型语言机</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>北京计算机外部设备三厂</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>19900100</v>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十六节北京计算机外部设备三厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>机械轻触链跟读机</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>北京计算机外部设备三厂</t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>19900400</v>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十六节北京计算机外部设备三厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>计算机</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>北京市无线电元件六厂</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十四节北京市无线电元件六厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>联想286微机</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>联想集团公司</t>
+        </is>
+      </c>
+      <c r="G216" t="n">
+        <v>19890400</v>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章行业归口电子工业企业·第二节联想集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>计算机系统及微机</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>中国惠普有限公司</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>产量据「年产量300台」。北京工业志·电子志·第四章中外合资电子工业企业·第四节中国惠普有限公司</t>
+        </is>
+      </c>
+      <c r="K217" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>集成电路大型通用电子计算机</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>北京有线电总厂</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第七节北京有线电总厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>HMJ200型</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>19750000</v>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十三节北京计算机一厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>DJM-330型</t>
+        </is>
+      </c>
+      <c r="G220" t="n">
+        <v>19770500</v>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十三节北京计算机一厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>DJM-310型</t>
+        </is>
+      </c>
+      <c r="G221" t="n">
+        <v>19810000</v>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十三节北京计算机一厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>STD-56</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十三节北京计算机一厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>CEC-1型</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十四节北京计算机二厂</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>中华学习机</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>CX-111</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「产量达91.6万台」。北京工业志·电子志·第二十四节北京计算机二厂</t>
+        </is>
+      </c>
+      <c r="K224" t="n">
+        <v>916000</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>CZ1206</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十四节北京计算机二厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>DJS-2024</t>
+        </is>
+      </c>
+      <c r="G226" t="n">
+        <v>19820000</v>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十四节北京计算机二厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>DJS-130</t>
+        </is>
+      </c>
+      <c r="G227" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产小型计算机258台」。北京工业志·电子志·第二十五节北京计算机三厂</t>
+        </is>
+      </c>
+      <c r="K227" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>DJS-140</t>
+        </is>
+      </c>
+      <c r="G228" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产小型计算机258台」。北京工业志·电子志·第二十五节北京计算机三厂</t>
+        </is>
+      </c>
+      <c r="K228" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>BD286-586</t>
+        </is>
+      </c>
+      <c r="G229" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产小型计算机258台」。北京工业志·电子志·第二十五节北京计算机三厂</t>
+        </is>
+      </c>
+      <c r="K229" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>PLAN2000</t>
+        </is>
+      </c>
+      <c r="G230" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产小型计算机258台」。北京工业志·电子志·第二十五节北京计算机三厂</t>
+        </is>
+      </c>
+      <c r="K230" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>ZDD25型</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第二十六节北京计算机外部设备三厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>S5004</t>
+        </is>
+      </c>
+      <c r="G232" t="n">
+        <v>19950300</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「累计生产长城微机31.6万台」。北京工业志·电子志·第三章行业归口电子工业企业·第一节中国长城计算机集团公司</t>
+        </is>
+      </c>
+      <c r="K232" t="n">
+        <v>316000</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>GW486</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章行业归口电子工业企业·第一节中国长城计算机集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>GW386</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章行业归口电子工业企业·第一节中国长城计算机集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>GW286</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章行业归口电子工业企业·第一节中国长城计算机集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>EISA486</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章行业归口电子工业企业·第二节联想集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>HT-86</t>
+        </is>
+      </c>
+      <c r="G237" t="n">
+        <v>19880000</v>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章行业归口电子工业企业·第六节北京希望电脑公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>H-01</t>
+        </is>
+      </c>
+      <c r="G238" t="n">
+        <v>19880000</v>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第三章行业归口电子工业企业·第六节北京希望电脑公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>HP1651</t>
+        </is>
+      </c>
+      <c r="G239" t="n">
+        <v>19870500</v>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第四节中国惠普有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="G240" t="n">
+        <v>19950000</v>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第七节北京四通办公设备有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>PC-81</t>
+        </is>
+      </c>
+      <c r="G241" t="n">
+        <v>19950000</v>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第七节北京四通办公设备有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>HF-86</t>
+        </is>
+      </c>
+      <c r="G242" t="n">
+        <v>19950000</v>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第四节北京第一无线电器材厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>DJS-1</t>
+        </is>
+      </c>
+      <c r="G243" t="n">
+        <v>19580801</v>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第七节北京有线电总厂</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>103机</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>103机</t>
+        </is>
+      </c>
+      <c r="G244" t="n">
+        <v>19580801</v>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第七节北京有线电总厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>DJS-21</t>
+        </is>
+      </c>
+      <c r="G245" t="n">
+        <v>19660000</v>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第七节北京有线电总厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>DJS-12</t>
+        </is>
+      </c>
+      <c r="G246" t="n">
+        <v>19730000</v>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第七节北京有线电总厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>150机</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第七节北京有线电总厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>151机</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第七节北京有线电总厂</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8535,7 +15307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -9161,12 +15933,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>北京无线电一厂</t>
+          <t>北京701厂</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>北京计算机一厂</t>
+          <t>第四机械工业部</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -9176,12 +15948,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1970年初，北京无线电一厂（后更名为北京计算机一厂）接受原航空部第20研究所的委托，开始研制大型晶体管模数混合计算机，1975年，完成研制任务，定名为HMJ-200大型晶体管模数混合计算机。</t>
+          <t>始建时名称。北京七O一厂原为第四机械工业部和北京市共同投资兴建的“小三线厂”，1970年，建于怀柔县山区。</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第四十二节北京七〇一厂</t>
         </is>
       </c>
     </row>
@@ -9191,27 +15963,1747 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>北京京海集团公司</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>计算机机房技术开发公司</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>19830700</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>始建时名称。北京京海集团公司成立于1983年7月，前身是计算机机房技术开发公司。</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章行业归口电子工业企业·第四节北京京海集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>北京北大方正集团公司</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>北京大学新技术公司</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>19860000</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>始建时名称。北京北大方正集团公司前身为北京大学新技术公司，是北京大学1986年创办的校办企业，1988年，改名为北京北大方正集团公司，位于海淀区中关村电子一条街北段。</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章行业归口电子工业企业·第三节北京北大方正集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>北京半导体器件五厂</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>北京市西城区半导体器件厂</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>19690900</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>19780400</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>始建时名称。北京半导体器件五厂前身是北京市西城区半导体器件厂，始建于1969年9月。</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十九节北京半导体器件五厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>北京半导体器件五厂</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>北京半导体器件五厂</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>19780400</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1978年4月，改名为北京半导体器件五厂。</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十九节北京半导体器件五厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>北京大华无线电仪器厂</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>北京微技测量仪器厂</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>19580800</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>始建时名称。北京大华无线电仪器厂（代号国营第768厂，原名北京微技测量仪器厂，华北无线电仪器厂）1958年8月开始筹建，1965年4月建成投产。</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第十节北京大华无线电仪器厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>北京市半导体器件一厂</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>北京市半导体器件一厂</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>19780600</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1978年6月，改名为北京市半导体器件一厂。</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十七节北京市半导体器件一厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>北京市可控硅元件厂</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>朝外大街乒乓球拍厂</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>19680000</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>19780000</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>以生产乒乓球拍为主的厂定名为朝外大街乒乓球拍厂，1968年开始试制可控硅元件，1970年，改名为朝阳可控硅元件厂。</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第四十一节北京市可控硅元件厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>北京市可控硅元件厂</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>北京半导体材料加工厂</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>19780000</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1978年，与东城区可控硅元件厂合并，1980年，改名为北京半导体材料加工厂，1985年，又改名为北京市可控硅元件厂。</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第四十一节北京市可控硅元件厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>北京市无线电元件一厂</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>北京竹藤制品厂</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>19640000</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>19680000</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1964年，改名为北京竹藤制品厂。</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十一节北京市无线电元件一厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>北京市无线电元件一厂</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>北京市无线电元件一厂</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>19680000</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1968年底，接收北京无线电电阻厂部分产品、设备和人员，转产电子元件，改名为北京市无线电元件一厂。</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十一节北京市无线电元件一厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>北京市调谐器厂</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>北京广播电视配件五厂</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>19790000</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1979年改名为北京广播电视配件五厂。</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十一节北京市调谐器厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>北京广播器材厂</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>北京人民广播器材厂</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>19500601</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>始建时名称。北京广播器材厂（代号国营第761厂，原名北京人民广播器材厂）1950年6月1日</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第九节北京广播器材厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>北京广播电视配件一厂</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>北京无线电非金属元件厂</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>19650000</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>19700000</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1965年，改名为北京无线电非金属元件厂。</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十九节北京广播电视配件一厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>北京广播电视配件一厂</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>北京无线电元件厂</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>19700000</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1970年，改名为北京无线电元件厂。</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十九节北京广播电视配件一厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>北京广播通讯电源厂</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>北京鞋底厂</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>19570000</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>19600000</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1957年改名为北京鞋底厂。</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十二节北京广播通讯电源厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>北京广播通讯电源厂</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>北京鞋厂</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>19600000</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>19720000</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1960年改名为北京鞋厂。</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十二节北京广播通讯电源厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>3</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>北京广播通讯电源厂</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>北京东风电池厂</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>19720000</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>19790500</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1970年该产锅镍蓄电池，并于1972年改名为北京东风电池厂。</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十二节北京广播通讯电源厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>4</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>北京广播通讯电源厂</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>北京广播电视配件六厂</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>19790500</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>19880000</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1979年5月，改名为北京广播电视配件六厂。</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十二节北京广播通讯电源厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>5</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>北京广播通讯电源厂</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>北京广播通讯电源厂</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>19880000</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1988年，改名为北京广播通讯电源厂。</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十二节北京广播通讯电源厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>北京无线电一厂</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>北京计算机一厂</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>19700000</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1970年初，北京无线电一厂（后更名为北京计算机一厂）接受原航空部第20研究所的委托，开始研制大型晶体管模数混合计算机，1975年，完成研制任务，定名为HMJ-200大型晶体管模数混合计算机。</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>北京无线电仪器二厂</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>之一的北京电子仪器厂</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>19590000</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>始建时名称。该厂前身之一的北京电子仪器厂，1959年，在生产收音机的同时即开始生产测量仪器，并成为全国最早生产电子测量仪器的企业之一。</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>北京无线电元件九厂</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>北京市东城区无线电元件厂</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>19600000</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>19620000</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>始建时名称。北京无线电元件九厂始建于1960年，前身是北京市东城区无线电元件厂。</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十五节北京无线电元件九厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>北京无线电元件九厂</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>北京无线电插接元件厂</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>19620000</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>19790000</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1962年改名为北京无线电插接元件厂。</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十五节北京无线电元件九厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>3</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>北京无线电元件九厂</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>北京无线电元件九厂</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>19790000</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1979年崇文元件四厂、朝阳精密元件厂并入北京无线电插接元件厂，改名为北京无线电元件九厂。</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十五节北京无线电元件九厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>北京无线电元件四厂</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>北京市石景山电容器厂</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>19670000</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>19790000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>始建时名称。北京无线电元件四厂前身是北京市石景山电容器厂，1967年建成投产，是国内较早从事电容器研制和生产的厂家之一。</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十三节北京无线电元件四厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>北京无线电元件四厂</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>北京无线电元件四厂</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>19790000</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1979年改名为北京无线电元件四厂。</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十三节北京无线电元件四厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>北京无线电厂</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>北京电子仪器厂</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>19590000</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1959年改名为北京电子仪器厂，1964年6月改为现厂名。</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十五节北京无线电厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>北京显像管总厂</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>北京市半导体器件五厂</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>19700000</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>19721100</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1970年改为北京市半导体器件五厂，生产低频大功率管。</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>北京显像管总厂</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>北京显值管厂</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>19721100</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>19900000</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1972年11月，改名为北京显值管厂。</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>3</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>北京显像管总厂</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>北京显像管总厂</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>19900000</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1990年，北京半导体设备一厂并入北京显像管厂，改名为北京显像管总厂。</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>4</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>北京显像管总厂</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>北京呢绒服装厂</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>始建时名称。北京显像管总厂前身是北京呢绒服装厂，1970年改为北京市半导体器件五厂，生产低频大功率管。</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>北京核仪器厂</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>北京市综合仪器厂</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>19560000</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>始建时名称。北京枚仪器厂前身为北京市综合仪器厂，是1956年中共北京市委、市人委遵照周恩来关于“在北京建立一个射线仪器厂”的指示筹资兴建的。</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第四节北京核仪器厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>北京牡丹电子集团公司</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>北京无线电精密元件厂</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>19650000</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>19731100</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>始建时名称。北京电视机厂前身为北京无线电精密元件厂，创建于1965年，当时主要生产微型继电器和斩该器。</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>北京牡丹电子集团公司</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>北京电视机厂</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>19731100</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1973年11月，改名为北京电视机厂，国家投资1000万元在海淀区花园路建设新厂，主要生产黑白、彩色电视机。</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>1</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>北京电视配件三厂</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>东红路塑料制品厂</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>19660000</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>19700000</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>始建时名称。北京电视配件三厂前身为东红路塑料制品厂，建于1966年。</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>北京电视配件三厂</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>东红路无线电元件厂</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>19700000</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>19750000</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1970年，开始生产云母电容器，改名为东红路无线电元件厂。</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>3</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>北京电视配件三厂</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>朝阳区东红路无线电元件厂</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>19750000</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1975年，改名为朝阳区东红路无线电元件厂。</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>1</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
           <t>北京联想计算机集团公司</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>联想集团公司</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>19880000</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>1988年，北京联想计算机集团公司（后更名为联想集团公司，以下简称联想集团）开始研制联想系列微机。</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>1</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>北京计算机一厂</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>北京市服务联社电器制造厂</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>19570000</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>19580000</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1957年，改名为北京市服务联社电器制造厂。</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十三节北京计算机一厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>北京计算机一厂</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>北京市无线电制造厂</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>19580000</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>19620000</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1958年，改名为北京市无线电制造厂。</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十三节北京计算机一厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>3</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>北京计算机一厂</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>北京无线电一厂</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>19620000</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>19790000</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1962年，改名为北京无线电一厂。</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十三节北京计算机一厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>4</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>北京计算机一厂</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>北京计算机一厂</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>19790000</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1979年，定名为北京计算机一厂。</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十三节北京计算机一厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>1</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>北京计算机三厂</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>北京无线电三厂</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>19650425</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>始建时名称。北京计算机三厂前身是北京无线电三厂，成立于1965年4月25日。</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十五节北京计算机三厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>1</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>北京计算机外部设备三厂</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>北京通讯设备厂</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>19790000</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1979年，改名为北京通讯设备厂。</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二十六节北京计算机外部设备三厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>1</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>北京邮电通信设备厂</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1941年9月建立的华北电信电话股份有限公司</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>19410900</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>始建时名称。其前身是1941年9月建立的华北电信电话股份有限公司修处（后更名为修缮所），现厂址位于北京市朝阳区将台路5号。</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第一节北京邮电通信设备厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>1</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>北京飞行电子总公司</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>北京第三无线电器材厂</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>19571000</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>始建时名称。北京飞行电子总公司原名北京第三无线电器材厂（代号国营第798厂），前身是1957年10月由民主德国援建的华北无线电器材联合厂三分厂。</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第六节北京飞行电子总公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>1</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>北京飞达电子集团公司</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>北京电影机械修理厂</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>19540000</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>19700000</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>始建时名称。北京录音机厂前身是北京电影机械修理厂，创建于1954年。</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>北京飞达电子集团公司</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>北京电影机械厂</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>19700000</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>19810000</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1970年改名为北京电影机械厂。</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>3</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>北京飞达电子集团公司</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>北京录音机厂</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>19810000</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1981年改名为北京录音机厂。</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>1</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>北大方正集团公司</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>北京大学新技术公司</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>19860000</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>始建时名称。北京北大方正集团公司前身为北京大学新技术公司，是北京大学1986年创办的校办企业，1988年，改名为北京北大方正集团公司，位于海淀区中关村电子一条街北段。</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章行业归口电子工业企业·第三节北京北大方正集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>1</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>联想集团公司</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>中国科学院计算所新技术发展公司</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>19841100</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>19870400</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>始建时名称。联想集团公司（前身为中国科学院计算所新技术发展公司）创建于1984年11月</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章行业归口电子工业企业·第二节联想集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>联想集团公司</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>中科院计算所计算机技术公司</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>19870400</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>19890800</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1987年4月，更名为中科院计算所计算机技术公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>3</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>联想集团公司</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>北京联想计算机集团公司</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>19890800</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>19941100</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1989年8月，更名为北京联想计算机集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>4</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>联想集团公司</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>联想集团公司</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>19941100</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1994年11月，更名为联想</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>1</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>首钢电子公司</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>首钢自动化研究所</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>19780800</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>始建时名称。首钢电子公司前身是首钢自动化研究所，创建于1978年8月。</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章行业归口电子工业企业·第七节首钢电子公司</t>
         </is>
       </c>
     </row>

--- a/CN_Electronic_Industry.xlsx
+++ b/CN_Electronic_Industry.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fact and Comp-Shanghai" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semi-Product" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comp-Product" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Name-History" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Fact and Comp-Shanghai" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Semi-Product" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Comp-Product" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Name-History" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -15307,7 +15307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -16924,26 +16924,31 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>北京显像管总厂</t>
+          <t>北京核仪器厂</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>北京呢绒服装厂</t>
+          <t>北京市综合仪器厂</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>19560000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>始建时名称。北京显像管总厂前身是北京呢绒服装厂，1970年改为北京市半导体器件五厂，生产低频大功率管。</t>
+          <t>始建时名称。北京枚仪器厂前身为北京市综合仪器厂，是1956年中共北京市委、市人委遵照周恩来关于“在北京建立一个射线仪器厂”的指示筹资兴建的。</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第四节北京核仪器厂</t>
         </is>
       </c>
     </row>
@@ -16953,33 +16958,38 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>北京核仪器厂</t>
+          <t>北京牡丹电子集团公司</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>北京市综合仪器厂</t>
+          <t>北京无线电精密元件厂</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>19560000</t>
+          <t>19650000</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>19731100</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>始建时名称。北京枚仪器厂前身为北京市综合仪器厂，是1956年中共北京市委、市人委遵照周恩来关于“在北京建立一个射线仪器厂”的指示筹资兴建的。</t>
+          <t>始建时名称。北京电视机厂前身为北京无线电精密元件厂，创建于1965年，当时主要生产微型继电器和斩该器。</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二章中央在京电子工业企业·第四节北京核仪器厂</t>
+          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -16988,22 +16998,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>北京无线电精密元件厂</t>
+          <t>北京电视机厂</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>19650000</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
           <t>19731100</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>始建时名称。北京电视机厂前身为北京无线电精密元件厂，创建于1965年，当时主要生产微型继电器和斩该器。</t>
+          <t>1973年11月，改名为北京电视机厂，国家投资1000万元在海淀区花园路建设新厂，主要生产黑白、彩色电视机。</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -17014,37 +17019,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>北京牡丹电子集团公司</t>
+          <t>北京电视配件三厂</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>北京电视机厂</t>
+          <t>东红路塑料制品厂</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>19731100</t>
+          <t>19660000</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>19700000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1973年11月，改名为北京电视机厂，国家投资1000万元在海淀区花园路建设新厂，主要生产黑白、彩色电视机。</t>
+          <t>始建时名称。北京电视配件三厂前身为东红路塑料制品厂，建于1966年。</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
+          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -17053,22 +17063,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>东红路塑料制品厂</t>
+          <t>东红路无线电元件厂</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>19660000</t>
+          <t>19700000</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>19700000</t>
+          <t>19750000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>始建时名称。北京电视配件三厂前身为东红路塑料制品厂，建于1966年。</t>
+          <t>1970年，开始生产云母电容器，改名为东红路无线电元件厂。</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -17079,7 +17089,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -17088,22 +17098,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>东红路无线电元件厂</t>
+          <t>朝阳区东红路无线电元件厂</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>19700000</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
           <t>19750000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1970年，开始生产云母电容器，改名为东红路无线电元件厂。</t>
+          <t>1975年，改名为朝阳区东红路无线电元件厂。</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -17114,31 +17119,31 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>北京电视配件三厂</t>
+          <t>北京联想计算机集团公司</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>朝阳区东红路无线电元件厂</t>
+          <t>联想集团公司</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>19750000</t>
+          <t>19880000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1975年，改名为朝阳区东红路无线电元件厂。</t>
+          <t>1988年，北京联想计算机集团公司（后更名为联想集团公司，以下简称联想集团）开始研制联想系列微机。</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
         </is>
       </c>
     </row>
@@ -17148,33 +17153,38 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>北京联想计算机集团公司</t>
+          <t>北京计算机一厂</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>联想集团公司</t>
+          <t>北京市服务联社电器制造厂</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>19880000</t>
+          <t>19570000</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>19580000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1988年，北京联想计算机集团公司（后更名为联想集团公司，以下简称联想集团）开始研制联想系列微机。</t>
+          <t>1957年，改名为北京市服务联社电器制造厂。</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+          <t>北京工业志·电子志·第二十三节北京计算机一厂</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -17183,22 +17193,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>北京市服务联社电器制造厂</t>
+          <t>北京市无线电制造厂</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>19570000</t>
+          <t>19580000</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>19580000</t>
+          <t>19620000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1957年，改名为北京市服务联社电器制造厂。</t>
+          <t>1958年，改名为北京市无线电制造厂。</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -17209,7 +17219,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -17218,22 +17228,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>北京市无线电制造厂</t>
+          <t>北京无线电一厂</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>19580000</t>
+          <t>19620000</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>19620000</t>
+          <t>19790000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1958年，改名为北京市无线电制造厂。</t>
+          <t>1962年，改名为北京无线电一厂。</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -17244,7 +17254,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -17253,22 +17263,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>北京无线电一厂</t>
+          <t>北京计算机一厂</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>19620000</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
           <t>19790000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1962年，改名为北京无线电一厂。</t>
+          <t>1979年，定名为北京计算机一厂。</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -17279,31 +17284,31 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>北京计算机一厂</t>
+          <t>北京计算机三厂</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>北京计算机一厂</t>
+          <t>北京无线电三厂</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>19790000</t>
+          <t>19650425</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1979年，定名为北京计算机一厂。</t>
+          <t>始建时名称。北京计算机三厂前身是北京无线电三厂，成立于1965年4月25日。</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十三节北京计算机一厂</t>
+          <t>北京工业志·电子志·第二十五节北京计算机三厂</t>
         </is>
       </c>
     </row>
@@ -17313,27 +17318,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>北京计算机三厂</t>
+          <t>北京计算机外部设备三厂</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>北京无线电三厂</t>
+          <t>北京通讯设备厂</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>19650425</t>
+          <t>19790000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>始建时名称。北京计算机三厂前身是北京无线电三厂，成立于1965年4月25日。</t>
+          <t>1979年，改名为北京通讯设备厂。</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十五节北京计算机三厂</t>
+          <t>北京工业志·电子志·第二十六节北京计算机外部设备三厂</t>
         </is>
       </c>
     </row>
@@ -17343,27 +17348,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>北京计算机外部设备三厂</t>
+          <t>北京邮电通信设备厂</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>北京通讯设备厂</t>
+          <t>1941年9月建立的华北电信电话股份有限公司</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>19790000</t>
+          <t>19410900</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1979年，改名为北京通讯设备厂。</t>
+          <t>始建时名称。其前身是1941年9月建立的华北电信电话股份有限公司修处（后更名为修缮所），现厂址位于北京市朝阳区将台路5号。</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十六节北京计算机外部设备三厂</t>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第一节北京邮电通信设备厂</t>
         </is>
       </c>
     </row>
@@ -17373,27 +17378,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>北京邮电通信设备厂</t>
+          <t>北京飞行电子总公司</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1941年9月建立的华北电信电话股份有限公司</t>
+          <t>北京第三无线电器材厂</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>19410900</t>
+          <t>19571000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>始建时名称。其前身是1941年9月建立的华北电信电话股份有限公司修处（后更名为修缮所），现厂址位于北京市朝阳区将台路5号。</t>
+          <t>始建时名称。北京飞行电子总公司原名北京第三无线电器材厂（代号国营第798厂），前身是1957年10月由民主德国援建的华北无线电器材联合厂三分厂。</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二章中央在京电子工业企业·第一节北京邮电通信设备厂</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第六节北京飞行电子总公司</t>
         </is>
       </c>
     </row>
@@ -17403,33 +17408,38 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>北京飞行电子总公司</t>
+          <t>北京飞达电子集团公司</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>北京第三无线电器材厂</t>
+          <t>北京电影机械修理厂</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>19571000</t>
+          <t>19540000</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>19700000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>始建时名称。北京飞行电子总公司原名北京第三无线电器材厂（代号国营第798厂），前身是1957年10月由民主德国援建的华北无线电器材联合厂三分厂。</t>
+          <t>始建时名称。北京录音机厂前身是北京电影机械修理厂，创建于1954年。</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第六节北京飞行电子总公司</t>
+          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -17438,22 +17448,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>北京电影机械修理厂</t>
+          <t>北京电影机械厂</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>19540000</t>
+          <t>19700000</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>19700000</t>
+          <t>19810000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>始建时名称。北京录音机厂前身是北京电影机械修理厂，创建于1954年。</t>
+          <t>1970年改名为北京电影机械厂。</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -17464,7 +17474,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -17473,22 +17483,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>北京电影机械厂</t>
+          <t>北京录音机厂</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>19700000</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
           <t>19810000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>1970年改名为北京电影机械厂。</t>
+          <t>1981年改名为北京录音机厂。</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -17499,31 +17504,31 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>北京飞达电子集团公司</t>
+          <t>北大方正集团公司</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>北京录音机厂</t>
+          <t>北京大学新技术公司</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>19810000</t>
+          <t>19860000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1981年改名为北京录音机厂。</t>
+          <t>始建时名称。北京北大方正集团公司前身为北京大学新技术公司，是北京大学1986年创办的校办企业，1988年，改名为北京北大方正集团公司，位于海淀区中关村电子一条街北段。</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
+          <t>北京工业志·电子志·第三章行业归口电子工业企业·第三节北京北大方正集团公司</t>
         </is>
       </c>
     </row>
@@ -17533,33 +17538,38 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>北大方正集团公司</t>
+          <t>联想集团公司</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>北京大学新技术公司</t>
+          <t>中国科学院计算所新技术发展公司</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>19860000</t>
+          <t>19841100</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>19870400</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>始建时名称。北京北大方正集团公司前身为北京大学新技术公司，是北京大学1986年创办的校办企业，1988年，改名为北京北大方正集团公司，位于海淀区中关村电子一条街北段。</t>
+          <t>始建时名称。联想集团公司（前身为中国科学院计算所新技术发展公司）创建于1984年11月</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章行业归口电子工业企业·第三节北京北大方正集团公司</t>
+          <t>北京工业志·电子志·第三章行业归口电子工业企业·第二节联想集团公司</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -17568,33 +17578,28 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>中国科学院计算所新技术发展公司</t>
+          <t>中科院计算所计算机技术公司</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>19841100</t>
+          <t>19870400</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>19870400</t>
+          <t>19890800</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>始建时名称。联想集团公司（前身为中国科学院计算所新技术发展公司）创建于1984年11月</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>北京工业志·电子志·第三章行业归口电子工业企业·第二节联想集团公司</t>
+          <t>1987年4月，更名为中科院计算所计算机技术公司</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -17603,28 +17608,28 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>中科院计算所计算机技术公司</t>
+          <t>北京联想计算机集团公司</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>19870400</t>
+          <t>19890800</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>19890800</t>
+          <t>19941100</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1987年4月，更名为中科院计算所计算机技术公司</t>
+          <t>1989年8月，更名为北京联想计算机集团公司</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -17633,75 +17638,45 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>北京联想计算机集团公司</t>
+          <t>联想集团公司</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>19890800</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
           <t>19941100</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>1989年8月，更名为北京联想计算机集团公司</t>
+          <t>1994年11月，更名为联想</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>联想集团公司</t>
+          <t>首钢电子公司</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>联想集团公司</t>
+          <t>首钢自动化研究所</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>19941100</t>
+          <t>19780800</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>1994年11月，更名为联想</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>1</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>首钢电子公司</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>首钢自动化研究所</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>19780800</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
           <t>始建时名称。首钢电子公司前身是首钢自动化研究所，创建于1978年8月。</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章行业归口电子工业企业·第七节首钢电子公司</t>
         </is>

--- a/CN_Electronic_Industry.xlsx
+++ b/CN_Electronic_Industry.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Fact and Comp-Shanghai" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Semi-Product" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Comp-Product" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Name-History" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fact and Comp-Shanghai" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semi-Product" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comp-Product" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Name-History" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -15307,7 +15307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -16006,6 +16006,11 @@
           <t>19860000</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>19880000</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>始建时名称。北京北大方正集团公司前身为北京大学新技术公司，是北京大学1986年创办的校办企业，1988年，改名为北京北大方正集团公司，位于海淀区中关村电子一条街北段。</t>
@@ -16019,42 +16024,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>北京半导体器件五厂</t>
+          <t>北京北大方正集团公司</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京市西城区半导体器件厂</t>
+          <t>北京北大方正集团公司</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>19690900</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>19780400</t>
+          <t>19880000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>始建时名称。北京半导体器件五厂前身是北京市西城区半导体器件厂，始建于1969年9月。</t>
+          <t>北京北大方正集团公司前身为北京大学新技术公司，是北京大学1986年创办的校办企业，1988年，改名为北京北大方正集团公司，位于海淀区中关村电子一条街北段。</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十九节北京半导体器件五厂</t>
+          <t>北京工业志·电子志·第三章行业归口电子工业企业·第三节北京北大方正集团公司</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -16063,17 +16063,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京半导体器件五厂</t>
+          <t>北京市西城区半导体器件厂</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>19690900</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>19780400</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1978年4月，改名为北京半导体器件五厂。</t>
+          <t>始建时名称。北京半导体器件五厂前身是北京市西城区半导体器件厂，始建于1969年9月。</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -16084,31 +16089,31 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>北京大华无线电仪器厂</t>
+          <t>北京半导体器件五厂</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京微技测量仪器厂</t>
+          <t>北京半导体器件五厂</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>19580800</t>
+          <t>19780400</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>始建时名称。北京大华无线电仪器厂（代号国营第768厂，原名北京微技测量仪器厂，华北无线电仪器厂）1958年8月开始筹建，1965年4月建成投产。</t>
+          <t>1978年4月，改名为北京半导体器件五厂。</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第十节北京大华无线电仪器厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十九节北京半导体器件五厂</t>
         </is>
       </c>
     </row>
@@ -16118,27 +16123,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>北京市半导体器件一厂</t>
+          <t>北京大华无线电仪器厂</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京市半导体器件一厂</t>
+          <t>北京微技测量仪器厂</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>19780600</t>
+          <t>19580800</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1978年6月，改名为北京市半导体器件一厂。</t>
+          <t>始建时名称。北京大华无线电仪器厂（代号国营第768厂，原名北京微技测量仪器厂，华北无线电仪器厂）1958年8月开始筹建，1965年4月建成投产。</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十七节北京市半导体器件一厂</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第十节北京大华无线电仪器厂</t>
         </is>
       </c>
     </row>
@@ -16148,38 +16153,33 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>北京市可控硅元件厂</t>
+          <t>北京市半导体器件一厂</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>朝外大街乒乓球拍厂</t>
+          <t>北京市半导体器件一厂</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>19680000</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>19780000</t>
+          <t>19780600</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>以生产乒乓球拍为主的厂定名为朝外大街乒乓球拍厂，1968年开始试制可控硅元件，1970年，改名为朝阳可控硅元件厂。</t>
+          <t>1978年6月，改名为北京市半导体器件一厂。</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第四十一节北京市可控硅元件厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十七节北京市半导体器件一厂</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -16188,17 +16188,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京半导体材料加工厂</t>
+          <t>朝外大街乒乓球拍厂</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>19780000</t>
+          <t>19680000</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>19680000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1978年，与东城区可控硅元件厂合并，1980年，改名为北京半导体材料加工厂，1985年，又改名为北京市可控硅元件厂。</t>
+          <t>以生产乒乓球拍为主的厂定名为朝外大街乒乓球拍厂，1968年开始试制可控硅元件，1970年，改名为朝阳可控硅元件厂。</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -16209,66 +16214,66 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>北京市无线电元件一厂</t>
+          <t>北京市可控硅元件厂</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京竹藤制品厂</t>
+          <t>北京市朝阳可控硅元件厂</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>19640000</t>
+          <t>19680000</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>19680000</t>
+          <t>19780000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1964年，改名为北京竹藤制品厂。</t>
+          <t>始建时名称。北京市可控硅元件厂前身是北京市朝阳可控硅元件厂。</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十一节北京市无线电元件一厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第四十一节北京市可控硅元件厂</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>北京市无线电元件一厂</t>
+          <t>北京市可控硅元件厂</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京市无线电元件一厂</t>
+          <t>北京半导体材料加工厂</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>19680000</t>
+          <t>19780000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1968年底，接收北京无线电电阻厂部分产品、设备和人员，转产电子元件，改名为北京市无线电元件一厂。</t>
+          <t>1978年，与东城区可控硅元件厂合并，1980年，改名为北京半导体材料加工厂，1985年，又改名为北京市可控硅元件厂。</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十一节北京市无线电元件一厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第四十一节北京市可控硅元件厂</t>
         </is>
       </c>
     </row>
@@ -16278,57 +16283,62 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>北京市调谐器厂</t>
+          <t>北京市无线电元件一厂</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京广播电视配件五厂</t>
+          <t>北京竹藤制品厂</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>19790000</t>
+          <t>19640000</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>19680000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1979年改名为北京广播电视配件五厂。</t>
+          <t>1964年，改名为北京竹藤制品厂。</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十一节北京市调谐器厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十一节北京市无线电元件一厂</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>北京广播器材厂</t>
+          <t>北京市无线电元件一厂</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京人民广播器材厂</t>
+          <t>北京市无线电元件一厂</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>19500601</t>
+          <t>19680000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>始建时名称。北京广播器材厂（代号国营第761厂，原名北京人民广播器材厂）1950年6月1日</t>
+          <t>1968年底，接收北京无线电电阻厂部分产品、设备和人员，转产电子元件，改名为北京市无线电元件一厂。</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第九节北京广播器材厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十一节北京市无线电元件一厂</t>
         </is>
       </c>
     </row>
@@ -16338,62 +16348,57 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>北京广播电视配件一厂</t>
+          <t>北京市调谐器厂</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京无线电非金属元件厂</t>
+          <t>北京广播电视配件五厂</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>19650000</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>19700000</t>
+          <t>19790000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1965年，改名为北京无线电非金属元件厂。</t>
+          <t>1979年改名为北京广播电视配件五厂。</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十九节北京广播电视配件一厂</t>
+          <t>北京工业志·电子志·第二十一节北京市调谐器厂</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>北京广播电视配件一厂</t>
+          <t>北京广播器材厂</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京无线电元件厂</t>
+          <t>北京人民广播器材厂</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>19700000</t>
+          <t>19500601</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1970年，改名为北京无线电元件厂。</t>
+          <t>始建时名称。北京广播器材厂（代号国营第761厂，原名北京人民广播器材厂）1950年6月1日</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十九节北京广播电视配件一厂</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第九节北京广播器材厂</t>
         </is>
       </c>
     </row>
@@ -16403,32 +16408,32 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>北京广播通讯电源厂</t>
+          <t>北京广播电视配件一厂</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京鞋底厂</t>
+          <t>北京无线电非金属元件厂</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>19570000</t>
+          <t>19650000</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>19600000</t>
+          <t>19700000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1957年改名为北京鞋底厂。</t>
+          <t>1965年，改名为北京无线电非金属元件厂。</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十二节北京广播通讯电源厂</t>
+          <t>北京工业志·电子志·第十九节北京广播电视配件一厂</t>
         </is>
       </c>
     </row>
@@ -16438,38 +16443,33 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>北京广播通讯电源厂</t>
+          <t>北京广播电视配件一厂</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京鞋厂</t>
+          <t>北京无线电元件厂</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>19600000</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>19720000</t>
+          <t>19700000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1960年改名为北京鞋厂。</t>
+          <t>1970年，改名为北京无线电元件厂。</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十二节北京广播通讯电源厂</t>
+          <t>北京工业志·电子志·第十九节北京广播电视配件一厂</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -16478,22 +16478,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京东风电池厂</t>
+          <t>北京鞋底厂</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>19720000</t>
+          <t>19570000</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>19790500</t>
+          <t>19600000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1970年该产锅镍蓄电池，并于1972年改名为北京东风电池厂。</t>
+          <t>1957年改名为北京鞋底厂。</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -16504,7 +16504,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京广播电视配件六厂</t>
+          <t>北京鞋厂</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>19790500</t>
+          <t>19600000</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>19880000</t>
+          <t>19720000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1979年5月，改名为北京广播电视配件六厂。</t>
+          <t>1960年改名为北京鞋厂。</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -16539,7 +16539,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -16548,17 +16548,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京广播通讯电源厂</t>
+          <t>北京东风电池厂</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>19880000</t>
+          <t>19720000</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>19790500</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1988年，改名为北京广播通讯电源厂。</t>
+          <t>1970年该产锅镍蓄电池，并于1972年改名为北京东风电池厂。</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -16569,61 +16574,66 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>北京无线电一厂</t>
+          <t>北京广播通讯电源厂</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京计算机一厂</t>
+          <t>北京广播电视配件六厂</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>19700000</t>
+          <t>19790500</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>19880000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1970年初，北京无线电一厂（后更名为北京计算机一厂）接受原航空部第20研究所的委托，开始研制大型晶体管模数混合计算机，1975年，完成研制任务，定名为HMJ-200大型晶体管模数混合计算机。</t>
+          <t>1979年5月，改名为北京广播电视配件六厂。</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
+          <t>北京工业志·电子志·第二十二节北京广播通讯电源厂</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>北京无线电仪器二厂</t>
+          <t>北京广播通讯电源厂</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>之一的北京电子仪器厂</t>
+          <t>北京广播通讯电源厂</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>19590000</t>
+          <t>19880000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>始建时名称。该厂前身之一的北京电子仪器厂，1959年，在生产收音机的同时即开始生产测量仪器，并成为全国最早生产电子测量仪器的企业之一。</t>
+          <t>1988年，改名为北京广播通讯电源厂。</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
+          <t>北京工业志·电子志·第二十二节北京广播通讯电源厂</t>
         </is>
       </c>
     </row>
@@ -16633,97 +16643,92 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>北京无线电元件九厂</t>
+          <t>北京无线电一厂</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>北京市东城区无线电元件厂</t>
+          <t>北京计算机一厂</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>19600000</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>19620000</t>
+          <t>19700000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>始建时名称。北京无线电元件九厂始建于1960年，前身是北京市东城区无线电元件厂。</t>
+          <t>1970年初，北京无线电一厂（后更名为北京计算机一厂）接受原航空部第20研究所的委托，开始研制大型晶体管模数混合计算机，1975年，完成研制任务，定名为HMJ-200大型晶体管模数混合计算机。</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十五节北京无线电元件九厂</t>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>北京无线电元件九厂</t>
+          <t>北京无线电仪器二厂</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>北京无线电插接元件厂</t>
+          <t>之一的北京电子仪器厂</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>19620000</t>
+          <t>19590000</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>19790000</t>
+          <t>19700400</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1962年改名为北京无线电插接元件厂。</t>
+          <t>始建时名称。该厂前身之一的北京电子仪器厂，1959年，在生产收音机的同时即开始生产测量仪器，并成为全国最早生产电子测量仪器的企业之一。</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十五节北京无线电元件九厂</t>
+          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>北京无线电元件九厂</t>
+          <t>北京无线电仪器二厂</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>北京无线电元件九厂</t>
+          <t>北京电子仪器厂</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>19790000</t>
+          <t>19700400</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1979年崇文元件四厂、朝阳精密元件厂并入北京无线电插接元件厂，改名为北京无线电元件九厂。</t>
+          <t>始建时名称。该厂前身之一的北京电子仪器厂，1959年，在生产收音机的同时即开始生产测量仪器，并成为全国最早生产电子测量仪器的企业之一。</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十五节北京无线电元件九厂</t>
+          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
         </is>
       </c>
     </row>
@@ -16733,32 +16738,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>北京无线电元件四厂</t>
+          <t>北京无线电元件九厂</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>北京市石景山电容器厂</t>
+          <t>北京市东城区无线电元件厂</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>19670000</t>
+          <t>19600000</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>19790000</t>
+          <t>19620000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>始建时名称。北京无线电元件四厂前身是北京市石景山电容器厂，1967年建成投产，是国内较早从事电容器研制和生产的厂家之一。</t>
+          <t>始建时名称。北京无线电元件九厂始建于1960年，前身是北京市东城区无线电元件厂。</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十三节北京无线电元件四厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十五节北京无线电元件九厂</t>
         </is>
       </c>
     </row>
@@ -16768,57 +16773,62 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>北京无线电元件四厂</t>
+          <t>北京无线电元件九厂</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>北京无线电元件四厂</t>
+          <t>北京无线电插接元件厂</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>19620000</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>19790000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1979年改名为北京无线电元件四厂。</t>
+          <t>1962年改名为北京无线电插接元件厂。</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十三节北京无线电元件四厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十五节北京无线电元件九厂</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>北京无线电厂</t>
+          <t>北京无线电元件九厂</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>北京电子仪器厂</t>
+          <t>北京无线电元件九厂</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>19590000</t>
+          <t>19790000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1959年改名为北京电子仪器厂，1964年6月改为现厂名。</t>
+          <t>1979年崇文元件四厂、朝阳精密元件厂并入北京无线电插接元件厂，改名为北京无线电元件九厂。</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十五节北京无线电厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十五节北京无线电元件九厂</t>
         </is>
       </c>
     </row>
@@ -16828,32 +16838,32 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>北京显像管总厂</t>
+          <t>北京无线电元件四厂</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>北京市半导体器件五厂</t>
+          <t>北京市石景山电容器厂</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>19700000</t>
+          <t>19670000</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>19721100</t>
+          <t>19790000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1970年改为北京市半导体器件五厂，生产低频大功率管。</t>
+          <t>始建时名称。北京无线电元件四厂前身是北京市石景山电容器厂，1967年建成投产，是国内较早从事电容器研制和生产的厂家之一。</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十三节北京无线电元件四厂</t>
         </is>
       </c>
     </row>
@@ -16863,62 +16873,57 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>北京显像管总厂</t>
+          <t>北京无线电元件四厂</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>北京显值管厂</t>
+          <t>北京无线电元件四厂</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>19721100</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>19900000</t>
+          <t>19790000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1972年11月，改名为北京显值管厂。</t>
+          <t>1979年改名为北京无线电元件四厂。</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十三节北京无线电元件四厂</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>北京显像管总厂</t>
+          <t>北京无线电厂</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>北京显像管总厂</t>
+          <t>北京电子仪器厂</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>19900000</t>
+          <t>19590000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1990年，北京半导体设备一厂并入北京显像管厂，改名为北京显像管总厂。</t>
+          <t>1959年改名为北京电子仪器厂，1964年6月改为现厂名。</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
+          <t>北京工业志·电子志·第十五节北京无线电厂</t>
         </is>
       </c>
     </row>
@@ -16928,92 +16933,97 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>北京核仪器厂</t>
+          <t>北京显像管总厂</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>北京市综合仪器厂</t>
+          <t>北京市半导体器件五厂</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>19560000</t>
+          <t>19700000</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>19721100</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>始建时名称。北京枚仪器厂前身为北京市综合仪器厂，是1956年中共北京市委、市人委遵照周恩来关于“在北京建立一个射线仪器厂”的指示筹资兴建的。</t>
+          <t>1970年改为北京市半导体器件五厂，生产低频大功率管。</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二章中央在京电子工业企业·第四节北京核仪器厂</t>
+          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>北京牡丹电子集团公司</t>
+          <t>北京显像管总厂</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>北京无线电精密元件厂</t>
+          <t>北京显值管厂</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>19650000</t>
+          <t>19721100</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>19731100</t>
+          <t>19900000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>始建时名称。北京电视机厂前身为北京无线电精密元件厂，创建于1965年，当时主要生产微型继电器和斩该器。</t>
+          <t>1972年11月，改名为北京显值管厂。</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
+          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>北京牡丹电子集团公司</t>
+          <t>北京显像管总厂</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>北京电视机厂</t>
+          <t>北京显像管总厂</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>19731100</t>
+          <t>19900000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1973年11月，改名为北京电视机厂，国家投资1000万元在海淀区花园路建设新厂，主要生产黑白、彩色电视机。</t>
+          <t>1990年，北京半导体设备一厂并入北京显像管厂，改名为北京显像管总厂。</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
+          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
         </is>
       </c>
     </row>
@@ -17023,127 +17033,122 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>北京电视配件三厂</t>
+          <t>北京有线电总厂</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>东红路塑料制品厂</t>
+          <t>北京有线电厂</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>19660000</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>19700000</t>
+          <t>19570900</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>始建时名称。北京电视配件三厂前身为东红路塑料制品厂，建于1966年。</t>
+          <t>始建时名称。北京有线电总厂原名北京有线电厂（代号国营第738厂），是“一五”时期由苏联援建的156项国家重点工程之一。</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第七节北京有线电总厂</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>北京电视配件三厂</t>
+          <t>北京核仪器厂</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>东红路无线电元件厂</t>
+          <t>北京市综合仪器厂</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>19700000</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>19750000</t>
+          <t>19560000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1970年，开始生产云母电容器，改名为东红路无线电元件厂。</t>
+          <t>始建时名称。北京枚仪器厂前身为北京市综合仪器厂，是1956年中共北京市委、市人委遵照周恩来关于“在北京建立一个射线仪器厂”的指示筹资兴建的。</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第四节北京核仪器厂</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>北京电视配件三厂</t>
+          <t>北京牡丹电子集团公司</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>朝阳区东红路无线电元件厂</t>
+          <t>北京无线电精密元件厂</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>19750000</t>
+          <t>19650000</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>19731100</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1975年，改名为朝阳区东红路无线电元件厂。</t>
+          <t>始建时名称。北京电视机厂前身为北京无线电精密元件厂，创建于1965年，当时主要生产微型继电器和斩该器。</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
+          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>北京联想计算机集团公司</t>
+          <t>北京牡丹电子集团公司</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>联想集团公司</t>
+          <t>北京电视机厂</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>19880000</t>
+          <t>19731100</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1988年，北京联想计算机集团公司（后更名为联想集团公司，以下简称联想集团）开始研制联想系列微机。</t>
+          <t>1973年11月，改名为北京电视机厂，国家投资1000万元在海淀区花园路建设新厂，主要生产黑白、彩色电视机。</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
         </is>
       </c>
     </row>
@@ -17153,32 +17158,32 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>北京计算机一厂</t>
+          <t>北京电视配件三厂</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>北京市服务联社电器制造厂</t>
+          <t>东红路塑料制品厂</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>19570000</t>
+          <t>19660000</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>19580000</t>
+          <t>19700000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1957年，改名为北京市服务联社电器制造厂。</t>
+          <t>始建时名称。北京电视配件三厂前身为东红路塑料制品厂，建于1966年。</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十三节北京计算机一厂</t>
+          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
         </is>
       </c>
     </row>
@@ -17188,32 +17193,32 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>北京计算机一厂</t>
+          <t>北京电视配件三厂</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>北京市无线电制造厂</t>
+          <t>东红路无线电元件厂</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>19580000</t>
+          <t>19700000</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>19620000</t>
+          <t>19750000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1958年，改名为北京市无线电制造厂。</t>
+          <t>1970年，开始生产云母电容器，改名为东红路无线电元件厂。</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十三节北京计算机一厂</t>
+          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
         </is>
       </c>
     </row>
@@ -17223,62 +17228,57 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>北京计算机一厂</t>
+          <t>北京电视配件三厂</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>北京无线电一厂</t>
+          <t>朝阳区东红路无线电元件厂</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>19620000</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>19790000</t>
+          <t>19750000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1962年，改名为北京无线电一厂。</t>
+          <t>1975年，改名为朝阳区东红路无线电元件厂。</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十三节北京计算机一厂</t>
+          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>北京计算机一厂</t>
+          <t>北京联想计算机集团公司</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>北京计算机一厂</t>
+          <t>联想集团公司</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>19790000</t>
+          <t>19880000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1979年，定名为北京计算机一厂。</t>
+          <t>1988年，北京联想计算机集团公司（后更名为联想集团公司，以下简称联想集团）开始研制联想系列微机。</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十三节北京计算机一厂</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
         </is>
       </c>
     </row>
@@ -17288,117 +17288,132 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>北京计算机三厂</t>
+          <t>北京计算机一厂</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>北京无线电三厂</t>
+          <t>北京市服务联社电器制造厂</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>19650425</t>
+          <t>19570000</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>19580000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>始建时名称。北京计算机三厂前身是北京无线电三厂，成立于1965年4月25日。</t>
+          <t>1957年，改名为北京市服务联社电器制造厂。</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十五节北京计算机三厂</t>
+          <t>北京工业志·电子志·第二十三节北京计算机一厂</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>北京计算机外部设备三厂</t>
+          <t>北京计算机一厂</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>北京通讯设备厂</t>
+          <t>北京市无线电制造厂</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>19790000</t>
+          <t>19580000</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>19620000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1979年，改名为北京通讯设备厂。</t>
+          <t>1958年，改名为北京市无线电制造厂。</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十六节北京计算机外部设备三厂</t>
+          <t>北京工业志·电子志·第二十三节北京计算机一厂</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>北京邮电通信设备厂</t>
+          <t>北京计算机一厂</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1941年9月建立的华北电信电话股份有限公司</t>
+          <t>北京无线电一厂</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>19410900</t>
+          <t>19620000</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>19790000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>始建时名称。其前身是1941年9月建立的华北电信电话股份有限公司修处（后更名为修缮所），现厂址位于北京市朝阳区将台路5号。</t>
+          <t>1962年，改名为北京无线电一厂。</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二章中央在京电子工业企业·第一节北京邮电通信设备厂</t>
+          <t>北京工业志·电子志·第二十三节北京计算机一厂</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>北京飞行电子总公司</t>
+          <t>北京计算机一厂</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>北京第三无线电器材厂</t>
+          <t>北京计算机一厂</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>19571000</t>
+          <t>19790000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>始建时名称。北京飞行电子总公司原名北京第三无线电器材厂（代号国营第798厂），前身是1957年10月由民主德国援建的华北无线电器材联合厂三分厂。</t>
+          <t>1979年，定名为北京计算机一厂。</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第六节北京飞行电子总公司</t>
+          <t>北京工业志·电子志·第二十三节北京计算机一厂</t>
         </is>
       </c>
     </row>
@@ -17408,127 +17423,122 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>北京飞达电子集团公司</t>
+          <t>北京计算机三厂</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>北京电影机械修理厂</t>
+          <t>北京无线电三厂</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>19540000</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>19700000</t>
+          <t>19650425</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>始建时名称。北京录音机厂前身是北京电影机械修理厂，创建于1954年。</t>
+          <t>始建时名称。北京计算机三厂前身是北京无线电三厂，成立于1965年4月25日。</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
+          <t>北京工业志·电子志·第二十五节北京计算机三厂</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>北京飞达电子集团公司</t>
+          <t>北京计算机外部设备三厂</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>北京电影机械厂</t>
+          <t>北京通讯设备厂</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>19700000</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>19810000</t>
+          <t>19790000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1970年改名为北京电影机械厂。</t>
+          <t>1979年，改名为北京通讯设备厂。</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
+          <t>北京工业志·电子志·第二十六节北京计算机外部设备三厂</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>北京飞达电子集团公司</t>
+          <t>北京邮电通信设备厂</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>北京录音机厂</t>
+          <t>1941年9月建立的华北电信电话股份有限公司</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>19810000</t>
+          <t>19410900</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>19410900</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>1981年改名为北京录音机厂。</t>
+          <t>始建时名称。其前身是1941年9月建立的华北电信电话股份有限公司修处（后更名为修缮所），现厂址位于北京市朝阳区将台路5号。</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第一节北京邮电通信设备厂</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>北大方正集团公司</t>
+          <t>北京邮电通信设备厂</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>北京大学新技术公司</t>
+          <t>华北电信电话股份有限公司</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>19860000</t>
+          <t>19410900</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>始建时名称。北京北大方正集团公司前身为北京大学新技术公司，是北京大学1986年创办的校办企业，1988年，改名为北京北大方正集团公司，位于海淀区中关村电子一条街北段。</t>
+          <t>始建时名称。其前身是1941年9月建立的华北电信电话股份有限公司修处（后更名为修缮所），现厂址位于北京市朝阳区将台路5号。</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章行业归口电子工业企业·第三节北京北大方正集团公司</t>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第一节北京邮电通信设备厂</t>
         </is>
       </c>
     </row>
@@ -17538,32 +17548,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>联想集团公司</t>
+          <t>北京飞行电子总公司</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>中国科学院计算所新技术发展公司</t>
+          <t>北京第三无线电器材厂</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>19841100</t>
+          <t>19571000</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>19870400</t>
+          <t>19640000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>始建时名称。联想集团公司（前身为中国科学院计算所新技术发展公司）创建于1984年11月</t>
+          <t>始建时名称。北京飞行电子总公司原名北京第三无线电器材厂（代号国营第798厂），前身是1957年10月由民主德国援建的华北无线电器材联合厂三分厂。</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章行业归口电子工业企业·第二节联想集团公司</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第六节北京飞行电子总公司</t>
         </is>
       </c>
     </row>
@@ -17573,110 +17583,305 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>联想集团公司</t>
+          <t>北京飞行电子总公司</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>中科院计算所计算机技术公司</t>
+          <t>北京第三无线电器材厂</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>19870400</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>19890800</t>
+          <t>19640000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1987年4月，更名为中科院计算所计算机技术公司</t>
+          <t>始建时名称。北京飞行电子总公司原名北京第三无线电器材厂（代号国营第798厂），前身是1957年10月由民主德国援建的华北无线电器材联合厂三分厂。</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第六节北京飞行电子总公司</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>联想集团公司</t>
+          <t>北京飞达电子集团公司</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>北京联想计算机集团公司</t>
+          <t>北京电影机械修理厂</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>19890800</t>
+          <t>19540000</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>19941100</t>
+          <t>19700000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1989年8月，更名为北京联想计算机集团公司</t>
+          <t>始建时名称。北京录音机厂前身是北京电影机械修理厂，创建于1954年。</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>联想集团公司</t>
+          <t>北京飞达电子集团公司</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>联想集团公司</t>
+          <t>北京电影机械厂</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>19941100</t>
+          <t>19700000</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>19810000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>1994年11月，更名为联想</t>
+          <t>1970年改名为北京电影机械厂。</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
+        <v>3</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>北京飞达电子集团公司</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>北京录音机厂</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>19810000</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1981年改名为北京录音机厂。</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
         <v>1</v>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>北大方正集团公司</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>北京大学新技术公司</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>19860000</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>始建时名称。北京北大方正集团公司前身为北京大学新技术公司，是北京大学1986年创办的校办企业，1988年，改名为北京北大方正集团公司，位于海淀区中关村电子一条街北段。</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章行业归口电子工业企业·第三节北京北大方正集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>1</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>联想集团公司</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>中国科学院计算所新技术发展公司</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>19841100</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>19870400</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>始建时名称。联想集团公司（前身为中国科学院计算所新技术发展公司）创建于1984年11月</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章行业归口电子工业企业·第二节联想集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>联想集团公司</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>中科院计算所计算机技术公司</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>19870400</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>19890800</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1987年4月，更名为中科院计算所计算机技术公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>3</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>联想集团公司</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>北京联想计算机集团公司</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>19890800</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>19941100</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1989年8月，更名为北京联想计算机集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>4</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>联想集团公司</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>联想集团公司</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>19941100</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1994年11月，更名为联想</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>1</v>
+      </c>
+      <c r="B80" t="inlineStr">
         <is>
           <t>首钢电子公司</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>首钢自动化研究所</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>19780800</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>始建时名称。首钢电子公司前身是首钢自动化研究所，创建于1978年8月。</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章行业归口电子工业企业·第七节首钢电子公司</t>
         </is>

--- a/CN_Electronic_Industry.xlsx
+++ b/CN_Electronic_Industry.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fact and Comp-Shanghai" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semi-Product" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comp-Product" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Name-History" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Fact and Comp-Shanghai" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Semi-Product" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Comp-Product" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Name-History" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -393,7 +393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T197"/>
+  <dimension ref="A1:U197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.28515625" customWidth="1" min="1" max="1"/>
@@ -459,6 +459,11 @@
           <t>统计年</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>区</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="I2" t="inlineStr">
@@ -1876,6 +1881,11 @@
           <t>北京工业志·电子志·第三章电子计算机</t>
         </is>
       </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1948,6 +1958,11 @@
           <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
         </is>
       </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>宣武</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2018,6 +2033,11 @@
           <t>北京工业志·电子志·第三章电子计算机·第三节计算器</t>
         </is>
       </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>东城</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2217,6 +2237,11 @@
           <t>北京工业志·电子志·第三章电子计算机</t>
         </is>
       </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>石景山</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2309,6 +2334,11 @@
           <t>北京工业志·电子志·第三章电子计算机</t>
         </is>
       </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2445,6 +2475,11 @@
           <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
         </is>
       </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2544,6 +2579,11 @@
           <t>联想集团</t>
         </is>
       </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2917,6 +2957,11 @@
           <t>北京工业志·电子志·第三章电子计算机</t>
         </is>
       </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>崇文</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2944,6 +2989,11 @@
           <t>北京工业志·电子志·第三章电子计算机</t>
         </is>
       </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3025,6 +3075,11 @@
           <t>北京工业志·电子志·第三章电子计算机</t>
         </is>
       </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3860,6 +3915,11 @@
           <t>北京工业志·电子志</t>
         </is>
       </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4322,6 +4382,11 @@
       <c r="T123" t="n">
         <v>1995</v>
       </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4386,6 +4451,11 @@
       <c r="T124" t="n">
         <v>1995</v>
       </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4442,6 +4512,11 @@
       <c r="T125" t="n">
         <v>1995</v>
       </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>东城</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4505,6 +4580,11 @@
       <c r="T126" t="n">
         <v>1995</v>
       </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4568,6 +4648,11 @@
       <c r="T127" t="n">
         <v>1995</v>
       </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>崇文</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4616,6 +4701,11 @@
       <c r="T128" t="n">
         <v>1995</v>
       </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>丰台</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4667,6 +4757,11 @@
       <c r="T129" t="n">
         <v>1995</v>
       </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4718,6 +4813,11 @@
       <c r="T130" t="n">
         <v>1995</v>
       </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>西城</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4771,6 +4871,11 @@
       <c r="T131" t="n">
         <v>1995</v>
       </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4832,6 +4937,11 @@
       <c r="T132" t="n">
         <v>1995</v>
       </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>宣武</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4849,7 +4959,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>改名北京广播器材厂-&gt;合并组建了北京市综合仪器厂-&gt;19590000之一的北京电子仪器厂-&gt;19620900东城无线电仪器装配厂和电讯仪表厂合并-&gt;19700000北京无线电二厂合并-&gt;北京电子仪器厂、北京无线电二厂合并</t>
+          <t>改名北京广播器材厂-&gt;合并组建了北京市综合仪器厂-&gt;19590000北京电子仪器厂-&gt;19620900东城无线电仪器装配厂和电讯仪表厂合并-&gt;19700000北京无线电二厂合并-&gt;北京电子仪器厂、北京无线电二厂合并</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -4890,6 +5000,11 @@
       <c r="T133" t="n">
         <v>1995</v>
       </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4943,6 +5058,11 @@
       <c r="T134" t="n">
         <v>1995</v>
       </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>西城</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5014,6 +5134,11 @@
       <c r="T135" t="n">
         <v>1995</v>
       </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5077,6 +5202,11 @@
       <c r="T136" t="n">
         <v>1990</v>
       </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>西城</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5137,6 +5267,11 @@
       <c r="T137" t="n">
         <v>1995</v>
       </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5256,6 +5391,11 @@
       <c r="T139" t="n">
         <v>1995</v>
       </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5307,6 +5447,11 @@
       <c r="T140" t="n">
         <v>1995</v>
       </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>宣武</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5368,6 +5513,11 @@
       <c r="T141" t="n">
         <v>1995</v>
       </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>西城</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5419,6 +5569,11 @@
       <c r="T142" t="n">
         <v>1995</v>
       </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>石景山</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5482,6 +5637,11 @@
       <c r="T143" t="n">
         <v>1995</v>
       </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>东城</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5546,6 +5706,11 @@
       <c r="T144" t="n">
         <v>1995</v>
       </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5607,6 +5772,11 @@
       <c r="T145" t="n">
         <v>1995</v>
       </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5673,6 +5843,11 @@
       <c r="T146" t="n">
         <v>1995</v>
       </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>崇文</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5734,6 +5909,11 @@
       <c r="T147" t="n">
         <v>1995</v>
       </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>西城</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5787,6 +5967,11 @@
       <c r="T148" t="n">
         <v>1995</v>
       </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>宣武</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5979,6 +6164,11 @@
       <c r="T151" t="n">
         <v>1995</v>
       </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6039,6 +6229,11 @@
       <c r="T152" t="n">
         <v>1995</v>
       </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6103,6 +6298,11 @@
       <c r="T153" t="n">
         <v>1995</v>
       </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6161,6 +6361,11 @@
       <c r="T154" t="n">
         <v>1995</v>
       </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6217,6 +6422,11 @@
       <c r="T155" t="n">
         <v>1995</v>
       </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6271,6 +6481,11 @@
       <c r="T156" t="n">
         <v>1995</v>
       </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6334,6 +6549,11 @@
       <c r="T157" t="n">
         <v>1995</v>
       </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6397,6 +6617,11 @@
       <c r="T158" t="n">
         <v>1995</v>
       </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6447,6 +6672,11 @@
       <c r="T159" t="n">
         <v>1995</v>
       </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6510,6 +6740,11 @@
       <c r="T160" t="n">
         <v>1995</v>
       </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6571,6 +6806,11 @@
       <c r="T161" t="n">
         <v>1995</v>
       </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6629,6 +6869,11 @@
       <c r="T162" t="n">
         <v>1995</v>
       </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6693,6 +6938,11 @@
       <c r="T163" t="n">
         <v>1995</v>
       </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6750,6 +7000,11 @@
       <c r="T164" t="n">
         <v>1995</v>
       </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6811,6 +7066,11 @@
       <c r="T165" t="n">
         <v>1995</v>
       </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6853,6 +7113,11 @@
       <c r="T166" t="n">
         <v>1995</v>
       </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6902,6 +7167,11 @@
       <c r="T167" t="n">
         <v>1995</v>
       </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>西城</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6993,6 +7263,11 @@
       <c r="T169" t="n">
         <v>1995</v>
       </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7043,6 +7318,11 @@
       </c>
       <c r="T170" t="n">
         <v>1995</v>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
       </c>
     </row>
     <row r="171">
@@ -16678,7 +16958,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>之一的北京电子仪器厂</t>
+          <t>北京电子仪器厂</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">

--- a/CN_Electronic_Industry.xlsx
+++ b/CN_Electronic_Industry.xlsx
@@ -393,7 +393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T197"/>
+  <dimension ref="A1:T209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.28515625" customWidth="1" min="1" max="1"/>
@@ -7646,6 +7646,364 @@
       <c r="R197" t="inlineStr">
         <is>
           <t>北京工业志·电子志</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>上海无线电十三厂</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>TQ一16中型通用数字集成电路计算机、J一101型计算机、专用电子计算机、TQ-21型数据处理机</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>19660600</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>19690200改名TQ一6型计算机</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>上海长宁拉手厂</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>第二台709型计算机</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>19730000</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>上海长江电子计算机厂</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>CJ-801单板微型机</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>上海交通大学</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>DJS一053微型计算机、DJS一052E微型计算机、生产单板微型计算机、单板微型计算机</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>华东师范大学</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>19730000</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·1. 电子管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>中国人民解放军总参谋部第五十六研究所</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>研究所</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>J一101型计算机</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据单位名</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>上海工业大学</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>联合公司</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>上海中兴无线电厂</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>新安电工厂</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>上海调节器厂</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>未见专条,据行文点名；行业据正文用词</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>上海炼油厂</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·第五节企业·四、 上海王安电脑发展公司</t>
         </is>
       </c>
     </row>
@@ -7660,7 +8018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F212"/>
+  <dimension ref="A1:G218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.7109375" customWidth="1" min="1" max="1"/>
@@ -7699,6 +8057,11 @@
           <t>产量</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Research Insti</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10993,6 +11356,92 @@
         <is>
           <t>型号据字面认出,研制单位未详。北京工业志·电子志·第四章中外合资电子工业企业·第十节北京大华无线电仪器厂</t>
         </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>厚膜电路</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>华东计算技术研究所</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>时采用新器件</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·第三节生产技术·一、 设计：</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>集成电路自动群测机</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>19750000</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·第三节生产技术·二、 工艺和设备</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>集成电路</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·第三节生产技术·二、 工艺和设备</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>推动了上海地区集成电路</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>717晶体管</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>19680000</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产35台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -11006,7 +11455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L248"/>
+  <dimension ref="A1:L321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23.28515625" customWidth="1" min="1" max="1"/>
@@ -15296,6 +15745,1224 @@
         </is>
       </c>
     </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>655大型计算机</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>华东计算技术研究所</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>上海元件五厂</t>
+        </is>
+      </c>
+      <c r="G249" t="n">
+        <v>19650000</v>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+      <c r="K249" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>KS-1箭载计算机</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>华东计算技术研究所</t>
+        </is>
+      </c>
+      <c r="G250" t="n">
+        <v>19690000</v>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>J-101型计算机</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>中国人民解放军总参谋部第五十六研究所</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>上海无线电十三厂</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>TQ-21型数据处理机</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>上海无线电十三厂</t>
+        </is>
+      </c>
+      <c r="G252" t="n">
+        <v>19770000</v>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>产量据「生产了25台」。上海电子仪表工业志·第一章电子计算机·4. 计算器</t>
+        </is>
+      </c>
+      <c r="K252" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>CJ-801单板微型机</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>上海长江电子计算机厂</t>
+        </is>
+      </c>
+      <c r="G253" t="n">
+        <v>19830000</v>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·3. 单板微型计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>东海系列微型计算机</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>上海电子计算机厂</t>
+        </is>
+      </c>
+      <c r="G254" t="n">
+        <v>19840000</v>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·第三节生产技术·二、 工艺和设备</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>TQ-5机</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>上海电子计算机厂</t>
+        </is>
+      </c>
+      <c r="G255" t="n">
+        <v>19710000</v>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>产量据「先后生产15台」。上海电子仪表工业志·第一章电子计算机·第五节企业·一、 上海电子计算机厂</t>
+        </is>
+      </c>
+      <c r="K255" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>TQ-16中型通用计算机</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>上海电子计算机厂</t>
+        </is>
+      </c>
+      <c r="G256" t="n">
+        <v>19730000</v>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>产量据「先后生产15台」。上海电子仪表工业志·第一章电子计算机·第五节企业·一、 上海电子计算机厂</t>
+        </is>
+      </c>
+      <c r="K256" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>DJS-131小型多功能通用计算机</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>上海电子计算机厂</t>
+        </is>
+      </c>
+      <c r="G257" t="n">
+        <v>19750000</v>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>产量据「先后生产15台」。上海电子仪表工业志·第一章电子计算机·第五节企业·一、 上海电子计算机厂</t>
+        </is>
+      </c>
+      <c r="K257" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>DJS-053微型计算机</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>上海市计算技术研究所</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>DJS-052E微型计算机</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>上海市计算技术研究所</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>单板微型计算机</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>上海市计算技术研究所</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>709型计算机</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>上海市计算技术研究所</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>上海长宁拉手厂</t>
+        </is>
+      </c>
+      <c r="G261" t="n">
+        <v>19710800</v>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>产量据「共生产73台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+      <c r="K261" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>DJS-053微型计算机</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>上海交通大学</t>
+        </is>
+      </c>
+      <c r="G262" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>产量据「共生产134台」。上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
+        </is>
+      </c>
+      <c r="K262" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>100B型等工业控制计算机</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>上海工业自动化仪表研究所</t>
+        </is>
+      </c>
+      <c r="G263" t="n">
+        <v>19830000</v>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>CJ-709中型集成电路计算机</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>上海微电脑厂</t>
+        </is>
+      </c>
+      <c r="G264" t="n">
+        <v>19730000</v>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·第五节企业·二、 上海微电脑厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>CJ-1001中型集成电路计算机</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>上海微电脑厂</t>
+        </is>
+      </c>
+      <c r="G265" t="n">
+        <v>19730000</v>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·第五节企业·二、 上海微电脑厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>DJS-051B微型机</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>上海微电脑厂</t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>19730000</v>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·第五节企业·二、 上海微电脑厂</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>王安CCS个人电脑</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>上海王安电脑发展公司</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·第五节企业·四、 上海王安电脑发展公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>VS系列超级小型机</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>上海王安电脑发展公司</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·第五节企业·四、 上海王安电脑发展公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>X-2型晶体管数字电子计算机</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>42</v>
+      </c>
+      <c r="D269" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G269" t="n">
+        <v>19651200</v>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>101型</t>
+        </is>
+      </c>
+      <c r="G270" t="n">
+        <v>19600000</v>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>10型</t>
+        </is>
+      </c>
+      <c r="G271" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>185小型计算机</t>
+        </is>
+      </c>
+      <c r="G272" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>0540的东海系列微型计算机</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>103型电子管数字计算机</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>30</v>
+      </c>
+      <c r="G274" t="n">
+        <v>19591200</v>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·1. 电子管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>501型</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G275" t="n">
+        <v>19600000</v>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·1. 电子管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>3型晶体管计算机</t>
+        </is>
+      </c>
+      <c r="G276" t="n">
+        <v>19631000</v>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·2. 晶体管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>905甲机</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·2. 晶体管计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>0540型</t>
+        </is>
+      </c>
+      <c r="G278" t="n">
+        <v>19850000</v>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>C25</t>
+        </is>
+      </c>
+      <c r="G279" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产471台」。上海电子仪表工业志·第一章电子计算机·1. 东海系列微型计算机</t>
+        </is>
+      </c>
+      <c r="K279" t="n">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>CJ-803</t>
+        </is>
+      </c>
+      <c r="G280" t="n">
+        <v>19830000</v>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 单板微型计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>CJ-804</t>
+        </is>
+      </c>
+      <c r="G281" t="n">
+        <v>19830000</v>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 单板微型计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Z80</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>8</v>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 单板微型计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>M0572</t>
+        </is>
+      </c>
+      <c r="G283" t="n">
+        <v>19871200</v>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·4. 加固型微型计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>386型</t>
+        </is>
+      </c>
+      <c r="G284" t="n">
+        <v>19890000</v>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「生产14套」。上海电子仪表工业志·第一章电子计算机·5. 微机工程工作站</t>
+        </is>
+      </c>
+      <c r="K284" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>ZST-2</t>
+        </is>
+      </c>
+      <c r="G285" t="n">
+        <v>19640000</v>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·6. 典型应用系统及软件</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>ZLQ-2</t>
+        </is>
+      </c>
+      <c r="G286" t="n">
+        <v>19850900</v>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产7套」。上海电子仪表工业志·第一章电子计算机·6. 典型应用系统及软件</t>
+        </is>
+      </c>
+      <c r="K286" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>905乙型</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·第三节生产技术·一、 设计：</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>TQ-6</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·第三节生产技术·三、 质量</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>DJS-131小型多功能计算机</t>
+        </is>
+      </c>
+      <c r="G289" t="n">
+        <v>19750000</v>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·第三节生产技术·三、 质量</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>709计算机</t>
+        </is>
+      </c>
+      <c r="G290" t="n">
+        <v>19770000</v>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产47台」。上海电子仪表工业志·第一章电子计算机·第五节企业·二、 上海微电脑厂</t>
+        </is>
+      </c>
+      <c r="K290" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>VS500</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·第五节企业·四、 上海王安电脑发展公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>VS800</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·第五节企业·四、 上海王安电脑发展公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>331型</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·第五节企业·四、 上海王安电脑发展公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>DJS-131</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>16</v>
+      </c>
+      <c r="C294" t="n">
+        <v>4</v>
+      </c>
+      <c r="D294" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>DJS-130</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>16型</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「生产了153台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+      <c r="K296" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>220计算机</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>260型</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>32</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>64K</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「生产了2台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+      <c r="K298" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>240型</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>第三代集成电路计算机</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>J-101型</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>TQ-11机</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>905丙机</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>905型</t>
+        </is>
+      </c>
+      <c r="G304" t="n">
+        <v>19790200</v>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>717晶体管计算机</t>
+        </is>
+      </c>
+      <c r="G305" t="n">
+        <v>19680000</v>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>研制单位未详。产量据「共生产35台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+      <c r="K305" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>TQ-5型计算机</t>
+        </is>
+      </c>
+      <c r="G306" t="n">
+        <v>19710000</v>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>研制单位未详。产量据「生产了2台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+      <c r="K306" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>691计算机</t>
+        </is>
+      </c>
+      <c r="G307" t="n">
+        <v>19730000</v>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>KS-1A箭载计算机</t>
+        </is>
+      </c>
+      <c r="G308" t="n">
+        <v>19750000</v>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>ZK45</t>
+        </is>
+      </c>
+      <c r="G309" t="n">
+        <v>19840000</v>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>JS系列工业控制机</t>
+        </is>
+      </c>
+      <c r="G310" t="n">
+        <v>19740000</v>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>TQ-3型工业控制机</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>研制单位未详。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>14型</t>
+        </is>
+      </c>
+      <c r="G312" t="n">
+        <v>19730000</v>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产10台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+      <c r="K312" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>19型</t>
+        </is>
+      </c>
+      <c r="G313" t="n">
+        <v>19740000</v>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产97台」。上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+        </is>
+      </c>
+      <c r="K313" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>12型</t>
+        </is>
+      </c>
+      <c r="G314" t="n">
+        <v>19720000</v>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「共生产24000多台」。上海电子仪表工业志·第一章电子计算机·4. 计算器</t>
+        </is>
+      </c>
+      <c r="K314" t="n">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>SC4332</t>
+        </is>
+      </c>
+      <c r="G315" t="n">
+        <v>19840000</v>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·4. 计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>LF-8083</t>
+        </is>
+      </c>
+      <c r="G316" t="n">
+        <v>19840000</v>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·4. 计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>300型</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·4. 计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>450型</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·4. 计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>650型</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·4. 计算器</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>203计算机</t>
+        </is>
+      </c>
+      <c r="G320" t="n">
+        <v>19770000</v>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。产量据「生产了25台」。上海电子仪表工业志·第一章电子计算机·4. 计算器</t>
+        </is>
+      </c>
+      <c r="K320" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>131计算机</t>
+        </is>
+      </c>
+      <c r="G321" t="n">
+        <v>19780000</v>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>型号据字面认出,研制单位未详。上海电子仪表工业志·第一章电子计算机·5. 典型应用系统及软件</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15307,7 +16974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -15783,32 +17450,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>中国科学院上海冶金研究所</t>
+          <t>上海微电脑厂</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>中央研究院工学研究所</t>
+          <t>上海长江电子计算机厂</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>19280000</t>
+          <t>19800000</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>19490000</t>
+          <t>19840000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>始建时名称</t>
+          <t>1980年改名为上海长江电子计算机厂。</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>据 Founder 列推定,待核</t>
+          <t>上海电子仪表工业志·第一章电子计算机·2. 长江微型计算机</t>
         </is>
       </c>
     </row>
@@ -15818,63 +17485,63 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>中国科学院上海冶金研究所</t>
+          <t>上海微电脑厂</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>中国科学院工学实验馆</t>
+          <t>上海微电脑厂</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>19490000</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>19530000</t>
+          <t>19840000</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1984年易名为上海微电脑厂，注册商标为CJ。</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>据 Founder 列推定,待核</t>
+          <t>上海电子仪表工业志·第一章电子计算机·2. 长江微型计算机</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>中国科学院上海冶金研究所</t>
+          <t>上海电子计算机厂</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>中国科学院冶金陶瓷研究所</t>
+          <t>上海电子计算机厂</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>19530000</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>19600000</t>
+          <t>19800000</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1970年迁至南京西路1486号，1980年更名为上海电子计算机厂。</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>据 Founder 列推定,待核</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -15883,17 +17550,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>中国科学院冶金研究所</t>
+          <t>中央研究院工学研究所</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>19600000</t>
+          <t>19280000</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>19700000</t>
+          <t>19490000</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>始建时名称</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -15904,7 +17576,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -15913,12 +17585,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>中国科学院上海冶金研究所</t>
+          <t>中国科学院工学实验馆</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>19700000</t>
+          <t>19490000</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>19530000</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -15929,126 +17606,116 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>北京701厂</t>
+          <t>中国科学院上海冶金研究所</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>第四机械工业部</t>
+          <t>中国科学院冶金陶瓷研究所</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>19700000</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>始建时名称。北京七O一厂原为第四机械工业部和北京市共同投资兴建的“小三线厂”，1970年，建于怀柔县山区。</t>
+          <t>19530000</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>19600000</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第四十二节北京七〇一厂</t>
+          <t>据 Founder 列推定,待核</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>北京京海集团公司</t>
+          <t>中国科学院上海冶金研究所</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>计算机机房技术开发公司</t>
+          <t>中国科学院冶金研究所</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>19830700</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>始建时名称。北京京海集团公司成立于1983年7月，前身是计算机机房技术开发公司。</t>
+          <t>19600000</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>19700000</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章行业归口电子工业企业·第四节北京京海集团公司</t>
+          <t>据 Founder 列推定,待核</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>北京北大方正集团公司</t>
+          <t>中国科学院上海冶金研究所</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>北京大学新技术公司</t>
+          <t>中国科学院上海冶金研究所</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>19860000</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>19880000</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>始建时名称。北京北大方正集团公司前身为北京大学新技术公司，是北京大学1986年创办的校办企业，1988年，改名为北京北大方正集团公司，位于海淀区中关村电子一条街北段。</t>
+          <t>19700000</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章行业归口电子工业企业·第三节北京北大方正集团公司</t>
+          <t>据 Founder 列推定,待核</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>北京北大方正集团公司</t>
+          <t>北京701厂</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>北京北大方正集团公司</t>
+          <t>第四机械工业部</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>19880000</t>
+          <t>19700000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>北京北大方正集团公司前身为北京大学新技术公司，是北京大学1986年创办的校办企业，1988年，改名为北京北大方正集团公司，位于海淀区中关村电子一条街北段。</t>
+          <t>始建时名称。北京七O一厂原为第四机械工业部和北京市共同投资兴建的“小三线厂”，1970年，建于怀柔县山区。</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章行业归口电子工业企业·第三节北京北大方正集团公司</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第四十二节北京七〇一厂</t>
         </is>
       </c>
     </row>
@@ -16058,92 +17725,92 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>北京半导体器件五厂</t>
+          <t>北京京海集团公司</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>北京市西城区半导体器件厂</t>
+          <t>计算机机房技术开发公司</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>19690900</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>19780400</t>
+          <t>19830700</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>始建时名称。北京半导体器件五厂前身是北京市西城区半导体器件厂，始建于1969年9月。</t>
+          <t>始建时名称。北京京海集团公司成立于1983年7月，前身是计算机机房技术开发公司。</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十九节北京半导体器件五厂</t>
+          <t>北京工业志·电子志·第三章行业归口电子工业企业·第四节北京京海集团公司</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>北京半导体器件五厂</t>
+          <t>北京北大方正集团公司</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京半导体器件五厂</t>
+          <t>北京大学新技术公司</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>19780400</t>
+          <t>19860000</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>19880000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1978年4月，改名为北京半导体器件五厂。</t>
+          <t>始建时名称。北京北大方正集团公司前身为北京大学新技术公司，是北京大学1986年创办的校办企业，1988年，改名为北京北大方正集团公司，位于海淀区中关村电子一条街北段。</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十九节北京半导体器件五厂</t>
+          <t>北京工业志·电子志·第三章行业归口电子工业企业·第三节北京北大方正集团公司</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>北京大华无线电仪器厂</t>
+          <t>北京北大方正集团公司</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京微技测量仪器厂</t>
+          <t>北京北大方正集团公司</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>19580800</t>
+          <t>19880000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>始建时名称。北京大华无线电仪器厂（代号国营第768厂，原名北京微技测量仪器厂，华北无线电仪器厂）1958年8月开始筹建，1965年4月建成投产。</t>
+          <t>北京北大方正集团公司前身为北京大学新技术公司，是北京大学1986年创办的校办企业，1988年，改名为北京北大方正集团公司，位于海淀区中关村电子一条街北段。</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第十节北京大华无线电仪器厂</t>
+          <t>北京工业志·电子志·第三章行业归口电子工业企业·第三节北京北大方正集团公司</t>
         </is>
       </c>
     </row>
@@ -16153,127 +17820,122 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>北京市半导体器件一厂</t>
+          <t>北京半导体器件五厂</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京市半导体器件一厂</t>
+          <t>北京市西城区半导体器件厂</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>19780600</t>
+          <t>19690900</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>19780400</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1978年6月，改名为北京市半导体器件一厂。</t>
+          <t>始建时名称。北京半导体器件五厂前身是北京市西城区半导体器件厂，始建于1969年9月。</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十七节北京市半导体器件一厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十九节北京半导体器件五厂</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>北京市可控硅元件厂</t>
+          <t>北京半导体器件五厂</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>朝外大街乒乓球拍厂</t>
+          <t>北京半导体器件五厂</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>19680000</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>19680000</t>
+          <t>19780400</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>以生产乒乓球拍为主的厂定名为朝外大街乒乓球拍厂，1968年开始试制可控硅元件，1970年，改名为朝阳可控硅元件厂。</t>
+          <t>1978年4月，改名为北京半导体器件五厂。</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第四十一节北京市可控硅元件厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十九节北京半导体器件五厂</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>北京市可控硅元件厂</t>
+          <t>北京大华无线电仪器厂</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京市朝阳可控硅元件厂</t>
+          <t>北京微技测量仪器厂</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>19680000</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>19780000</t>
+          <t>19580800</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>始建时名称。北京市可控硅元件厂前身是北京市朝阳可控硅元件厂。</t>
+          <t>始建时名称。北京大华无线电仪器厂（代号国营第768厂，原名北京微技测量仪器厂，华北无线电仪器厂）1958年8月开始筹建，1965年4月建成投产。</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第四十一节北京市可控硅元件厂</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第十节北京大华无线电仪器厂</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>北京市可控硅元件厂</t>
+          <t>北京市半导体器件一厂</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京半导体材料加工厂</t>
+          <t>北京市半导体器件一厂</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>19780000</t>
+          <t>19780600</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1978年，与东城区可控硅元件厂合并，1980年，改名为北京半导体材料加工厂，1985年，又改名为北京市可控硅元件厂。</t>
+          <t>1978年6月，改名为北京市半导体器件一厂。</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第四十一节北京市可控硅元件厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十七节北京市半导体器件一厂</t>
         </is>
       </c>
     </row>
@@ -16283,17 +17945,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>北京市无线电元件一厂</t>
+          <t>北京市可控硅元件厂</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>北京竹藤制品厂</t>
+          <t>朝外大街乒乓球拍厂</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>19640000</t>
+          <t>19680000</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -16303,12 +17965,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1964年，改名为北京竹藤制品厂。</t>
+          <t>以生产乒乓球拍为主的厂定名为朝外大街乒乓球拍厂，1968年开始试制可控硅元件，1970年，改名为朝阳可控硅元件厂。</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十一节北京市无线电元件一厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第四十一节北京市可控硅元件厂</t>
         </is>
       </c>
     </row>
@@ -16318,12 +17980,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>北京市无线电元件一厂</t>
+          <t>北京市可控硅元件厂</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京市无线电元件一厂</t>
+          <t>北京市朝阳可控硅元件厂</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -16331,44 +17993,49 @@
           <t>19680000</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>19780000</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1968年底，接收北京无线电电阻厂部分产品、设备和人员，转产电子元件，改名为北京市无线电元件一厂。</t>
+          <t>始建时名称。北京市可控硅元件厂前身是北京市朝阳可控硅元件厂。</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十一节北京市无线电元件一厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第四十一节北京市可控硅元件厂</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>北京市调谐器厂</t>
+          <t>北京市可控硅元件厂</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京广播电视配件五厂</t>
+          <t>北京半导体材料加工厂</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>19790000</t>
+          <t>19780000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1979年改名为北京广播电视配件五厂。</t>
+          <t>1978年，与东城区可控硅元件厂合并，1980年，改名为北京半导体材料加工厂，1985年，又改名为北京市可控硅元件厂。</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十一节北京市调谐器厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第四十一节北京市可控硅元件厂</t>
         </is>
       </c>
     </row>
@@ -16378,92 +18045,92 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>北京广播器材厂</t>
+          <t>北京市无线电元件一厂</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京人民广播器材厂</t>
+          <t>北京竹藤制品厂</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>19500601</t>
+          <t>19640000</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>19680000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>始建时名称。北京广播器材厂（代号国营第761厂，原名北京人民广播器材厂）1950年6月1日</t>
+          <t>1964年，改名为北京竹藤制品厂。</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第九节北京广播器材厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十一节北京市无线电元件一厂</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>北京广播电视配件一厂</t>
+          <t>北京市无线电元件一厂</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京无线电非金属元件厂</t>
+          <t>北京市无线电元件一厂</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>19650000</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>19700000</t>
+          <t>19680000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1965年，改名为北京无线电非金属元件厂。</t>
+          <t>1968年底，接收北京无线电电阻厂部分产品、设备和人员，转产电子元件，改名为北京市无线电元件一厂。</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十九节北京广播电视配件一厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十一节北京市无线电元件一厂</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>北京广播电视配件一厂</t>
+          <t>北京市调谐器厂</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京无线电元件厂</t>
+          <t>北京广播电视配件五厂</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>19700000</t>
+          <t>19790000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1970年，改名为北京无线电元件厂。</t>
+          <t>1979年改名为北京广播电视配件五厂。</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十九节北京广播电视配件一厂</t>
+          <t>北京工业志·电子志·第二十一节北京市调谐器厂</t>
         </is>
       </c>
     </row>
@@ -16473,108 +18140,98 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>北京广播通讯电源厂</t>
+          <t>北京广播器材厂</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京鞋底厂</t>
+          <t>北京人民广播器材厂</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>19570000</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>19600000</t>
+          <t>19500601</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1957年改名为北京鞋底厂。</t>
+          <t>始建时名称。北京广播器材厂（代号国营第761厂，原名北京人民广播器材厂）1950年6月1日</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十二节北京广播通讯电源厂</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第九节北京广播器材厂</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>北京广播通讯电源厂</t>
+          <t>北京广播电视配件一厂</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京鞋厂</t>
+          <t>北京无线电非金属元件厂</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>19600000</t>
+          <t>19650000</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>19720000</t>
+          <t>19700000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1960年改名为北京鞋厂。</t>
+          <t>1965年，改名为北京无线电非金属元件厂。</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十二节北京广播通讯电源厂</t>
+          <t>北京工业志·电子志·第十九节北京广播电视配件一厂</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>北京广播通讯电源厂</t>
+          <t>北京广播电视配件一厂</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京东风电池厂</t>
+          <t>北京无线电元件厂</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>19720000</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>19790500</t>
+          <t>19700000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1970年该产锅镍蓄电池，并于1972年改名为北京东风电池厂。</t>
+          <t>1970年，改名为北京无线电元件厂。</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十二节北京广播通讯电源厂</t>
+          <t>北京工业志·电子志·第十九节北京广播电视配件一厂</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -16583,22 +18240,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京广播电视配件六厂</t>
+          <t>北京鞋底厂</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>19790500</t>
+          <t>19570000</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>19880000</t>
+          <t>19600000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1979年5月，改名为北京广播电视配件六厂。</t>
+          <t>1957年改名为北京鞋底厂。</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -16609,7 +18266,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -16618,17 +18275,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>北京广播通讯电源厂</t>
+          <t>北京鞋厂</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>19880000</t>
+          <t>19600000</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>19720000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1988年，改名为北京广播通讯电源厂。</t>
+          <t>1960年改名为北京鞋厂。</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -16639,96 +18301,101 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>北京无线电一厂</t>
+          <t>北京广播通讯电源厂</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>北京计算机一厂</t>
+          <t>北京东风电池厂</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>19700000</t>
+          <t>19720000</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>19790500</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1970年初，北京无线电一厂（后更名为北京计算机一厂）接受原航空部第20研究所的委托，开始研制大型晶体管模数混合计算机，1975年，完成研制任务，定名为HMJ-200大型晶体管模数混合计算机。</t>
+          <t>1970年该产锅镍蓄电池，并于1972年改名为北京东风电池厂。</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
+          <t>北京工业志·电子志·第二十二节北京广播通讯电源厂</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>北京无线电仪器二厂</t>
+          <t>北京广播通讯电源厂</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>之一的北京电子仪器厂</t>
+          <t>北京广播电视配件六厂</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>19590000</t>
+          <t>19790500</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>19700400</t>
+          <t>19880000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>始建时名称。该厂前身之一的北京电子仪器厂，1959年，在生产收音机的同时即开始生产测量仪器，并成为全国最早生产电子测量仪器的企业之一。</t>
+          <t>1979年5月，改名为北京广播电视配件六厂。</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
+          <t>北京工业志·电子志·第二十二节北京广播通讯电源厂</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>北京无线电仪器二厂</t>
+          <t>北京广播通讯电源厂</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>北京电子仪器厂</t>
+          <t>北京广播通讯电源厂</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>19700400</t>
+          <t>19880000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>始建时名称。该厂前身之一的北京电子仪器厂，1959年，在生产收音机的同时即开始生产测量仪器，并成为全国最早生产电子测量仪器的企业之一。</t>
+          <t>1988年，改名为北京广播通讯电源厂。</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
+          <t>北京工业志·电子志·第二十二节北京广播通讯电源厂</t>
         </is>
       </c>
     </row>
@@ -16738,97 +18405,92 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>北京无线电元件九厂</t>
+          <t>北京无线电一厂</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>北京市东城区无线电元件厂</t>
+          <t>北京计算机一厂</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>19600000</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>19620000</t>
+          <t>19700000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>始建时名称。北京无线电元件九厂始建于1960年，前身是北京市东城区无线电元件厂。</t>
+          <t>1970年初，北京无线电一厂（后更名为北京计算机一厂）接受原航空部第20研究所的委托，开始研制大型晶体管模数混合计算机，1975年，完成研制任务，定名为HMJ-200大型晶体管模数混合计算机。</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十五节北京无线电元件九厂</t>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>北京无线电元件九厂</t>
+          <t>北京无线电仪器二厂</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>北京无线电插接元件厂</t>
+          <t>之一的北京电子仪器厂</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>19620000</t>
+          <t>19590000</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>19790000</t>
+          <t>19700400</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1962年改名为北京无线电插接元件厂。</t>
+          <t>始建时名称。该厂前身之一的北京电子仪器厂，1959年，在生产收音机的同时即开始生产测量仪器，并成为全国最早生产电子测量仪器的企业之一。</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十五节北京无线电元件九厂</t>
+          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>北京无线电元件九厂</t>
+          <t>北京无线电仪器二厂</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>北京无线电元件九厂</t>
+          <t>北京电子仪器厂</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>19790000</t>
+          <t>19700400</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1979年崇文元件四厂、朝阳精密元件厂并入北京无线电插接元件厂，改名为北京无线电元件九厂。</t>
+          <t>始建时名称。该厂前身之一的北京电子仪器厂，1959年，在生产收音机的同时即开始生产测量仪器，并成为全国最早生产电子测量仪器的企业之一。</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十五节北京无线电元件九厂</t>
+          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
         </is>
       </c>
     </row>
@@ -16838,32 +18500,32 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>北京无线电元件四厂</t>
+          <t>北京无线电元件九厂</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>北京市石景山电容器厂</t>
+          <t>北京市东城区无线电元件厂</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>19670000</t>
+          <t>19600000</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>19790000</t>
+          <t>19620000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>始建时名称。北京无线电元件四厂前身是北京市石景山电容器厂，1967年建成投产，是国内较早从事电容器研制和生产的厂家之一。</t>
+          <t>始建时名称。北京无线电元件九厂始建于1960年，前身是北京市东城区无线电元件厂。</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十三节北京无线电元件四厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十五节北京无线电元件九厂</t>
         </is>
       </c>
     </row>
@@ -16873,57 +18535,62 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>北京无线电元件四厂</t>
+          <t>北京无线电元件九厂</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>北京无线电元件四厂</t>
+          <t>北京无线电插接元件厂</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>19620000</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>19790000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1979年改名为北京无线电元件四厂。</t>
+          <t>1962年改名为北京无线电插接元件厂。</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十三节北京无线电元件四厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十五节北京无线电元件九厂</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>北京无线电厂</t>
+          <t>北京无线电元件九厂</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>北京电子仪器厂</t>
+          <t>北京无线电元件九厂</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>19590000</t>
+          <t>19790000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1959年改名为北京电子仪器厂，1964年6月改为现厂名。</t>
+          <t>1979年崇文元件四厂、朝阳精密元件厂并入北京无线电插接元件厂，改名为北京无线电元件九厂。</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十五节北京无线电厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十五节北京无线电元件九厂</t>
         </is>
       </c>
     </row>
@@ -16933,32 +18600,32 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>北京显像管总厂</t>
+          <t>北京无线电元件四厂</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>北京市半导体器件五厂</t>
+          <t>北京市石景山电容器厂</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>19700000</t>
+          <t>19670000</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>19721100</t>
+          <t>19790000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1970年改为北京市半导体器件五厂，生产低频大功率管。</t>
+          <t>始建时名称。北京无线电元件四厂前身是北京市石景山电容器厂，1967年建成投产，是国内较早从事电容器研制和生产的厂家之一。</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十三节北京无线电元件四厂</t>
         </is>
       </c>
     </row>
@@ -16968,62 +18635,57 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>北京显像管总厂</t>
+          <t>北京无线电元件四厂</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>北京显值管厂</t>
+          <t>北京无线电元件四厂</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>19721100</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>19900000</t>
+          <t>19790000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1972年11月，改名为北京显值管厂。</t>
+          <t>1979年改名为北京无线电元件四厂。</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十三节北京无线电元件四厂</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>北京显像管总厂</t>
+          <t>北京无线电厂</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>北京显像管总厂</t>
+          <t>北京电子仪器厂</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>19900000</t>
+          <t>19590000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1990年，北京半导体设备一厂并入北京显像管厂，改名为北京显像管总厂。</t>
+          <t>1959年改名为北京电子仪器厂，1964年6月改为现厂名。</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
+          <t>北京工业志·电子志·第十五节北京无线电厂</t>
         </is>
       </c>
     </row>
@@ -17033,122 +18695,127 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>北京有线电总厂</t>
+          <t>北京显像管总厂</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>北京有线电厂</t>
+          <t>北京市半导体器件五厂</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>19570900</t>
+          <t>19700000</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>19721100</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>始建时名称。北京有线电总厂原名北京有线电厂（代号国营第738厂），是“一五”时期由苏联援建的156项国家重点工程之一。</t>
+          <t>1970年改为北京市半导体器件五厂，生产低频大功率管。</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第七节北京有线电总厂</t>
+          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>北京核仪器厂</t>
+          <t>北京显像管总厂</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>北京市综合仪器厂</t>
+          <t>北京显值管厂</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>19560000</t>
+          <t>19721100</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>19900000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>始建时名称。北京枚仪器厂前身为北京市综合仪器厂，是1956年中共北京市委、市人委遵照周恩来关于“在北京建立一个射线仪器厂”的指示筹资兴建的。</t>
+          <t>1972年11月，改名为北京显值管厂。</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二章中央在京电子工业企业·第四节北京核仪器厂</t>
+          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>北京牡丹电子集团公司</t>
+          <t>北京显像管总厂</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>北京无线电精密元件厂</t>
+          <t>北京显像管总厂</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>19650000</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>19731100</t>
+          <t>19900000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>始建时名称。北京电视机厂前身为北京无线电精密元件厂，创建于1965年，当时主要生产微型继电器和斩该器。</t>
+          <t>1990年，北京半导体设备一厂并入北京显像管厂，改名为北京显像管总厂。</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
+          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>北京牡丹电子集团公司</t>
+          <t>北京有线电总厂</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>北京电视机厂</t>
+          <t>北京有线电厂</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>19731100</t>
+          <t>19570900</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1973年11月，改名为北京电视机厂，国家投资1000万元在海淀区花园路建设新厂，主要生产黑白、彩色电视机。</t>
+          <t>始建时名称。北京有线电总厂原名北京有线电厂（代号国营第738厂），是“一五”时期由苏联援建的156项国家重点工程之一。</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第七节北京有线电总厂</t>
         </is>
       </c>
     </row>
@@ -17158,97 +18825,92 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>北京电视配件三厂</t>
+          <t>北京核仪器厂</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>东红路塑料制品厂</t>
+          <t>北京市综合仪器厂</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>19660000</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>19700000</t>
+          <t>19560000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>始建时名称。北京电视配件三厂前身为东红路塑料制品厂，建于1966年。</t>
+          <t>始建时名称。北京枚仪器厂前身为北京市综合仪器厂，是1956年中共北京市委、市人委遵照周恩来关于“在北京建立一个射线仪器厂”的指示筹资兴建的。</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第四节北京核仪器厂</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>北京电视配件三厂</t>
+          <t>北京牡丹电子集团公司</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>东红路无线电元件厂</t>
+          <t>北京无线电精密元件厂</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>19700000</t>
+          <t>19650000</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>19750000</t>
+          <t>19731100</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1970年，开始生产云母电容器，改名为东红路无线电元件厂。</t>
+          <t>始建时名称。北京电视机厂前身为北京无线电精密元件厂，创建于1965年，当时主要生产微型继电器和斩该器。</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
+          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>北京电视配件三厂</t>
+          <t>北京牡丹电子集团公司</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>朝阳区东红路无线电元件厂</t>
+          <t>北京电视机厂</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>19750000</t>
+          <t>19731100</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1975年，改名为朝阳区东红路无线电元件厂。</t>
+          <t>1973年11月，改名为北京电视机厂，国家投资1000万元在海淀区花园路建设新厂，主要生产黑白、彩色电视机。</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
+          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
         </is>
       </c>
     </row>
@@ -17258,138 +18920,133 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>北京联想计算机集团公司</t>
+          <t>北京电视配件三厂</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>联想集团公司</t>
+          <t>东红路塑料制品厂</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>19880000</t>
+          <t>19660000</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>19700000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1988年，北京联想计算机集团公司（后更名为联想集团公司，以下简称联想集团）开始研制联想系列微机。</t>
+          <t>始建时名称。北京电视配件三厂前身为东红路塑料制品厂，建于1966年。</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>北京计算机一厂</t>
+          <t>北京电视配件三厂</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>北京市服务联社电器制造厂</t>
+          <t>东红路无线电元件厂</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>19570000</t>
+          <t>19700000</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>19580000</t>
+          <t>19750000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1957年，改名为北京市服务联社电器制造厂。</t>
+          <t>1970年，开始生产云母电容器，改名为东红路无线电元件厂。</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十三节北京计算机一厂</t>
+          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>北京计算机一厂</t>
+          <t>北京电视配件三厂</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>北京市无线电制造厂</t>
+          <t>朝阳区东红路无线电元件厂</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>19580000</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>19620000</t>
+          <t>19750000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1958年，改名为北京市无线电制造厂。</t>
+          <t>1975年，改名为朝阳区东红路无线电元件厂。</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十三节北京计算机一厂</t>
+          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>北京计算机一厂</t>
+          <t>北京联想计算机集团公司</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>北京无线电一厂</t>
+          <t>联想集团公司</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>19620000</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>19790000</t>
+          <t>19880000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1962年，改名为北京无线电一厂。</t>
+          <t>1988年，北京联想计算机集团公司（后更名为联想集团公司，以下简称联想集团）开始研制联想系列微机。</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十三节北京计算机一厂</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -17398,17 +19055,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>北京计算机一厂</t>
+          <t>北京市服务联社电器制造厂</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>19790000</t>
+          <t>19570000</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>19580000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1979年，定名为北京计算机一厂。</t>
+          <t>1957年，改名为北京市服务联社电器制造厂。</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -17419,126 +19081,131 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>北京计算机三厂</t>
+          <t>北京计算机一厂</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>北京无线电三厂</t>
+          <t>北京市无线电制造厂</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>19650425</t>
+          <t>19580000</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>19620000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>始建时名称。北京计算机三厂前身是北京无线电三厂，成立于1965年4月25日。</t>
+          <t>1958年，改名为北京市无线电制造厂。</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十五节北京计算机三厂</t>
+          <t>北京工业志·电子志·第二十三节北京计算机一厂</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>北京计算机外部设备三厂</t>
+          <t>北京计算机一厂</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>北京通讯设备厂</t>
+          <t>北京无线电一厂</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>19620000</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>19790000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1979年，改名为北京通讯设备厂。</t>
+          <t>1962年，改名为北京无线电一厂。</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十六节北京计算机外部设备三厂</t>
+          <t>北京工业志·电子志·第二十三节北京计算机一厂</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>北京邮电通信设备厂</t>
+          <t>北京计算机一厂</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1941年9月建立的华北电信电话股份有限公司</t>
+          <t>北京计算机一厂</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>19410900</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>19410900</t>
+          <t>19790000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>始建时名称。其前身是1941年9月建立的华北电信电话股份有限公司修处（后更名为修缮所），现厂址位于北京市朝阳区将台路5号。</t>
+          <t>1979年，定名为北京计算机一厂。</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二章中央在京电子工业企业·第一节北京邮电通信设备厂</t>
+          <t>北京工业志·电子志·第二十三节北京计算机一厂</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>北京邮电通信设备厂</t>
+          <t>北京计算机三厂</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>华北电信电话股份有限公司</t>
+          <t>北京无线电三厂</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>19410900</t>
+          <t>19650425</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>始建时名称。其前身是1941年9月建立的华北电信电话股份有限公司修处（后更名为修缮所），现厂址位于北京市朝阳区将台路5号。</t>
+          <t>始建时名称。北京计算机三厂前身是北京无线电三厂，成立于1965年4月25日。</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二章中央在京电子工业企业·第一节北京邮电通信设备厂</t>
+          <t>北京工业志·电子志·第二十五节北京计算机三厂</t>
         </is>
       </c>
     </row>
@@ -17548,162 +19215,157 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>北京飞行电子总公司</t>
+          <t>北京计算机外部设备三厂</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>北京第三无线电器材厂</t>
+          <t>北京通讯设备厂</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>19571000</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>19640000</t>
+          <t>19790000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>始建时名称。北京飞行电子总公司原名北京第三无线电器材厂（代号国营第798厂），前身是1957年10月由民主德国援建的华北无线电器材联合厂三分厂。</t>
+          <t>1979年，改名为北京通讯设备厂。</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第六节北京飞行电子总公司</t>
+          <t>北京工业志·电子志·第二十六节北京计算机外部设备三厂</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>北京飞行电子总公司</t>
+          <t>北京邮电通信设备厂</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>北京第三无线电器材厂</t>
+          <t>1941年9月建立的华北电信电话股份有限公司</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>19640000</t>
+          <t>19410900</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>19410900</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>始建时名称。北京飞行电子总公司原名北京第三无线电器材厂（代号国营第798厂），前身是1957年10月由民主德国援建的华北无线电器材联合厂三分厂。</t>
+          <t>始建时名称。其前身是1941年9月建立的华北电信电话股份有限公司修处（后更名为修缮所），现厂址位于北京市朝阳区将台路5号。</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第六节北京飞行电子总公司</t>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第一节北京邮电通信设备厂</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>北京飞达电子集团公司</t>
+          <t>北京邮电通信设备厂</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>北京电影机械修理厂</t>
+          <t>华北电信电话股份有限公司</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>19540000</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>19700000</t>
+          <t>19410900</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>始建时名称。北京录音机厂前身是北京电影机械修理厂，创建于1954年。</t>
+          <t>始建时名称。其前身是1941年9月建立的华北电信电话股份有限公司修处（后更名为修缮所），现厂址位于北京市朝阳区将台路5号。</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第一节北京邮电通信设备厂</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>北京飞达电子集团公司</t>
+          <t>北京飞行电子总公司</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>北京电影机械厂</t>
+          <t>北京第三无线电器材厂</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>19700000</t>
+          <t>19571000</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>19810000</t>
+          <t>19640000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>1970年改名为北京电影机械厂。</t>
+          <t>始建时名称。北京飞行电子总公司原名北京第三无线电器材厂（代号国营第798厂），前身是1957年10月由民主德国援建的华北无线电器材联合厂三分厂。</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第六节北京飞行电子总公司</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>北京飞达电子集团公司</t>
+          <t>北京飞行电子总公司</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>北京录音机厂</t>
+          <t>北京第三无线电器材厂</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>19810000</t>
+          <t>19640000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>1981年改名为北京录音机厂。</t>
+          <t>始建时名称。北京飞行电子总公司原名北京第三无线电器材厂（代号国营第798厂），前身是1957年10月由民主德国援建的华北无线电器材联合厂三分厂。</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第六节北京飞行电子总公司</t>
         </is>
       </c>
     </row>
@@ -17713,128 +19375,133 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>北大方正集团公司</t>
+          <t>北京飞达电子集团公司</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>北京大学新技术公司</t>
+          <t>北京电影机械修理厂</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>19860000</t>
+          <t>19540000</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>19700000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>始建时名称。北京北大方正集团公司前身为北京大学新技术公司，是北京大学1986年创办的校办企业，1988年，改名为北京北大方正集团公司，位于海淀区中关村电子一条街北段。</t>
+          <t>始建时名称。北京录音机厂前身是北京电影机械修理厂，创建于1954年。</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章行业归口电子工业企业·第三节北京北大方正集团公司</t>
+          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>联想集团公司</t>
+          <t>北京飞达电子集团公司</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>中国科学院计算所新技术发展公司</t>
+          <t>北京电影机械厂</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>19841100</t>
+          <t>19700000</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>19870400</t>
+          <t>19810000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>始建时名称。联想集团公司（前身为中国科学院计算所新技术发展公司）创建于1984年11月</t>
+          <t>1970年改名为北京电影机械厂。</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章行业归口电子工业企业·第二节联想集团公司</t>
+          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>联想集团公司</t>
+          <t>北京飞达电子集团公司</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>中科院计算所计算机技术公司</t>
+          <t>北京录音机厂</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>19870400</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>19890800</t>
+          <t>19810000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>1987年4月，更名为中科院计算所计算机技术公司</t>
+          <t>1981年改名为北京录音机厂。</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>联想集团公司</t>
+          <t>北大方正集团公司</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>北京联想计算机集团公司</t>
+          <t>北京大学新技术公司</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>19890800</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>19941100</t>
+          <t>19860000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>1989年8月，更名为北京联想计算机集团公司</t>
+          <t>始建时名称。北京北大方正集团公司前身为北京大学新技术公司，是北京大学1986年创办的校办企业，1988年，改名为北京北大方正集团公司，位于海淀区中关村电子一条街北段。</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章行业归口电子工业企业·第三节北京北大方正集团公司</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -17843,45 +19510,140 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>联想集团公司</t>
+          <t>中国科学院计算所新技术发展公司</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>19941100</t>
+          <t>19841100</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>19870400</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1994年11月，更名为联想</t>
+          <t>始建时名称。联想集团公司（前身为中国科学院计算所新技术发展公司）创建于1984年11月</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章行业归口电子工业企业·第二节联想集团公司</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
+        <v>2</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>联想集团公司</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>中科院计算所计算机技术公司</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>19870400</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>19890800</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1987年4月，更名为中科院计算所计算机技术公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>3</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>联想集团公司</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>北京联想计算机集团公司</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>19890800</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>19941100</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>1989年8月，更名为北京联想计算机集团公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>4</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>联想集团公司</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>联想集团公司</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>19941100</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1994年11月，更名为联想</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
         <v>1</v>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>首钢电子公司</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>首钢自动化研究所</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>19780800</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>始建时名称。首钢电子公司前身是首钢自动化研究所，创建于1978年8月。</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章行业归口电子工业企业·第七节首钢电子公司</t>
         </is>

--- a/CN_Electronic_Industry.xlsx
+++ b/CN_Electronic_Industry.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fact and Comp-Shanghai" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semi-Product" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comp-Product" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Name-History" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Fact and Comp-Shanghai" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Semi-Product" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Comp-Product" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Name-History" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -393,7 +393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T209"/>
+  <dimension ref="A1:U209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.28515625" customWidth="1" min="1" max="1"/>
@@ -459,6 +459,11 @@
           <t>统计年</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>区</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="I2" t="inlineStr">
@@ -1876,6 +1881,11 @@
           <t>北京工业志·电子志·第三章电子计算机</t>
         </is>
       </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1948,6 +1958,11 @@
           <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
         </is>
       </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>宣武</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2018,6 +2033,11 @@
           <t>北京工业志·电子志·第三章电子计算机·第三节计算器</t>
         </is>
       </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>东城</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2217,6 +2237,11 @@
           <t>北京工业志·电子志·第三章电子计算机</t>
         </is>
       </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>石景山</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2309,6 +2334,11 @@
           <t>北京工业志·电子志·第三章电子计算机</t>
         </is>
       </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2445,6 +2475,11 @@
           <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
         </is>
       </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2544,6 +2579,11 @@
           <t>联想集团</t>
         </is>
       </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2917,6 +2957,11 @@
           <t>北京工业志·电子志·第三章电子计算机</t>
         </is>
       </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>崇文</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2944,6 +2989,11 @@
           <t>北京工业志·电子志·第三章电子计算机</t>
         </is>
       </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3025,6 +3075,11 @@
           <t>北京工业志·电子志·第三章电子计算机</t>
         </is>
       </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3860,6 +3915,11 @@
           <t>北京工业志·电子志</t>
         </is>
       </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4322,6 +4382,11 @@
       <c r="T123" t="n">
         <v>1995</v>
       </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4386,6 +4451,11 @@
       <c r="T124" t="n">
         <v>1995</v>
       </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4442,6 +4512,11 @@
       <c r="T125" t="n">
         <v>1995</v>
       </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>东城</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4505,6 +4580,11 @@
       <c r="T126" t="n">
         <v>1995</v>
       </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4568,6 +4648,11 @@
       <c r="T127" t="n">
         <v>1995</v>
       </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>崇文</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4616,6 +4701,11 @@
       <c r="T128" t="n">
         <v>1995</v>
       </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>丰台</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4667,6 +4757,11 @@
       <c r="T129" t="n">
         <v>1995</v>
       </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4718,6 +4813,11 @@
       <c r="T130" t="n">
         <v>1995</v>
       </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>西城</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4771,6 +4871,11 @@
       <c r="T131" t="n">
         <v>1995</v>
       </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4832,6 +4937,11 @@
       <c r="T132" t="n">
         <v>1995</v>
       </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>宣武</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4849,7 +4959,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>改名北京广播器材厂-&gt;合并组建了北京市综合仪器厂-&gt;19590000之一的北京电子仪器厂-&gt;19620900东城无线电仪器装配厂和电讯仪表厂合并-&gt;19700000北京无线电二厂合并-&gt;北京电子仪器厂、北京无线电二厂合并</t>
+          <t>改名北京广播器材厂-&gt;合并组建了北京市综合仪器厂-&gt;19590000北京电子仪器厂-&gt;19620900东城无线电仪器装配厂和电讯仪表厂合并-&gt;19700000北京无线电二厂合并-&gt;北京电子仪器厂、北京无线电二厂合并</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -4890,6 +5000,11 @@
       <c r="T133" t="n">
         <v>1995</v>
       </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4943,6 +5058,11 @@
       <c r="T134" t="n">
         <v>1995</v>
       </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>西城</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5014,6 +5134,11 @@
       <c r="T135" t="n">
         <v>1995</v>
       </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5077,6 +5202,11 @@
       <c r="T136" t="n">
         <v>1990</v>
       </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>西城</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5137,6 +5267,11 @@
       <c r="T137" t="n">
         <v>1995</v>
       </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5256,6 +5391,11 @@
       <c r="T139" t="n">
         <v>1995</v>
       </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5307,6 +5447,11 @@
       <c r="T140" t="n">
         <v>1995</v>
       </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>宣武</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5368,6 +5513,11 @@
       <c r="T141" t="n">
         <v>1995</v>
       </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>西城</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5419,6 +5569,11 @@
       <c r="T142" t="n">
         <v>1995</v>
       </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>石景山</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5482,6 +5637,11 @@
       <c r="T143" t="n">
         <v>1995</v>
       </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>东城</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5546,6 +5706,11 @@
       <c r="T144" t="n">
         <v>1995</v>
       </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5607,6 +5772,11 @@
       <c r="T145" t="n">
         <v>1995</v>
       </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5673,6 +5843,11 @@
       <c r="T146" t="n">
         <v>1995</v>
       </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>崇文</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5734,6 +5909,11 @@
       <c r="T147" t="n">
         <v>1995</v>
       </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>西城</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5787,6 +5967,11 @@
       <c r="T148" t="n">
         <v>1995</v>
       </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>宣武</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5979,6 +6164,11 @@
       <c r="T151" t="n">
         <v>1995</v>
       </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6039,6 +6229,11 @@
       <c r="T152" t="n">
         <v>1995</v>
       </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6103,6 +6298,11 @@
       <c r="T153" t="n">
         <v>1995</v>
       </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6161,6 +6361,11 @@
       <c r="T154" t="n">
         <v>1995</v>
       </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6217,6 +6422,11 @@
       <c r="T155" t="n">
         <v>1995</v>
       </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6271,6 +6481,11 @@
       <c r="T156" t="n">
         <v>1995</v>
       </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6334,6 +6549,11 @@
       <c r="T157" t="n">
         <v>1995</v>
       </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6397,6 +6617,11 @@
       <c r="T158" t="n">
         <v>1995</v>
       </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6447,6 +6672,11 @@
       <c r="T159" t="n">
         <v>1995</v>
       </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6510,6 +6740,11 @@
       <c r="T160" t="n">
         <v>1995</v>
       </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6571,6 +6806,11 @@
       <c r="T161" t="n">
         <v>1995</v>
       </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6629,6 +6869,11 @@
       <c r="T162" t="n">
         <v>1995</v>
       </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6693,6 +6938,11 @@
       <c r="T163" t="n">
         <v>1995</v>
       </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6750,6 +7000,11 @@
       <c r="T164" t="n">
         <v>1995</v>
       </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6811,6 +7066,11 @@
       <c r="T165" t="n">
         <v>1995</v>
       </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6853,6 +7113,11 @@
       <c r="T166" t="n">
         <v>1995</v>
       </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6902,6 +7167,11 @@
       <c r="T167" t="n">
         <v>1995</v>
       </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>西城</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6993,6 +7263,11 @@
       <c r="T169" t="n">
         <v>1995</v>
       </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7043,6 +7318,11 @@
       </c>
       <c r="T170" t="n">
         <v>1995</v>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
       </c>
     </row>
     <row r="171">
@@ -18440,7 +18720,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>之一的北京电子仪器厂</t>
+          <t>北京电子仪器厂</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">

--- a/CN_Electronic_Industry.xlsx
+++ b/CN_Electronic_Industry.xlsx
@@ -393,7 +393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U209"/>
+  <dimension ref="A1:U204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.28515625" customWidth="1" min="1" max="1"/>
@@ -2170,11 +2170,16 @@
           <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
         </is>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>联想计算机集团公司</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>联想计算机集团公司</t>
+          <t>首钢电子公司</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2182,9 +2187,12 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>联想系列微机</t>
+      <c r="D46" t="n">
+        <v>19790000</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>改名自动化研究所</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2194,19 +2202,24 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>石景山</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>首钢电子公司</t>
+          <t>北京工控计算机厂</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2215,12 +2228,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>19790000</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>改名自动化研究所</t>
-        </is>
+        <v>19830000</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2229,24 +2237,19 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>石景山</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>北京工控计算机厂</t>
+          <t>北京工业大学电子厂</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2254,8 +2257,10 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="D48" t="n">
-        <v>19830000</v>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>TP系列微型打印机</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2264,7 +2269,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -2276,7 +2281,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>北京工业大学电子厂</t>
+          <t>北京四通办公设备有限公司</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2284,10 +2289,8 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>TP系列微型打印机</t>
-        </is>
+      <c r="D49" t="n">
+        <v>19870000</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2302,13 +2305,18 @@
       <c r="R49" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>北京四通办公设备有限公司</t>
+          <t>电子部6所</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2316,8 +2324,10 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="D50" t="n">
-        <v>19870000</v>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>长城0520B微型机</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2332,18 +2342,13 @@
       <c r="R50" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>电子部6所</t>
+          <t>北京市计算机技术研究所</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2353,8 +2358,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>长城0520B微型机</t>
-        </is>
+          <t>生产10台BCM0530机、10台BCM0530机</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>19790000</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2363,19 +2371,24 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机；北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>市计算机技术研究所</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>北京市计算机技术研究所</t>
+          <t>四机部15所</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2385,11 +2398,8 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>生产10台BCM0530机、10台BCM0530机</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>19790000</v>
+          <t>DJS-200系列计算机</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2398,24 +2408,19 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机；北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>市计算机技术研究所</t>
+          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>四机部15所</t>
+          <t>北京计算机三厂</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2425,7 +2430,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DJS-200系列计算机</t>
+          <t>DJS-5小型晶体管鼓字计算机</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2435,19 +2440,24 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>朝阳</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>北京计算机三厂</t>
+          <t>北京市无线电制造厂</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2455,9 +2465,9 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>DJS-5小型晶体管鼓字计算机</t>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>改名北京无线电一厂</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2467,35 +2477,28 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>朝阳</t>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>北京市无线电制造厂</t>
+          <t>北京电子显示设备厂</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>电子计算机</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>改名北京无线电一厂</t>
-        </is>
+          <t>外围设备</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>19830700</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2509,23 +2512,25 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·三、 显示器</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>北京电子显示设备厂</t>
+          <t>联想集团公司</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>外围设备</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>19830700</v>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>并投人批量生产联想激光打印机、联想激光打印机、联想系列微机</t>
+        </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2539,25 +2544,33 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·三、 显示器</t>
+          <t>北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·四、 打印机</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>联想集团</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>联想集团公司</t>
+          <t>自动化研究所</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>电子计算机</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>并投人批量生产联想激光打印机、联想激光打印机、联想系列微机</t>
-        </is>
+          <t>研究所</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>19790000</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2566,38 +2579,25 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·四、 打印机</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>联想集团</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>海淀</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 计算机辅助软件工程系统</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>自动化研究所</t>
+          <t>长沙工业学院</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>研究所</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>19790000</v>
+          <t>电子计算机</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2606,24 +2606,29 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 计算机辅助软件工程系统</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>长沙工业学院</t>
+          <t>电子部第15所</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>NCI-2780超级小型计算机</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2645,7 +2650,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>电子部第15所</t>
+          <t>四机部6所</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2655,7 +2660,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NCI-2780超级小型计算机</t>
+          <t>微型计算机、S-100总线单板系列机</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2670,14 +2675,14 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>四机部6所</t>
+          <t>安徽无线电厂</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2687,7 +2692,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>微型计算机、S-100总线单板系列机</t>
+          <t>微型计算机</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2709,7 +2714,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>安徽无线电厂</t>
+          <t>北京崇文电子仪器厂</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2741,7 +2746,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>北京崇文电子仪器厂</t>
+          <t>北京市计算机服务公司</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2751,7 +2756,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>微型计算机</t>
+          <t>0520CH机</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2761,19 +2766,24 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>计算机服务公司</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>北京市计算机服务公司</t>
+          <t>北京开关厂</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2781,9 +2791,9 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>0520CH机</t>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>19060000改名北京控制机厂</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2793,24 +2803,19 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>计算机服务公司</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>北京开关厂</t>
+          <t>北京计算机配件五厂</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2818,10 +2823,8 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>19060000改名北京控制机厂</t>
-        </is>
+      <c r="D65" t="n">
+        <v>19830000</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2830,7 +2833,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -2842,7 +2845,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>北京计算机配件五厂</t>
+          <t>华北制药厂</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2850,17 +2853,19 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="D66" t="n">
-        <v>19830000</v>
-      </c>
       <c r="G66" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>亚运村</t>
+        </is>
+      </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -2872,24 +2877,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>华北制药厂</t>
+          <t>美国COMPAQ公司</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>电子计算机</t>
-        </is>
+          <t>外围设备</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>19830700</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>亚运村</t>
-        </is>
-      </c>
       <c r="Q67" t="inlineStr">
         <is>
           <t>未见专条,据行文点名；行业据正文用词</t>
@@ -2897,23 +2900,20 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>美国COMPAQ公司</t>
+          <t>北京计算机外部设备三厂</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>外围设备</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>19830700</v>
+          <t>电子计算机</t>
+        </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2922,19 +2922,24 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>崇文</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>北京计算机外部设备三厂</t>
+          <t>中国长城计算机集团公司</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2959,14 +2964,14 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>崇文</t>
+          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>中国长城计算机集团公司</t>
+          <t>北京科海高技术集团公司</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2981,24 +2986,19 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>北大方正集团公司</t>
+          <t>北京希望电脑公司</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3013,19 +3013,24 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>北京科海高技术集团公司</t>
+          <t>北京王码电脑公司</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3040,7 +3045,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -3052,7 +3057,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>北京希望电脑公司</t>
+          <t>电子部15所</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3067,24 +3072,19 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>北京王码电脑公司</t>
+          <t>北京航星机器制造公司</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -3111,7 +3111,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>电子部15所</t>
+          <t>哈尔滨军事工程学院</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3131,19 +3131,24 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>哈军工</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>北京航星机器制造公司</t>
+          <t>四机部标准化研究所4所</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>电子计算机</t>
+          <t>研究所</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3153,19 +3158,19 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>哈尔滨军事工程学院</t>
+          <t>北京市计算机工业总公司</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3180,29 +3185,24 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
-        </is>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>哈军工</t>
+          <t>北京工业志·电子志·第三章电子计算机·第三节计算器</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>四机部标准化研究所4所</t>
+          <t>北京东风电视机厂</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>研究所</t>
+          <t>外围设备</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3212,19 +3212,19 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·三、 显示器</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>北京市计算机工业总公司</t>
+          <t>一机部15所</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3239,24 +3239,24 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>北京东风电视机厂</t>
+          <t>北京大学</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>外围设备</t>
+          <t>电子计算机</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3271,14 +3271,14 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·三、 显示器</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·二、 汉字信息系统</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>一机部15所</t>
+          <t>北京大学计算机技术研究所</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3293,24 +3293,24 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·二、 汉字信息系统</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>北京大学</t>
+          <t>中科院自动化研究所</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>电子计算机</t>
+          <t>研究所</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3320,24 +3320,24 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·二、 汉字信息系统</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 计算机辅助软件工程系统</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>北京大学计算机技术研究所</t>
+          <t>北京市半导体器件二厂</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>电子计算机</t>
+          <t>半导体</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3352,19 +3352,19 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·二、 汉字信息系统</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>中科院自动化研究所</t>
+          <t>清华大学计算机厂</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>研究所</t>
+          <t>电子计算机</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3379,19 +3379,19 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 计算机辅助软件工程系统</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>北京市半导体器件二厂</t>
+          <t>北京师范大学</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>电子计算机</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3401,19 +3401,19 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>清华大学计算机厂</t>
+          <t>上海复旦大学</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3428,24 +3428,29 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>北京师范大学</t>
+          <t>山东省烟台市电子技术研究所</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>电子计算机</t>
+          <t>研究所</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3455,7 +3460,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -3467,13 +3472,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>上海复旦大学</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>电子计算机</t>
-        </is>
+          <t>北京四通集团公司</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>19870000</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3482,29 +3485,24 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
-        </is>
-      </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>复旦大学</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（四） 文字处理机</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>山东省烟台市电子技术研究所</t>
+          <t>北京开关厂平谷分厂</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>研究所</t>
+          <t>电子计算机</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3514,23 +3512,25 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>北京四通集团公司</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>19870000</v>
+          <t>北京控制机厂</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3539,24 +3539,24 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（四） 文字处理机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>北京开关厂平谷分厂</t>
+          <t>北京电器科学研究院</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>电子计算机</t>
+          <t>研究所</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -3578,7 +3578,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>北京控制机厂</t>
+          <t>兰州炼油厂</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -3605,12 +3605,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>北京电器科学研究院</t>
+          <t>大庆石油化工总厂</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>研究所</t>
+          <t>电子计算机</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -3632,7 +3632,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>兰州炼油厂</t>
+          <t>唐山陡河发电总厂</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3653,18 +3653,23 @@
       <c r="R94" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>陡河发电总厂</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>大庆石油化工总厂</t>
+          <t>首钢自动化研究所</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>电子计算机</t>
+          <t>研究所</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3674,7 +3679,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -3686,12 +3691,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>唐山陡河发电总厂</t>
+          <t>中国管理科学研究院</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>电子计算机</t>
+          <t>研究所</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3701,7 +3706,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -3713,7 +3718,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>陡河发电总厂</t>
+          <t>华胜计算机公司</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3728,24 +3733,24 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·六、 工作站</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>首钢自动化研究所</t>
+          <t>中国软件技术公司</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>研究所</t>
+          <t>外围设备</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3755,24 +3760,24 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>中国管理科学研究院</t>
+          <t>北京华海新技术开发公司</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>研究所</t>
+          <t>外围设备</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3782,24 +3787,19 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>华胜计算机公司</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>电子计算机</t>
+          <t>北京西城广播设备厂</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -3809,24 +3809,19 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·六、 工作站</t>
+          <t>北京工业志·电子志</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>中国软件技术公司</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>外围设备</t>
+          <t>北京无线电厂</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -3836,24 +3831,24 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
+          <t>北京工业志·电子志</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>北京华海新技术开发公司</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>外围设备</t>
+          <t>国营774厂音响分厂</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -3863,19 +3858,19 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
+          <t>北京工业志·电子志</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>北京西城广播设备厂</t>
+          <t>508所</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -3890,14 +3885,14 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>北京工业志·电子志</t>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>北京无线电厂</t>
+          <t>302所</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -3912,19 +3907,14 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>北京工业志·电子志</t>
-        </is>
-      </c>
-      <c r="U104" t="inlineStr">
-        <is>
-          <t>海淀</t>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>国营774厂音响分厂</t>
+          <t>六机部705所</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -3939,14 +3929,14 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>北京工业志·电子志</t>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>508所</t>
+          <t>航空部601所</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -3968,7 +3958,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>302所</t>
+          <t>北京三洋电子有限公司</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -3983,14 +3973,14 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第三节计算器</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>上海华东师范大学</t>
+          <t>北京第三棉纺织厂</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4005,19 +3995,14 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
-        </is>
-      </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>华东师范</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>六机部705所</t>
+          <t>中国人民解放军3509厂</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4032,14 +4017,14 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>航空部601所</t>
+          <t>第二钢轧厂</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4054,14 +4039,14 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>北京三洋电子有限公司</t>
+          <t>南京微电机厂</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4076,14 +4061,14 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(二) 单板机</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>北京第三棉纺织厂</t>
+          <t>机电部4所</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4098,14 +4083,14 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>中国人民解放军3509厂</t>
+          <t>新疆水泥厂</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4120,14 +4105,14 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>第二钢轧厂</t>
+          <t>双羊水泥厂</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4142,14 +4127,14 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>南京微电机厂</t>
+          <t>美国钢铁公司</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4164,14 +4149,14 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(二) 单板机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>机电部4所</t>
+          <t>北京水泵厂</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4186,14 +4171,14 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>新疆水泥厂</t>
+          <t>华胜公司</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4208,14 +4193,14 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·六、 工作站</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>双羊水泥厂</t>
+          <t>首钢公司</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4230,36 +4215,98 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>美国钢铁公司</t>
-        </is>
+          <t>北京东光电工厂</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>19680200</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>酒仙桥路12号</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>1499</v>
+      </c>
+      <c r="J119" t="n">
+        <v>142</v>
+      </c>
+      <c r="L119" t="n">
+        <v>90600</v>
+      </c>
+      <c r="M119" t="n">
+        <v>11100</v>
+      </c>
+      <c r="N119" t="n">
+        <v>686</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名</t>
+          <t>行业据正文用词</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+          <t>北京工业志·电子志·第十二节北京东光电工厂</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>国营第878厂</t>
+        </is>
+      </c>
+      <c r="T119" t="n">
+        <v>1995</v>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>朝阳</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>北京水泵厂</t>
+          <t>北京牡丹电子集团公司</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>外围设备</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>彩色电视机</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>19900216</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>19650000北京无线电精密元件厂-&gt;19731100改名北京电视机厂-&gt;北京电视机厂与北京电子显示设各厂合并-&gt;19910000北京东风电视机厂合并</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4267,21 +4314,63 @@
           <t>Beijing</t>
         </is>
       </c>
+      <c r="I120" t="n">
+        <v>5617</v>
+      </c>
+      <c r="J120" t="n">
+        <v>896</v>
+      </c>
+      <c r="L120" t="n">
+        <v>136200</v>
+      </c>
+      <c r="M120" t="n">
+        <v>45000</v>
+      </c>
+      <c r="N120" t="n">
+        <v>146000</v>
+      </c>
+      <c r="O120" t="n">
+        <v>107000</v>
+      </c>
+      <c r="P120" t="n">
+        <v>2504.5</v>
+      </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名</t>
+          <t>行业据正文用词</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
+        </is>
+      </c>
+      <c r="T120" t="n">
+        <v>1995</v>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>华胜公司</t>
+          <t>北京电视设备厂</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>彩色摄像机、彩色锁相同步机、J52等十余种型号的录像机</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>19710500</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>国营761厂电视车间与北京被服厂合并</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4289,21 +4378,65 @@
           <t>Beijing</t>
         </is>
       </c>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>未见专条,据行文点名</t>
-        </is>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>东四北大街107号</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>1139</v>
+      </c>
+      <c r="J121" t="n">
+        <v>264</v>
+      </c>
+      <c r="L121" t="n">
+        <v>18100</v>
+      </c>
+      <c r="M121" t="n">
+        <v>12000</v>
+      </c>
+      <c r="N121" t="n">
+        <v>29200</v>
+      </c>
+      <c r="P121" t="n">
+        <v>1972</v>
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·六、 工作站</t>
+          <t>北京工业志·电子志·第十四节北京电视设备厂</t>
+        </is>
+      </c>
+      <c r="T121" t="n">
+        <v>1995</v>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>东城</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>首钢公司</t>
+          <t>北京飞达电子集团公司</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>收录机</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>19930200</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>19540000北京电影机械修理厂-&gt;19700000改名北京电影机械厂-&gt;19810000改名北京录音机厂</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4311,21 +4444,49 @@
           <t>Beijing</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>苏州街75号</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>792</v>
+      </c>
+      <c r="J122" t="n">
+        <v>95</v>
+      </c>
+      <c r="L122" t="n">
+        <v>30200</v>
+      </c>
+      <c r="N122" t="n">
+        <v>1444</v>
+      </c>
+      <c r="P122" t="n">
+        <v>30.9</v>
+      </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名</t>
+          <t>行业据正文用词</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
+          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
+        </is>
+      </c>
+      <c r="T122" t="n">
+        <v>1995</v>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>北京东光电工厂</t>
+          <t>北京显像管总厂</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4333,8 +4494,15 @@
           <t>半导体</t>
         </is>
       </c>
-      <c r="D123" t="n">
-        <v>19680200</v>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>低频大功率管、23厘米黑白显像管和50厘米显像管、35厘米黑白显像管、彩色显示管</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>19700000北京呢绒服装厂-&gt;19721100改名北京显值管厂-&gt;19900000改名北京显像管总厂</t>
+        </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -4343,26 +4511,26 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>酒仙桥路12号</t>
+          <t>光明西路1号</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1499</v>
+        <v>1023</v>
       </c>
       <c r="J123" t="n">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="L123" t="n">
-        <v>90600</v>
+        <v>52800</v>
       </c>
       <c r="M123" t="n">
-        <v>11100</v>
+        <v>4637.2</v>
       </c>
       <c r="N123" t="n">
-        <v>686</v>
+        <v>1124</v>
       </c>
       <c r="P123" t="n">
-        <v>0.6</v>
+        <v>5.3</v>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
@@ -4371,12 +4539,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十二节北京东光电工厂</t>
-        </is>
-      </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>国营第878厂</t>
+          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
         </is>
       </c>
       <c r="T123" t="n">
@@ -4384,32 +4547,22 @@
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>朝阳</t>
+          <t>崇文</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>北京牡丹电子集团公司</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>外围设备</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>彩色电视机</t>
+          <t>北京广播电视配件一厂</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>19900216</v>
+        <v>19540000</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>19650000北京无线电精密元件厂-&gt;19731100改名北京电视机厂-&gt;北京电视机厂与北京电子显示设各厂合并-&gt;19910000北京东风电视机厂合并</t>
+          <t>19570000合并改建为北京无线电电匣厂-&gt;19610000并入北京电子仪器厂-&gt;19650000改名北京无线电非金属元件厂-&gt;19700000改名北京无线电元件厂</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -4417,35 +4570,29 @@
           <t>Beijing</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>东铁匠营横七条30号</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>5617</v>
+        <v>910</v>
       </c>
       <c r="J124" t="n">
-        <v>896</v>
+        <v>62</v>
       </c>
       <c r="L124" t="n">
-        <v>136200</v>
+        <v>34800</v>
       </c>
       <c r="M124" t="n">
-        <v>45000</v>
+        <v>2918.8</v>
       </c>
       <c r="N124" t="n">
-        <v>146000</v>
-      </c>
-      <c r="O124" t="n">
-        <v>107000</v>
-      </c>
-      <c r="P124" t="n">
-        <v>2504.5</v>
-      </c>
-      <c r="Q124" t="inlineStr">
-        <is>
-          <t>行业据正文用词</t>
-        </is>
+        <v>929</v>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
+          <t>北京工业志·电子志·第十九节北京广播电视配件一厂</t>
         </is>
       </c>
       <c r="T124" t="n">
@@ -4453,27 +4600,22 @@
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>海淀</t>
+          <t>丰台</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>北京电视设备厂</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>彩色摄像机、彩色锁相同步机、J52等十余种型号的录像机</t>
+          <t>北京电视配件三厂</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>19710500</v>
+        <v>19900000</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>国营761厂电视车间与北京被服厂合并</t>
+          <t>改名北京广播电视配件三厂-&gt;19660000东红路塑料制品厂-&gt;19700000改名东红路无线电元件厂-&gt;19750000改名朝阳区东红路无线电元件厂</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4483,30 +4625,30 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>东四北大街107号</t>
+          <t>酒仙桥南路5号</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1139</v>
+        <v>1057</v>
       </c>
       <c r="J125" t="n">
-        <v>264</v>
+        <v>130</v>
       </c>
       <c r="L125" t="n">
-        <v>18100</v>
+        <v>35200</v>
       </c>
       <c r="M125" t="n">
-        <v>12000</v>
+        <v>7816.1</v>
       </c>
       <c r="N125" t="n">
-        <v>29200</v>
+        <v>12700</v>
       </c>
       <c r="P125" t="n">
-        <v>1972</v>
+        <v>1812.7</v>
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十四节北京电视设备厂</t>
+          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
         </is>
       </c>
       <c r="T125" t="n">
@@ -4514,32 +4656,22 @@
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>东城</t>
+          <t>朝阳</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>北京飞达电子集团公司</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>半导体</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>收录机</t>
+          <t>北京市调谐器厂</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>19930200</v>
+        <v>19810200</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>19540000北京电影机械修理厂-&gt;19700000改名北京电影机械厂-&gt;19810000改名北京录音机厂</t>
+          <t>19691000合并为西城区无线电元件厂-&gt;19790000改名北京广播电视配件五厂</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4549,32 +4681,30 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>苏州街75号</t>
+          <t>家来街月台胡同18号</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>792</v>
+        <v>545</v>
       </c>
       <c r="J126" t="n">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="L126" t="n">
-        <v>30200</v>
+        <v>39700</v>
+      </c>
+      <c r="M126" t="n">
+        <v>2835.3</v>
       </c>
       <c r="N126" t="n">
-        <v>1444</v>
-      </c>
-      <c r="P126" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="Q126" t="inlineStr">
-        <is>
-          <t>行业据正文用词</t>
-        </is>
+        <v>1245</v>
+      </c>
+      <c r="O126" t="n">
+        <v>1504.8</v>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
+          <t>北京工业志·电子志·第二十一节北京市调谐器厂</t>
         </is>
       </c>
       <c r="T126" t="n">
@@ -4582,29 +4712,27 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>海淀</t>
+          <t>西城</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>北京显像管总厂</t>
+          <t>北京广播通讯电源厂</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>半导体</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>低频大功率管、23厘米黑白显像管和50厘米显像管、35厘米黑白显像管、彩色显示管</t>
-        </is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>19540000</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>19700000北京呢绒服装厂-&gt;19721100改名北京显值管厂-&gt;19900000改名北京显像管总厂</t>
+          <t>19570000改名北京鞋底厂-&gt;19600000改名北京鞋厂-&gt;19720000改名北京东风电池厂-&gt;19790500改名北京广播电视配件六厂-&gt;19880000改名北京广播通讯电源厂</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -4612,28 +4740,20 @@
           <t>Beijing</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>光明西路1号</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>1023</v>
+        <v>396</v>
       </c>
       <c r="J127" t="n">
-        <v>138</v>
+        <v>15</v>
       </c>
       <c r="L127" t="n">
-        <v>52800</v>
-      </c>
-      <c r="M127" t="n">
-        <v>4637.2</v>
+        <v>30100</v>
       </c>
       <c r="N127" t="n">
-        <v>1124</v>
+        <v>240</v>
       </c>
       <c r="P127" t="n">
-        <v>5.3</v>
+        <v>55.7</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -4642,7 +4762,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
+          <t>北京工业志·电子志·第二十二节北京广播通讯电源厂</t>
         </is>
       </c>
       <c r="T127" t="n">
@@ -4650,22 +4770,27 @@
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>崇文</t>
+          <t>朝阳</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>北京广播电视配件一厂</t>
+          <t>北京无线电仪器厂</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>半导体</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>19540000</v>
+        <v>19620600</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>19570000合并改建为北京无线电电匣厂-&gt;19610000并入北京电子仪器厂-&gt;19650000改名北京无线电非金属元件厂-&gt;19700000改名北京无线电元件厂</t>
+          <t>北京崇文电器仪器厂、北京电器厂合并</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -4675,27 +4800,35 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>东铁匠营横七条30号</t>
+          <t>福长街四条4号</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>910</v>
+        <v>709</v>
       </c>
       <c r="J128" t="n">
-        <v>62</v>
+        <v>172</v>
       </c>
       <c r="L128" t="n">
-        <v>34800</v>
+        <v>21200</v>
       </c>
       <c r="M128" t="n">
-        <v>2918.8</v>
+        <v>1873.8</v>
       </c>
       <c r="N128" t="n">
-        <v>929</v>
+        <v>3453</v>
+      </c>
+      <c r="P128" t="n">
+        <v>165.5</v>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十九节北京广播电视配件一厂</t>
+          <t>北京工业志·电子志·第二十七节北京无线电仪器厂</t>
         </is>
       </c>
       <c r="T128" t="n">
@@ -4703,22 +4836,27 @@
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>丰台</t>
+          <t>宣武</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>北京电视配件三厂</t>
+          <t>北京无线电仪器二厂</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>半导体</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>19900000</v>
+        <v>19700400</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>改名北京广播电视配件三厂-&gt;19660000东红路塑料制品厂-&gt;19700000改名东红路无线电元件厂-&gt;19750000改名朝阳区东红路无线电元件厂</t>
+          <t>改名北京广播器材厂-&gt;合并组建了北京市综合仪器厂-&gt;19590000北京电子仪器厂-&gt;19620900东城无线电仪器装配厂和电讯仪表厂合并-&gt;19700000北京无线电二厂合并-&gt;北京电子仪器厂、北京无线电二厂合并</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -4728,30 +4866,32 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>酒仙桥南路5号</t>
+          <t>符台路2号</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1057</v>
-      </c>
-      <c r="J129" t="n">
-        <v>130</v>
+        <v>622</v>
       </c>
       <c r="L129" t="n">
-        <v>35200</v>
+        <v>36900</v>
       </c>
       <c r="M129" t="n">
-        <v>7816.1</v>
+        <v>2209</v>
       </c>
       <c r="N129" t="n">
-        <v>12700</v>
-      </c>
-      <c r="P129" t="n">
-        <v>1812.7</v>
+        <v>237</v>
+      </c>
+      <c r="O129" t="n">
+        <v>206.7</v>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
+          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
         </is>
       </c>
       <c r="T129" t="n">
@@ -4766,15 +4906,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>北京市调谐器厂</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>19810200</v>
+          <t>北京广播器材厂</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>广播发射机、电视发射机、电视差转机、盒式录像机</t>
+        </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>19691000合并为西城区无线电元件厂-&gt;19790000改名北京广播电视配件五厂</t>
+          <t>19500601北京人民广播器材厂</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -4784,30 +4926,30 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>家来街月台胡同18号</t>
+          <t>今四环胡同4号</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>545</v>
+        <v>3486</v>
       </c>
       <c r="J130" t="n">
-        <v>21</v>
+        <v>783</v>
       </c>
       <c r="L130" t="n">
-        <v>39700</v>
+        <v>227200</v>
       </c>
       <c r="M130" t="n">
-        <v>2835.3</v>
+        <v>23900</v>
       </c>
       <c r="N130" t="n">
-        <v>1245</v>
-      </c>
-      <c r="O130" t="n">
-        <v>1504.8</v>
+        <v>7904.9</v>
+      </c>
+      <c r="P130" t="n">
+        <v>683.6</v>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十一节北京市调谐器厂</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第九节北京广播器材厂</t>
         </is>
       </c>
       <c r="T130" t="n">
@@ -4822,20 +4964,25 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>北京广播通讯电源厂</t>
+          <t>北京邮电通信设备厂</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>电子计算机</t>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>生产微波三大固体器件、微波三大固体器件</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>19540000</v>
+        <v>19410900</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>19570000改名北京鞋底厂-&gt;19600000改名北京鞋厂-&gt;19720000改名北京东风电池厂-&gt;19790500改名北京广播电视配件六厂-&gt;19880000改名北京广播通讯电源厂</t>
+          <t>组建了4个合资公司-&gt;1941年9月建立的华北电信电话股份有限公司</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -4843,20 +4990,28 @@
           <t>Beijing</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>将台路5号</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>396</v>
+        <v>1367</v>
       </c>
       <c r="J131" t="n">
-        <v>15</v>
+        <v>724</v>
       </c>
       <c r="L131" t="n">
-        <v>30100</v>
+        <v>86000</v>
+      </c>
+      <c r="M131" t="n">
+        <v>8359.4</v>
       </c>
       <c r="N131" t="n">
-        <v>240</v>
+        <v>7489</v>
       </c>
       <c r="P131" t="n">
-        <v>55.7</v>
+        <v>189</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -4865,7 +5020,12 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十二节北京广播通讯电源厂</t>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第一节北京邮电通信设备厂</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>邮电506厂</t>
         </is>
       </c>
       <c r="T131" t="n">
@@ -4880,7 +5040,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>北京无线电仪器厂</t>
+          <t>北京通信元件厂</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4888,12 +5048,9 @@
           <t>半导体</t>
         </is>
       </c>
-      <c r="D132" t="n">
-        <v>19620600</v>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>北京崇文电器仪器厂、北京电器厂合并</t>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>半导体器件、高反压复合场效应晶体管、和销售BP机</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -4903,26 +5060,26 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>福长街四条4号</t>
-        </is>
-      </c>
-      <c r="I132" t="n">
-        <v>709</v>
+          <t>新街口外大街28号</t>
+        </is>
       </c>
       <c r="J132" t="n">
-        <v>172</v>
+        <v>450</v>
       </c>
       <c r="L132" t="n">
-        <v>21200</v>
+        <v>70000</v>
       </c>
       <c r="M132" t="n">
-        <v>1873.8</v>
+        <v>3040.9</v>
       </c>
       <c r="N132" t="n">
-        <v>3453</v>
+        <v>4423.4</v>
+      </c>
+      <c r="O132" t="n">
+        <v>12000</v>
       </c>
       <c r="P132" t="n">
-        <v>165.5</v>
+        <v>360</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -4931,35 +5088,37 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十七节北京无线电仪器厂</t>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第二节邮电部北京通信元件厂</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>邮电508厂</t>
         </is>
       </c>
       <c r="T132" t="n">
-        <v>1995</v>
+        <v>1990</v>
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>宣武</t>
+          <t>西城</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>北京无线电仪器二厂</t>
+          <t>北京长城无线电厂</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>半导体</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>19700400</v>
+          <t>电子计算机</t>
+        </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>改名北京广播器材厂-&gt;合并组建了北京市综合仪器厂-&gt;19590000北京电子仪器厂-&gt;19620900东城无线电仪器装配厂和电讯仪表厂合并-&gt;19700000北京无线电二厂合并-&gt;北京电子仪器厂、北京无线电二厂合并</t>
+          <t>19740000下放北京市</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -4969,23 +5128,23 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>符台路2号</t>
+          <t>学院南路34号</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>622</v>
+        <v>790</v>
       </c>
       <c r="L133" t="n">
-        <v>36900</v>
+        <v>36300</v>
       </c>
       <c r="M133" t="n">
-        <v>2209</v>
+        <v>3226</v>
       </c>
       <c r="N133" t="n">
-        <v>237</v>
-      </c>
-      <c r="O133" t="n">
-        <v>206.7</v>
+        <v>3523</v>
+      </c>
+      <c r="P133" t="n">
+        <v>12.9</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -4994,7 +5153,12 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第三节北京长城无线电厂</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>国营第6971厂</t>
         </is>
       </c>
       <c r="T133" t="n">
@@ -5002,24 +5166,27 @@
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>朝阳</t>
+          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>北京广播器材厂</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>广播发射机、电视发射机、电视差转机、盒式录像机</t>
-        </is>
+          <t>北京核仪器厂</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>19560000</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>19500601北京人民广播器材厂</t>
+          <t>当时的北京市电器厂、北京市钻探机械厂、北京市公私合营电话器材厂和亚细亚商行喇叭组四单位合并-&gt;北京市综合仪器厂-&gt;19620000划归第二机械工业部-&gt;19630000二机部北京第十研究所合并</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5029,45 +5196,45 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>今四环胡同4号</t>
+          <t>东环北路42号</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>3486</v>
+        <v>1307</v>
       </c>
       <c r="J134" t="n">
-        <v>783</v>
+        <v>348</v>
       </c>
       <c r="L134" t="n">
-        <v>227200</v>
-      </c>
-      <c r="M134" t="n">
-        <v>23900</v>
+        <v>181500</v>
       </c>
       <c r="N134" t="n">
-        <v>7904.9</v>
+        <v>2148</v>
+      </c>
+      <c r="O134" t="n">
+        <v>2201</v>
       </c>
       <c r="P134" t="n">
-        <v>683.6</v>
+        <v>287</v>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第九节北京广播器材厂</t>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第四节北京核仪器厂</t>
         </is>
       </c>
       <c r="T134" t="n">
         <v>1995</v>
       </c>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>西城</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>北京邮电通信设备厂</t>
+          <t>北京建中机器厂</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5075,18 +5242,8 @@
           <t>半导体</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>生产微波三大固体器件、微波三大固体器件</t>
-        </is>
-      </c>
       <c r="D135" t="n">
-        <v>19410900</v>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>组建了4个合资公司-&gt;1941年9月建立的华北电信电话股份有限公司</t>
-        </is>
+        <v>19561000</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -5095,26 +5252,23 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>将台路5号</t>
+          <t>酒仙桥万红路1号</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1367</v>
+        <v>1418</v>
       </c>
       <c r="J135" t="n">
-        <v>724</v>
+        <v>290</v>
       </c>
       <c r="L135" t="n">
-        <v>86000</v>
-      </c>
-      <c r="M135" t="n">
-        <v>8359.4</v>
+        <v>133700</v>
       </c>
       <c r="N135" t="n">
-        <v>7489</v>
+        <v>4348.8</v>
       </c>
       <c r="P135" t="n">
-        <v>189</v>
+        <v>138.5</v>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
@@ -5123,12 +5277,12 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二章中央在京电子工业企业·第一节北京邮电通信设备厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第一节北京建中机器厂</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>邮电506厂</t>
+          <t>国营第700厂</t>
         </is>
       </c>
       <c r="T135" t="n">
@@ -5143,17 +5297,15 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>北京通信元件厂</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>半导体</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>半导体器件、高反压复合场效应晶体管、和销售BP机</t>
+          <t>北京市电声器材总厂</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>北京扬声器厂、北京无线电元件十四厂、北京广播电视配件四厂合并</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5163,55 +5315,45 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>新街口外大街28号</t>
-        </is>
+          <t>广安门内德泉胡同10号</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>722</v>
       </c>
       <c r="J136" t="n">
-        <v>450</v>
+        <v>39</v>
       </c>
       <c r="L136" t="n">
-        <v>70000</v>
+        <v>48500</v>
       </c>
       <c r="M136" t="n">
-        <v>3040.9</v>
+        <v>3087</v>
       </c>
       <c r="N136" t="n">
-        <v>4423.4</v>
-      </c>
-      <c r="O136" t="n">
-        <v>12000</v>
+        <v>1165</v>
       </c>
       <c r="P136" t="n">
-        <v>360</v>
-      </c>
-      <c r="Q136" t="inlineStr">
-        <is>
-          <t>行业据正文用词</t>
-        </is>
+        <v>48.2</v>
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二章中央在京电子工业企业·第二节邮电部北京通信元件厂</t>
-        </is>
-      </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>邮电508厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十节北京市电声器材总厂</t>
         </is>
       </c>
       <c r="T136" t="n">
-        <v>1990</v>
+        <v>1995</v>
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>西城</t>
+          <t>宣武</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>北京长城无线电厂</t>
+          <t>北京市无线电元件一厂</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5219,9 +5361,12 @@
           <t>电子计算机</t>
         </is>
       </c>
+      <c r="D137" t="n">
+        <v>19680000</v>
+      </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>19740000下放北京市</t>
+          <t>19640000改名北京竹藤制品厂-&gt;19680000改名北京市无线电元件一厂</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5231,23 +5376,26 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>学院南路34号</t>
+          <t>德胜门外后九条小市口胡同1号</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>790</v>
+        <v>448</v>
+      </c>
+      <c r="J137" t="n">
+        <v>52</v>
       </c>
       <c r="L137" t="n">
-        <v>36300</v>
+        <v>11500</v>
       </c>
       <c r="M137" t="n">
-        <v>3226</v>
+        <v>2209.8</v>
       </c>
       <c r="N137" t="n">
-        <v>3523</v>
+        <v>910.3</v>
       </c>
       <c r="P137" t="n">
-        <v>12.9</v>
+        <v>93.8</v>
       </c>
       <c r="Q137" t="inlineStr">
         <is>
@@ -5256,12 +5404,7 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二章中央在京电子工业企业·第三节北京长城无线电厂</t>
-        </is>
-      </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>国营第6971厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十一节北京市无线电元件一厂</t>
         </is>
       </c>
       <c r="T137" t="n">
@@ -5269,27 +5412,22 @@
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>海淀</t>
+          <t>西城</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>北京核仪器厂</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>半导体</t>
+          <t>北京无线电元件四厂</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>19560000</v>
+        <v>19670000</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>当时的北京市电器厂、北京市钻探机械厂、北京市公私合营电话器材厂和亚细亚商行喇叭组四单位合并-&gt;北京市综合仪器厂-&gt;19620000划归第二机械工业部-&gt;19630000二机部北京第十研究所合并</t>
+          <t>北京市石景山电容器厂-&gt;19780000划归北京市仪表工业局-&gt;19790000改名北京无线电元件四厂</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -5299,54 +5437,64 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>东环北路42号</t>
+          <t>古城北路甲4号</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1307</v>
+        <v>511</v>
       </c>
       <c r="J138" t="n">
-        <v>348</v>
+        <v>51</v>
       </c>
       <c r="L138" t="n">
-        <v>181500</v>
+        <v>13700</v>
+      </c>
+      <c r="M138" t="n">
+        <v>2090.4</v>
       </c>
       <c r="N138" t="n">
-        <v>2148</v>
-      </c>
-      <c r="O138" t="n">
-        <v>2201</v>
+        <v>3054</v>
       </c>
       <c r="P138" t="n">
-        <v>287</v>
-      </c>
-      <c r="Q138" t="inlineStr">
-        <is>
-          <t>行业据正文用词</t>
-        </is>
+        <v>416.1</v>
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二章中央在京电子工业企业·第四节北京核仪器厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十三节北京无线电元件四厂</t>
         </is>
       </c>
       <c r="T138" t="n">
         <v>1995</v>
       </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>石景山</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>北京建中机器厂</t>
+          <t>北京市无线电元件六厂</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>计算机、收录机</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>19561000</v>
+        <v>19700100</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>19720300年8月与北京皮毛三厂合并-&gt;19790300并入北京市无线电元件六厂</t>
+        </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -5355,23 +5503,23 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>酒仙桥万红路1号</t>
+          <t>北京站东街10号</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1418</v>
+        <v>747</v>
       </c>
       <c r="J139" t="n">
-        <v>290</v>
+        <v>108</v>
       </c>
       <c r="L139" t="n">
-        <v>133700</v>
-      </c>
-      <c r="N139" t="n">
-        <v>4348.8</v>
+        <v>12600</v>
+      </c>
+      <c r="M139" t="n">
+        <v>1844.3</v>
       </c>
       <c r="P139" t="n">
-        <v>138.5</v>
+        <v>0.1</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -5380,12 +5528,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第一节北京建中机器厂</t>
-        </is>
-      </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>国营第700厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十四节北京市无线电元件六厂</t>
         </is>
       </c>
       <c r="T139" t="n">
@@ -5393,22 +5536,27 @@
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>朝阳</t>
+          <t>东城</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>北京市电声器材总厂</t>
+          <t>北京无线电元件九厂</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>19800000</v>
+        <v>19600000</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>北京扬声器厂、北京无线电元件十四厂、北京广播电视配件四厂合并</t>
+          <t>北京市东城区无线电元件厂-&gt;19620000改名北京无线电插接元件厂-&gt;19790000改名北京无线电元件九厂</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5418,30 +5566,38 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>广安门内德泉胡同10号</t>
+          <t>深沟村</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>722</v>
+        <v>785</v>
       </c>
       <c r="J140" t="n">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="L140" t="n">
-        <v>48500</v>
+        <v>51700</v>
       </c>
       <c r="M140" t="n">
-        <v>3087</v>
+        <v>3258.4</v>
       </c>
       <c r="N140" t="n">
-        <v>1165</v>
+        <v>3182</v>
+      </c>
+      <c r="O140" t="n">
+        <v>905.8</v>
       </c>
       <c r="P140" t="n">
-        <v>48.2</v>
+        <v>143.5</v>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十节北京市电声器材总厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十五节北京无线电元件九厂</t>
         </is>
       </c>
       <c r="T140" t="n">
@@ -5449,27 +5605,27 @@
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>宣武</t>
+          <t>朝阳</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>北京市无线电元件一厂</t>
+          <t>北京市半导体器件一厂</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>电子计算机</t>
+          <t>半导体</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>19680000</v>
+        <v>19650000</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>19640000改名北京竹藤制品厂-&gt;19680000改名北京市无线电元件一厂</t>
+          <t>组建的北京市无线电综合元件厂-&gt;19780600改名北京市半导体器件一厂</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5479,35 +5635,35 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>德胜门外后九条小市口胡同1号</t>
+          <t>幸福三村北街1号</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>448</v>
+        <v>874</v>
       </c>
       <c r="J141" t="n">
-        <v>52</v>
+        <v>192</v>
       </c>
       <c r="L141" t="n">
-        <v>11500</v>
+        <v>33700</v>
       </c>
       <c r="M141" t="n">
-        <v>2209.8</v>
+        <v>4427.5</v>
       </c>
       <c r="N141" t="n">
-        <v>910.3</v>
+        <v>889</v>
       </c>
       <c r="P141" t="n">
-        <v>93.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>行业据正文用词</t>
+          <t>行业据单位名</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十一节北京市无线电元件一厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十七节北京市半导体器件一厂</t>
         </is>
       </c>
       <c r="T141" t="n">
@@ -5515,22 +5671,35 @@
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>西城</t>
+          <t>朝阳</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>北京无线电元件四厂</t>
+          <t>北京市半导体器件三厂</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>错三极管、中高档电子琴音律发生器电路</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>19670000</v>
+        <v>19680000</v>
+      </c>
+      <c r="E142" t="n">
+        <v>19680000</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>北京市石景山电容器厂-&gt;19780000划归北京市仪表工业局-&gt;19790000改名北京无线电元件四厂</t>
+          <t>北京市第二轻工业局所属的金漆厂、玉器厂和象牙厂合并-&gt;19730900划归北京市位器仪表工业局领导后</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5540,30 +5709,32 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>古城北路甲4号</t>
+          <t>龙潭路3号</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>511</v>
+        <v>813</v>
       </c>
       <c r="J142" t="n">
-        <v>51</v>
+        <v>126</v>
       </c>
       <c r="L142" t="n">
-        <v>13700</v>
-      </c>
-      <c r="M142" t="n">
-        <v>2090.4</v>
+        <v>40500</v>
       </c>
       <c r="N142" t="n">
-        <v>3054</v>
+        <v>1058.8</v>
       </c>
       <c r="P142" t="n">
-        <v>416.1</v>
+        <v>83.7</v>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>行业据单位名</t>
+        </is>
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十三节北京无线电元件四厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十八节北京市半导体器件三厂</t>
         </is>
       </c>
       <c r="T142" t="n">
@@ -5571,32 +5742,27 @@
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>石景山</t>
+          <t>崇文</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>北京市无线电元件六厂</t>
+          <t>北京半导体器件五厂</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>电子计算机</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>计算机、收录机</t>
+          <t>半导体</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>19700100</v>
+        <v>19690900</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>19720300年8月与北京皮毛三厂合并-&gt;19790300并入北京市无线电元件六厂</t>
+          <t>北京市西城区半导体器件厂-&gt;19780400改名北京半导体器件五厂</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -5606,32 +5772,35 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>北京站东街10号</t>
+          <t>德胜门外五路通14号</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>747</v>
+        <v>635</v>
       </c>
       <c r="J143" t="n">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="L143" t="n">
-        <v>12600</v>
-      </c>
-      <c r="M143" t="n">
-        <v>1844.3</v>
+        <v>21000</v>
+      </c>
+      <c r="N143" t="n">
+        <v>1141</v>
+      </c>
+      <c r="O143" t="n">
+        <v>1466</v>
       </c>
       <c r="P143" t="n">
-        <v>0.1</v>
+        <v>89.8</v>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>行业据正文用词</t>
+          <t>行业据单位名</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十四节北京市无线电元件六厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十九节北京半导体器件五厂</t>
         </is>
       </c>
       <c r="T143" t="n">
@@ -5639,27 +5808,27 @@
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>东城</t>
+          <t>西城</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>北京无线电元件九厂</t>
+          <t>北京市半导体器件六厂</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>电子计算机</t>
+          <t>半导体</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>19600000</v>
+        <v>19800000</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>北京市东城区无线电元件厂-&gt;19620000改名北京无线电插接元件厂-&gt;19790000改名北京无线电元件九厂</t>
+          <t>合并后的器件六厂-&gt;原北京市半导体器件六厂与北京市半导体器件七厂合并</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -5667,40 +5836,34 @@
           <t>Beijing</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>深沟村</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>785</v>
+        <v>482</v>
       </c>
       <c r="J144" t="n">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="L144" t="n">
-        <v>51700</v>
-      </c>
-      <c r="M144" t="n">
-        <v>3258.4</v>
+        <v>10600</v>
       </c>
       <c r="N144" t="n">
-        <v>3182</v>
-      </c>
-      <c r="O144" t="n">
-        <v>905.8</v>
+        <v>4546</v>
       </c>
       <c r="P144" t="n">
-        <v>143.5</v>
+        <v>97.8</v>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>行业据正文用词</t>
+          <t>行业据单位名</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十五节北京无线电元件九厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第四十节北京市半导体器件六厂</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>半导体器件六厂</t>
         </is>
       </c>
       <c r="T144" t="n">
@@ -5708,14 +5871,14 @@
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>朝阳</t>
+          <t>宣武</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>北京市半导体器件一厂</t>
+          <t>北京市可控硅元件厂</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5724,11 +5887,11 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>19650000</v>
+        <v>19680000</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>组建的北京市无线电综合元件厂-&gt;19780600改名北京市半导体器件一厂</t>
+          <t>北京市朝阳可控硅元件厂-&gt;19680000改名朝外大街乒乓球拍厂-&gt;19780000改名北京半导体材料加工厂</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -5738,26 +5901,26 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>幸福三村北街1号</t>
+          <t>建国门外砖厂胡同12号</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>874</v>
+        <v>292</v>
       </c>
       <c r="J145" t="n">
-        <v>192</v>
+        <v>27</v>
       </c>
       <c r="L145" t="n">
-        <v>33700</v>
-      </c>
-      <c r="M145" t="n">
-        <v>4427.5</v>
+        <v>16500</v>
       </c>
       <c r="N145" t="n">
-        <v>889</v>
+        <v>456</v>
+      </c>
+      <c r="O145" t="n">
+        <v>350.1</v>
       </c>
       <c r="P145" t="n">
-        <v>78.40000000000001</v>
+        <v>19.4</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
@@ -5766,22 +5929,17 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十七节北京市半导体器件一厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第四十一节北京市可控硅元件厂</t>
         </is>
       </c>
       <c r="T145" t="n">
         <v>1995</v>
       </c>
-      <c r="U145" t="inlineStr">
-        <is>
-          <t>朝阳</t>
-        </is>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>北京市半导体器件三厂</t>
+          <t>北京701厂</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5791,18 +5949,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>错三极管、中高档电子琴音律发生器电路</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>19680000</v>
-      </c>
-      <c r="E146" t="n">
-        <v>19680000</v>
+          <t>微波二极管</t>
+        </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>北京市第二轻工业局所属的金漆厂、玉器厂和象牙厂合并-&gt;19730900划归北京市位器仪表工业局领导后</t>
+          <t>19700000第四机械工业部-&gt;19790000朝阳器件厂合并</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -5812,60 +5964,66 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>龙潭路3号</t>
+          <t>双桥西里7号</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>813</v>
+        <v>832</v>
       </c>
       <c r="J146" t="n">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="L146" t="n">
-        <v>40500</v>
+        <v>21800</v>
+      </c>
+      <c r="M146" t="n">
+        <v>1885.1</v>
       </c>
       <c r="N146" t="n">
-        <v>1058.8</v>
+        <v>1947</v>
+      </c>
+      <c r="O146" t="n">
+        <v>1754.9</v>
       </c>
       <c r="P146" t="n">
-        <v>83.7</v>
+        <v>12</v>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>行业据单位名</t>
+          <t>行业据正文用词</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十八节北京市半导体器件三厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第四十二节北京七〇一厂</t>
         </is>
       </c>
       <c r="T146" t="n">
         <v>1995</v>
       </c>
-      <c r="U146" t="inlineStr">
-        <is>
-          <t>崇文</t>
-        </is>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>北京半导体器件五厂</t>
+          <t>北京无线电工具设备厂</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>外围设备</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>球磨机、油压机、游丝辗压机、自动刺铆机</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>19690900</v>
+        <v>19640000</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>北京市西城区半导体器件厂-&gt;19780400改名北京半导体器件五厂</t>
+          <t>合并组建为北京无线电工具设备厂</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -5875,35 +6033,34 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>德胜门外五路通14号</t>
+          <t>酒仙桥路2号</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>635</v>
+        <v>1269</v>
       </c>
       <c r="J147" t="n">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="L147" t="n">
-        <v>21000</v>
-      </c>
-      <c r="N147" t="n">
-        <v>1141</v>
-      </c>
-      <c r="O147" t="n">
-        <v>1466</v>
-      </c>
-      <c r="P147" t="n">
-        <v>89.8</v>
+        <v>107000</v>
+      </c>
+      <c r="M147" t="n">
+        <v>5295.9</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>行业据单位名</t>
+          <t>行业据正文用词</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十九节北京半导体器件五厂</t>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第二节北京无线电工具设备厂</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>国营第706厂</t>
         </is>
       </c>
       <c r="T147" t="n">
@@ -5911,27 +6068,27 @@
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>西城</t>
+          <t>朝阳</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>北京市半导体器件六厂</t>
+          <t>北京晨星无线电器材厂</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>电子计算机</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>19800000</v>
+        <v>19500000</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>合并后的器件六厂-&gt;原北京市半导体器件六厂与北京市半导体器件七厂合并</t>
+          <t>19590000并入华北无线电器材联合厂为七分厂</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -5939,29 +6096,36 @@
           <t>Beijing</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>酒仙桥路2号</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>482</v>
-      </c>
-      <c r="J148" t="n">
-        <v>71</v>
+        <v>1513</v>
       </c>
       <c r="L148" t="n">
-        <v>10600</v>
+        <v>49100</v>
       </c>
       <c r="N148" t="n">
-        <v>4546</v>
+        <v>8709.5</v>
       </c>
       <c r="P148" t="n">
-        <v>97.8</v>
+        <v>130.9</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>行业据单位名</t>
+          <t>行业据正文用词</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第四十节北京市半导体器件六厂</t>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第三节北京晨星无线电器材厂</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>国营第707厂</t>
         </is>
       </c>
       <c r="T148" t="n">
@@ -5969,27 +6133,32 @@
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>宣武</t>
+          <t>朝阳</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>北京市可控硅元件厂</t>
+          <t>北京北大方正集团公司</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>制造的5大系列电脑</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>19680000</v>
+        <v>19860000</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>北京市朝阳可控硅元件厂-&gt;19680000改名朝外大街乒乓球拍厂-&gt;19780000改名北京半导体材料加工厂</t>
+          <t>北京大学新技术公司</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -5997,62 +6166,68 @@
           <t>Beijing</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>建国门外砖厂胡同12号</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>292</v>
+        <v>672</v>
       </c>
       <c r="J149" t="n">
-        <v>27</v>
+        <v>404</v>
       </c>
       <c r="L149" t="n">
-        <v>16500</v>
+        <v>12000</v>
+      </c>
+      <c r="M149" t="n">
+        <v>4217.4</v>
       </c>
       <c r="N149" t="n">
-        <v>456</v>
+        <v>13200</v>
       </c>
       <c r="O149" t="n">
-        <v>350.1</v>
+        <v>84700</v>
       </c>
       <c r="P149" t="n">
-        <v>19.4</v>
+        <v>9443.1</v>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>行业据单位名</t>
+          <t>行业据正文用词</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第四十一节北京市可控硅元件厂</t>
+          <t>北京工业志·电子志·第三章行业归口电子工业企业·第三节北京北大方正集团公司</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>北大方正集团公司</t>
         </is>
       </c>
       <c r="T149" t="n">
         <v>1995</v>
       </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>北京701厂</t>
+          <t>北京京海集团公司</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>半导体</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>微波二极管</t>
-        </is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>19830700</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>19700000第四机械工业部-&gt;19790000朝阳器件厂合并</t>
+          <t>计算机机房技术开发公司</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -6062,29 +6237,23 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>双桥西里7号</t>
+          <t>白石桥络33号</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>832</v>
+        <v>727</v>
       </c>
       <c r="J150" t="n">
-        <v>114</v>
+        <v>349</v>
       </c>
       <c r="L150" t="n">
-        <v>21800</v>
+        <v>2268</v>
       </c>
       <c r="M150" t="n">
-        <v>1885.1</v>
-      </c>
-      <c r="N150" t="n">
-        <v>1947</v>
+        <v>8674</v>
       </c>
       <c r="O150" t="n">
-        <v>1754.9</v>
-      </c>
-      <c r="P150" t="n">
-        <v>12</v>
+        <v>45599.99999999999</v>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
@@ -6093,36 +6262,31 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第四十二节北京七〇一厂</t>
+          <t>北京工业志·电子志·第三章行业归口电子工业企业·第四节北京京海集团公司</t>
         </is>
       </c>
       <c r="T150" t="n">
         <v>1995</v>
       </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>北京无线电工具设备厂</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>外围设备</t>
+          <t>北京·松下彩色显像管有限公司</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>球磨机、油压机、游丝辗压机、自动刺铆机</t>
+          <t>14型球面彩色显像管、线并行生产两个品种的彩管、两个品种的彩管</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>19640000</v>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>合并组建为北京无线电工具设备厂</t>
-        </is>
+        <v>19870900</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -6131,34 +6295,35 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>酒仙桥路2号</t>
+          <t>酒仙桥北路9号</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1269</v>
+        <v>4180</v>
       </c>
       <c r="J151" t="n">
-        <v>123</v>
+        <v>570</v>
       </c>
       <c r="L151" t="n">
-        <v>107000</v>
+        <v>136000</v>
       </c>
       <c r="M151" t="n">
-        <v>5295.9</v>
-      </c>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>行业据正文用词</t>
-        </is>
+        <v>159200</v>
+      </c>
+      <c r="N151" t="n">
+        <v>274300</v>
+      </c>
+      <c r="P151" t="n">
+        <v>12020</v>
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二章中央在京电子工业企业·第二节北京无线电工具设备厂</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第一节北京·松下彩色显像管有限公司</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>国营第706厂</t>
+          <t>BMCC</t>
         </is>
       </c>
       <c r="T151" t="n">
@@ -6173,21 +6338,16 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>北京晨星无线电器材厂</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>电子计算机</t>
+          <t>北京飞利浦有限公司</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>经营值携式收录机</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>19500000</v>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>19590000并入华北无线电器材联合厂为七分厂</t>
-        </is>
+        <v>19850810</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -6196,34 +6356,33 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>酒仙桥路2号</t>
+          <t>北洼路4号</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1513</v>
+        <v>647</v>
+      </c>
+      <c r="J152" t="n">
+        <v>85</v>
       </c>
       <c r="L152" t="n">
-        <v>49100</v>
+        <v>8000</v>
+      </c>
+      <c r="M152" t="n">
+        <v>2187.9</v>
       </c>
       <c r="N152" t="n">
-        <v>8709.5</v>
+        <v>33000</v>
+      </c>
+      <c r="O152" t="n">
+        <v>21800</v>
       </c>
       <c r="P152" t="n">
-        <v>130.9</v>
-      </c>
-      <c r="Q152" t="inlineStr">
-        <is>
-          <t>行业据正文用词</t>
-        </is>
+        <v>1021.5</v>
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二章中央在京电子工业企业·第三节北京晨星无线电器材厂</t>
-        </is>
-      </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>国营第707厂</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第三节北京飞利浦有限公司</t>
         </is>
       </c>
       <c r="T152" t="n">
@@ -6231,14 +6390,14 @@
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>朝阳</t>
+          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>北京北大方正集团公司</t>
+          <t>中国惠普有限公司</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6248,42 +6407,36 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>制造的5大系列电脑</t>
+          <t>经营业务范围包括计算机系统及微机</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>19860000</v>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>北京大学新技术公司</t>
-        </is>
+        <v>19850600</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>建国门外东三环南路2号</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>672</v>
+        <v>585</v>
       </c>
       <c r="J153" t="n">
-        <v>404</v>
-      </c>
-      <c r="L153" t="n">
-        <v>12000</v>
+        <v>358</v>
       </c>
       <c r="M153" t="n">
-        <v>4217.4</v>
+        <v>8758.299999999999</v>
       </c>
       <c r="N153" t="n">
-        <v>13200</v>
-      </c>
-      <c r="O153" t="n">
-        <v>84700</v>
+        <v>3763</v>
       </c>
       <c r="P153" t="n">
-        <v>9443.1</v>
+        <v>32700</v>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
@@ -6292,7 +6445,12 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章行业归口电子工业企业·第三节北京北大方正集团公司</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第四节中国惠普有限公司</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>CHP</t>
         </is>
       </c>
       <c r="T153" t="n">
@@ -6300,14 +6458,14 @@
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>海淀</t>
+          <t>朝阳</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>北京京海集团公司</t>
+          <t>北京有线电总厂</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6315,12 +6473,17 @@
           <t>电子计算机</t>
         </is>
       </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>生产步进制自动电话交换机、步进制自动电话交换机、生产纵横制自动电话交换机、纵横制自动电话交换机</t>
+        </is>
+      </c>
       <c r="D154" t="n">
-        <v>19830700</v>
+        <v>19570900</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>计算机机房技术开发公司</t>
+          <t>北京有线电厂</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -6330,23 +6493,23 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>白石桥络33号</t>
+          <t>酒仙桥路14号</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>727</v>
-      </c>
-      <c r="J154" t="n">
-        <v>349</v>
+        <v>3259</v>
       </c>
       <c r="L154" t="n">
-        <v>2268</v>
+        <v>321700</v>
       </c>
       <c r="M154" t="n">
-        <v>8674</v>
-      </c>
-      <c r="O154" t="n">
-        <v>45599.99999999999</v>
+        <v>18700</v>
+      </c>
+      <c r="N154" t="n">
+        <v>54800.00000000001</v>
+      </c>
+      <c r="P154" t="n">
+        <v>3202</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
@@ -6355,7 +6518,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章行业归口电子工业企业·第四节北京京海集团公司</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第七节北京有线电总厂</t>
         </is>
       </c>
       <c r="T154" t="n">
@@ -6363,60 +6526,54 @@
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t>海淀</t>
+          <t>朝阳</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>北京·松下彩色显像管有限公司</t>
+          <t>北京·松下电子部品有限公司</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>14型球面彩色显像管、线并行生产两个品种的彩管、两个品种的彩管</t>
+          <t>销售电视机</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>19870900</v>
+        <v>19930900</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>酒仙桥北路9号</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>4180</v>
+        <v>720</v>
       </c>
       <c r="J155" t="n">
-        <v>570</v>
+        <v>130</v>
       </c>
       <c r="L155" t="n">
-        <v>136000</v>
-      </c>
-      <c r="M155" t="n">
-        <v>159200</v>
+        <v>19600</v>
       </c>
       <c r="N155" t="n">
-        <v>274300</v>
-      </c>
-      <c r="P155" t="n">
-        <v>12020</v>
+        <v>30900</v>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第一节北京·松下彩色显像管有限公司</t>
-        </is>
-      </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>BMCC</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第六节北京·松下电子部品有限公司</t>
         </is>
       </c>
       <c r="T155" t="n">
@@ -6431,16 +6588,21 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>北京飞利浦有限公司</t>
+          <t>北京第一无线电器材厂</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>半导体</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>经营值携式收录机</t>
+          <t>电子节能灯等显示管、收录音机</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>19850810</v>
+        <v>19571000</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -6449,33 +6611,37 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>北洼路4号</t>
+          <t>酒仙桥路2号</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>647</v>
+        <v>2050</v>
       </c>
       <c r="J156" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="L156" t="n">
-        <v>8000</v>
-      </c>
-      <c r="M156" t="n">
-        <v>2187.9</v>
+        <v>120000</v>
       </c>
       <c r="N156" t="n">
-        <v>33000</v>
-      </c>
-      <c r="O156" t="n">
-        <v>21800</v>
+        <v>3771</v>
       </c>
       <c r="P156" t="n">
-        <v>1021.5</v>
+        <v>163.8</v>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第三节北京飞利浦有限公司</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第四节北京第一无线电器材厂</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>国营第797厂</t>
         </is>
       </c>
       <c r="T156" t="n">
@@ -6483,28 +6649,23 @@
       </c>
       <c r="U156" t="inlineStr">
         <is>
-          <t>海淀</t>
+          <t>朝阳</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>中国惠普有限公司</t>
+          <t>北京第二无线电器材厂</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>电子计算机</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>经营业务范围包括计算机系统及微机</t>
+          <t>半导体</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>19850600</v>
+        <v>19640000</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -6513,23 +6674,26 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>建国门外东三环南路2号</t>
+          <t>酒仙桥路4号</t>
         </is>
       </c>
       <c r="I157" t="n">
-        <v>585</v>
+        <v>1529</v>
       </c>
       <c r="J157" t="n">
-        <v>358</v>
+        <v>67</v>
+      </c>
+      <c r="L157" t="n">
+        <v>104100</v>
       </c>
       <c r="M157" t="n">
-        <v>8758.299999999999</v>
+        <v>10000</v>
       </c>
       <c r="N157" t="n">
-        <v>3763</v>
+        <v>3686</v>
       </c>
       <c r="P157" t="n">
-        <v>32700</v>
+        <v>111.3</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
@@ -6538,12 +6702,12 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第四节中国惠普有限公司</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第五节北京第二无线电器材厂</t>
         </is>
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>CHP</t>
+          <t>国营第718厂</t>
         </is>
       </c>
       <c r="T157" t="n">
@@ -6558,26 +6722,16 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>北京有线电总厂</t>
+          <t>北京电子动力公司</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>电子计算机</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>生产步进制自动电话交换机、步进制自动电话交换机、生产纵横制自动电话交换机、纵横制自动电话交换机</t>
+          <t>半导体</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>19570900</v>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>北京有线电厂</t>
-        </is>
+        <v>19570000</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -6586,23 +6740,23 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>酒仙桥路14号</t>
+          <t>酒仙桥路4号</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>3259</v>
+        <v>2847</v>
+      </c>
+      <c r="J158" t="n">
+        <v>237</v>
       </c>
       <c r="L158" t="n">
-        <v>321700</v>
-      </c>
-      <c r="M158" t="n">
-        <v>18700</v>
+        <v>319000</v>
       </c>
       <c r="N158" t="n">
-        <v>54800.00000000001</v>
+        <v>11900</v>
       </c>
       <c r="P158" t="n">
-        <v>3202</v>
+        <v>366</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -6611,7 +6765,12 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第七节北京有线电总厂</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第八节北京电子动力公司</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>国营第751厂</t>
         </is>
       </c>
       <c r="T158" t="n">
@@ -6626,38 +6785,52 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>北京·松下电子部品有限公司</t>
+          <t>北京大华无线电仪器厂</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>电子计算机</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>销售电视机</t>
+          <t>半导体</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>19930900</v>
+        <v>19580800</v>
+      </c>
+      <c r="E159" t="n">
+        <v>19841200</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>北京微技测量仪器厂</t>
+        </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>学院路5号</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>720</v>
+        <v>1258</v>
       </c>
       <c r="J159" t="n">
-        <v>130</v>
+        <v>298</v>
       </c>
       <c r="L159" t="n">
-        <v>19600</v>
-      </c>
-      <c r="N159" t="n">
-        <v>30900</v>
+        <v>192000</v>
+      </c>
+      <c r="M159" t="n">
+        <v>742.6</v>
+      </c>
+      <c r="O159" t="n">
+        <v>2282.7</v>
+      </c>
+      <c r="P159" t="n">
+        <v>624.2</v>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
@@ -6666,7 +6839,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第六节北京·松下电子部品有限公司</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第十节北京大华无线电仪器厂</t>
         </is>
       </c>
       <c r="T159" t="n">
@@ -6674,14 +6847,14 @@
       </c>
       <c r="U159" t="inlineStr">
         <is>
-          <t>朝阳</t>
+          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>北京第一无线电器材厂</t>
+          <t>北京东方电子集团股份有限公司</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -6691,11 +6864,16 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>电子节能灯等显示管、收录音机</t>
+          <t>18种电子管</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>19571000</v>
+        <v>19520000</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>19920618组建了北京东方电子集团公司-&gt;19930408组建为北京东方电子集团股份有限公司</t>
+        </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -6704,23 +6882,17 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>酒仙桥路2号</t>
-        </is>
-      </c>
-      <c r="I160" t="n">
-        <v>2050</v>
-      </c>
-      <c r="J160" t="n">
-        <v>77</v>
+          <t>酒仙桥路10号</t>
+        </is>
       </c>
       <c r="L160" t="n">
-        <v>120000</v>
-      </c>
-      <c r="N160" t="n">
-        <v>3771</v>
+        <v>320000</v>
+      </c>
+      <c r="M160" t="n">
+        <v>25000</v>
       </c>
       <c r="P160" t="n">
-        <v>163.8</v>
+        <v>1859</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
@@ -6729,12 +6901,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第四节北京第一无线电器材厂</t>
-        </is>
-      </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>国营第797厂</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第十一节 北京东方电子集团股份有限公司</t>
         </is>
       </c>
       <c r="T160" t="n">
@@ -6749,7 +6916,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>北京第二无线电器材厂</t>
+          <t>北京飞行电子总公司</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -6760,6 +6927,11 @@
       <c r="D161" t="n">
         <v>19640000</v>
       </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>19571000北京第三无线电器材厂</t>
+        </is>
+      </c>
       <c r="G161" t="inlineStr">
         <is>
           <t>Beijing</t>
@@ -6771,22 +6943,22 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1529</v>
+        <v>2639</v>
       </c>
       <c r="J161" t="n">
-        <v>67</v>
+        <v>285</v>
       </c>
       <c r="L161" t="n">
-        <v>104100</v>
+        <v>211700</v>
       </c>
       <c r="M161" t="n">
-        <v>10000</v>
+        <v>13600</v>
       </c>
       <c r="N161" t="n">
-        <v>3686</v>
+        <v>8188</v>
       </c>
       <c r="P161" t="n">
-        <v>111.3</v>
+        <v>45.8</v>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
@@ -6795,12 +6967,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第五节北京第二无线电器材厂</t>
-        </is>
-      </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>国营第718厂</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第六节北京飞行电子总公司</t>
         </is>
       </c>
       <c r="T161" t="n">
@@ -6815,41 +6982,30 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>北京电子动力公司</t>
+          <t>北京市电镀总厂</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>电子计算机</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>19570000</v>
+        <v>19580000</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>酒仙桥路4号</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>2847</v>
+        <v>488</v>
       </c>
       <c r="J162" t="n">
-        <v>237</v>
+        <v>20</v>
       </c>
       <c r="L162" t="n">
-        <v>319000</v>
-      </c>
-      <c r="N162" t="n">
-        <v>11900</v>
-      </c>
-      <c r="P162" t="n">
-        <v>366</v>
+        <v>24800</v>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
@@ -6858,12 +7014,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第八节北京电子动力公司</t>
-        </is>
-      </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>国营第751厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第二十九节北京市电镀总厂</t>
         </is>
       </c>
       <c r="T162" t="n">
@@ -6878,24 +7029,11 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>北京大华无线电仪器厂</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>半导体</t>
+          <t>北京市无线电元件二厂</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>19580800</v>
-      </c>
-      <c r="E163" t="n">
-        <v>19841200</v>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>北京微技测量仪器厂</t>
-        </is>
+        <v>19681200</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -6904,35 +7042,33 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>学院路5号</t>
+          <t>德胜门外塔院胡同8号</t>
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1258</v>
+        <v>540</v>
       </c>
       <c r="J163" t="n">
-        <v>298</v>
+        <v>58</v>
       </c>
       <c r="L163" t="n">
-        <v>192000</v>
+        <v>4887</v>
       </c>
       <c r="M163" t="n">
-        <v>742.6</v>
+        <v>1796.9</v>
+      </c>
+      <c r="N163" t="n">
+        <v>1614</v>
       </c>
       <c r="O163" t="n">
-        <v>2282.7</v>
+        <v>989.1</v>
       </c>
       <c r="P163" t="n">
-        <v>624.2</v>
-      </c>
-      <c r="Q163" t="inlineStr">
-        <is>
-          <t>行业据正文用词</t>
-        </is>
+        <v>79.59999999999999</v>
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第十节北京大华无线电仪器厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十二节北京市无线电元件二厂</t>
         </is>
       </c>
       <c r="T163" t="n">
@@ -6940,33 +7076,18 @@
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>海淀</t>
+          <t>西城</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>北京东方电子集团股份有限公司</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>半导体</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>18种电子管</t>
+          <t>北京市无线电元件十厂</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>19520000</v>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>19920618组建了北京东方电子集团公司-&gt;19930408组建为北京东方电子集团股份有限公司</t>
-        </is>
+        <v>19710000</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -6975,41 +7096,40 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>酒仙桥路10号</t>
-        </is>
+          <t>朝阳门外二条67号</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>654</v>
+      </c>
+      <c r="J164" t="n">
+        <v>32</v>
       </c>
       <c r="L164" t="n">
-        <v>320000</v>
+        <v>56300</v>
       </c>
       <c r="M164" t="n">
-        <v>25000</v>
+        <v>3673</v>
+      </c>
+      <c r="N164" t="n">
+        <v>4742</v>
       </c>
       <c r="P164" t="n">
-        <v>1859</v>
-      </c>
-      <c r="Q164" t="inlineStr">
-        <is>
-          <t>行业据正文用词</t>
-        </is>
+        <v>54.8</v>
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第十一节 北京东方电子集团股份有限公司</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十六节北京市无线电元件十厂</t>
         </is>
       </c>
       <c r="T164" t="n">
         <v>1995</v>
       </c>
-      <c r="U164" t="inlineStr">
-        <is>
-          <t>朝阳</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>北京飞行电子总公司</t>
+          <t>北京国兴电子有限公司</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -7018,40 +7138,24 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>19640000</v>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>19571000北京第三无线电器材厂</t>
-        </is>
+        <v>19880400</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>酒仙桥路4号</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>2639</v>
+        <v>775</v>
       </c>
       <c r="J165" t="n">
-        <v>285</v>
+        <v>132</v>
       </c>
       <c r="L165" t="n">
-        <v>211700</v>
-      </c>
-      <c r="M165" t="n">
-        <v>13600</v>
+        <v>10400</v>
       </c>
       <c r="N165" t="n">
-        <v>8188</v>
-      </c>
-      <c r="P165" t="n">
-        <v>45.8</v>
+        <v>10400</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
@@ -7060,7 +7164,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第六节北京飞行电子总公司</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第二节北京国兴电子有限公司</t>
         </is>
       </c>
       <c r="T165" t="n">
@@ -7068,46 +7172,55 @@
       </c>
       <c r="U165" t="inlineStr">
         <is>
-          <t>朝阳</t>
+          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>北京市电镀总厂</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>电子计算机</t>
+          <t>北京国际交换系统有限公司</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>19580000</v>
+        <v>19901100</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>酒仙桥路14号</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>488</v>
+        <v>1108</v>
       </c>
       <c r="J166" t="n">
-        <v>20</v>
+        <v>404</v>
       </c>
       <c r="L166" t="n">
-        <v>24800</v>
+        <v>3929</v>
+      </c>
+      <c r="N166" t="n">
+        <v>110400</v>
+      </c>
+      <c r="O166" t="n">
+        <v>102300</v>
+      </c>
+      <c r="P166" t="n">
+        <v>24000</v>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>行业据正文用词</t>
+          <t>另有他年数字:floor=1990年</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第二十九节北京市电镀总厂</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第五节北京国际交换系统有限公司</t>
         </is>
       </c>
       <c r="T166" t="n">
@@ -7122,213 +7235,95 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>北京市无线电元件二厂</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>19681200</v>
+          <t>北京电视机厂</t>
+        </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>德胜门外塔院胡同8号</t>
-        </is>
-      </c>
-      <c r="I167" t="n">
-        <v>540</v>
-      </c>
-      <c r="J167" t="n">
-        <v>58</v>
-      </c>
-      <c r="L167" t="n">
-        <v>4887</v>
-      </c>
-      <c r="M167" t="n">
-        <v>1796.9</v>
-      </c>
-      <c r="N167" t="n">
-        <v>1614</v>
-      </c>
-      <c r="O167" t="n">
-        <v>989.1</v>
-      </c>
-      <c r="P167" t="n">
-        <v>79.59999999999999</v>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及</t>
+        </is>
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十二节北京市无线电元件二厂</t>
-        </is>
-      </c>
-      <c r="T167" t="n">
-        <v>1995</v>
-      </c>
-      <c r="U167" t="inlineStr">
-        <is>
-          <t>西城</t>
+          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>北京市无线电元件十厂</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>19710000</v>
+          <t>北京电子显示设各厂</t>
+        </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>朝阳门外二条67号</t>
-        </is>
-      </c>
-      <c r="I168" t="n">
-        <v>654</v>
-      </c>
-      <c r="J168" t="n">
-        <v>32</v>
-      </c>
-      <c r="L168" t="n">
-        <v>56300</v>
-      </c>
-      <c r="M168" t="n">
-        <v>3673</v>
-      </c>
-      <c r="N168" t="n">
-        <v>4742</v>
-      </c>
-      <c r="P168" t="n">
-        <v>54.8</v>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>志中未见专条,仅由他条提及</t>
+        </is>
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十六节北京市无线电元件十厂</t>
-        </is>
-      </c>
-      <c r="T168" t="n">
-        <v>1995</v>
+          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
+        </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>北京国兴电子有限公司</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>半导体</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>19880400</v>
+          <t>北京市无线电元件三厂</t>
+        </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
-      <c r="I169" t="n">
-        <v>775</v>
-      </c>
-      <c r="J169" t="n">
-        <v>132</v>
-      </c>
-      <c r="L169" t="n">
-        <v>10400</v>
-      </c>
-      <c r="N169" t="n">
-        <v>10400</v>
-      </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>行业据正文用词</t>
+          <t>志中未见专条,仅由他条提及</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第二节北京国兴电子有限公司</t>
-        </is>
-      </c>
-      <c r="T169" t="n">
-        <v>1995</v>
-      </c>
-      <c r="U169" t="inlineStr">
-        <is>
-          <t>海淀</t>
+          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>北京国际交换系统有限公司</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>19901100</v>
+          <t>国营761厂</t>
+        </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>酒仙桥路14号</t>
-        </is>
-      </c>
-      <c r="I170" t="n">
-        <v>1108</v>
-      </c>
-      <c r="J170" t="n">
-        <v>404</v>
-      </c>
-      <c r="L170" t="n">
-        <v>3929</v>
-      </c>
-      <c r="N170" t="n">
-        <v>110400</v>
-      </c>
-      <c r="O170" t="n">
-        <v>102300</v>
-      </c>
-      <c r="P170" t="n">
-        <v>24000</v>
-      </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>另有他年数字:floor=1990年</t>
+          <t>志中未见专条,仅由他条提及</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第五节北京国际交换系统有限公司</t>
-        </is>
-      </c>
-      <c r="T170" t="n">
-        <v>1995</v>
-      </c>
-      <c r="U170" t="inlineStr">
-        <is>
-          <t>朝阳</t>
+          <t>北京工业志·电子志·第十四节北京电视设备厂</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>北京电视机厂</t>
+          <t>公私合营广播器材厂</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -7343,14 +7338,14 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
+          <t>北京工业志·电子志·第十五节北京无线电厂</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>北京电子显示设各厂</t>
+          <t>北京电子仪器厂</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -7365,14 +7360,14 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
+          <t>北京工业志·电子志·第十五节北京无线电厂</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>北京市无线电元件三厂</t>
+          <t>北京录音机厂</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -7387,14 +7382,14 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
+          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>国营761厂</t>
+          <t>北京鸿达电器公司</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -7409,14 +7404,14 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十四节北京电视设备厂</t>
+          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>公私合营广播器材厂</t>
+          <t>北京飞达电子有限公司</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -7431,14 +7426,19 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十五节北京无线电厂</t>
+          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>北京电子仪器厂</t>
+          <t>北京市半导体器件五厂</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>半导体</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -7448,19 +7448,19 @@
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>志中未见专条,仅由他条提及</t>
+          <t>志中未见专条,仅由他条提及；行业据单位名</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十五节北京无线电厂</t>
+          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>北京录音机厂</t>
+          <t>北京显像管厂</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -7475,14 +7475,14 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
+          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>北京鸿达电器公司</t>
+          <t>北京无线电电匣厂</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -7497,14 +7497,14 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
+          <t>北京工业志·电子志·第十九节北京广播电视配件一厂</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>北京飞达电子有限公司</t>
+          <t>北京安乐福塑料制品有限公司</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -7519,19 +7519,14 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
+          <t>北京工业志·电子志·第十九节北京广播电视配件一厂</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>北京市半导体器件五厂</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>半导体</t>
+          <t>北京松下彩色显像管有限公司</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -7541,19 +7536,19 @@
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>志中未见专条,仅由他条提及；行业据单位名</t>
+          <t>志中未见专条,仅由他条提及</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
+          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>北京显像管厂</t>
+          <t>北京无线电二厂</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -7568,14 +7563,14 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
+          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>北京无线电电匣厂</t>
+          <t>北京人民广播器材厂</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -7590,14 +7585,14 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十九节北京广播电视配件一厂</t>
+          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>北京安乐福塑料制品有限公司</t>
+          <t>华北无线电器材联合厂</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -7612,14 +7607,14 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十九节北京广播电视配件一厂</t>
+          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>北京松下彩色显像管有限公司</t>
+          <t>国营774厂</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -7634,14 +7629,14 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
+          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>北京无线电二厂</t>
+          <t>北京市综合仪器厂</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -7663,7 +7658,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>北京人民广播器材厂</t>
+          <t>北京铭信电子有限公司</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -7678,14 +7673,14 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十一节北京市无线电元件一厂</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>华北无线电器材联合厂</t>
+          <t>北京无线电插接元件厂</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -7700,14 +7695,14 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十五节北京无线电元件九厂</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>国营774厂</t>
+          <t>中国邮电工业总公司</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -7722,14 +7717,14 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第一节北京邮电通信设备厂</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>北京市综合仪器厂</t>
+          <t>海淀区学院</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -7744,14 +7739,14 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第三节北京长城无线电厂</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>北京铭信电子有限公司</t>
+          <t>中国烟草总公司</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -7766,14 +7761,14 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十一节北京市无线电元件一厂</t>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第三节北京长城无线电厂</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>北京无线电插接元件厂</t>
+          <t>北京第三无线电器材厂</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -7788,19 +7783,14 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十五节北京无线电元件九厂</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第六节北京飞行电子总公司</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>半导体器件六厂</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>半导体</t>
+          <t>北京旭硝子电子玻璃有限公司</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -7810,19 +7800,37 @@
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>志中未见专条,仅由他条提及；行业据单位名</t>
+          <t>未见专条,据行文点名</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第四十节北京市半导体器件六厂</t>
+          <t>北京工业志·电子志</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>中国邮电工业总公司</t>
+          <t>上海无线电十三厂</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>TQ一16中型通用数字集成电路计算机、J一101型计算机、专用电子计算机、TQ-21型数据处理机</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>19660600</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>19690200改名TQ一6型计算机</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -7832,20 +7840,33 @@
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>志中未见专条,仅由他条提及</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二章中央在京电子工业企业·第一节北京邮电通信设备厂</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>海淀区学院</t>
-        </is>
+          <t>上海长宁拉手厂</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>第二台709型计算机</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>19730000</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -7854,19 +7875,29 @@
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>志中未见专条,仅由他条提及</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二章中央在京电子工业企业·第三节北京长城无线电厂</t>
+          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>中国烟草总公司</t>
+          <t>上海长江电子计算机厂</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>CJ-801单板微型机</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -7876,19 +7907,29 @@
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>志中未见专条,仅由他条提及</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二章中央在京电子工业企业·第三节北京长城无线电厂</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>北京第三无线电器材厂</t>
+          <t>上海交通大学</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>DJS一053微型计算机、DJS一052E微型计算机、生产单板微型计算机、单板微型计算机</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -7898,59 +7939,64 @@
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>志中未见专条,仅由他条提及</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第六节北京飞行电子总公司</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>北京旭硝子电子玻璃有限公司</t>
-        </is>
+          <t>华东师范大学</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>19730000</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>北京工业志·电子志</t>
+          <t>上海电子仪表工业志·第一章电子计算机·1. 电子管计算机</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>上海华东师范大学</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>上海无线电十三厂</t>
+          <t>中国人民解放军总参谋部第五十六研究所</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>电子计算机</t>
+          <t>研究所</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>TQ一16中型通用数字集成电路计算机、J一101型计算机、专用电子计算机、TQ-21型数据处理机</t>
-        </is>
-      </c>
-      <c r="D198" t="n">
-        <v>19660600</v>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>19690200改名TQ一6型计算机</t>
+          <t>J一101型计算机</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -7960,19 +8006,19 @@
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>上海长宁拉手厂</t>
+          <t>上海工业大学</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -7980,14 +8026,6 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>第二台709型计算机</t>
-        </is>
-      </c>
-      <c r="D199" t="n">
-        <v>19730000</v>
-      </c>
       <c r="G199" t="inlineStr">
         <is>
           <t>Beijing</t>
@@ -8000,14 +8038,14 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>上海长江电子计算机厂</t>
+          <t>联合公司</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -8015,11 +8053,6 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>CJ-801单板微型机</t>
-        </is>
-      </c>
       <c r="G200" t="inlineStr">
         <is>
           <t>Beijing</t>
@@ -8027,7 +8060,7 @@
       </c>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
@@ -8039,7 +8072,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>上海交通大学</t>
+          <t>上海中兴无线电厂</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -8047,11 +8080,6 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>DJS一053微型计算机、DJS一052E微型计算机、生产单板微型计算机、单板微型计算机</t>
-        </is>
-      </c>
       <c r="G201" t="inlineStr">
         <is>
           <t>Beijing</t>
@@ -8064,14 +8092,14 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>华东师范大学</t>
+          <t>新安电工厂</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -8079,9 +8107,6 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="D202" t="n">
-        <v>19730000</v>
-      </c>
       <c r="G202" t="inlineStr">
         <is>
           <t>Beijing</t>
@@ -8094,24 +8119,19 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·1. 电子管计算机</t>
+          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>中国人民解放军总参谋部第五十六研究所</t>
+          <t>上海调节器厂</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>研究所</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>J一101型计算机</t>
+          <t>电子计算机</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -8121,7 +8141,7 @@
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
@@ -8133,12 +8153,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>上海工业大学</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>电子计算机</t>
+          <t>上海炼油厂</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -8148,140 +8163,10 @@
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>志中未见专条,仅由他条提及</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
-        <is>
-          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>联合公司</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>电子计算机</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>Beijing</t>
-        </is>
-      </c>
-      <c r="Q205" t="inlineStr">
-        <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
-        </is>
-      </c>
-      <c r="R205" t="inlineStr">
-        <is>
-          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>上海中兴无线电厂</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>电子计算机</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>Beijing</t>
-        </is>
-      </c>
-      <c r="Q206" t="inlineStr">
-        <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
-        </is>
-      </c>
-      <c r="R206" t="inlineStr">
-        <is>
-          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>新安电工厂</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>电子计算机</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>Beijing</t>
-        </is>
-      </c>
-      <c r="Q207" t="inlineStr">
-        <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
-        </is>
-      </c>
-      <c r="R207" t="inlineStr">
-        <is>
-          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>上海调节器厂</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>电子计算机</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>Beijing</t>
-        </is>
-      </c>
-      <c r="Q208" t="inlineStr">
-        <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
-        </is>
-      </c>
-      <c r="R208" t="inlineStr">
-        <is>
-          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>上海炼油厂</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>Beijing</t>
-        </is>
-      </c>
-      <c r="Q209" t="inlineStr">
-        <is>
-          <t>志中未见专条,仅由他条提及</t>
-        </is>
-      </c>
-      <c r="R209" t="inlineStr">
         <is>
           <t>上海电子仪表工业志·第一章电子计算机·第五节企业·四、 上海王安电脑发展公司</t>
         </is>

--- a/CN_Electronic_Industry.xlsx
+++ b/CN_Electronic_Industry.xlsx
@@ -393,7 +393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U204"/>
+  <dimension ref="A1:U202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.28515625" customWidth="1" min="1" max="1"/>
@@ -518,6 +518,11 @@
           <t>电子计算机</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TQ-16中型通用数字集成电路计算机、J-101型计算机、专用电子计算机、TQ-21型数据处理机</t>
+        </is>
+      </c>
       <c r="D3" t="n">
         <v>19660601</v>
       </c>
@@ -555,9 +560,14 @@
       <c r="P3" t="n">
         <v>510.2</v>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+        </is>
+      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>上五十三</t>
+          <t>上五十三、上海无线电十三厂</t>
         </is>
       </c>
     </row>
@@ -1165,6 +1175,11 @@
       <c r="D18" t="n">
         <v>19890000</v>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>漕河泾新兴技术开发区桂平路481号</t>
@@ -1258,6 +1273,11 @@
           <t>轻工业部上海科学研究所仪表组-&gt;上海仪器仪表医疗器械综合研究所-&gt;第一机械工业部热工仪表科学研究所-&gt;上海工业自动化仪表研究所</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>漕宝路103号</t>
@@ -1346,6 +1366,11 @@
           <t>中国电气科学院微电机室+上海华富电器厂-&gt;国防科学技术委员会第十研究员上海微电机研究所</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>龙华路647号</t>
@@ -1385,6 +1410,11 @@
           <t>国防科学技术委员会第十研究院传输线研究室</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>逸仙路23号</t>
@@ -1424,6 +1454,11 @@
           <t>上海市计算中心</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>愚园路546号</t>
@@ -1463,6 +1498,11 @@
           <t>中国科学器材公司上海分公司所属科学仪器修配厂</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>武宁路423号</t>
@@ -1499,6 +1539,11 @@
           <t>上海金星制铜厂-&gt;1961年上海仪表铜厂-&gt;1968年划归四机部</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>真南路3500号</t>
@@ -1566,6 +1611,11 @@
           <t>上海市电讯电器工业公司中心试验室-&gt;19580800中国科学院上海无线电技术研究所-&gt;1960归属上海市仪表电讯工业局-&gt;19610800并入上海无线电元件研究所-&gt;19620800合并上海市仪表电讯工艺研究所-&gt;19690701划归国防科学技术委员会，组建成航空电子设备研究所</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>淮海西路432号</t>
@@ -1596,6 +1646,11 @@
           <t>精密医疗器材厂与上海仪表厂合并-&gt;19750200改名上海新跃仪表厂-&gt;19861212从新跃仪表厂划出</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>522</v>
       </c>
@@ -1625,6 +1680,11 @@
           <t>上海电表厂中心试验室-&gt;第一机械工业部上海电工仪器研究室-&gt;19580603改称上海电工仪器研究室-&gt;19640506上海电工仪器研究所-&gt;19791200上海仪器仪表研究所</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>龙江路225号</t>
@@ -1651,11 +1711,16 @@
           <t>研究所</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>国营738厂</t>
+          <t>清华大学</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1665,22 +1730,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>生产微型计算机、微型计算机、0520CH机、生产10台BCM0530机</t>
+          <t>DJS-5小型晶体管鼓字计算机、555型小型台式模拟计算机、微型计算机、0520CH机</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>19860000</v>
+        <v>19600000</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>自动导航专用的集成电路</t>
-        </is>
-      </c>
       <c r="Q32" t="inlineStr">
         <is>
           <t>未见专条,据行文点名；行业据正文用词</t>
@@ -1688,19 +1748,14 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>北京有线电厂、国营有线电厂</t>
+          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>清华大学</t>
+          <t>北京无线电一厂</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1710,11 +1765,16 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DJS-5小型晶体管鼓字计算机、555型小型台式模拟计算机、微型计算机、0520CH机</t>
+          <t>大型晶体管模数混合计算机</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>19600000</v>
+        <v>19700000</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>19700000改名北京计算机一厂</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1728,14 +1788,14 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>北京无线电一厂</t>
+          <t>北京计算机五厂</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1745,15 +1805,15 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>大型晶体管模数混合计算机</t>
+          <t>微型计算机、天坛牌TEC系列学习机</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>19700000</v>
+        <v>19840600</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>19700000改名北京计算机一厂</t>
+          <t>19840600改名北京计算机五厂</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1763,19 +1823,19 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第三节计算器</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>北京计算机五厂</t>
+          <t>中科院计算所</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1785,16 +1845,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>微型计算机、天坛牌TEC系列学习机</t>
+          <t>119电子管通用数字计算机、109乙计算机</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>19840600</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>19840600改名北京计算机五厂</t>
-        </is>
+        <v>19560600</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1803,19 +1858,19 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+          <t>北京工业志·电子志·第三章电子计算机</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>中科院计算所</t>
+          <t>北京计算机一厂</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1825,11 +1880,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>119电子管通用数字计算机、109乙计算机</t>
+          <t>大型晶体管模数混合计算机、S-100总线单板系列机</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>19560600</v>
+        <v>19700000</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1838,19 +1893,24 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>北京计算机一厂</t>
+          <t>北京北优计算机系统有限公司</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1860,11 +1920,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>大型晶体管模数混合计算机、S-100总线单板系列机</t>
+          <t>BUCC微型机</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>19700000</v>
+        <v>19950200</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1879,32 +1939,29 @@
       <c r="R37" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>北京北优计算机系统有限公司</t>
+          <t>北京无线电三厂</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>电子计算机</t>
+          <t>半导体</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BUCC微型机</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>19950200</v>
+          <t>DJS-5小型晶体管鼓字计算机、DJS-4晶体管台式数字计算机</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>19050400改名北京计算机三厂</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1913,35 +1970,38 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>宣武</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>北京无线电三厂</t>
+          <t>航空部第20研究所</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>研究所</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DJS-5小型晶体管鼓字计算机、DJS-4晶体管台式数字计算机</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>19050400改名北京计算机三厂</t>
-        </is>
+          <t>大型晶体管模数混合计算机</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>19700000</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1950,38 +2010,33 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>宣武</t>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>航空部第20研究所</t>
+          <t>北京计算机二厂</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>研究所</t>
+          <t>电子计算机</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>大型晶体管模数混合计算机</t>
+          <t>BY-0520I型银行信息处理机</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>19700000</v>
+        <v>19790000</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1995,14 +2050,19 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>东城</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>北京计算机二厂</t>
+          <t>中国科学院计算所</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2010,13 +2070,8 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>BY-0520I型银行信息处理机</t>
-        </is>
-      </c>
       <c r="D41" t="n">
-        <v>19790000</v>
+        <v>19841100</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2025,24 +2080,19 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第三节计算器</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>东城</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·二、 汉字信息系统</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>中国科学院计算所</t>
+          <t>中国科学院计算所公司</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2072,7 +2122,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>中国科学院计算所公司</t>
+          <t>北京市旅游汽车公司</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2081,7 +2131,12 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>19841100</v>
+        <v>19840600</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>19840600改名北京计算机五厂</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2095,14 +2150,14 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·二、 汉字信息系统</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 管理信息系统</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>北京市旅游汽车公司</t>
+          <t>北京联想计算机集团公司</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2110,12 +2165,14 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="D44" t="n">
-        <v>19840600</v>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>联想系列微机</t>
+        </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>19840600改名北京计算机五厂</t>
+          <t>19880000改名联想集团公司</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2125,19 +2182,24 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 管理信息系统</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>联想计算机集团公司</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>北京联想计算机集团公司</t>
+          <t>首钢电子公司</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2145,14 +2207,12 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>联想系列微机</t>
-        </is>
+      <c r="D45" t="n">
+        <v>19790000</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>19880000改名联想集团公司</t>
+          <t>改名自动化研究所</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2162,24 +2222,24 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>联想计算机集团公司</t>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>石景山</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>首钢电子公司</t>
+          <t>北京工控计算机厂</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2188,12 +2248,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>19790000</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>改名自动化研究所</t>
-        </is>
+        <v>19830000</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2202,24 +2257,19 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>石景山</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>北京工控计算机厂</t>
+          <t>北京工业大学电子厂</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2227,8 +2277,10 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="D47" t="n">
-        <v>19830000</v>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>TP系列微型打印机</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2237,7 +2289,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -2249,7 +2301,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>北京工业大学电子厂</t>
+          <t>北京四通办公设备有限公司</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2257,10 +2309,8 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>TP系列微型打印机</t>
-        </is>
+      <c r="D48" t="n">
+        <v>19870000</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2275,13 +2325,18 @@
       <c r="R48" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>北京四通办公设备有限公司</t>
+          <t>电子部6所</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2289,8 +2344,10 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="D49" t="n">
-        <v>19870000</v>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>长城0520B微型机</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2305,18 +2362,13 @@
       <c r="R49" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>电子部6所</t>
+          <t>北京市计算机技术研究所</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2326,8 +2378,11 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>长城0520B微型机</t>
-        </is>
+          <t>生产10台BCM0530机、10台BCM0530机</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>19790000</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2336,19 +2391,24 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机；北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>市计算机技术研究所</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>北京市计算机技术研究所</t>
+          <t>四机部15所</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2358,11 +2418,8 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>生产10台BCM0530机、10台BCM0530机</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>19790000</v>
+          <t>DJS-200系列计算机</t>
+        </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2371,24 +2428,19 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机；北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>市计算机技术研究所</t>
+          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>四机部15所</t>
+          <t>北京计算机三厂</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2398,7 +2450,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DJS-200系列计算机</t>
+          <t>DJS-5小型晶体管鼓字计算机</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2408,19 +2460,24 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>朝阳</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>北京计算机三厂</t>
+          <t>北京市无线电制造厂</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2428,9 +2485,9 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>DJS-5小型晶体管鼓字计算机</t>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>改名北京无线电一厂</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2440,35 +2497,28 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>朝阳</t>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>北京市无线电制造厂</t>
+          <t>北京电子显示设备厂</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>电子计算机</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>改名北京无线电一厂</t>
-        </is>
+          <t>外围设备</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>19830700</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2482,23 +2532,25 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·三、 显示器</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>北京电子显示设备厂</t>
+          <t>联想集团公司</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>外围设备</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>19830700</v>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>并投人批量生产联想激光打印机、联想激光打印机、联想系列微机</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2512,25 +2564,33 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·三、 显示器</t>
+          <t>北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·四、 打印机</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>联想集团</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>联想集团公司</t>
+          <t>自动化研究所</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>电子计算机</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>并投人批量生产联想激光打印机、联想激光打印机、联想系列微机</t>
-        </is>
+          <t>研究所</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>19790000</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2539,64 +2599,56 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·四、 打印机</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>联想集团</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>海淀</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 计算机辅助软件工程系统</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>自动化研究所</t>
+          <t>长沙工业学院</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>研究所</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>19790000</v>
+          <t>电子计算机</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Changsha</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 计算机辅助软件工程系统</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>长沙工业学院</t>
+          <t>电子部第15所</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>NCI-2780超级小型计算机</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2618,7 +2670,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>电子部第15所</t>
+          <t>四机部6所</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2628,7 +2680,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NCI-2780超级小型计算机</t>
+          <t>微型计算机、S-100总线单板系列机</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2643,14 +2695,14 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>四机部6所</t>
+          <t>安徽无线电厂</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2660,7 +2712,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>微型计算机、S-100总线单板系列机</t>
+          <t>微型计算机</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2682,7 +2734,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>安徽无线电厂</t>
+          <t>北京崇文电子仪器厂</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2714,7 +2766,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>北京崇文电子仪器厂</t>
+          <t>北京市计算机服务公司</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2724,7 +2776,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>微型计算机</t>
+          <t>0520CH机</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2734,19 +2786,24 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>计算机服务公司</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>北京市计算机服务公司</t>
+          <t>北京开关厂</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2754,9 +2811,9 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>0520CH机</t>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>19060000改名北京控制机厂</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2766,24 +2823,19 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>计算机服务公司</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>北京开关厂</t>
+          <t>北京计算机配件五厂</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2791,10 +2843,8 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>19060000改名北京控制机厂</t>
-        </is>
+      <c r="D64" t="n">
+        <v>19830000</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2803,7 +2853,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -2815,7 +2865,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>北京计算机配件五厂</t>
+          <t>华北制药厂</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2823,17 +2873,19 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="D65" t="n">
-        <v>19830000</v>
-      </c>
       <c r="G65" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>亚运村</t>
+        </is>
+      </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -2845,24 +2897,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>华北制药厂</t>
+          <t>美国COMPAQ公司</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>电子计算机</t>
-        </is>
+          <t>外围设备</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>19830700</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>亚运村</t>
-        </is>
-      </c>
       <c r="Q66" t="inlineStr">
         <is>
           <t>未见专条,据行文点名；行业据正文用词</t>
@@ -2870,23 +2920,20 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>美国COMPAQ公司</t>
+          <t>北京计算机外部设备三厂</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>外围设备</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>19830700</v>
+          <t>电子计算机</t>
+        </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2895,19 +2942,24 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
+          <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>崇文</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>北京计算机外部设备三厂</t>
+          <t>中国长城计算机集团公司</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2932,14 +2984,14 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>崇文</t>
+          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>中国长城计算机集团公司</t>
+          <t>北京科海高技术集团公司</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2954,24 +3006,19 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>北京科海高技术集团公司</t>
+          <t>北京希望电脑公司</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2986,19 +3033,24 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>北京希望电脑公司</t>
+          <t>北京王码电脑公司</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,18 +3071,13 @@
       <c r="R71" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>北京王码电脑公司</t>
+          <t>电子部15所</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3045,7 +3092,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -3057,7 +3104,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>电子部15所</t>
+          <t>北京航星机器制造公司</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3084,7 +3131,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>北京航星机器制造公司</t>
+          <t>哈尔滨军事工程学院</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3094,7 +3141,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Harbin</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -3104,19 +3151,24 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>哈军工</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>哈尔滨军事工程学院</t>
+          <t>四机部标准化研究所4所</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>电子计算机</t>
+          <t>研究所</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3126,29 +3178,24 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第一节数字计算机·二、 晶体管计算机</t>
-        </is>
-      </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>哈军工</t>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>四机部标准化研究所4所</t>
+          <t>北京市计算机工业总公司</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>研究所</t>
+          <t>电子计算机</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3163,19 +3210,19 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第三节计算器</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>北京市计算机工业总公司</t>
+          <t>北京东风电视机厂</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>电子计算机</t>
+          <t>外围设备</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3185,24 +3232,24 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+          <t>北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·三、 显示器</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>北京东风电视机厂</t>
+          <t>一机部15所</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>外围设备</t>
+          <t>电子计算机</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3217,14 +3264,14 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第四节计算机外部设备·三、 显示器</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>一机部15所</t>
+          <t>北京大学</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3244,14 +3291,14 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·二、 汉字信息系统</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>北京大学</t>
+          <t>北京大学计算机技术研究所</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3266,7 +3313,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -3278,12 +3325,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>北京大学计算机技术研究所</t>
+          <t>中科院自动化研究所</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>电子计算机</t>
+          <t>研究所</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3298,19 +3345,19 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·二、 汉字信息系统</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 计算机辅助软件工程系统</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>中科院自动化研究所</t>
+          <t>北京市半导体器件二厂</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>研究所</t>
+          <t>半导体</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3325,19 +3372,19 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 计算机辅助软件工程系统</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>北京市半导体器件二厂</t>
+          <t>清华大学计算机厂</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>电子计算机</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3352,14 +3399,14 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·三、 集成电路计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>清华大学计算机厂</t>
+          <t>北京师范大学</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3374,7 +3421,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -3386,7 +3433,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>北京师范大学</t>
+          <t>上海复旦大学</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3396,7 +3443,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -3407,18 +3454,23 @@
       <c r="R85" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>复旦大学</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>上海复旦大学</t>
+          <t>山东省烟台市电子技术研究所</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>电子计算机</t>
+          <t>研究所</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3428,30 +3480,23 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
-        </is>
-      </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>复旦大学</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>山东省烟台市电子技术研究所</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>研究所</t>
-        </is>
+          <t>北京四通集团公司</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>19870000</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3460,23 +3505,25 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（四） 文字处理机</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>北京四通集团公司</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>19870000</v>
+          <t>北京开关厂平谷分厂</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3485,19 +3532,19 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（四） 文字处理机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>北京开关厂平谷分厂</t>
+          <t>北京控制机厂</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3512,7 +3559,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -3524,12 +3571,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>北京控制机厂</t>
+          <t>北京电器科学研究院</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>电子计算机</t>
+          <t>研究所</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3551,22 +3598,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>北京电器科学研究院</t>
+          <t>兰州炼油厂</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>研究所</t>
+          <t>电子计算机</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Lanzhou</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -3578,7 +3625,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>兰州炼油厂</t>
+          <t>大庆石油化工总厂</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3605,7 +3652,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>大庆石油化工总厂</t>
+          <t>唐山陡河发电总厂</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3615,7 +3662,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Tangshan</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -3626,18 +3673,23 @@
       <c r="R93" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>陡河发电总厂</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>唐山陡河发电总厂</t>
+          <t>首钢自动化研究所</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>电子计算机</t>
+          <t>研究所</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3647,24 +3699,19 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
-        </is>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>陡河发电总厂</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>首钢自动化研究所</t>
+          <t>中国管理科学研究院</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3691,12 +3738,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>中国管理科学研究院</t>
+          <t>华胜计算机公司</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>研究所</t>
+          <t>电子计算机</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3711,19 +3758,19 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·六、 工作站</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>华胜计算机公司</t>
+          <t>中国软件技术公司</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>电子计算机</t>
+          <t>外围设备</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3733,19 +3780,19 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·六、 工作站</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>中国软件技术公司</t>
+          <t>北京华海新技术开发公司</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3772,12 +3819,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>北京华海新技术开发公司</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>外围设备</t>
+          <t>北京西城广播设备厂</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3787,19 +3829,19 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
+          <t>北京工业志·电子志</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>北京西城广播设备厂</t>
+          <t>北京无线电厂</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -3815,13 +3857,18 @@
       <c r="R100" t="inlineStr">
         <is>
           <t>北京工业志·电子志</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>北京无线电厂</t>
+          <t>国营774厂音响分厂</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -3837,18 +3884,13 @@
       <c r="R101" t="inlineStr">
         <is>
           <t>北京工业志·电子志</t>
-        </is>
-      </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>国营774厂音响分厂</t>
+          <t>508所</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -3863,14 +3905,14 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>北京工业志·电子志</t>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>508所</t>
+          <t>302所</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -3892,7 +3934,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>302所</t>
+          <t>六机部705所</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -3914,7 +3956,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>六机部705所</t>
+          <t>航空部601所</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -3936,7 +3978,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>航空部601所</t>
+          <t>北京三洋电子有限公司</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -3951,14 +3993,14 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·二、 模数混合计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第三节计算器</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>北京三洋电子有限公司</t>
+          <t>北京第三棉纺织厂</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -3973,14 +4015,14 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第三节计算器</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>北京第三棉纺织厂</t>
+          <t>中国人民解放军3509厂</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4002,7 +4044,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>中国人民解放军3509厂</t>
+          <t>第二钢轧厂</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4024,12 +4066,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>第二钢轧厂</t>
+          <t>南京微电机厂</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Nanjing</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -4039,14 +4081,14 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·一、 系统软件及其应用</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(二) 单板机</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>南京微电机厂</t>
+          <t>机电部4所</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4061,14 +4103,14 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(二) 单板机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>机电部4所</t>
+          <t>新疆水泥厂</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4083,14 +4125,14 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·(三) 学习机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>新疆水泥厂</t>
+          <t>双羊水泥厂</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4112,7 +4154,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>双羊水泥厂</t>
+          <t>美国钢铁公司</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4134,7 +4176,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>美国钢铁公司</t>
+          <t>北京水泵厂</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4156,7 +4198,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>北京水泵厂</t>
+          <t>华胜公司</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4171,14 +4213,14 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·五、 工业控制计算机</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·六、 工作站</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>华胜公司</t>
+          <t>首钢公司</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4193,73 +4235,125 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·六、 工作站</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>首钢公司</t>
-        </is>
+          <t>北京东光电工厂</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>19680200</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>酒仙桥路12号</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>1499</v>
+      </c>
+      <c r="J118" t="n">
+        <v>142</v>
+      </c>
+      <c r="L118" t="n">
+        <v>90600</v>
+      </c>
+      <c r="M118" t="n">
+        <v>11100</v>
+      </c>
+      <c r="N118" t="n">
+        <v>686</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名</t>
+          <t>行业据正文用词</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·七、 终端设备</t>
+          <t>北京工业志·电子志·第十二节北京东光电工厂</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>国营第878厂</t>
+        </is>
+      </c>
+      <c r="T118" t="n">
+        <v>1995</v>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>朝阳</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>北京东光电工厂</t>
+          <t>北京牡丹电子集团公司</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>外围设备</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>彩色电视机</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>19680200</v>
+        <v>19900216</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>19650000北京无线电精密元件厂-&gt;19731100改名北京电视机厂-&gt;北京电视机厂与北京电子显示设各厂合并-&gt;19910000北京东风电视机厂合并</t>
+        </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>酒仙桥路12号</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>1499</v>
+        <v>5617</v>
       </c>
       <c r="J119" t="n">
-        <v>142</v>
+        <v>896</v>
       </c>
       <c r="L119" t="n">
-        <v>90600</v>
+        <v>136200</v>
       </c>
       <c r="M119" t="n">
-        <v>11100</v>
+        <v>45000</v>
       </c>
       <c r="N119" t="n">
-        <v>686</v>
+        <v>146000</v>
+      </c>
+      <c r="O119" t="n">
+        <v>107000</v>
       </c>
       <c r="P119" t="n">
-        <v>0.6</v>
+        <v>2504.5</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
@@ -4268,12 +4362,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十二节北京东光电工厂</t>
-        </is>
-      </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>国营第878厂</t>
+          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
         </is>
       </c>
       <c r="T119" t="n">
@@ -4281,32 +4370,27 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>朝阳</t>
+          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>北京牡丹电子集团公司</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>外围设备</t>
+          <t>北京电视设备厂</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>彩色电视机</t>
+          <t>彩色摄像机、彩色锁相同步机、J52等十余种型号的录像机</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>19900216</v>
+        <v>19710500</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>19650000北京无线电精密元件厂-&gt;19731100改名北京电视机厂-&gt;北京电视机厂与北京电子显示设各厂合并-&gt;19910000北京东风电视机厂合并</t>
+          <t>国营761厂电视车间与北京被服厂合并</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4314,35 +4398,32 @@
           <t>Beijing</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>东四北大街107号</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>5617</v>
+        <v>1139</v>
       </c>
       <c r="J120" t="n">
-        <v>896</v>
+        <v>264</v>
       </c>
       <c r="L120" t="n">
-        <v>136200</v>
+        <v>18100</v>
       </c>
       <c r="M120" t="n">
-        <v>45000</v>
+        <v>12000</v>
       </c>
       <c r="N120" t="n">
-        <v>146000</v>
-      </c>
-      <c r="O120" t="n">
-        <v>107000</v>
+        <v>29200</v>
       </c>
       <c r="P120" t="n">
-        <v>2504.5</v>
-      </c>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>行业据正文用词</t>
-        </is>
+        <v>1972</v>
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
+          <t>北京工业志·电子志·第十四节北京电视设备厂</t>
         </is>
       </c>
       <c r="T120" t="n">
@@ -4350,27 +4431,32 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>海淀</t>
+          <t>东城</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>北京电视设备厂</t>
+          <t>北京飞达电子集团公司</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>半导体</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>彩色摄像机、彩色锁相同步机、J52等十余种型号的录像机</t>
+          <t>收录机</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>19710500</v>
+        <v>19930200</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>国营761厂电视车间与北京被服厂合并</t>
+          <t>19540000北京电影机械修理厂-&gt;19700000改名北京电影机械厂-&gt;19810000改名北京录音机厂</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4380,30 +4466,32 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>东四北大街107号</t>
+          <t>苏州街75号</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1139</v>
+        <v>792</v>
       </c>
       <c r="J121" t="n">
-        <v>264</v>
+        <v>95</v>
       </c>
       <c r="L121" t="n">
-        <v>18100</v>
-      </c>
-      <c r="M121" t="n">
-        <v>12000</v>
+        <v>30200</v>
       </c>
       <c r="N121" t="n">
-        <v>29200</v>
+        <v>1444</v>
       </c>
       <c r="P121" t="n">
-        <v>1972</v>
+        <v>30.9</v>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十四节北京电视设备厂</t>
+          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
         </is>
       </c>
       <c r="T121" t="n">
@@ -4411,14 +4499,14 @@
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>东城</t>
+          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>北京飞达电子集团公司</t>
+          <t>北京显像管总厂</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4428,15 +4516,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>收录机</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>19930200</v>
+          <t>低频大功率管、23厘米黑白显像管和50厘米显像管、35厘米黑白显像管、彩色显示管</t>
+        </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>19540000北京电影机械修理厂-&gt;19700000改名北京电影机械厂-&gt;19810000改名北京录音机厂</t>
+          <t>19700000北京呢绒服装厂-&gt;19721100改名北京显值管厂-&gt;19900000改名北京显像管总厂</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4446,23 +4531,26 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>苏州街75号</t>
+          <t>光明西路1号</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>792</v>
+        <v>1023</v>
       </c>
       <c r="J122" t="n">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="L122" t="n">
-        <v>30200</v>
+        <v>52800</v>
+      </c>
+      <c r="M122" t="n">
+        <v>4637.2</v>
       </c>
       <c r="N122" t="n">
-        <v>1444</v>
+        <v>1124</v>
       </c>
       <c r="P122" t="n">
-        <v>30.9</v>
+        <v>5.3</v>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
@@ -4471,7 +4559,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
+          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
         </is>
       </c>
       <c r="T122" t="n">
@@ -4479,29 +4567,22 @@
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>海淀</t>
+          <t>崇文</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>北京显像管总厂</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>半导体</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>低频大功率管、23厘米黑白显像管和50厘米显像管、35厘米黑白显像管、彩色显示管</t>
-        </is>
+          <t>北京广播电视配件一厂</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>19540000</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>19700000北京呢绒服装厂-&gt;19721100改名北京显值管厂-&gt;19900000改名北京显像管总厂</t>
+          <t>19570000合并改建为北京无线电电匣厂-&gt;19610000并入北京电子仪器厂-&gt;19650000改名北京无线电非金属元件厂-&gt;19700000改名北京无线电元件厂</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4511,35 +4592,27 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>光明西路1号</t>
+          <t>东铁匠营横七条30号</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1023</v>
+        <v>910</v>
       </c>
       <c r="J123" t="n">
-        <v>138</v>
+        <v>62</v>
       </c>
       <c r="L123" t="n">
-        <v>52800</v>
+        <v>34800</v>
       </c>
       <c r="M123" t="n">
-        <v>4637.2</v>
+        <v>2918.8</v>
       </c>
       <c r="N123" t="n">
-        <v>1124</v>
-      </c>
-      <c r="P123" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="Q123" t="inlineStr">
-        <is>
-          <t>行业据正文用词</t>
-        </is>
+        <v>929</v>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
+          <t>北京工业志·电子志·第十九节北京广播电视配件一厂</t>
         </is>
       </c>
       <c r="T123" t="n">
@@ -4547,22 +4620,22 @@
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>崇文</t>
+          <t>丰台</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>北京广播电视配件一厂</t>
+          <t>北京电视配件三厂</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>19540000</v>
+        <v>19900000</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>19570000合并改建为北京无线电电匣厂-&gt;19610000并入北京电子仪器厂-&gt;19650000改名北京无线电非金属元件厂-&gt;19700000改名北京无线电元件厂</t>
+          <t>改名北京广播电视配件三厂-&gt;19660000东红路塑料制品厂-&gt;19700000改名东红路无线电元件厂-&gt;19750000改名朝阳区东红路无线电元件厂</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -4572,27 +4645,30 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>东铁匠营横七条30号</t>
+          <t>酒仙桥南路5号</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>910</v>
+        <v>1057</v>
       </c>
       <c r="J124" t="n">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="L124" t="n">
-        <v>34800</v>
+        <v>35200</v>
       </c>
       <c r="M124" t="n">
-        <v>2918.8</v>
+        <v>7816.1</v>
       </c>
       <c r="N124" t="n">
-        <v>929</v>
+        <v>12700</v>
+      </c>
+      <c r="P124" t="n">
+        <v>1812.7</v>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十九节北京广播电视配件一厂</t>
+          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
         </is>
       </c>
       <c r="T124" t="n">
@@ -4600,22 +4676,22 @@
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>丰台</t>
+          <t>朝阳</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>北京电视配件三厂</t>
+          <t>北京市调谐器厂</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>19900000</v>
+        <v>19810200</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>改名北京广播电视配件三厂-&gt;19660000东红路塑料制品厂-&gt;19700000改名东红路无线电元件厂-&gt;19750000改名朝阳区东红路无线电元件厂</t>
+          <t>19691000合并为西城区无线电元件厂-&gt;19790000改名北京广播电视配件五厂</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4625,30 +4701,30 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>酒仙桥南路5号</t>
+          <t>家来街月台胡同18号</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1057</v>
+        <v>545</v>
       </c>
       <c r="J125" t="n">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="L125" t="n">
-        <v>35200</v>
+        <v>39700</v>
       </c>
       <c r="M125" t="n">
-        <v>7816.1</v>
+        <v>2835.3</v>
       </c>
       <c r="N125" t="n">
-        <v>12700</v>
-      </c>
-      <c r="P125" t="n">
-        <v>1812.7</v>
+        <v>1245</v>
+      </c>
+      <c r="O125" t="n">
+        <v>1504.8</v>
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
+          <t>北京工业志·电子志·第二十一节北京市调谐器厂</t>
         </is>
       </c>
       <c r="T125" t="n">
@@ -4656,22 +4732,27 @@
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>朝阳</t>
+          <t>西城</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>北京市调谐器厂</t>
+          <t>北京广播通讯电源厂</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>19810200</v>
+        <v>19540000</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>19691000合并为西城区无线电元件厂-&gt;19790000改名北京广播电视配件五厂</t>
+          <t>19570000改名北京鞋底厂-&gt;19600000改名北京鞋厂-&gt;19720000改名北京东风电池厂-&gt;19790500改名北京广播电视配件六厂-&gt;19880000改名北京广播通讯电源厂</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4679,32 +4760,29 @@
           <t>Beijing</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>家来街月台胡同18号</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>545</v>
+        <v>396</v>
       </c>
       <c r="J126" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L126" t="n">
-        <v>39700</v>
-      </c>
-      <c r="M126" t="n">
-        <v>2835.3</v>
+        <v>30100</v>
       </c>
       <c r="N126" t="n">
-        <v>1245</v>
-      </c>
-      <c r="O126" t="n">
-        <v>1504.8</v>
+        <v>240</v>
+      </c>
+      <c r="P126" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十一节北京市调谐器厂</t>
+          <t>北京工业志·电子志·第二十二节北京广播通讯电源厂</t>
         </is>
       </c>
       <c r="T126" t="n">
@@ -4712,27 +4790,27 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>西城</t>
+          <t>朝阳</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>北京广播通讯电源厂</t>
+          <t>北京无线电仪器厂</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>电子计算机</t>
+          <t>半导体</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>19540000</v>
+        <v>19620600</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>19570000改名北京鞋底厂-&gt;19600000改名北京鞋厂-&gt;19720000改名北京东风电池厂-&gt;19790500改名北京广播电视配件六厂-&gt;19880000改名北京广播通讯电源厂</t>
+          <t>北京崇文电器仪器厂、北京电器厂合并</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -4740,20 +4818,28 @@
           <t>Beijing</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>福长街四条4号</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>396</v>
+        <v>709</v>
       </c>
       <c r="J127" t="n">
-        <v>15</v>
+        <v>172</v>
       </c>
       <c r="L127" t="n">
-        <v>30100</v>
+        <v>21200</v>
+      </c>
+      <c r="M127" t="n">
+        <v>1873.8</v>
       </c>
       <c r="N127" t="n">
-        <v>240</v>
+        <v>3453</v>
       </c>
       <c r="P127" t="n">
-        <v>55.7</v>
+        <v>165.5</v>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
@@ -4762,7 +4848,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十二节北京广播通讯电源厂</t>
+          <t>北京工业志·电子志·第二十七节北京无线电仪器厂</t>
         </is>
       </c>
       <c r="T127" t="n">
@@ -4770,14 +4856,14 @@
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>朝阳</t>
+          <t>宣武</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>北京无线电仪器厂</t>
+          <t>北京无线电仪器二厂</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4786,11 +4872,11 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>19620600</v>
+        <v>19700400</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>北京崇文电器仪器厂、北京电器厂合并</t>
+          <t>改名北京广播器材厂-&gt;合并组建了北京市综合仪器厂-&gt;19590000北京电子仪器厂-&gt;19620900东城无线电仪器装配厂和电讯仪表厂合并-&gt;19700000北京无线电二厂合并-&gt;北京电子仪器厂、北京无线电二厂合并</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -4800,26 +4886,23 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>福长街四条4号</t>
+          <t>符台路2号</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>709</v>
-      </c>
-      <c r="J128" t="n">
-        <v>172</v>
+        <v>622</v>
       </c>
       <c r="L128" t="n">
-        <v>21200</v>
+        <v>36900</v>
       </c>
       <c r="M128" t="n">
-        <v>1873.8</v>
+        <v>2209</v>
       </c>
       <c r="N128" t="n">
-        <v>3453</v>
-      </c>
-      <c r="P128" t="n">
-        <v>165.5</v>
+        <v>237</v>
+      </c>
+      <c r="O128" t="n">
+        <v>206.7</v>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
@@ -4828,7 +4911,7 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十七节北京无线电仪器厂</t>
+          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
         </is>
       </c>
       <c r="T128" t="n">
@@ -4836,27 +4919,24 @@
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>宣武</t>
+          <t>朝阳</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>北京无线电仪器二厂</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>半导体</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>19700400</v>
+          <t>北京广播器材厂</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>广播发射机、电视发射机、电视差转机、盒式录像机</t>
+        </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>改名北京广播器材厂-&gt;合并组建了北京市综合仪器厂-&gt;19590000北京电子仪器厂-&gt;19620900东城无线电仪器装配厂和电讯仪表厂合并-&gt;19700000北京无线电二厂合并-&gt;北京电子仪器厂、北京无线电二厂合并</t>
+          <t>19500601北京人民广播器材厂</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -4866,32 +4946,30 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>符台路2号</t>
+          <t>今四环胡同4号</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>622</v>
+        <v>3486</v>
+      </c>
+      <c r="J129" t="n">
+        <v>783</v>
       </c>
       <c r="L129" t="n">
-        <v>36900</v>
+        <v>227200</v>
       </c>
       <c r="M129" t="n">
-        <v>2209</v>
+        <v>23900</v>
       </c>
       <c r="N129" t="n">
-        <v>237</v>
-      </c>
-      <c r="O129" t="n">
-        <v>206.7</v>
-      </c>
-      <c r="Q129" t="inlineStr">
-        <is>
-          <t>行业据正文用词</t>
-        </is>
+        <v>7904.9</v>
+      </c>
+      <c r="P129" t="n">
+        <v>683.6</v>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第九节北京广播器材厂</t>
         </is>
       </c>
       <c r="T129" t="n">
@@ -4899,24 +4977,32 @@
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>朝阳</t>
+          <t>西城</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>北京广播器材厂</t>
+          <t>北京邮电通信设备厂</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>半导体</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>广播发射机、电视发射机、电视差转机、盒式录像机</t>
-        </is>
+          <t>生产微波三大固体器件、微波三大固体器件</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>19410900</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>19500601北京人民广播器材厂</t>
+          <t>组建了4个合资公司-&gt;1941年9月建立的华北电信电话股份有限公司</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -4926,30 +5012,40 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>今四环胡同4号</t>
+          <t>将台路5号</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3486</v>
+        <v>1367</v>
       </c>
       <c r="J130" t="n">
-        <v>783</v>
+        <v>724</v>
       </c>
       <c r="L130" t="n">
-        <v>227200</v>
+        <v>86000</v>
       </c>
       <c r="M130" t="n">
-        <v>23900</v>
+        <v>8359.4</v>
       </c>
       <c r="N130" t="n">
-        <v>7904.9</v>
+        <v>7489</v>
       </c>
       <c r="P130" t="n">
-        <v>683.6</v>
+        <v>189</v>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第九节北京广播器材厂</t>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第一节北京邮电通信设备厂</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>邮电506厂</t>
         </is>
       </c>
       <c r="T130" t="n">
@@ -4957,14 +5053,14 @@
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>西城</t>
+          <t>朝阳</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>北京邮电通信设备厂</t>
+          <t>北京通信元件厂</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4974,15 +5070,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>生产微波三大固体器件、微波三大固体器件</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>19410900</v>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>组建了4个合资公司-&gt;1941年9月建立的华北电信电话股份有限公司</t>
+          <t>半导体器件、高反压复合场效应晶体管、和销售BP机</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -4992,26 +5080,26 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>将台路5号</t>
-        </is>
-      </c>
-      <c r="I131" t="n">
-        <v>1367</v>
+          <t>新街口外大街28号</t>
+        </is>
       </c>
       <c r="J131" t="n">
-        <v>724</v>
+        <v>450</v>
       </c>
       <c r="L131" t="n">
-        <v>86000</v>
+        <v>70000</v>
       </c>
       <c r="M131" t="n">
-        <v>8359.4</v>
+        <v>3040.9</v>
       </c>
       <c r="N131" t="n">
-        <v>7489</v>
+        <v>4423.4</v>
+      </c>
+      <c r="O131" t="n">
+        <v>12000</v>
       </c>
       <c r="P131" t="n">
-        <v>189</v>
+        <v>360</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
@@ -5020,37 +5108,37 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二章中央在京电子工业企业·第一节北京邮电通信设备厂</t>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第二节邮电部北京通信元件厂</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>邮电506厂</t>
+          <t>邮电508厂</t>
         </is>
       </c>
       <c r="T131" t="n">
-        <v>1995</v>
+        <v>1990</v>
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>朝阳</t>
+          <t>西城</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>北京通信元件厂</t>
+          <t>北京长城无线电厂</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>半导体</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>半导体器件、高反压复合场效应晶体管、和销售BP机</t>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>19740000下放北京市</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5060,26 +5148,23 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>新街口外大街28号</t>
-        </is>
-      </c>
-      <c r="J132" t="n">
-        <v>450</v>
+          <t>学院南路34号</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>790</v>
       </c>
       <c r="L132" t="n">
-        <v>70000</v>
+        <v>36300</v>
       </c>
       <c r="M132" t="n">
-        <v>3040.9</v>
+        <v>3226</v>
       </c>
       <c r="N132" t="n">
-        <v>4423.4</v>
-      </c>
-      <c r="O132" t="n">
-        <v>12000</v>
+        <v>3523</v>
       </c>
       <c r="P132" t="n">
-        <v>360</v>
+        <v>12.9</v>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
@@ -5088,37 +5173,40 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二章中央在京电子工业企业·第二节邮电部北京通信元件厂</t>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第三节北京长城无线电厂</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>邮电508厂</t>
+          <t>国营第6971厂</t>
         </is>
       </c>
       <c r="T132" t="n">
-        <v>1990</v>
+        <v>1995</v>
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>西城</t>
+          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>北京长城无线电厂</t>
+          <t>北京核仪器厂</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>电子计算机</t>
-        </is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>19560000</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>19740000下放北京市</t>
+          <t>当时的北京市电器厂、北京市钻探机械厂、北京市公私合营电话器材厂和亚细亚商行喇叭组四单位合并-&gt;北京市综合仪器厂-&gt;19620000划归第二机械工业部-&gt;19630000二机部北京第十研究所合并</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5128,23 +5216,26 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>学院南路34号</t>
+          <t>东环北路42号</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>790</v>
+        <v>1307</v>
+      </c>
+      <c r="J133" t="n">
+        <v>348</v>
       </c>
       <c r="L133" t="n">
-        <v>36300</v>
-      </c>
-      <c r="M133" t="n">
-        <v>3226</v>
+        <v>181500</v>
       </c>
       <c r="N133" t="n">
-        <v>3523</v>
+        <v>2148</v>
+      </c>
+      <c r="O133" t="n">
+        <v>2201</v>
       </c>
       <c r="P133" t="n">
-        <v>12.9</v>
+        <v>287</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
@@ -5153,27 +5244,17 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二章中央在京电子工业企业·第三节北京长城无线电厂</t>
-        </is>
-      </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>国营第6971厂</t>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第四节北京核仪器厂</t>
         </is>
       </c>
       <c r="T133" t="n">
         <v>1995</v>
       </c>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t>海淀</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>北京核仪器厂</t>
+          <t>北京建中机器厂</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5182,12 +5263,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>19560000</v>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>当时的北京市电器厂、北京市钻探机械厂、北京市公私合营电话器材厂和亚细亚商行喇叭组四单位合并-&gt;北京市综合仪器厂-&gt;19620000划归第二机械工业部-&gt;19630000二机部北京第十研究所合并</t>
-        </is>
+        <v>19561000</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -5196,26 +5272,23 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>东环北路42号</t>
+          <t>酒仙桥万红路1号</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1307</v>
+        <v>1418</v>
       </c>
       <c r="J134" t="n">
-        <v>348</v>
+        <v>290</v>
       </c>
       <c r="L134" t="n">
-        <v>181500</v>
+        <v>133700</v>
       </c>
       <c r="N134" t="n">
-        <v>2148</v>
-      </c>
-      <c r="O134" t="n">
-        <v>2201</v>
+        <v>4348.8</v>
       </c>
       <c r="P134" t="n">
-        <v>287</v>
+        <v>138.5</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
@@ -5224,26 +5297,36 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二章中央在京电子工业企业·第四节北京核仪器厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第一节北京建中机器厂</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>国营第700厂</t>
         </is>
       </c>
       <c r="T134" t="n">
         <v>1995</v>
       </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>北京建中机器厂</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>半导体</t>
+          <t>北京市电声器材总厂</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>19561000</v>
+        <v>19800000</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>北京扬声器厂、北京无线电元件十四厂、北京广播电视配件四厂合并</t>
+        </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -5252,37 +5335,30 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>酒仙桥万红路1号</t>
+          <t>广安门内德泉胡同10号</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1418</v>
+        <v>722</v>
       </c>
       <c r="J135" t="n">
-        <v>290</v>
+        <v>39</v>
       </c>
       <c r="L135" t="n">
-        <v>133700</v>
+        <v>48500</v>
+      </c>
+      <c r="M135" t="n">
+        <v>3087</v>
       </c>
       <c r="N135" t="n">
-        <v>4348.8</v>
+        <v>1165</v>
       </c>
       <c r="P135" t="n">
-        <v>138.5</v>
-      </c>
-      <c r="Q135" t="inlineStr">
-        <is>
-          <t>行业据正文用词</t>
-        </is>
+        <v>48.2</v>
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第一节北京建中机器厂</t>
-        </is>
-      </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>国营第700厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十节北京市电声器材总厂</t>
         </is>
       </c>
       <c r="T135" t="n">
@@ -5290,22 +5366,27 @@
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>朝阳</t>
+          <t>宣武</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>北京市电声器材总厂</t>
+          <t>北京市无线电元件一厂</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>19800000</v>
+        <v>19680000</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>北京扬声器厂、北京无线电元件十四厂、北京广播电视配件四厂合并</t>
+          <t>19640000改名北京竹藤制品厂-&gt;19680000改名北京市无线电元件一厂</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5315,30 +5396,35 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>广安门内德泉胡同10号</t>
+          <t>德胜门外后九条小市口胡同1号</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>722</v>
+        <v>448</v>
       </c>
       <c r="J136" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="L136" t="n">
-        <v>48500</v>
+        <v>11500</v>
       </c>
       <c r="M136" t="n">
-        <v>3087</v>
+        <v>2209.8</v>
       </c>
       <c r="N136" t="n">
-        <v>1165</v>
+        <v>910.3</v>
       </c>
       <c r="P136" t="n">
-        <v>48.2</v>
+        <v>93.8</v>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十节北京市电声器材总厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十一节北京市无线电元件一厂</t>
         </is>
       </c>
       <c r="T136" t="n">
@@ -5346,27 +5432,22 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>宣武</t>
+          <t>西城</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>北京市无线电元件一厂</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>电子计算机</t>
+          <t>北京无线电元件四厂</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>19680000</v>
+        <v>19670000</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>19640000改名北京竹藤制品厂-&gt;19680000改名北京市无线电元件一厂</t>
+          <t>北京市石景山电容器厂-&gt;19780000划归北京市仪表工业局-&gt;19790000改名北京无线电元件四厂</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5376,35 +5457,30 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>德胜门外后九条小市口胡同1号</t>
+          <t>古城北路甲4号</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>448</v>
+        <v>511</v>
       </c>
       <c r="J137" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L137" t="n">
-        <v>11500</v>
+        <v>13700</v>
       </c>
       <c r="M137" t="n">
-        <v>2209.8</v>
+        <v>2090.4</v>
       </c>
       <c r="N137" t="n">
-        <v>910.3</v>
+        <v>3054</v>
       </c>
       <c r="P137" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="Q137" t="inlineStr">
-        <is>
-          <t>行业据正文用词</t>
-        </is>
+        <v>416.1</v>
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十一节北京市无线电元件一厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十三节北京无线电元件四厂</t>
         </is>
       </c>
       <c r="T137" t="n">
@@ -5412,22 +5488,32 @@
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>西城</t>
+          <t>石景山</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>北京无线电元件四厂</t>
+          <t>北京市无线电元件六厂</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>计算机、收录机</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>19670000</v>
+        <v>19700100</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>北京市石景山电容器厂-&gt;19780000划归北京市仪表工业局-&gt;19790000改名北京无线电元件四厂</t>
+          <t>19720300年8月与北京皮毛三厂合并-&gt;19790300并入北京市无线电元件六厂</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -5437,30 +5523,32 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>古城北路甲4号</t>
+          <t>北京站东街10号</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>511</v>
+        <v>747</v>
       </c>
       <c r="J138" t="n">
-        <v>51</v>
+        <v>108</v>
       </c>
       <c r="L138" t="n">
-        <v>13700</v>
+        <v>12600</v>
       </c>
       <c r="M138" t="n">
-        <v>2090.4</v>
-      </c>
-      <c r="N138" t="n">
-        <v>3054</v>
+        <v>1844.3</v>
       </c>
       <c r="P138" t="n">
-        <v>416.1</v>
+        <v>0.1</v>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十三节北京无线电元件四厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十四节北京市无线电元件六厂</t>
         </is>
       </c>
       <c r="T138" t="n">
@@ -5468,14 +5556,14 @@
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>石景山</t>
+          <t>东城</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>北京市无线电元件六厂</t>
+          <t>北京无线电元件九厂</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5483,17 +5571,12 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>计算机、收录机</t>
-        </is>
-      </c>
       <c r="D139" t="n">
-        <v>19700100</v>
+        <v>19600000</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>19720300年8月与北京皮毛三厂合并-&gt;19790300并入北京市无线电元件六厂</t>
+          <t>北京市东城区无线电元件厂-&gt;19620000改名北京无线电插接元件厂-&gt;19790000改名北京无线电元件九厂</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5503,23 +5586,29 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>北京站东街10号</t>
+          <t>深沟村</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>747</v>
+        <v>785</v>
       </c>
       <c r="J139" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="L139" t="n">
-        <v>12600</v>
+        <v>51700</v>
       </c>
       <c r="M139" t="n">
-        <v>1844.3</v>
+        <v>3258.4</v>
+      </c>
+      <c r="N139" t="n">
+        <v>3182</v>
+      </c>
+      <c r="O139" t="n">
+        <v>905.8</v>
       </c>
       <c r="P139" t="n">
-        <v>0.1</v>
+        <v>143.5</v>
       </c>
       <c r="Q139" t="inlineStr">
         <is>
@@ -5528,7 +5617,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十四节北京市无线电元件六厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十五节北京无线电元件九厂</t>
         </is>
       </c>
       <c r="T139" t="n">
@@ -5536,27 +5625,27 @@
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>东城</t>
+          <t>朝阳</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>北京无线电元件九厂</t>
+          <t>北京市半导体器件一厂</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>电子计算机</t>
+          <t>半导体</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>19600000</v>
+        <v>19650000</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>北京市东城区无线电元件厂-&gt;19620000改名北京无线电插接元件厂-&gt;19790000改名北京无线电元件九厂</t>
+          <t>组建的北京市无线电综合元件厂-&gt;19780600改名北京市半导体器件一厂</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5566,38 +5655,35 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>深沟村</t>
+          <t>幸福三村北街1号</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>785</v>
+        <v>874</v>
       </c>
       <c r="J140" t="n">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="L140" t="n">
-        <v>51700</v>
+        <v>33700</v>
       </c>
       <c r="M140" t="n">
-        <v>3258.4</v>
+        <v>4427.5</v>
       </c>
       <c r="N140" t="n">
-        <v>3182</v>
-      </c>
-      <c r="O140" t="n">
-        <v>905.8</v>
+        <v>889</v>
       </c>
       <c r="P140" t="n">
-        <v>143.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>行业据正文用词</t>
+          <t>行业据单位名</t>
         </is>
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十五节北京无线电元件九厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十七节北京市半导体器件一厂</t>
         </is>
       </c>
       <c r="T140" t="n">
@@ -5612,7 +5698,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>北京市半导体器件一厂</t>
+          <t>北京市半导体器件三厂</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5620,12 +5706,20 @@
           <t>半导体</t>
         </is>
       </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>错三极管、中高档电子琴音律发生器电路</t>
+        </is>
+      </c>
       <c r="D141" t="n">
-        <v>19650000</v>
+        <v>19680000</v>
+      </c>
+      <c r="E141" t="n">
+        <v>19680000</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>组建的北京市无线电综合元件厂-&gt;19780600改名北京市半导体器件一厂</t>
+          <t>北京市第二轻工业局所属的金漆厂、玉器厂和象牙厂合并-&gt;19730900划归北京市位器仪表工业局领导后</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5635,26 +5729,23 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>幸福三村北街1号</t>
+          <t>龙潭路3号</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>874</v>
+        <v>813</v>
       </c>
       <c r="J141" t="n">
-        <v>192</v>
+        <v>126</v>
       </c>
       <c r="L141" t="n">
-        <v>33700</v>
-      </c>
-      <c r="M141" t="n">
-        <v>4427.5</v>
+        <v>40500</v>
       </c>
       <c r="N141" t="n">
-        <v>889</v>
+        <v>1058.8</v>
       </c>
       <c r="P141" t="n">
-        <v>78.40000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
@@ -5663,7 +5754,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十七节北京市半导体器件一厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十八节北京市半导体器件三厂</t>
         </is>
       </c>
       <c r="T141" t="n">
@@ -5671,14 +5762,14 @@
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>朝阳</t>
+          <t>崇文</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>北京市半导体器件三厂</t>
+          <t>北京半导体器件五厂</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5686,20 +5777,12 @@
           <t>半导体</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>错三极管、中高档电子琴音律发生器电路</t>
-        </is>
-      </c>
       <c r="D142" t="n">
-        <v>19680000</v>
-      </c>
-      <c r="E142" t="n">
-        <v>19680000</v>
+        <v>19690900</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>北京市第二轻工业局所属的金漆厂、玉器厂和象牙厂合并-&gt;19730900划归北京市位器仪表工业局领导后</t>
+          <t>北京市西城区半导体器件厂-&gt;19780400改名北京半导体器件五厂</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5709,23 +5792,26 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>龙潭路3号</t>
+          <t>德胜门外五路通14号</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>813</v>
+        <v>635</v>
       </c>
       <c r="J142" t="n">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="L142" t="n">
-        <v>40500</v>
+        <v>21000</v>
       </c>
       <c r="N142" t="n">
-        <v>1058.8</v>
+        <v>1141</v>
+      </c>
+      <c r="O142" t="n">
+        <v>1466</v>
       </c>
       <c r="P142" t="n">
-        <v>83.7</v>
+        <v>89.8</v>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
@@ -5734,7 +5820,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十八节北京市半导体器件三厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十九节北京半导体器件五厂</t>
         </is>
       </c>
       <c r="T142" t="n">
@@ -5742,14 +5828,14 @@
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>崇文</t>
+          <t>西城</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>北京半导体器件五厂</t>
+          <t>北京市半导体器件六厂</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5758,11 +5844,11 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>19690900</v>
+        <v>19800000</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>北京市西城区半导体器件厂-&gt;19780400改名北京半导体器件五厂</t>
+          <t>合并后的器件六厂-&gt;原北京市半导体器件六厂与北京市半导体器件七厂合并</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -5770,28 +5856,20 @@
           <t>Beijing</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>德胜门外五路通14号</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>635</v>
+        <v>482</v>
       </c>
       <c r="J143" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="L143" t="n">
-        <v>21000</v>
+        <v>10600</v>
       </c>
       <c r="N143" t="n">
-        <v>1141</v>
-      </c>
-      <c r="O143" t="n">
-        <v>1466</v>
+        <v>4546</v>
       </c>
       <c r="P143" t="n">
-        <v>89.8</v>
+        <v>97.8</v>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
@@ -5800,7 +5878,12 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十九节北京半导体器件五厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第四十节北京市半导体器件六厂</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>半导体器件六厂</t>
         </is>
       </c>
       <c r="T143" t="n">
@@ -5808,14 +5891,14 @@
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>西城</t>
+          <t>宣武</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>北京市半导体器件六厂</t>
+          <t>北京市可控硅元件厂</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5824,11 +5907,11 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>19800000</v>
+        <v>19680000</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>合并后的器件六厂-&gt;原北京市半导体器件六厂与北京市半导体器件七厂合并</t>
+          <t>北京市朝阳可控硅元件厂-&gt;19680000改名朝外大街乒乓球拍厂-&gt;19780000改名北京半导体材料加工厂</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -5836,20 +5919,28 @@
           <t>Beijing</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>建国门外砖厂胡同12号</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>482</v>
+        <v>292</v>
       </c>
       <c r="J144" t="n">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="L144" t="n">
-        <v>10600</v>
+        <v>16500</v>
       </c>
       <c r="N144" t="n">
-        <v>4546</v>
+        <v>456</v>
+      </c>
+      <c r="O144" t="n">
+        <v>350.1</v>
       </c>
       <c r="P144" t="n">
-        <v>97.8</v>
+        <v>19.4</v>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
@@ -5858,27 +5949,17 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第四十节北京市半导体器件六厂</t>
-        </is>
-      </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>半导体器件六厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第四十一节北京市可控硅元件厂</t>
         </is>
       </c>
       <c r="T144" t="n">
         <v>1995</v>
       </c>
-      <c r="U144" t="inlineStr">
-        <is>
-          <t>宣武</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>北京市可控硅元件厂</t>
+          <t>北京701厂</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5886,12 +5967,14 @@
           <t>半导体</t>
         </is>
       </c>
-      <c r="D145" t="n">
-        <v>19680000</v>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>微波二极管</t>
+        </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>北京市朝阳可控硅元件厂-&gt;19680000改名朝外大街乒乓球拍厂-&gt;19780000改名北京半导体材料加工厂</t>
+          <t>19700000第四机械工业部-&gt;19790000朝阳器件厂合并</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -5901,35 +5984,38 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>建国门外砖厂胡同12号</t>
+          <t>双桥西里7号</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>292</v>
+        <v>832</v>
       </c>
       <c r="J145" t="n">
-        <v>27</v>
+        <v>114</v>
       </c>
       <c r="L145" t="n">
-        <v>16500</v>
+        <v>21800</v>
+      </c>
+      <c r="M145" t="n">
+        <v>1885.1</v>
       </c>
       <c r="N145" t="n">
-        <v>456</v>
+        <v>1947</v>
       </c>
       <c r="O145" t="n">
-        <v>350.1</v>
+        <v>1754.9</v>
       </c>
       <c r="P145" t="n">
-        <v>19.4</v>
+        <v>12</v>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>行业据单位名</t>
+          <t>行业据正文用词</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第四十一节北京市可控硅元件厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第四十二节北京七〇一厂</t>
         </is>
       </c>
       <c r="T145" t="n">
@@ -5939,22 +6025,25 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>北京701厂</t>
+          <t>北京无线电工具设备厂</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>外围设备</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>微波二极管</t>
-        </is>
+          <t>球磨机、油压机、游丝辗压机、自动刺铆机</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>19640000</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>19700000第四机械工业部-&gt;19790000朝阳器件厂合并</t>
+          <t>合并组建为北京无线电工具设备厂</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -5964,29 +6053,20 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>双桥西里7号</t>
+          <t>酒仙桥路2号</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>832</v>
+        <v>1269</v>
       </c>
       <c r="J146" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="L146" t="n">
-        <v>21800</v>
+        <v>107000</v>
       </c>
       <c r="M146" t="n">
-        <v>1885.1</v>
-      </c>
-      <c r="N146" t="n">
-        <v>1947</v>
-      </c>
-      <c r="O146" t="n">
-        <v>1754.9</v>
-      </c>
-      <c r="P146" t="n">
-        <v>12</v>
+        <v>5295.9</v>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
@@ -5995,35 +6075,40 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第四十二节北京七〇一厂</t>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第二节北京无线电工具设备厂</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>国营第706厂</t>
         </is>
       </c>
       <c r="T146" t="n">
         <v>1995</v>
       </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>朝阳</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>北京无线电工具设备厂</t>
+          <t>北京晨星无线电器材厂</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>外围设备</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>球磨机、油压机、游丝辗压机、自动刺铆机</t>
+          <t>电子计算机</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>19640000</v>
+        <v>19500000</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>合并组建为北京无线电工具设备厂</t>
+          <t>19590000并入华北无线电器材联合厂为七分厂</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -6037,16 +6122,16 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1269</v>
-      </c>
-      <c r="J147" t="n">
-        <v>123</v>
+        <v>1513</v>
       </c>
       <c r="L147" t="n">
-        <v>107000</v>
-      </c>
-      <c r="M147" t="n">
-        <v>5295.9</v>
+        <v>49100</v>
+      </c>
+      <c r="N147" t="n">
+        <v>8709.5</v>
+      </c>
+      <c r="P147" t="n">
+        <v>130.9</v>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
@@ -6055,12 +6140,12 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二章中央在京电子工业企业·第二节北京无线电工具设备厂</t>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第三节北京晨星无线电器材厂</t>
         </is>
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>国营第706厂</t>
+          <t>国营第707厂</t>
         </is>
       </c>
       <c r="T147" t="n">
@@ -6075,7 +6160,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>北京晨星无线电器材厂</t>
+          <t>北京北大方正集团公司</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6083,12 +6168,17 @@
           <t>电子计算机</t>
         </is>
       </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>制造的5大系列电脑</t>
+        </is>
+      </c>
       <c r="D148" t="n">
-        <v>19500000</v>
+        <v>19860000</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>19590000并入华北无线电器材联合厂为七分厂</t>
+          <t>北京大学新技术公司</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -6096,22 +6186,26 @@
           <t>Beijing</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>酒仙桥路2号</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>1513</v>
+        <v>672</v>
+      </c>
+      <c r="J148" t="n">
+        <v>404</v>
       </c>
       <c r="L148" t="n">
-        <v>49100</v>
+        <v>12000</v>
+      </c>
+      <c r="M148" t="n">
+        <v>4217.4</v>
       </c>
       <c r="N148" t="n">
-        <v>8709.5</v>
+        <v>13200</v>
+      </c>
+      <c r="O148" t="n">
+        <v>84700</v>
       </c>
       <c r="P148" t="n">
-        <v>130.9</v>
+        <v>9443.1</v>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
@@ -6120,12 +6214,12 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二章中央在京电子工业企业·第三节北京晨星无线电器材厂</t>
+          <t>北京工业志·电子志·第三章行业归口电子工业企业·第三节北京北大方正集团公司</t>
         </is>
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>国营第707厂</t>
+          <t>北大方正集团公司</t>
         </is>
       </c>
       <c r="T148" t="n">
@@ -6133,14 +6227,14 @@
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>朝阳</t>
+          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>北京北大方正集团公司</t>
+          <t>北京京海集团公司</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6148,17 +6242,12 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>制造的5大系列电脑</t>
-        </is>
-      </c>
       <c r="D149" t="n">
-        <v>19860000</v>
+        <v>19830700</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>北京大学新技术公司</t>
+          <t>计算机机房技术开发公司</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -6166,26 +6255,25 @@
           <t>Beijing</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>白石桥络33号</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>672</v>
+        <v>727</v>
       </c>
       <c r="J149" t="n">
-        <v>404</v>
+        <v>349</v>
       </c>
       <c r="L149" t="n">
-        <v>12000</v>
+        <v>2268</v>
       </c>
       <c r="M149" t="n">
-        <v>4217.4</v>
-      </c>
-      <c r="N149" t="n">
-        <v>13200</v>
+        <v>8674</v>
       </c>
       <c r="O149" t="n">
-        <v>84700</v>
-      </c>
-      <c r="P149" t="n">
-        <v>9443.1</v>
+        <v>45599.99999999999</v>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
@@ -6194,12 +6282,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章行业归口电子工业企业·第三节北京北大方正集团公司</t>
-        </is>
-      </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>北大方正集团公司</t>
+          <t>北京工业志·电子志·第三章行业归口电子工业企业·第四节北京京海集团公司</t>
         </is>
       </c>
       <c r="T149" t="n">
@@ -6214,21 +6297,16 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>北京京海集团公司</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>电子计算机</t>
+          <t>北京·松下彩色显像管有限公司</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>14型球面彩色显像管、线并行生产两个品种的彩管、两个品种的彩管</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>19830700</v>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>计算机机房技术开发公司</t>
-        </is>
+        <v>19870900</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -6237,32 +6315,35 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>白石桥络33号</t>
+          <t>酒仙桥北路9号</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>727</v>
+        <v>4180</v>
       </c>
       <c r="J150" t="n">
-        <v>349</v>
+        <v>570</v>
       </c>
       <c r="L150" t="n">
-        <v>2268</v>
+        <v>136000</v>
       </c>
       <c r="M150" t="n">
-        <v>8674</v>
-      </c>
-      <c r="O150" t="n">
-        <v>45599.99999999999</v>
-      </c>
-      <c r="Q150" t="inlineStr">
-        <is>
-          <t>行业据正文用词</t>
-        </is>
+        <v>159200</v>
+      </c>
+      <c r="N150" t="n">
+        <v>274300</v>
+      </c>
+      <c r="P150" t="n">
+        <v>12020</v>
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章行业归口电子工业企业·第四节北京京海集团公司</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第一节北京·松下彩色显像管有限公司</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>BMCC</t>
         </is>
       </c>
       <c r="T150" t="n">
@@ -6270,23 +6351,23 @@
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>海淀</t>
+          <t>朝阳</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>北京·松下彩色显像管有限公司</t>
+          <t>北京飞利浦有限公司</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>14型球面彩色显像管、线并行生产两个品种的彩管、两个品种的彩管</t>
+          <t>经营值携式收录机</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>19870900</v>
+        <v>19850810</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -6295,35 +6376,33 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>酒仙桥北路9号</t>
+          <t>北洼路4号</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>4180</v>
+        <v>647</v>
       </c>
       <c r="J151" t="n">
-        <v>570</v>
+        <v>85</v>
       </c>
       <c r="L151" t="n">
-        <v>136000</v>
+        <v>8000</v>
       </c>
       <c r="M151" t="n">
-        <v>159200</v>
+        <v>2187.9</v>
       </c>
       <c r="N151" t="n">
-        <v>274300</v>
+        <v>33000</v>
+      </c>
+      <c r="O151" t="n">
+        <v>21800</v>
       </c>
       <c r="P151" t="n">
-        <v>12020</v>
+        <v>1021.5</v>
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第一节北京·松下彩色显像管有限公司</t>
-        </is>
-      </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>BMCC</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第三节北京飞利浦有限公司</t>
         </is>
       </c>
       <c r="T151" t="n">
@@ -6331,23 +6410,28 @@
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>朝阳</t>
+          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>北京飞利浦有限公司</t>
+          <t>中国惠普有限公司</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>经营值携式收录机</t>
+          <t>经营业务范围包括计算机系统及微机</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>19850810</v>
+        <v>19850600</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -6356,33 +6440,37 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>北洼路4号</t>
+          <t>建国门外东三环南路2号</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>647</v>
+        <v>585</v>
       </c>
       <c r="J152" t="n">
-        <v>85</v>
-      </c>
-      <c r="L152" t="n">
-        <v>8000</v>
+        <v>358</v>
       </c>
       <c r="M152" t="n">
-        <v>2187.9</v>
+        <v>8758.299999999999</v>
       </c>
       <c r="N152" t="n">
-        <v>33000</v>
-      </c>
-      <c r="O152" t="n">
-        <v>21800</v>
+        <v>3763</v>
       </c>
       <c r="P152" t="n">
-        <v>1021.5</v>
+        <v>32700</v>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第三节北京飞利浦有限公司</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第四节中国惠普有限公司</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>CHP</t>
         </is>
       </c>
       <c r="T152" t="n">
@@ -6390,14 +6478,14 @@
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>海淀</t>
+          <t>朝阳</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>中国惠普有限公司</t>
+          <t>北京有线电总厂</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6407,11 +6495,16 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>经营业务范围包括计算机系统及微机</t>
+          <t>生产步进制自动电话交换机、步进制自动电话交换机、生产纵横制自动电话交换机、纵横制自动电话交换机、生产微型计算机、微型计算机、0520CH机、生产10台BCM0530机</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>19850600</v>
+        <v>19570900</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>北京有线电厂</t>
+        </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -6420,23 +6513,23 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>建国门外东三环南路2号</t>
+          <t>酒仙桥路14号</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>585</v>
-      </c>
-      <c r="J153" t="n">
-        <v>358</v>
+        <v>3259</v>
+      </c>
+      <c r="L153" t="n">
+        <v>321700</v>
       </c>
       <c r="M153" t="n">
-        <v>8758.299999999999</v>
+        <v>18700</v>
       </c>
       <c r="N153" t="n">
-        <v>3763</v>
+        <v>54800.00000000001</v>
       </c>
       <c r="P153" t="n">
-        <v>32700</v>
+        <v>3202</v>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
@@ -6445,12 +6538,12 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第四节中国惠普有限公司</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第七节北京有线电总厂</t>
         </is>
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>CHP</t>
+          <t>国营738厂、北京有线电厂、国营有线电厂</t>
         </is>
       </c>
       <c r="T153" t="n">
@@ -6465,7 +6558,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>北京有线电总厂</t>
+          <t>北京·松下电子部品有限公司</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6475,41 +6568,28 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>生产步进制自动电话交换机、步进制自动电话交换机、生产纵横制自动电话交换机、纵横制自动电话交换机</t>
+          <t>销售电视机</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>19570900</v>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>北京有线电厂</t>
-        </is>
+        <v>19930900</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>酒仙桥路14号</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>3259</v>
+        <v>720</v>
+      </c>
+      <c r="J154" t="n">
+        <v>130</v>
       </c>
       <c r="L154" t="n">
-        <v>321700</v>
-      </c>
-      <c r="M154" t="n">
-        <v>18700</v>
+        <v>19600</v>
       </c>
       <c r="N154" t="n">
-        <v>54800.00000000001</v>
-      </c>
-      <c r="P154" t="n">
-        <v>3202</v>
+        <v>30900</v>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
@@ -6518,7 +6598,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第七节北京有线电总厂</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第六节北京·松下电子部品有限公司</t>
         </is>
       </c>
       <c r="T154" t="n">
@@ -6533,38 +6613,46 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>北京·松下电子部品有限公司</t>
+          <t>北京第一无线电器材厂</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>电子计算机</t>
+          <t>半导体</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>销售电视机</t>
+          <t>电子节能灯等显示管、收录音机</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>19930900</v>
+        <v>19571000</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>酒仙桥路2号</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>720</v>
+        <v>2050</v>
       </c>
       <c r="J155" t="n">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="L155" t="n">
-        <v>19600</v>
+        <v>120000</v>
       </c>
       <c r="N155" t="n">
-        <v>30900</v>
+        <v>3771</v>
+      </c>
+      <c r="P155" t="n">
+        <v>163.8</v>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
@@ -6573,7 +6661,12 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第六节北京·松下电子部品有限公司</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第四节北京第一无线电器材厂</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>国营第797厂</t>
         </is>
       </c>
       <c r="T155" t="n">
@@ -6588,7 +6681,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>北京第一无线电器材厂</t>
+          <t>北京第二无线电器材厂</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -6596,13 +6689,8 @@
           <t>半导体</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>电子节能灯等显示管、收录音机</t>
-        </is>
-      </c>
       <c r="D156" t="n">
-        <v>19571000</v>
+        <v>19640000</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -6611,23 +6699,26 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>酒仙桥路2号</t>
+          <t>酒仙桥路4号</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2050</v>
+        <v>1529</v>
       </c>
       <c r="J156" t="n">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="L156" t="n">
-        <v>120000</v>
+        <v>104100</v>
+      </c>
+      <c r="M156" t="n">
+        <v>10000</v>
       </c>
       <c r="N156" t="n">
-        <v>3771</v>
+        <v>3686</v>
       </c>
       <c r="P156" t="n">
-        <v>163.8</v>
+        <v>111.3</v>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
@@ -6636,12 +6727,12 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第四节北京第一无线电器材厂</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第五节北京第二无线电器材厂</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>国营第797厂</t>
+          <t>国营第718厂</t>
         </is>
       </c>
       <c r="T156" t="n">
@@ -6656,7 +6747,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>北京第二无线电器材厂</t>
+          <t>北京电子动力公司</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -6665,7 +6756,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>19640000</v>
+        <v>19570000</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -6678,22 +6769,19 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1529</v>
+        <v>2847</v>
       </c>
       <c r="J157" t="n">
-        <v>67</v>
+        <v>237</v>
       </c>
       <c r="L157" t="n">
-        <v>104100</v>
-      </c>
-      <c r="M157" t="n">
-        <v>10000</v>
+        <v>319000</v>
       </c>
       <c r="N157" t="n">
-        <v>3686</v>
+        <v>11900</v>
       </c>
       <c r="P157" t="n">
-        <v>111.3</v>
+        <v>366</v>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
@@ -6702,12 +6790,12 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第五节北京第二无线电器材厂</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第八节北京电子动力公司</t>
         </is>
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>国营第718厂</t>
+          <t>国营第751厂</t>
         </is>
       </c>
       <c r="T157" t="n">
@@ -6722,7 +6810,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>北京电子动力公司</t>
+          <t>北京大华无线电仪器厂</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -6731,7 +6819,15 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>19570000</v>
+        <v>19580800</v>
+      </c>
+      <c r="E158" t="n">
+        <v>19841200</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>北京微技测量仪器厂</t>
+        </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -6740,23 +6836,26 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>酒仙桥路4号</t>
+          <t>学院路5号</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2847</v>
+        <v>1258</v>
       </c>
       <c r="J158" t="n">
-        <v>237</v>
+        <v>298</v>
       </c>
       <c r="L158" t="n">
-        <v>319000</v>
-      </c>
-      <c r="N158" t="n">
-        <v>11900</v>
+        <v>192000</v>
+      </c>
+      <c r="M158" t="n">
+        <v>742.6</v>
+      </c>
+      <c r="O158" t="n">
+        <v>2282.7</v>
       </c>
       <c r="P158" t="n">
-        <v>366</v>
+        <v>624.2</v>
       </c>
       <c r="Q158" t="inlineStr">
         <is>
@@ -6765,12 +6864,7 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第八节北京电子动力公司</t>
-        </is>
-      </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>国营第751厂</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第十节北京大华无线电仪器厂</t>
         </is>
       </c>
       <c r="T158" t="n">
@@ -6778,14 +6872,14 @@
       </c>
       <c r="U158" t="inlineStr">
         <is>
-          <t>朝阳</t>
+          <t>海淀</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>北京大华无线电仪器厂</t>
+          <t>北京东方电子集团股份有限公司</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -6793,15 +6887,17 @@
           <t>半导体</t>
         </is>
       </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>18种电子管</t>
+        </is>
+      </c>
       <c r="D159" t="n">
-        <v>19580800</v>
-      </c>
-      <c r="E159" t="n">
-        <v>19841200</v>
+        <v>19520000</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>北京微技测量仪器厂</t>
+          <t>19920618组建了北京东方电子集团公司-&gt;19930408组建为北京东方电子集团股份有限公司</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -6811,26 +6907,17 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>学院路5号</t>
-        </is>
-      </c>
-      <c r="I159" t="n">
-        <v>1258</v>
-      </c>
-      <c r="J159" t="n">
-        <v>298</v>
+          <t>酒仙桥路10号</t>
+        </is>
       </c>
       <c r="L159" t="n">
-        <v>192000</v>
+        <v>320000</v>
       </c>
       <c r="M159" t="n">
-        <v>742.6</v>
-      </c>
-      <c r="O159" t="n">
-        <v>2282.7</v>
+        <v>25000</v>
       </c>
       <c r="P159" t="n">
-        <v>624.2</v>
+        <v>1859</v>
       </c>
       <c r="Q159" t="inlineStr">
         <is>
@@ -6839,7 +6926,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第十节北京大华无线电仪器厂</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第十一节 北京东方电子集团股份有限公司</t>
         </is>
       </c>
       <c r="T159" t="n">
@@ -6847,14 +6934,14 @@
       </c>
       <c r="U159" t="inlineStr">
         <is>
-          <t>海淀</t>
+          <t>朝阳</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>北京东方电子集团股份有限公司</t>
+          <t>北京飞行电子总公司</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -6862,17 +6949,12 @@
           <t>半导体</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>18种电子管</t>
-        </is>
-      </c>
       <c r="D160" t="n">
-        <v>19520000</v>
+        <v>19640000</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>19920618组建了北京东方电子集团公司-&gt;19930408组建为北京东方电子集团股份有限公司</t>
+          <t>19571000北京第三无线电器材厂</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -6882,17 +6964,26 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>酒仙桥路10号</t>
-        </is>
+          <t>酒仙桥路4号</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>2639</v>
+      </c>
+      <c r="J160" t="n">
+        <v>285</v>
       </c>
       <c r="L160" t="n">
-        <v>320000</v>
+        <v>211700</v>
       </c>
       <c r="M160" t="n">
-        <v>25000</v>
+        <v>13600</v>
+      </c>
+      <c r="N160" t="n">
+        <v>8188</v>
       </c>
       <c r="P160" t="n">
-        <v>1859</v>
+        <v>45.8</v>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
@@ -6901,7 +6992,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第十一节 北京东方电子集团股份有限公司</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第六节北京飞行电子总公司</t>
         </is>
       </c>
       <c r="T160" t="n">
@@ -6916,49 +7007,30 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>北京飞行电子总公司</t>
+          <t>北京市电镀总厂</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>电子计算机</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>19640000</v>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>19571000北京第三无线电器材厂</t>
-        </is>
+        <v>19580000</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>酒仙桥路4号</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>2639</v>
+        <v>488</v>
       </c>
       <c r="J161" t="n">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="L161" t="n">
-        <v>211700</v>
-      </c>
-      <c r="M161" t="n">
-        <v>13600</v>
-      </c>
-      <c r="N161" t="n">
-        <v>8188</v>
-      </c>
-      <c r="P161" t="n">
-        <v>45.8</v>
+        <v>24800</v>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
@@ -6967,7 +7039,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第六节北京飞行电子总公司</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第二十九节北京市电镀总厂</t>
         </is>
       </c>
       <c r="T161" t="n">
@@ -6982,39 +7054,46 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>北京市电镀总厂</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>电子计算机</t>
+          <t>北京市无线电元件二厂</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>19580000</v>
+        <v>19681200</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>德胜门外塔院胡同8号</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>488</v>
+        <v>540</v>
       </c>
       <c r="J162" t="n">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="L162" t="n">
-        <v>24800</v>
-      </c>
-      <c r="Q162" t="inlineStr">
-        <is>
-          <t>行业据正文用词</t>
-        </is>
+        <v>4887</v>
+      </c>
+      <c r="M162" t="n">
+        <v>1796.9</v>
+      </c>
+      <c r="N162" t="n">
+        <v>1614</v>
+      </c>
+      <c r="O162" t="n">
+        <v>989.1</v>
+      </c>
+      <c r="P162" t="n">
+        <v>79.59999999999999</v>
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第二十九节北京市电镀总厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十二节北京市无线电元件二厂</t>
         </is>
       </c>
       <c r="T162" t="n">
@@ -7022,18 +7101,18 @@
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>朝阳</t>
+          <t>西城</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>北京市无线电元件二厂</t>
+          <t>北京市无线电元件十厂</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>19681200</v>
+        <v>19710000</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -7042,129 +7121,131 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>德胜门外塔院胡同8号</t>
+          <t>朝阳门外二条67号</t>
         </is>
       </c>
       <c r="I163" t="n">
-        <v>540</v>
+        <v>654</v>
       </c>
       <c r="J163" t="n">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="L163" t="n">
-        <v>4887</v>
+        <v>56300</v>
       </c>
       <c r="M163" t="n">
-        <v>1796.9</v>
+        <v>3673</v>
       </c>
       <c r="N163" t="n">
-        <v>1614</v>
-      </c>
-      <c r="O163" t="n">
-        <v>989.1</v>
+        <v>4742</v>
       </c>
       <c r="P163" t="n">
-        <v>79.59999999999999</v>
+        <v>54.8</v>
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十二节北京市无线电元件二厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十六节北京市无线电元件十厂</t>
         </is>
       </c>
       <c r="T163" t="n">
         <v>1995</v>
       </c>
-      <c r="U163" t="inlineStr">
-        <is>
-          <t>西城</t>
-        </is>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>北京市无线电元件十厂</t>
+          <t>北京国兴电子有限公司</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>半导体</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>19710000</v>
+        <v>19880400</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>朝阳门外二条67号</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>654</v>
+        <v>775</v>
       </c>
       <c r="J164" t="n">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="L164" t="n">
-        <v>56300</v>
-      </c>
-      <c r="M164" t="n">
-        <v>3673</v>
+        <v>10400</v>
       </c>
       <c r="N164" t="n">
-        <v>4742</v>
-      </c>
-      <c r="P164" t="n">
-        <v>54.8</v>
+        <v>10400</v>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>行业据正文用词</t>
+        </is>
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十六节北京市无线电元件十厂</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第二节北京国兴电子有限公司</t>
         </is>
       </c>
       <c r="T164" t="n">
         <v>1995</v>
       </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>海淀</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>北京国兴电子有限公司</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>半导体</t>
+          <t>北京国际交换系统有限公司</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>19880400</v>
+        <v>19901100</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>酒仙桥路14号</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>775</v>
+        <v>1108</v>
       </c>
       <c r="J165" t="n">
-        <v>132</v>
+        <v>404</v>
       </c>
       <c r="L165" t="n">
-        <v>10400</v>
+        <v>3929</v>
       </c>
       <c r="N165" t="n">
-        <v>10400</v>
+        <v>110400</v>
+      </c>
+      <c r="O165" t="n">
+        <v>102300</v>
+      </c>
+      <c r="P165" t="n">
+        <v>24000</v>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>行业据正文用词</t>
+          <t>另有他年数字:floor=1990年</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第二节北京国兴电子有限公司</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第五节北京国际交换系统有限公司</t>
         </is>
       </c>
       <c r="T165" t="n">
@@ -7172,70 +7253,36 @@
       </c>
       <c r="U165" t="inlineStr">
         <is>
-          <t>海淀</t>
+          <t>朝阳</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>北京国际交换系统有限公司</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>19901100</v>
+          <t>北京电视机厂</t>
+        </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
           <t>Beijing</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>酒仙桥路14号</t>
-        </is>
-      </c>
-      <c r="I166" t="n">
-        <v>1108</v>
-      </c>
-      <c r="J166" t="n">
-        <v>404</v>
-      </c>
-      <c r="L166" t="n">
-        <v>3929</v>
-      </c>
-      <c r="N166" t="n">
-        <v>110400</v>
-      </c>
-      <c r="O166" t="n">
-        <v>102300</v>
-      </c>
-      <c r="P166" t="n">
-        <v>24000</v>
-      </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>另有他年数字:floor=1990年</t>
+          <t>志中未见专条,仅由他条提及</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第五节北京国际交换系统有限公司</t>
-        </is>
-      </c>
-      <c r="T166" t="n">
-        <v>1995</v>
-      </c>
-      <c r="U166" t="inlineStr">
-        <is>
-          <t>朝阳</t>
+          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>北京电视机厂</t>
+          <t>北京电子显示设各厂</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -7257,7 +7304,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>北京电子显示设各厂</t>
+          <t>北京市无线电元件三厂</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -7279,7 +7326,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>北京市无线电元件三厂</t>
+          <t>国营761厂</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -7294,14 +7341,14 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
+          <t>北京工业志·电子志·第十四节北京电视设备厂</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>国营761厂</t>
+          <t>公私合营广播器材厂</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -7316,14 +7363,14 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十四节北京电视设备厂</t>
+          <t>北京工业志·电子志·第十五节北京无线电厂</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>公私合营广播器材厂</t>
+          <t>北京电子仪器厂</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -7345,7 +7392,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>北京电子仪器厂</t>
+          <t>北京录音机厂</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -7360,14 +7407,14 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十五节北京无线电厂</t>
+          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>北京录音机厂</t>
+          <t>北京鸿达电器公司</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -7389,7 +7436,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>北京鸿达电器公司</t>
+          <t>北京飞达电子有限公司</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -7411,7 +7458,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>北京飞达电子有限公司</t>
+          <t>北京市半导体器件五厂</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>半导体</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -7421,24 +7473,19 @@
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>志中未见专条,仅由他条提及</t>
+          <t>志中未见专条,仅由他条提及；行业据单位名</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
+          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>北京市半导体器件五厂</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>半导体</t>
+          <t>北京显像管厂</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -7448,7 +7495,7 @@
       </c>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>志中未见专条,仅由他条提及；行业据单位名</t>
+          <t>志中未见专条,仅由他条提及</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
@@ -7460,7 +7507,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>北京显像管厂</t>
+          <t>北京无线电电匣厂</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -7475,14 +7522,14 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
+          <t>北京工业志·电子志·第十九节北京广播电视配件一厂</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>北京无线电电匣厂</t>
+          <t>北京安乐福塑料制品有限公司</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -7504,7 +7551,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>北京安乐福塑料制品有限公司</t>
+          <t>北京松下彩色显像管有限公司</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -7519,14 +7566,14 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十九节北京广播电视配件一厂</t>
+          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>北京松下彩色显像管有限公司</t>
+          <t>北京无线电二厂</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -7541,14 +7588,14 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
+          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>北京无线电二厂</t>
+          <t>北京人民广播器材厂</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -7570,7 +7617,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>北京人民广播器材厂</t>
+          <t>华北无线电器材联合厂</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -7592,7 +7639,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>华北无线电器材联合厂</t>
+          <t>国营774厂</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -7614,7 +7661,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>国营774厂</t>
+          <t>北京市综合仪器厂</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -7636,7 +7683,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>北京市综合仪器厂</t>
+          <t>北京铭信电子有限公司</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -7651,14 +7698,14 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十一节北京市无线电元件一厂</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>北京铭信电子有限公司</t>
+          <t>北京无线电插接元件厂</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -7673,14 +7720,14 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十一节北京市无线电元件一厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十五节北京无线电元件九厂</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>北京无线电插接元件厂</t>
+          <t>中国邮电工业总公司</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -7695,14 +7742,14 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十五节北京无线电元件九厂</t>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第一节北京邮电通信设备厂</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>中国邮电工业总公司</t>
+          <t>海淀区学院</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -7717,14 +7764,14 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二章中央在京电子工业企业·第一节北京邮电通信设备厂</t>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第三节北京长城无线电厂</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>海淀区学院</t>
+          <t>中国烟草总公司</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -7746,7 +7793,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>中国烟草总公司</t>
+          <t>北京第三无线电器材厂</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -7761,14 +7808,14 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二章中央在京电子工业企业·第三节北京长城无线电厂</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第六节北京飞行电子总公司</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>北京第三无线电器材厂</t>
+          <t>北京旭硝子电子玻璃有限公司</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -7778,41 +7825,54 @@
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>志中未见专条,仅由他条提及</t>
+          <t>未见专条,据行文点名</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第六节北京飞行电子总公司</t>
+          <t>北京工业志·电子志</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>北京旭硝子电子玻璃有限公司</t>
-        </is>
+          <t>上海长宁拉手厂</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>电子计算机</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>第二台709型计算机</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>19730000</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>北京工业志·电子志</t>
+          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>上海无线电十三厂</t>
+          <t>上海长江电子计算机厂</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -7822,25 +7882,17 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>TQ一16中型通用数字集成电路计算机、J一101型计算机、专用电子计算机、TQ-21型数据处理机</t>
-        </is>
-      </c>
-      <c r="D193" t="n">
-        <v>19660600</v>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>19690200改名TQ一6型计算机</t>
+          <t>CJ-801单板微型机</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
@@ -7852,7 +7904,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>上海长宁拉手厂</t>
+          <t>上海交通大学</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -7862,15 +7914,12 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>第二台709型计算机</t>
-        </is>
-      </c>
-      <c r="D194" t="n">
-        <v>19730000</v>
+          <t>DJS-053微型计算机、DJS-052E微型计算机、生产单板微型计算机、单板微型计算机</t>
+        </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
@@ -7880,14 +7929,14 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>上海长江电子计算机厂</t>
+          <t>华东师范大学</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -7895,41 +7944,44 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>CJ-801单板微型机</t>
-        </is>
+      <c r="D195" t="n">
+        <v>19730000</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+          <t>上海电子仪表工业志·第一章电子计算机·1. 电子管计算机</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>上海华东师范大学</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>上海交通大学</t>
+          <t>中国人民解放军总参谋部第五十六研究所</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>电子计算机</t>
+          <t>研究所</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>DJS一053微型计算机、DJS一052E微型计算机、生产单板微型计算机、单板微型计算机</t>
+          <t>J-101型计算机</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -7939,19 +7991,19 @@
       </c>
       <c r="Q196" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>未见专条,据行文点名；行业据单位名</t>
         </is>
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>华东师范大学</t>
+          <t>上海工业大学</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -7959,9 +8011,6 @@
           <t>电子计算机</t>
         </is>
       </c>
-      <c r="D197" t="n">
-        <v>19730000</v>
-      </c>
       <c r="G197" t="inlineStr">
         <is>
           <t>Shanghai</t>
@@ -7974,29 +8023,19 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·1. 电子管计算机</t>
-        </is>
-      </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>上海华东师范大学</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>中国人民解放军总参谋部第五十六研究所</t>
+          <t>联合公司</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>研究所</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>J一101型计算机</t>
+          <t>电子计算机</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -8006,19 +8045,19 @@
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据单位名</t>
+          <t>未见专条,据行文点名；行业据正文用词</t>
         </is>
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>上海工业大学</t>
+          <t>上海中兴无线电厂</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -8028,7 +8067,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="Q199" t="inlineStr">
@@ -8038,14 +8077,14 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>联合公司</t>
+          <t>新安电工厂</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -8065,14 +8104,14 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
+          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>上海中兴无线电厂</t>
+          <t>上海调节器厂</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -8082,7 +8121,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="Q201" t="inlineStr">
@@ -8099,74 +8138,20 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>新安电工厂</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>电子计算机</t>
+          <t>上海炼油厂</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
+          <t>志中未见专条,仅由他条提及</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
-        <is>
-          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>上海调节器厂</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>电子计算机</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>Beijing</t>
-        </is>
-      </c>
-      <c r="Q203" t="inlineStr">
-        <is>
-          <t>未见专条,据行文点名；行业据正文用词</t>
-        </is>
-      </c>
-      <c r="R203" t="inlineStr">
-        <is>
-          <t>上海电子仪表工业志·第一章电子计算机·3. 集成电路计算机</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>上海炼油厂</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>Beijing</t>
-        </is>
-      </c>
-      <c r="Q204" t="inlineStr">
-        <is>
-          <t>志中未见专条,仅由他条提及</t>
-        </is>
-      </c>
-      <c r="R204" t="inlineStr">
         <is>
           <t>上海电子仪表工业志·第一章电子计算机·第五节企业·四、 上海王安电脑发展公司</t>
         </is>
@@ -17139,7 +17124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -17685,17 +17670,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海电子计算机厂</t>
+          <t>上海无线电十三厂</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>19660601</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>19800000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1970年迁至南京西路1486号，1980年更名为上海电子计算机厂。</t>
+          <t>1980 年更名前的名称。同一节里两种写法各记了一笔,并重复行时补上这一段——「改名叫自己」的末段前头总得有段别的名字才立得住。别名「上无十三」。</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -17706,42 +17696,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>中国科学院上海冶金研究所</t>
+          <t>上海电子计算机厂</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>中央研究院工学研究所</t>
+          <t>上海电子计算机厂</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>19280000</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>19490000</t>
+          <t>19800000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>始建时名称</t>
+          <t>1970年迁至南京西路1486号，1980年更名为上海电子计算机厂。</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>据 Founder 列推定,待核</t>
+          <t>上海电子仪表工业志·第一章电子计算机·第一节沿革</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -17750,17 +17735,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>中国科学院工学实验馆</t>
+          <t>中央研究院工学研究所</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>19280000</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>19490000</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>19530000</t>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>始建时名称</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -17771,7 +17761,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -17780,17 +17770,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>中国科学院冶金陶瓷研究所</t>
+          <t>中国科学院工学实验馆</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>19490000</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>19530000</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>19600000</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -17801,7 +17791,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -17810,17 +17800,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>中国科学院冶金研究所</t>
+          <t>中国科学院冶金陶瓷研究所</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>19530000</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>19600000</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>19700000</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -17831,7 +17821,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -17840,10 +17830,15 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>中国科学院上海冶金研究所</t>
+          <t>中国科学院冶金研究所</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
+        <is>
+          <t>19600000</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>19700000</t>
         </is>
@@ -17856,16 +17851,16 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>北京701厂</t>
+          <t>中国科学院上海冶金研究所</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>第四机械工业部</t>
+          <t>中国科学院上海冶金研究所</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -17873,14 +17868,9 @@
           <t>19700000</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>始建时名称。北京七O一厂原为第四机械工业部和北京市共同投资兴建的“小三线厂”，1970年，建于怀柔县山区。</t>
-        </is>
-      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第四十二节北京七〇一厂</t>
+          <t>据 Founder 列推定,待核</t>
         </is>
       </c>
     </row>
@@ -17890,27 +17880,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>北京京海集团公司</t>
+          <t>北京701厂</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>计算机机房技术开发公司</t>
+          <t>第四机械工业部</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>19830700</t>
+          <t>19700000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>始建时名称。北京京海集团公司成立于1983年7月，前身是计算机机房技术开发公司。</t>
+          <t>始建时名称。北京七O一厂原为第四机械工业部和北京市共同投资兴建的“小三线厂”，1970年，建于怀柔县山区。</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章行业归口电子工业企业·第四节北京京海集团公司</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第四十二节北京七〇一厂</t>
         </is>
       </c>
     </row>
@@ -17920,38 +17910,33 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>北京北大方正集团公司</t>
+          <t>北京京海集团公司</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>北京大学新技术公司</t>
+          <t>计算机机房技术开发公司</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>19860000</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>19880000</t>
+          <t>19830700</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>始建时名称。北京北大方正集团公司前身为北京大学新技术公司，是北京大学1986年创办的校办企业，1988年，改名为北京北大方正集团公司，位于海淀区中关村电子一条街北段。</t>
+          <t>始建时名称。北京京海集团公司成立于1983年7月，前身是计算机机房技术开发公司。</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章行业归口电子工业企业·第三节北京北大方正集团公司</t>
+          <t>北京工业志·电子志·第三章行业归口电子工业企业·第四节北京京海集团公司</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -17960,17 +17945,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>北京北大方正集团公司</t>
+          <t>北京大学新技术公司</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>19860000</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>19880000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>北京北大方正集团公司前身为北京大学新技术公司，是北京大学1986年创办的校办企业，1988年，改名为北京北大方正集团公司，位于海淀区中关村电子一条街北段。</t>
+          <t>始建时名称。北京北大方正集团公司前身为北京大学新技术公司，是北京大学1986年创办的校办企业，1988年，改名为北京北大方正集团公司，位于海淀区中关村电子一条街北段。</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -17981,42 +17971,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>北京半导体器件五厂</t>
+          <t>北京北大方正集团公司</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>北京市西城区半导体器件厂</t>
+          <t>北京北大方正集团公司</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>19690900</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>19780400</t>
+          <t>19880000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>始建时名称。北京半导体器件五厂前身是北京市西城区半导体器件厂，始建于1969年9月。</t>
+          <t>北京北大方正集团公司前身为北京大学新技术公司，是北京大学1986年创办的校办企业，1988年，改名为北京北大方正集团公司，位于海淀区中关村电子一条街北段。</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十九节北京半导体器件五厂</t>
+          <t>北京工业志·电子志·第三章行业归口电子工业企业·第三节北京北大方正集团公司</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -18025,17 +18010,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>北京半导体器件五厂</t>
+          <t>北京市西城区半导体器件厂</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>19690900</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>19780400</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1978年4月，改名为北京半导体器件五厂。</t>
+          <t>始建时名称。北京半导体器件五厂前身是北京市西城区半导体器件厂，始建于1969年9月。</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -18046,31 +18036,31 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>北京大华无线电仪器厂</t>
+          <t>北京半导体器件五厂</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>北京微技测量仪器厂</t>
+          <t>北京半导体器件五厂</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>19580800</t>
+          <t>19780400</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>始建时名称。北京大华无线电仪器厂（代号国营第768厂，原名北京微技测量仪器厂，华北无线电仪器厂）1958年8月开始筹建，1965年4月建成投产。</t>
+          <t>1978年4月，改名为北京半导体器件五厂。</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第十节北京大华无线电仪器厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十九节北京半导体器件五厂</t>
         </is>
       </c>
     </row>
@@ -18080,27 +18070,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>北京市半导体器件一厂</t>
+          <t>北京大华无线电仪器厂</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>北京市半导体器件一厂</t>
+          <t>北京微技测量仪器厂</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>19780600</t>
+          <t>19580800</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1978年6月，改名为北京市半导体器件一厂。</t>
+          <t>始建时名称。北京大华无线电仪器厂（代号国营第768厂，原名北京微技测量仪器厂，华北无线电仪器厂）1958年8月开始筹建，1965年4月建成投产。</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十七节北京市半导体器件一厂</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第十节北京大华无线电仪器厂</t>
         </is>
       </c>
     </row>
@@ -18110,38 +18100,33 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>北京市可控硅元件厂</t>
+          <t>北京市半导体器件一厂</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>朝外大街乒乓球拍厂</t>
+          <t>北京市半导体器件一厂</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>19680000</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>19680000</t>
+          <t>19780600</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>以生产乒乓球拍为主的厂定名为朝外大街乒乓球拍厂，1968年开始试制可控硅元件，1970年，改名为朝阳可控硅元件厂。</t>
+          <t>1978年6月，改名为北京市半导体器件一厂。</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第四十一节北京市可控硅元件厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十七节北京市半导体器件一厂</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -18150,7 +18135,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>北京市朝阳可控硅元件厂</t>
+          <t>朝外大街乒乓球拍厂</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -18160,12 +18145,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>19780000</t>
+          <t>19680000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>始建时名称。北京市可控硅元件厂前身是北京市朝阳可控硅元件厂。</t>
+          <t>以生产乒乓球拍为主的厂定名为朝外大街乒乓球拍厂，1968年开始试制可控硅元件，1970年，改名为朝阳可控硅元件厂。</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -18176,7 +18161,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -18185,17 +18170,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>北京半导体材料加工厂</t>
+          <t>北京市朝阳可控硅元件厂</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>19680000</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>19780000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1978年，与东城区可控硅元件厂合并，1980年，改名为北京半导体材料加工厂，1985年，又改名为北京市可控硅元件厂。</t>
+          <t>始建时名称。北京市可控硅元件厂前身是北京市朝阳可控硅元件厂。</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -18206,42 +18196,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>北京市无线电元件一厂</t>
+          <t>北京市可控硅元件厂</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>北京竹藤制品厂</t>
+          <t>北京半导体材料加工厂</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>19640000</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>19680000</t>
+          <t>19780000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1964年，改名为北京竹藤制品厂。</t>
+          <t>1978年，与东城区可控硅元件厂合并，1980年，改名为北京半导体材料加工厂，1985年，又改名为北京市可控硅元件厂。</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十一节北京市无线电元件一厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第四十一节北京市可控硅元件厂</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -18250,17 +18235,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>北京市无线电元件一厂</t>
+          <t>北京竹藤制品厂</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>19640000</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>19680000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1968年底，接收北京无线电电阻厂部分产品、设备和人员，转产电子元件，改名为北京市无线电元件一厂。</t>
+          <t>1964年，改名为北京竹藤制品厂。</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -18271,31 +18261,31 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>北京市调谐器厂</t>
+          <t>北京市无线电元件一厂</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>北京广播电视配件五厂</t>
+          <t>北京市无线电元件一厂</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>19790000</t>
+          <t>19680000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1979年改名为北京广播电视配件五厂。</t>
+          <t>1968年底，接收北京无线电电阻厂部分产品、设备和人员，转产电子元件，改名为北京市无线电元件一厂。</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十一节北京市调谐器厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十一节北京市无线电元件一厂</t>
         </is>
       </c>
     </row>
@@ -18305,27 +18295,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>北京广播器材厂</t>
+          <t>北京市调谐器厂</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>北京人民广播器材厂</t>
+          <t>北京广播电视配件五厂</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>19500601</t>
+          <t>19790000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>始建时名称。北京广播器材厂（代号国营第761厂，原名北京人民广播器材厂）1950年6月1日</t>
+          <t>1979年改名为北京广播电视配件五厂。</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第九节北京广播器材厂</t>
+          <t>北京工业志·电子志·第二十一节北京市调谐器厂</t>
         </is>
       </c>
     </row>
@@ -18335,38 +18325,33 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>北京广播电视配件一厂</t>
+          <t>北京广播器材厂</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>北京无线电非金属元件厂</t>
+          <t>北京人民广播器材厂</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>19650000</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>19700000</t>
+          <t>19500601</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1965年，改名为北京无线电非金属元件厂。</t>
+          <t>始建时名称。北京广播器材厂（代号国营第761厂，原名北京人民广播器材厂）1950年6月1日</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十九节北京广播电视配件一厂</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第九节北京广播器材厂</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -18375,17 +18360,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>北京无线电元件厂</t>
+          <t>北京无线电非金属元件厂</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>19650000</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>19700000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1970年，改名为北京无线电元件厂。</t>
+          <t>1965年，改名为北京无线电非金属元件厂。</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -18396,42 +18386,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>北京广播通讯电源厂</t>
+          <t>北京广播电视配件一厂</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>北京鞋底厂</t>
+          <t>北京无线电元件厂</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>19570000</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>19600000</t>
+          <t>19700000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1957年改名为北京鞋底厂。</t>
+          <t>1970年，改名为北京无线电元件厂。</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十二节北京广播通讯电源厂</t>
+          <t>北京工业志·电子志·第十九节北京广播电视配件一厂</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -18440,22 +18425,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>北京鞋厂</t>
+          <t>北京鞋底厂</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>19570000</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>19600000</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>19720000</t>
-        </is>
-      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1960年改名为北京鞋厂。</t>
+          <t>1957年改名为北京鞋底厂。</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -18466,7 +18451,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -18475,22 +18460,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>北京东风电池厂</t>
+          <t>北京鞋厂</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>19600000</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>19720000</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>19790500</t>
-        </is>
-      </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1970年该产锅镍蓄电池，并于1972年改名为北京东风电池厂。</t>
+          <t>1960年改名为北京鞋厂。</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -18501,7 +18486,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -18510,22 +18495,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>北京广播电视配件六厂</t>
+          <t>北京东风电池厂</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>19720000</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>19790500</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>19880000</t>
-        </is>
-      </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1979年5月，改名为北京广播电视配件六厂。</t>
+          <t>1970年该产锅镍蓄电池，并于1972年改名为北京东风电池厂。</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -18536,7 +18521,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -18545,17 +18530,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>北京广播通讯电源厂</t>
+          <t>北京广播电视配件六厂</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>19790500</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>19880000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1988年，改名为北京广播通讯电源厂。</t>
+          <t>1979年5月，改名为北京广播电视配件六厂。</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -18566,31 +18556,31 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>北京无线电一厂</t>
+          <t>北京广播通讯电源厂</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>北京计算机一厂</t>
+          <t>北京广播通讯电源厂</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>19700000</t>
+          <t>19880000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1970年初，北京无线电一厂（后更名为北京计算机一厂）接受原航空部第20研究所的委托，开始研制大型晶体管模数混合计算机，1975年，完成研制任务，定名为HMJ-200大型晶体管模数混合计算机。</t>
+          <t>1988年，改名为北京广播通讯电源厂。</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
+          <t>北京工业志·电子志·第二十二节北京广播通讯电源厂</t>
         </is>
       </c>
     </row>
@@ -18600,38 +18590,33 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>北京无线电仪器二厂</t>
+          <t>北京无线电一厂</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>北京电子仪器厂</t>
+          <t>北京计算机一厂</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>19590000</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>19700400</t>
+          <t>19700000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>始建时名称。该厂前身之一的北京电子仪器厂，1959年，在生产收音机的同时即开始生产测量仪器，并成为全国最早生产电子测量仪器的企业之一。</t>
+          <t>1970年初，北京无线电一厂（后更名为北京计算机一厂）接受原航空部第20研究所的委托，开始研制大型晶体管模数混合计算机，1975年，完成研制任务，定名为HMJ-200大型晶体管模数混合计算机。</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
+          <t>北京工业志·电子志·第三章电子计算机·第二节模拟与混合计算机·一、 模拟计算机</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -18644,6 +18629,11 @@
         </is>
       </c>
       <c r="D47" t="inlineStr">
+        <is>
+          <t>19590000</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
         <is>
           <t>19700400</t>
         </is>
@@ -18661,42 +18651,37 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>北京无线电元件九厂</t>
+          <t>北京无线电仪器二厂</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>北京市东城区无线电元件厂</t>
+          <t>北京电子仪器厂</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>19600000</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>19620000</t>
+          <t>19700400</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>始建时名称。北京无线电元件九厂始建于1960年，前身是北京市东城区无线电元件厂。</t>
+          <t>始建时名称。该厂前身之一的北京电子仪器厂，1959年，在生产收音机的同时即开始生产测量仪器，并成为全国最早生产电子测量仪器的企业之一。</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十五节北京无线电元件九厂</t>
+          <t>北京工业志·电子志·第二十八节北京无线电仪器二厂</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -18705,22 +18690,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>北京无线电插接元件厂</t>
+          <t>北京市东城区无线电元件厂</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>19600000</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>19620000</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>19790000</t>
-        </is>
-      </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1962年改名为北京无线电插接元件厂。</t>
+          <t>始建时名称。北京无线电元件九厂始建于1960年，前身是北京市东城区无线电元件厂。</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -18731,7 +18716,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -18740,17 +18725,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>北京无线电元件九厂</t>
+          <t>北京无线电插接元件厂</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>19620000</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>19790000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1979年崇文元件四厂、朝阳精密元件厂并入北京无线电插接元件厂，改名为北京无线电元件九厂。</t>
+          <t>1962年改名为北京无线电插接元件厂。</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -18761,42 +18751,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>北京无线电元件四厂</t>
+          <t>北京无线电元件九厂</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>北京市石景山电容器厂</t>
+          <t>北京无线电元件九厂</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>19670000</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
           <t>19790000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>始建时名称。北京无线电元件四厂前身是北京市石景山电容器厂，1967年建成投产，是国内较早从事电容器研制和生产的厂家之一。</t>
+          <t>1979年崇文元件四厂、朝阳精密元件厂并入北京无线电插接元件厂，改名为北京无线电元件九厂。</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第一章直属电子工业企业·第三十三节北京无线电元件四厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十五节北京无线电元件九厂</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -18805,17 +18790,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>北京无线电元件四厂</t>
+          <t>北京市石景山电容器厂</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t>19670000</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>19790000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1979年改名为北京无线电元件四厂。</t>
+          <t>始建时名称。北京无线电元件四厂前身是北京市石景山电容器厂，1967年建成投产，是国内较早从事电容器研制和生产的厂家之一。</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -18826,31 +18816,31 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>北京无线电厂</t>
+          <t>北京无线电元件四厂</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>北京电子仪器厂</t>
+          <t>北京无线电元件四厂</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>19590000</t>
+          <t>19790000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1959年改名为北京电子仪器厂，1964年6月改为现厂名。</t>
+          <t>1979年改名为北京无线电元件四厂。</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十五节北京无线电厂</t>
+          <t>北京工业志·电子志·第一章直属电子工业企业·第三十三节北京无线电元件四厂</t>
         </is>
       </c>
     </row>
@@ -18860,38 +18850,33 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>北京显像管总厂</t>
+          <t>北京无线电厂</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>北京市半导体器件五厂</t>
+          <t>北京电子仪器厂</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>19700000</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>19721100</t>
+          <t>19590000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1970年改为北京市半导体器件五厂，生产低频大功率管。</t>
+          <t>1959年改名为北京电子仪器厂，1964年6月改为现厂名。</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
+          <t>北京工业志·电子志·第十五节北京无线电厂</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -18900,22 +18885,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>北京显值管厂</t>
+          <t>北京市半导体器件五厂</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t>19700000</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>19721100</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>19900000</t>
-        </is>
-      </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1972年11月，改名为北京显值管厂。</t>
+          <t>1970年改为北京市半导体器件五厂，生产低频大功率管。</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -18926,7 +18911,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -18935,17 +18920,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>北京显像管总厂</t>
+          <t>北京显值管厂</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t>19721100</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>19900000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1990年，北京半导体设备一厂并入北京显像管厂，改名为北京显像管总厂。</t>
+          <t>1972年11月，改名为北京显值管厂。</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -18956,31 +18946,31 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>北京有线电总厂</t>
+          <t>北京显像管总厂</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>北京有线电厂</t>
+          <t>北京显像管总厂</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>19570900</t>
+          <t>19900000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>始建时名称。北京有线电总厂原名北京有线电厂（代号国营第738厂），是“一五”时期由苏联援建的156项国家重点工程之一。</t>
+          <t>1990年，北京半导体设备一厂并入北京显像管厂，改名为北京显像管总厂。</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第七节北京有线电总厂</t>
+          <t>北京工业志·电子志·第十八节北京显像管总厂</t>
         </is>
       </c>
     </row>
@@ -18990,27 +18980,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>北京核仪器厂</t>
+          <t>北京有线电总厂</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>北京市综合仪器厂</t>
+          <t>北京有线电厂</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>19560000</t>
+          <t>19570900</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>始建时名称。北京枚仪器厂前身为北京市综合仪器厂，是1956年中共北京市委、市人委遵照周恩来关于“在北京建立一个射线仪器厂”的指示筹资兴建的。</t>
+          <t>始建时名称。北京有线电总厂原名北京有线电厂（代号国营第738厂），是“一五”时期由苏联援建的156项国家重点工程之一。</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二章中央在京电子工业企业·第四节北京核仪器厂</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第七节北京有线电总厂</t>
         </is>
       </c>
     </row>
@@ -19020,38 +19010,33 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>北京牡丹电子集团公司</t>
+          <t>北京核仪器厂</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>北京无线电精密元件厂</t>
+          <t>北京市综合仪器厂</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>19650000</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>19731100</t>
+          <t>19560000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>始建时名称。北京电视机厂前身为北京无线电精密元件厂，创建于1965年，当时主要生产微型继电器和斩该器。</t>
+          <t>始建时名称。北京枚仪器厂前身为北京市综合仪器厂，是1956年中共北京市委、市人委遵照周恩来关于“在北京建立一个射线仪器厂”的指示筹资兴建的。</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第四节北京核仪器厂</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -19060,17 +19045,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>北京电视机厂</t>
+          <t>北京无线电精密元件厂</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t>19650000</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>19731100</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1973年11月，改名为北京电视机厂，国家投资1000万元在海淀区花园路建设新厂，主要生产黑白、彩色电视机。</t>
+          <t>始建时名称。北京电视机厂前身为北京无线电精密元件厂，创建于1965年，当时主要生产微型继电器和斩该器。</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -19081,42 +19071,37 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>北京电视配件三厂</t>
+          <t>北京牡丹电子集团公司</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>东红路塑料制品厂</t>
+          <t>北京电视机厂</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>19660000</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>19700000</t>
+          <t>19731100</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>始建时名称。北京电视配件三厂前身为东红路塑料制品厂，建于1966年。</t>
+          <t>1973年11月，改名为北京电视机厂，国家投资1000万元在海淀区花园路建设新厂，主要生产黑白、彩色电视机。</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
+          <t>北京工业志·电子志·第十三节北京牡丹电子集团公司</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -19125,22 +19110,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>东红路无线电元件厂</t>
+          <t>东红路塑料制品厂</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t>19660000</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
           <t>19700000</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>19750000</t>
-        </is>
-      </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1970年，开始生产云母电容器，改名为东红路无线电元件厂。</t>
+          <t>始建时名称。北京电视配件三厂前身为东红路塑料制品厂，建于1966年。</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -19151,7 +19136,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -19160,17 +19145,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>朝阳区东红路无线电元件厂</t>
+          <t>东红路无线电元件厂</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t>19700000</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>19750000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1975年，改名为朝阳区东红路无线电元件厂。</t>
+          <t>1970年，开始生产云母电容器，改名为东红路无线电元件厂。</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -19181,31 +19171,31 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>北京联想计算机集团公司</t>
+          <t>北京电视配件三厂</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>联想集团公司</t>
+          <t>朝阳区东红路无线电元件厂</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>19880000</t>
+          <t>19750000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1988年，北京联想计算机集团公司（后更名为联想集团公司，以下简称联想集团）开始研制联想系列微机。</t>
+          <t>1975年，改名为朝阳区东红路无线电元件厂。</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
+          <t>北京工业志·电子志·第二十节北京电视配件三厂</t>
         </is>
       </c>
     </row>
@@ -19215,38 +19205,33 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>北京计算机一厂</t>
+          <t>北京联想计算机集团公司</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>北京市服务联社电器制造厂</t>
+          <t>联想集团公司</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>19570000</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>19580000</t>
+          <t>19880000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1957年，改名为北京市服务联社电器制造厂。</t>
+          <t>1988年，北京联想计算机集团公司（后更名为联想集团公司，以下简称联想集团）开始研制联想系列微机。</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十三节北京计算机一厂</t>
+          <t>北京工业志·电子志·第三章电子计算机·第五节计算机软件·四、 做型计算机·（一） 微机及其系统</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -19255,22 +19240,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>北京市无线电制造厂</t>
+          <t>北京市服务联社电器制造厂</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t>19570000</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>19580000</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>19620000</t>
-        </is>
-      </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1958年，改名为北京市无线电制造厂。</t>
+          <t>1957年，改名为北京市服务联社电器制造厂。</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -19281,7 +19266,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -19290,22 +19275,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>北京无线电一厂</t>
+          <t>北京市无线电制造厂</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>19580000</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>19620000</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>19790000</t>
-        </is>
-      </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1962年，改名为北京无线电一厂。</t>
+          <t>1958年，改名为北京市无线电制造厂。</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -19316,7 +19301,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -19325,17 +19310,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>北京计算机一厂</t>
+          <t>北京无线电一厂</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t>19620000</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>19790000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>1979年，定名为北京计算机一厂。</t>
+          <t>1962年，改名为北京无线电一厂。</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -19346,31 +19336,31 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>北京计算机三厂</t>
+          <t>北京计算机一厂</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>北京无线电三厂</t>
+          <t>北京计算机一厂</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>19650425</t>
+          <t>19790000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>始建时名称。北京计算机三厂前身是北京无线电三厂，成立于1965年4月25日。</t>
+          <t>1979年，定名为北京计算机一厂。</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十五节北京计算机三厂</t>
+          <t>北京工业志·电子志·第二十三节北京计算机一厂</t>
         </is>
       </c>
     </row>
@@ -19380,27 +19370,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>北京计算机外部设备三厂</t>
+          <t>北京计算机三厂</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>北京通讯设备厂</t>
+          <t>北京无线电三厂</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>19790000</t>
+          <t>19650425</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>1979年，改名为北京通讯设备厂。</t>
+          <t>始建时名称。北京计算机三厂前身是北京无线电三厂，成立于1965年4月25日。</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二十六节北京计算机外部设备三厂</t>
+          <t>北京工业志·电子志·第二十五节北京计算机三厂</t>
         </is>
       </c>
     </row>
@@ -19410,38 +19400,33 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>北京邮电通信设备厂</t>
+          <t>北京计算机外部设备三厂</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1941年9月建立的华北电信电话股份有限公司</t>
+          <t>北京通讯设备厂</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>19410900</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>19410900</t>
+          <t>19790000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>始建时名称。其前身是1941年9月建立的华北电信电话股份有限公司修处（后更名为修缮所），现厂址位于北京市朝阳区将台路5号。</t>
+          <t>1979年，改名为北京通讯设备厂。</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第二章中央在京电子工业企业·第一节北京邮电通信设备厂</t>
+          <t>北京工业志·电子志·第二十六节北京计算机外部设备三厂</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -19450,10 +19435,15 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>华北电信电话股份有限公司</t>
+          <t>1941年9月建立的华北电信电话股份有限公司</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
+        <is>
+          <t>19410900</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
         <is>
           <t>19410900</t>
         </is>
@@ -19471,42 +19461,37 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>北京飞行电子总公司</t>
+          <t>北京邮电通信设备厂</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>北京第三无线电器材厂</t>
+          <t>华北电信电话股份有限公司</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>19571000</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>19640000</t>
+          <t>19410900</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>始建时名称。北京飞行电子总公司原名北京第三无线电器材厂（代号国营第798厂），前身是1957年10月由民主德国援建的华北无线电器材联合厂三分厂。</t>
+          <t>始建时名称。其前身是1941年9月建立的华北电信电话股份有限公司修处（后更名为修缮所），现厂址位于北京市朝阳区将台路5号。</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第四章中外合资电子工业企业·第六节北京飞行电子总公司</t>
+          <t>北京工业志·电子志·第二章中央在京电子工业企业·第一节北京邮电通信设备厂</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -19519,6 +19504,11 @@
         </is>
       </c>
       <c r="D74" t="inlineStr">
+        <is>
+          <t>19571000</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
         <is>
           <t>19640000</t>
         </is>
@@ -19536,42 +19526,37 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>北京飞达电子集团公司</t>
+          <t>北京飞行电子总公司</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>北京电影机械修理厂</t>
+          <t>北京第三无线电器材厂</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>19540000</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>19700000</t>
+          <t>19640000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>始建时名称。北京录音机厂前身是北京电影机械修理厂，创建于1954年。</t>
+          <t>始建时名称。北京飞行电子总公司原名北京第三无线电器材厂（代号国营第798厂），前身是1957年10月由民主德国援建的华北无线电器材联合厂三分厂。</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
+          <t>北京工业志·电子志·第四章中外合资电子工业企业·第六节北京飞行电子总公司</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -19580,22 +19565,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>北京电影机械厂</t>
+          <t>北京电影机械修理厂</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t>19540000</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>19700000</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>19810000</t>
-        </is>
-      </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>1970年改名为北京电影机械厂。</t>
+          <t>始建时名称。北京录音机厂前身是北京电影机械修理厂，创建于1954年。</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -19606,7 +19591,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -19615,17 +19600,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>北京录音机厂</t>
+          <t>北京电影机械厂</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t>19700000</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
           <t>19810000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>1981年改名为北京录音机厂。</t>
+          <t>1970年改名为北京电影机械厂。</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -19636,31 +19626,31 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>北大方正集团公司</t>
+          <t>北京飞达电子集团公司</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>北京大学新技术公司</t>
+          <t>北京录音机厂</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>19860000</t>
+          <t>19810000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>始建时名称。北京北大方正集团公司前身为北京大学新技术公司，是北京大学1986年创办的校办企业，1988年，改名为北京北大方正集团公司，位于海淀区中关村电子一条街北段。</t>
+          <t>1981年改名为北京录音机厂。</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章行业归口电子工业企业·第三节北京北大方正集团公司</t>
+          <t>北京工业志·电子志·第十七节北京飞达电子集团公司</t>
         </is>
       </c>
     </row>
@@ -19670,38 +19660,33 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>联想集团公司</t>
+          <t>北大方正集团公司</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>中国科学院计算所新技术发展公司</t>
+          <t>北京大学新技术公司</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>19841100</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>19870400</t>
+          <t>19860000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>始建时名称。联想集团公司（前身为中国科学院计算所新技术发展公司）创建于1984年11月</t>
+          <t>始建时名称。北京北大方正集团公司前身为北京大学新技术公司，是北京大学1986年创办的校办企业，1988年，改名为北京北大方正集团公司，位于海淀区中关村电子一条街北段。</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>北京工业志·电子志·第三章行业归口电子工业企业·第二节联想集团公司</t>
+          <t>北京工业志·电子志·第三章行业归口电子工业企业·第三节北京北大方正集团公司</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -19710,28 +19695,33 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>中科院计算所计算机技术公司</t>
+          <t>中国科学院计算所新技术发展公司</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t>19841100</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>19870400</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>19890800</t>
-        </is>
-      </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>1987年4月，更名为中科院计算所计算机技术公司</t>
+          <t>始建时名称。联想集团公司（前身为中国科学院计算所新技术发展公司）创建于1984年11月</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>北京工业志·电子志·第三章行业归口电子工业企业·第二节联想集团公司</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -19740,28 +19730,28 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>北京联想计算机集团公司</t>
+          <t>中科院计算所计算机技术公司</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t>19870400</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>19890800</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>19941100</t>
-        </is>
-      </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>1989年8月，更名为北京联想计算机集团公司</t>
+          <t>1987年4月，更名为中科院计算所计算机技术公司</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -19770,45 +19760,75 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>联想集团公司</t>
+          <t>北京联想计算机集团公司</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t>19890800</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>19941100</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>1994年11月，更名为联想</t>
+          <t>1989年8月，更名为北京联想计算机集团公司</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
+        <v>4</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>联想集团公司</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>联想集团公司</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>19941100</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>1994年11月，更名为联想</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
         <v>1</v>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>首钢电子公司</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>首钢自动化研究所</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>19780800</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>始建时名称。首钢电子公司前身是首钢自动化研究所，创建于1978年8月。</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>北京工业志·电子志·第三章行业归口电子工业企业·第七节首钢电子公司</t>
         </is>

--- a/CN_Electronic_Industry.xlsx
+++ b/CN_Electronic_Industry.xlsx
@@ -6,7 +6,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="21000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Fact and Comp-Shanghai" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="厂所名录" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Semi-Product" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Comp-Product" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Name-History" sheetId="4" state="visible" r:id="rId4"/>

--- a/CN_Electronic_Industry.xlsx
+++ b/CN_Electronic_Industry.xlsx
@@ -7,9 +7,9 @@
   </bookViews>
   <sheets>
     <sheet name="厂所名录" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Semi-Product" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Comp-Product" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Name-History" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="器件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="整机" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="名称沿革" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>

--- a/CN_Electronic_Industry.xlsx
+++ b/CN_Electronic_Industry.xlsx
@@ -10,6 +10,7 @@
     <sheet name="器件" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="整机" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="名称沿革" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="机构沿革" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -19,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -48,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -19837,4 +19842,86 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>年月</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>前身</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>关系</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>后继</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>出处</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>19600721</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>一亚电工厂、交直电工厂</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>合并</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>上海无线电十四厂</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>据 Founder 列迁来,待核</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>